--- a/assets/SEOVideos.xlsx
+++ b/assets/SEOVideos.xlsx
@@ -532,16 +532,16 @@
       <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Agricultural Services Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Agricultural Services Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Agronomy", "Crop Production", "Livestock Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agronomy"
-- "Crop Production"
-- "Livestock Management"
-- "Pest and Disease Control"
-- "Soil and Water Management"
-- "Farm Management"]
-#Hashtags
+Watch as we build a job-winning Agricultural Services Director from scratch, highlighting key sections and how to effectively showcase your skills in Agronomy, Crop Production, Livestock Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agronomy
+- Crop Production
+- Livestock Management
+- Pest and Disease Control
+- Soil and Water Management
+- Farm Management
+#resume
 #AgriculturalServicesDirectorResume #AgriculturalServicesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -592,16 +592,16 @@
       <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Agricultural Services Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Agricultural Services Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Agronomy", "Crop Production", "Livestock Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agronomy"
-- "Crop Production"
-- "Livestock Management"
-- "Pest and Disease Control"
-- "Soil and Water Management"
-- "Farm Management"]
-#Hashtags
+Watch as we build a job-winning Agricultural Services Director from scratch, highlighting key sections and how to effectively showcase your skills in Agronomy, Crop Production, Livestock Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agronomy
+- Crop Production
+- Livestock Management
+- Pest and Disease Control
+- Soil and Water Management
+- Farm Management
+#resume
 #AgriculturalServicesDirectorResume #AgriculturalServicesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -652,16 +652,16 @@
       <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Alcohol and Drug Abuse Assistance Program Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Alcohol and Drug Abuse Assistance Program Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Substance Use Disorder Assessment", "Treatment Planning", "Case Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Substance Use Disorder Assessment"
-- "Treatment Planning"
-- "Case Management"
-- "Client Advocacy"
-- "Crisis Intervention"
-- "Group Therapy Facilitation"]
-#Hashtags
+Watch as we build a job-winning Alcohol and Drug Abuse Assistance Program Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Substance Use Disorder Assessment, Treatment Planning, Case Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Substance Use Disorder Assessment
+- Treatment Planning
+- Case Management
+- Client Advocacy
+- Crisis Intervention
+- Group Therapy Facilitation
+#resume
 #AlcoholAndDrugAbuseAssistanceProgramAdministratorResume #AlcoholAndDrugAbuseAssistanceProgramAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -712,16 +712,16 @@
       <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Arts and Humanities Council Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Arts and Humanities Council Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Arts Program Management", "Cultural Event Coordination", "Arts Education Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Arts Program Management"
-- "Cultural Event Coordination"
-- "Arts Education Development"
-- "Grant Writing and Administration"
-- "Strategic Planning for Arts Organizations"
-- "Arts Advocacy and Policy Development"]
-#Hashtags
+Watch as we build a job-winning Arts and Humanities Council Director from scratch, highlighting key sections and how to effectively showcase your skills in Arts Program Management, Cultural Event Coordination, Arts Education Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Arts Program Management
+- Cultural Event Coordination
+- Arts Education Development
+- Grant Writing and Administration
+- Strategic Planning for Arts Organizations
+- Arts Advocacy and Policy Development
+#resume
 #ArtsAndHumanitiesCouncilDirectorResume #ArtsAndHumanitiesCouncilDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -772,16 +772,16 @@
       <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Bakery Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Bakery Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Baking Techniques", "Yeast Handling", "Dough Preparation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Baking Techniques"
-- "Yeast Handling"
-- "Dough Preparation"
-- "Bread Scoring"
-- "Sourdough Culture Management"
-- "Food Safety and Sanitation"]
-#Hashtags
+Watch as we build a job-winning Bakery Manager from scratch, highlighting key sections and how to effectively showcase your skills in Baking Techniques, Yeast Handling, Dough Preparation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Baking Techniques
+- Yeast Handling
+- Dough Preparation
+- Bread Scoring
+- Sourdough Culture Management
+- Food Safety and Sanitation
+#resume
 #BakeryManagerResume #BakeryManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -832,16 +832,16 @@
       <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Bank President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Bank President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Management", "Risk Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Management"
-- "Risk Management"
-- "Business Development"
-- "Customer Relationship Management"
-- "Leadership and Motivation"]
-#Hashtags
+Watch as we build a job-winning Bank President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Management, Risk Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Management
+- Risk Management
+- Business Development
+- Customer Relationship Management
+- Leadership and Motivation
+#resume
 #BankPresidentResume #BankPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -892,16 +892,16 @@
       <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Book Publisher? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Book Publisher from scratch, highlighting key sections and how to effectively showcase your skills in ["Proofreading", "Copyediting", "Acquisition", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Proofreading"
-- "Copyediting"
-- "Acquisition"
-- "Manuscript Evaluation"
-- "Book Development"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Book Publisher from scratch, highlighting key sections and how to effectively showcase your skills in Proofreading, Copyediting, Acquisition, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Proofreading
+- Copyediting
+- Acquisition
+- Manuscript Evaluation
+- Book Development
+- Project Management
+#resume
 #BookPublisherResume #BookPublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -952,16 +952,16 @@
       <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Brokerage Office Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Brokerage Office Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Brokerage Operations", "Financial Analysis", "Risk Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Brokerage Operations"
-- "Financial Analysis"
-- "Risk Management"
-- "Investment Strategies"
-- "Regulatory Compliance"
-- "Client Relationship Management"]
-#Hashtags
+Watch as we build a job-winning Brokerage Office Manager from scratch, highlighting key sections and how to effectively showcase your skills in Brokerage Operations, Financial Analysis, Risk Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Brokerage Operations
+- Financial Analysis
+- Risk Management
+- Investment Strategies
+- Regulatory Compliance
+- Client Relationship Management
+#resume
 #BrokerageOfficeManagerResume #BrokerageOfficeManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1012,16 +1012,16 @@
       <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Bureau Chief? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Bureau Chief from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "Contract Creation and Negotiation", "Data Analysis and Interpretation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "Contract Creation and Negotiation"
-- "Data Analysis and Interpretation"
-- "Department Supervision"
-- "Employee Discipline and Performance Management"
-- "Financial Planning and Forecasting"]
-#Hashtags
+Watch as we build a job-winning Bureau Chief from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, Contract Creation and Negotiation, Data Analysis and Interpretation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- Contract Creation and Negotiation
+- Data Analysis and Interpretation
+- Department Supervision
+- Employee Discipline and Performance Management
+- Financial Planning and Forecasting
+#resume
 #BureauChiefResume #BureauChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1072,16 +1072,16 @@
       <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Development Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Development Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Market Analysis", "Competitive Intelligence", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Market Analysis"
-- "Competitive Intelligence"
-- "Strategic Planning"
-- "Client Relationship Management"
-- "Sales Forecasting"
-- "Business Development"]
-#Hashtags
+Watch as we build a job-winning Business Development Officer from scratch, highlighting key sections and how to effectively showcase your skills in Market Analysis, Competitive Intelligence, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Market Analysis
+- Competitive Intelligence
+- Strategic Planning
+- Client Relationship Management
+- Sales Forecasting
+- Business Development
+#resume
 #BusinessDevelopmentOfficerResume #BusinessDevelopmentOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1132,16 +1132,16 @@
       <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Enterprise Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Enterprise Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Acumen", "Business Process Improvement", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Acumen"
-- "Business Process Improvement"
-- "Strategic Planning"
-- "Business Analysis"
-- "Project Management"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Business Enterprise Officer from scratch, highlighting key sections and how to effectively showcase your skills in Financial Acumen, Business Process Improvement, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Acumen
+- Business Process Improvement
+- Strategic Planning
+- Business Analysis
+- Project Management
+- Risk Management
+#resume
 #BusinessEnterpriseOfficerResume #BusinessEnterpriseOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1192,16 +1192,16 @@
       <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Analysis", "Operations Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Analysis"
-- "Operations Management"
-- "Marketing and Sales"
-- "Business Development"
-- "Team Leadership"]
-#Hashtags
+Watch as we build a job-winning Business Executive from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Analysis, Operations Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Analysis
+- Operations Management
+- Marketing and Sales
+- Business Development
+- Team Leadership
+#resume
 #BusinessExecutiveResume #BusinessExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1252,16 +1252,16 @@
       <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Cemetery Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Cemetery Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Burial Site Planning", "Funeral Planning", "Grave Maintenance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Burial Site Planning"
-- "Funeral Planning"
-- "Grave Maintenance"
-- "Grief Counseling"
-- "Human Remains Disposal"
-- "Monument Installation"]
-#Hashtags
+Watch as we build a job-winning Cemetery Manager from scratch, highlighting key sections and how to effectively showcase your skills in Burial Site Planning, Funeral Planning, Grave Maintenance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Burial Site Planning
+- Funeral Planning
+- Grave Maintenance
+- Grief Counseling
+- Human Remains Disposal
+- Monument Installation
+#resume
 #CemeteryManagerResume #CemeteryManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1312,16 +1312,16 @@
       <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chairman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chairman from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Board Management", "Corporate Governance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Board Management"
-- "Corporate Governance"
-- "Risk Management"
-- "Leadership"
-- "Communication"]
-#Hashtags
+Watch as we build a job-winning Chairman from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Board Management, Corporate Governance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Board Management
+- Corporate Governance
+- Risk Management
+- Leadership
+- Communication
+#resume
 #ChairmanResume #Chairman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1372,16 +1372,16 @@
       <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chancellor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chancellor from scratch, highlighting key sections and how to effectively showcase your skills in ["Academic Leadership", "Strategic Planning", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Academic Leadership"
-- "Strategic Planning"
-- "Budget Management"
-- "Faculty Development"
-- "Student Success"
-- "Alumni Relations"]
-#Hashtags
+Watch as we build a job-winning Chancellor from scratch, highlighting key sections and how to effectively showcase your skills in Academic Leadership, Strategic Planning, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Academic Leadership
+- Strategic Planning
+- Budget Management
+- Faculty Development
+- Student Success
+- Alumni Relations
+#resume
 #ChancellorResume #Chancellor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1432,16 +1432,16 @@
       <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Administrative Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Administrative Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Operations Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Operations Management"
-- "Human Resources Management"
-- "Compliance Management"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Chief Administrative Officer from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Operations Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Operations Management
+- Human Resources Management
+- Compliance Management
+- Risk Management
+#resume
 #ChiefAdministrativeOfficerResume #ChiefAdministrativeOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1492,18 +1492,18 @@
       <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Diversity Officer (CDO)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Diversity Officer (CDO) from scratch, highlighting key sections and how to effectively showcase your skills in ["Diversity,  Equity,  and Inclusion (DEI) Strategy Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Diversity
+Watch as we build a job-winning Chief Diversity Officer (CDO) from scratch, highlighting key sections and how to effectively showcase your skills in Diversity,  Equity,  and Inclusion (DEI) Strategy Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Diversity
 - Equity
-- and Inclusion (DEI) Strategy Development"
-- "Unconscious Bias Training and Education"
-- "Employee Resource Group (ERG) Management"
-- "Supplier Diversity Program Implementation"
-- "Cross-Cultural Communication and Sensitivity"
-- "Organizational Culture Transformation"]
-#Hashtags
+- and Inclusion (DEI) Strategy Development
+- Unconscious Bias Training and Education
+- Employee Resource Group (ERG) Management
+- Supplier Diversity Program Implementation
+- Cross-Cultural Communication and Sensitivity
+- Organizational Culture Transformation
+#resume
 #ChiefDiversityOfficerCdoResume #ChiefDiversityOfficerCdo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1554,16 +1554,16 @@
       <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Executive Officer (CEO)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Executive Officer (CEO) from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Management", "Team Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Management"
-- "Team Leadership"
-- "Stakeholder Management"
-- "Risk Management"
-- "Business Development"]
-#Hashtags
+Watch as we build a job-winning Chief Executive Officer (CEO) from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Management, Team Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Management
+- Team Leadership
+- Stakeholder Management
+- Risk Management
+- Business Development
+#resume
 #ChiefExecutiveOfficerCeoResume #ChiefExecutiveOfficerCeo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1614,16 +1614,16 @@
       <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Financial Officer (CFO)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Financial Officer (CFO) from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Planning and Analysis", "Budgeting and Forecasting", "Financial Reporting and Compliance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Planning and Analysis"
-- "Budgeting and Forecasting"
-- "Financial Reporting and Compliance"
-- "Risk Management"
-- "Strategic Planning"
-- "Treasury Management"]
-#Hashtags
+Watch as we build a job-winning Chief Financial Officer (CFO) from scratch, highlighting key sections and how to effectively showcase your skills in Financial Planning and Analysis, Budgeting and Forecasting, Financial Reporting and Compliance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Planning and Analysis
+- Budgeting and Forecasting
+- Financial Reporting and Compliance
+- Risk Management
+- Strategic Planning
+- Treasury Management
+#resume
 #ChiefFinancialOfficerCfoResume #ChiefFinancialOfficerCfo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1674,16 +1674,16 @@
       <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Innovation Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Innovation Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Innovation Management", "Disruptive Technology Analysis", "Trend Forecasting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Innovation Management"
-- "Disruptive Technology Analysis"
-- "Trend Forecasting"
-- "Business Model Innovation"
-- "Product Development"
-- "Intellectual Property Management"]
-#Hashtags
+Watch as we build a job-winning Chief Innovation Officer from scratch, highlighting key sections and how to effectively showcase your skills in Innovation Management, Disruptive Technology Analysis, Trend Forecasting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Innovation Management
+- Disruptive Technology Analysis
+- Trend Forecasting
+- Business Model Innovation
+- Product Development
+- Intellectual Property Management
+#resume
 #ChiefInnovationOfficerResume #ChiefInnovationOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1734,16 +1734,16 @@
       <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Nursing Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Nursing Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Leadership and Management", "Strategic Planning and Execution", "Operational Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Leadership and Management"
-- "Strategic Planning and Execution"
-- "Operational Management"
-- "Patient Care Delivery"
-- "Quality Improvement"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Chief Nursing Officer from scratch, highlighting key sections and how to effectively showcase your skills in Leadership and Management, Strategic Planning and Execution, Operational Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Leadership and Management
+- Strategic Planning and Execution
+- Operational Management
+- Patient Care Delivery
+- Quality Improvement
+- Budget Management
+#resume
 #ChiefNursingOfficerResume #ChiefNursingOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1794,16 +1794,16 @@
       <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Operating Officer (COO)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Operating Officer (COO) from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Operational Management", "Financial Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Operational Management"
-- "Financial Management"
-- "Team Leadership"
-- "Process Improvement"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Chief Operating Officer (COO) from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Operational Management, Financial Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Operational Management
+- Financial Management
+- Team Leadership
+- Process Improvement
+- Risk Management
+#resume
 #ChiefOperatingOfficerCooResume #ChiefOperatingOfficerCoo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1854,16 +1854,16 @@
       <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Warden? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Warden from scratch, highlighting key sections and how to effectively showcase your skills in ["Fire Safety Management", "Emergency Response Planning", "Incident Command Systems (ICS)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Fire Safety Management"
-- "Emergency Response Planning"
-- "Incident Command Systems (ICS)"
-- "Fire Prevention"
-- "Building Evacuation Procedures"
-- "CPR and First Aid"]
-#Hashtags
+Watch as we build a job-winning Chief Warden from scratch, highlighting key sections and how to effectively showcase your skills in Fire Safety Management, Emergency Response Planning, Incident Command Systems (ICS), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Fire Safety Management
+- Emergency Response Planning
+- Incident Command Systems (ICS)
+- Fire Prevention
+- Building Evacuation Procedures
+- CPR and First Aid
+#resume
 #ChiefWardenResume #ChiefWarden #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1914,16 +1914,16 @@
       <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "Financial Planning", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "Financial Planning"
-- "Strategic Planning"
-- "Grant Writing"
-- "Economic Development"
-- "Government Relations"]
-#Hashtags
+Watch as we build a job-winning City Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, Financial Planning, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- Financial Planning
+- Strategic Planning
+- Grant Writing
+- Economic Development
+- Government Relations
+#resume
 #CityAdministratorResume #CityAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1974,16 +1974,16 @@
       <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Infrastructure Planning and Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Infrastructure Planning and Development"
-- "Public Policy Analysis"
-- "Stakeholder Engagement"
-- "Human Resource Management"]
-#Hashtags
+Watch as we build a job-winning City Manager from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Infrastructure Planning and Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Infrastructure Planning and Development
+- Public Policy Analysis
+- Stakeholder Engagement
+- Human Resource Management
+#resume
 #CityManagerResume #CityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2034,16 +2034,16 @@
       <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Project Management", "Construction Management", "Contract Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Project Management"
-- "Construction Management"
-- "Contract Management"
-- "Budgeting and Cost Control"
-- "Scheduling and Planning"
-- "Safety Management"]
-#Hashtags
+Watch as we build a job-winning City Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Project Management, Construction Management, Contract Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Project Management
+- Construction Management
+- Contract Management
+- Budgeting and Cost Control
+- Scheduling and Planning
+- Safety Management
+#resume
 #CitySuperintendentResume #CitySuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2094,16 +2094,16 @@
       <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Superintendent of Schools? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Superintendent of Schools from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Curriculum Development", "Instructional Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Curriculum Development"
-- "Instructional Leadership"
-- "School Finance"
-- "Data Analysis"
-- "Stakeholder Relations"]
-#Hashtags
+Watch as we build a job-winning City Superintendent of Schools from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Curriculum Development, Instructional Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Curriculum Development
+- Instructional Leadership
+- School Finance
+- Data Analysis
+- Stakeholder Relations
+#resume
 #CitySuperintendentOfSchoolsResume #CitySuperintendentOfSchools #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2154,16 +2154,16 @@
       <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "Strategic Planning", "Public Administration", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "Strategic Planning"
-- "Public Administration"
-- "Policy Analysis"
-- "Performance Management"
-- "Community Engagement"]
-#Hashtags
+Watch as we build a job-winning City Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, Strategic Planning, Public Administration, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- Strategic Planning
+- Public Administration
+- Policy Analysis
+- Performance Management
+- Community Engagement
+#resume
 #CitySupervisorResume #CitySupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2214,16 +2214,16 @@
       <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Classification and Treatment Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Classification and Treatment Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Statistical Analysis", "Risk Assessment and Management", "Case Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Statistical Analysis"
-- "Risk Assessment and Management"
-- "Case Management"
-- "Program Development and Implementation"
-- "Trauma-Informed Care"
-- "Supervision and Leadership"]
-#Hashtags
+Watch as we build a job-winning Classification and Treatment Director from scratch, highlighting key sections and how to effectively showcase your skills in Statistical Analysis, Risk Assessment and Management, Case Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Statistical Analysis
+- Risk Assessment and Management
+- Case Management
+- Program Development and Implementation
+- Trauma-Informed Care
+- Supervision and Leadership
+#resume
 #ClassificationAndTreatmentDirectorResume #ClassificationAndTreatmentDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2274,16 +2274,16 @@
       <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect College President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning College President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Board Governance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Board Governance"
-- "Fundraising"
-- "Alumni Relations"
-- "Crisis Management"]
-#Hashtags
+Watch as we build a job-winning College President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Board Governance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Board Governance
+- Fundraising
+- Alumni Relations
+- Crisis Management
+#resume
 #CollegePresidentResume #CollegePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2334,16 +2334,16 @@
       <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Commissioner of Internal Revenue? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Commissioner of Internal Revenue from scratch, highlighting key sections and how to effectively showcase your skills in ["Tax Policy Development and Implementation", "Tax Law Interpretation and Enforcement", "Tax Administration and Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Tax Policy Development and Implementation"
-- "Tax Law Interpretation and Enforcement"
-- "Tax Administration and Management"
-- "Budget and Financial Planning"
-- "Strategic Planning and Leadership"
-- "Public Policy Analysis and Advocacy"]
-#Hashtags
+Watch as we build a job-winning Commissioner of Internal Revenue from scratch, highlighting key sections and how to effectively showcase your skills in Tax Policy Development and Implementation, Tax Law Interpretation and Enforcement, Tax Administration and Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Tax Policy Development and Implementation
+- Tax Law Interpretation and Enforcement
+- Tax Administration and Management
+- Budget and Financial Planning
+- Strategic Planning and Leadership
+- Public Policy Analysis and Advocacy
+#resume
 #CommissionerOfInternalRevenueResume #CommissionerOfInternalRevenue #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2394,16 +2394,16 @@
       <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Community Services and Health Education Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Community Services and Health Education Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Program Planning", "Community Assessment", "Health Education", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Program Planning"
-- "Community Assessment"
-- "Health Education"
-- "Grant Writing"
-- "Needs Assessment"
-- "Public Speaking"]
-#Hashtags
+Watch as we build a job-winning Community Services and Health Education Officer from scratch, highlighting key sections and how to effectively showcase your skills in Program Planning, Community Assessment, Health Education, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Program Planning
+- Community Assessment
+- Health Education
+- Grant Writing
+- Needs Assessment
+- Public Speaking
+#resume
 #CommunityServicesAndHealthEducationOfficerResume #CommunityServicesAndHealthEducationOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2454,16 +2454,16 @@
       <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Compliance Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Compliance Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Risk Management", "Compliance Auditing", "Regulatory Compliance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Risk Management"
-- "Compliance Auditing"
-- "Regulatory Compliance"
-- "Internal Controls"
-- "Ethics and Compliance"
-- "Data Privacy"]
-#Hashtags
+Watch as we build a job-winning Compliance Director from scratch, highlighting key sections and how to effectively showcase your skills in Risk Management, Compliance Auditing, Regulatory Compliance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Risk Management
+- Compliance Auditing
+- Regulatory Compliance
+- Internal Controls
+- Ethics and Compliance
+- Data Privacy
+#resume
 #ComplianceDirectorResume #ComplianceDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2514,16 +2514,16 @@
       <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Conservation of Resources Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Conservation of Resources Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Resource Management", "Natural Resource Conservation", "Ecosystem Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Resource Management"
-- "Natural Resource Conservation"
-- "Ecosystem Management"
-- "Land Use Planning"
-- "Water Resource Management"
-- "Forestry"]
-#Hashtags
+Watch as we build a job-winning Conservation of Resources Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Resource Management, Natural Resource Conservation, Ecosystem Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Resource Management
+- Natural Resource Conservation
+- Ecosystem Management
+- Land Use Planning
+- Water Resource Management
+- Forestry
+#resume
 #ConservationOfResourcesCommissionerResume #ConservationOfResourcesCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2574,16 +2574,16 @@
       <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Consumer Affairs Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Consumer Affairs Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Consumer Advocacy", "Dispute Resolution", "Complaint Handling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Consumer Advocacy"
-- "Dispute Resolution"
-- "Complaint Handling"
-- "Regulatory Compliance"
-- "Product Development"
-- "Customer Experience Management"]
-#Hashtags
+Watch as we build a job-winning Consumer Affairs Director from scratch, highlighting key sections and how to effectively showcase your skills in Consumer Advocacy, Dispute Resolution, Complaint Handling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Consumer Advocacy
+- Dispute Resolution
+- Complaint Handling
+- Regulatory Compliance
+- Product Development
+- Customer Experience Management
+#resume
 #ConsumerAffairsDirectorResume #ConsumerAffairsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2634,16 +2634,16 @@
       <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Consumer Affairs Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Consumer Affairs Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Consumer Advocacy", "Dispute Resolution", "Complaint Handling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Consumer Advocacy"
-- "Dispute Resolution"
-- "Complaint Handling"
-- "Regulatory Compliance"
-- "Product Development"
-- "Customer Experience Management"]
-#Hashtags
+Watch as we build a job-winning Consumer Affairs Director from scratch, highlighting key sections and how to effectively showcase your skills in Consumer Advocacy, Dispute Resolution, Complaint Handling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Consumer Advocacy
+- Dispute Resolution
+- Complaint Handling
+- Regulatory Compliance
+- Product Development
+- Customer Experience Management
+#resume
 #ConsumerAffairsDirectorResume #ConsumerAffairsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2694,16 +2694,16 @@
       <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Administrative Support", "Meeting Management", "Travel Coordination", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Administrative Support"
-- "Meeting Management"
-- "Travel Coordination"
-- "Event Planning"
-- "Office Management"
-- "Vendor Management"]
-#Hashtags
+Watch as we build a job-winning Corporate Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Administrative Support, Meeting Management, Travel Coordination, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Administrative Support
+- Meeting Management
+- Travel Coordination
+- Event Planning
+- Office Management
+- Vendor Management
+#resume
 #CorporateAdministratorResume #CorporateAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2754,16 +2754,16 @@
       <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Analysis", "Leadership and Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Analysis"
-- "Leadership and Management"
-- "Corporate Governance"
-- "Risk Management"
-- "Business Development"]
-#Hashtags
+Watch as we build a job-winning Corporate Executive from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Analysis, Leadership and Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Analysis
+- Leadership and Management
+- Corporate Governance
+- Risk Management
+- Business Development
+#resume
 #CorporateExecutiveResume #CorporateExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2814,16 +2814,16 @@
       <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Modeling", "Project Management", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Modeling"
-- "Project Management"
-- "Strategic Planning"
-- "Business Analysis"
-- "Corporate Governance"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Corporate Manager from scratch, highlighting key sections and how to effectively showcase your skills in Financial Modeling, Project Management, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Modeling
+- Project Management
+- Strategic Planning
+- Business Analysis
+- Corporate Governance
+- Risk Management
+#resume
 #CorporateManagerResume #CorporateManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2874,16 +2874,16 @@
       <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Corporate Governance", "Legal Compliance", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Corporate Governance"
-- "Legal Compliance"
-- "Strategic Planning"
-- "Board Relations"
-- "Corporate Finance"
-- "Regulatory Compliance"]
-#Hashtags
+Watch as we build a job-winning Corporate Officer from scratch, highlighting key sections and how to effectively showcase your skills in Corporate Governance, Legal Compliance, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Corporate Governance
+- Legal Compliance
+- Strategic Planning
+- Board Relations
+- Corporate Finance
+- Regulatory Compliance
+#resume
 #CorporateOfficerResume #CorporateOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2934,16 +2934,16 @@
       <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Planner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Planner from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Business Analysis", "Financial Modeling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Business Analysis"
-- "Financial Modeling"
-- "Market Research"
-- "Risk Management"
-- "Scenario Planning"]
-#Hashtags
+Watch as we build a job-winning Corporate Planner from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Business Analysis, Financial Modeling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Business Analysis
+- Financial Modeling
+- Market Research
+- Risk Management
+- Scenario Planning
+#resume
 #CorporatePlannerResume #CorporatePlanner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2994,16 +2994,16 @@
       <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporation Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporation Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Corporate Governance", "Compliance Management", "Risk Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Corporate Governance"
-- "Compliance Management"
-- "Risk Management"
-- "Fiduciary Duties"
-- "Corporate Law"
-- "Business Ethics"]
-#Hashtags
+Watch as we build a job-winning Corporation Officer from scratch, highlighting key sections and how to effectively showcase your skills in Corporate Governance, Compliance Management, Risk Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Corporate Governance
+- Compliance Management
+- Risk Management
+- Fiduciary Duties
+- Corporate Law
+- Business Ethics
+#resume
 #CorporationOfficerResume #CorporationOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3054,16 +3054,16 @@
       <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Correctional Agency Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Correctional Agency Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Correctional Management", "Offender Rehabilitation", "Policy Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Correctional Management"
-- "Offender Rehabilitation"
-- "Policy Development"
-- "Program Evaluation"
-- "Budget Management"
-- "Staff Development"]
-#Hashtags
+Watch as we build a job-winning Correctional Agency Director from scratch, highlighting key sections and how to effectively showcase your skills in Correctional Management, Offender Rehabilitation, Policy Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Correctional Management
+- Offender Rehabilitation
+- Policy Development
+- Program Evaluation
+- Budget Management
+- Staff Development
+#resume
 #CorrectionalAgencyDirectorResume #CorrectionalAgencyDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3114,16 +3114,16 @@
       <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Council On Aging Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Council On Aging Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Program Management", "Advocacy and Outreach", "Geriatric Care Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Program Management"
-- "Advocacy and Outreach"
-- "Geriatric Care Management"
-- "Aging Services Policy"
-- "Community Collaboration"
-- "Budgeting and Financial Management"]
-#Hashtags
+Watch as we build a job-winning Council On Aging Director from scratch, highlighting key sections and how to effectively showcase your skills in Program Management, Advocacy and Outreach, Geriatric Care Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Program Management
+- Advocacy and Outreach
+- Geriatric Care Management
+- Aging Services Policy
+- Community Collaboration
+- Budgeting and Financial Management
+#resume
 #CouncilOnAgingDirectorResume #CouncilOnAgingDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3174,16 +3174,16 @@
       <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect County Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning County Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Analysis", "Human Resources Management", "Project Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Analysis"
-- "Human Resources Management"
-- "Project Management"
-- "Leadership"
-- "Negotiation"
-- "Public Policy"]
-#Hashtags
+Watch as we build a job-winning County Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Budget Analysis, Human Resources Management, Project Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Analysis
+- Human Resources Management
+- Project Management
+- Leadership
+- Negotiation
+- Public Policy
+#resume
 #CountyAdministratorResume #CountyAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3234,16 +3234,16 @@
       <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect County Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning County Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Policy Analysis", "Budgeting and Financial Management", "Land Use Planning and Zoning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Policy Analysis"
-- "Budgeting and Financial Management"
-- "Land Use Planning and Zoning"
-- "Economic Development"
-- "Community Engagement and Outreach"
-- "Negotiation and Conflict Resolution"]
-#Hashtags
+Watch as we build a job-winning County Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Public Policy Analysis, Budgeting and Financial Management, Land Use Planning and Zoning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Policy Analysis
+- Budgeting and Financial Management
+- Land Use Planning and Zoning
+- Economic Development
+- Community Engagement and Outreach
+- Negotiation and Conflict Resolution
+#resume
 #CountyCommissionerResume #CountyCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3294,16 +3294,16 @@
       <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect County Superintendent of Schools? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning County Superintendent of Schools from scratch, highlighting key sections and how to effectively showcase your skills in ["Educational Leadership", "Curriculum Development", "Student Assessment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Educational Leadership"
-- "Curriculum Development"
-- "Student Assessment"
-- "Budget Management"
-- "School Law"
-- "Community Relations"]
-#Hashtags
+Watch as we build a job-winning County Superintendent of Schools from scratch, highlighting key sections and how to effectively showcase your skills in Educational Leadership, Curriculum Development, Student Assessment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Educational Leadership
+- Curriculum Development
+- Student Assessment
+- Budget Management
+- School Law
+- Community Relations
+#resume
 #CountySuperintendentOfSchoolsResume #CountySuperintendentOfSchools #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3354,16 +3354,16 @@
       <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect County Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning County Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "County Planning and Development", "Economic Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "County Planning and Development"
-- "Economic Development"
-- "Environmental Management"
-- "Financial Management"
-- "Government Relations"]
-#Hashtags
+Watch as we build a job-winning County Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, County Planning and Development, Economic Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- County Planning and Development
+- Economic Development
+- Environmental Management
+- Financial Management
+- Government Relations
+#resume
 #CountySupervisorResume #CountySupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3414,16 +3414,16 @@
       <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Department Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Department Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Inventory Management", "Budgeting and Forecasting", "Team Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Inventory Management"
-- "Budgeting and Forecasting"
-- "Team Management"
-- "Customer Relationship Management"
-- "Problem Solving"
-- "Communication Skills"]
-#Hashtags
+Watch as we build a job-winning Department Manager from scratch, highlighting key sections and how to effectively showcase your skills in Inventory Management, Budgeting and Forecasting, Team Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Inventory Management
+- Budgeting and Forecasting
+- Team Management
+- Customer Relationship Management
+- Problem Solving
+- Communication Skills
+#resume
 #DepartmentManagerResume #DepartmentManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3474,16 +3474,16 @@
       <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Department Store Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Department Store Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Inventory Management", "Sales Forecasting", "Customer Relationship Management (CRM)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Inventory Management"
-- "Sales Forecasting"
-- "Customer Relationship Management (CRM)"
-- "Budgeting"
-- "Staff Management"
-- "Sales Management"]
-#Hashtags
+Watch as we build a job-winning Department Store Manager from scratch, highlighting key sections and how to effectively showcase your skills in Inventory Management, Sales Forecasting, Customer Relationship Management (CRM), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Inventory Management
+- Sales Forecasting
+- Customer Relationship Management (CRM)
+- Budgeting
+- Staff Management
+- Sales Management
+#resume
 #DepartmentStoreManagerResume #DepartmentStoreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3534,16 +3534,16 @@
       <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Deputy District Customs Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Deputy District Customs Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Customs Regulations and Procedures", "International Trade Law", "Risk Assessment and Mitigation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Customs Regulations and Procedures"
-- "International Trade Law"
-- "Risk Assessment and Mitigation"
-- "Enforcement and Investigations"
-- "Leadership and Management"
-- "Strategic Planning"]
-#Hashtags
+Watch as we build a job-winning Deputy District Customs Director from scratch, highlighting key sections and how to effectively showcase your skills in Customs Regulations and Procedures, International Trade Law, Risk Assessment and Mitigation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Customs Regulations and Procedures
+- International Trade Law
+- Risk Assessment and Mitigation
+- Enforcement and Investigations
+- Leadership and Management
+- Strategic Planning
+#resume
 #DeputyDistrictCustomsDirectorResume #DeputyDistrictCustomsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3594,16 +3594,16 @@
       <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Deputy Insurance Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Deputy Insurance Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Insurance Law", "Regulatory Compliance", "Financial Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Insurance Law"
-- "Regulatory Compliance"
-- "Financial Analysis"
-- "Risk Management"
-- "Insurance Policy Development"
-- "Insurance Market Analysis"]
-#Hashtags
+Watch as we build a job-winning Deputy Insurance Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Insurance Law, Regulatory Compliance, Financial Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Insurance Law
+- Regulatory Compliance
+- Financial Analysis
+- Risk Management
+- Insurance Policy Development
+- Insurance Market Analysis
+#resume
 #DeputyInsuranceCommissionerResume #DeputyInsuranceCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3654,16 +3654,16 @@
       <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Director of Vital Statistics? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Director of Vital Statistics from scratch, highlighting key sections and how to effectively showcase your skills in ["Data Management", "Vital Records Administration", "Statistical Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Data Management"
-- "Vital Records Administration"
-- "Statistical Analysis"
-- "Project Management"
-- "Budget Management"
-- "Legal and Ethical Considerations"]
-#Hashtags
+Watch as we build a job-winning Director of Vital Statistics from scratch, highlighting key sections and how to effectively showcase your skills in Data Management, Vital Records Administration, Statistical Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Data Management
+- Vital Records Administration
+- Statistical Analysis
+- Project Management
+- Budget Management
+- Legal and Ethical Considerations
+#resume
 #DirectorOfVitalStatisticsResume #DirectorOfVitalStatistics #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3714,16 +3714,16 @@
       <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect District Customs Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning District Customs Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Customs Regulations and Procedures", "Tariff Classification", "Valuation of Merchandise", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Customs Regulations and Procedures"
-- "Tariff Classification"
-- "Valuation of Merchandise"
-- "Duty Collection and Accounting"
-- "Customs Enforcement and Investigations"
-- "Import/Export Compliance"]
-#Hashtags
+Watch as we build a job-winning District Customs Director from scratch, highlighting key sections and how to effectively showcase your skills in Customs Regulations and Procedures, Tariff Classification, Valuation of Merchandise, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Customs Regulations and Procedures
+- Tariff Classification
+- Valuation of Merchandise
+- Duty Collection and Accounting
+- Customs Enforcement and Investigations
+- Import/Export Compliance
+#resume
 #DistrictCustomsDirectorResume #DistrictCustomsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3774,16 +3774,16 @@
       <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Economic Development Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Economic Development Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Economic Development Strategy Development", "Business Attraction and Retention", "Community Outreach and Engagement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Economic Development Strategy Development"
-- "Business Attraction and Retention"
-- "Community Outreach and Engagement"
-- "Grant Writing and Management"
-- "Data Analysis and Reporting"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Economic Development Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Economic Development Strategy Development, Business Attraction and Retention, Community Outreach and Engagement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Economic Development Strategy Development
+- Business Attraction and Retention
+- Community Outreach and Engagement
+- Grant Writing and Management
+- Data Analysis and Reporting
+- Project Management
+#resume
 #EconomicDevelopmentCoordinatorResume #EconomicDevelopmentCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3834,16 +3834,16 @@
       <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Educational Institution President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Educational Institution President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Institutional Management", "Academic Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Institutional Management"
-- "Academic Leadership"
-- "Budget Management"
-- "Stakeholder Relations"
-- "Curriculum Development"]
-#Hashtags
+Watch as we build a job-winning Educational Institution President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Institutional Management, Academic Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Institutional Management
+- Academic Leadership
+- Budget Management
+- Stakeholder Relations
+- Curriculum Development
+#resume
 #EducationalInstitutionPresidentResume #EducationalInstitutionPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3894,16 +3894,16 @@
       <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Election Assistant? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Election Assistant from scratch, highlighting key sections and how to effectively showcase your skills in ["Ballot Processing", "Voter Registration", "Election Canvassing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Ballot Processing"
-- "Voter Registration"
-- "Election Canvassing"
-- "Poll Worker Training"
-- "Absentee Voting Management"
-- "Early Voting Procedures"]
-#Hashtags
+Watch as we build a job-winning Election Assistant from scratch, highlighting key sections and how to effectively showcase your skills in Ballot Processing, Voter Registration, Election Canvassing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Ballot Processing
+- Voter Registration
+- Election Canvassing
+- Poll Worker Training
+- Absentee Voting Management
+- Early Voting Procedures
+#resume
 #ElectionAssistantResume #ElectionAssistant #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3954,16 +3954,16 @@
       <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Employment Research and Planning Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Employment Research and Planning Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Labor Market Analysis", "Workforce Planning", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Labor Market Analysis"
-- "Workforce Planning"
-- "Strategic Planning"
-- "Data Analysis"
-- "Forecasting"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Employment Research and Planning Director from scratch, highlighting key sections and how to effectively showcase your skills in Labor Market Analysis, Workforce Planning, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Labor Market Analysis
+- Workforce Planning
+- Strategic Planning
+- Data Analysis
+- Forecasting
+- Project Management
+#resume
 #EmploymentResearchAndPlanningDirectorResume #EmploymentResearchAndPlanningDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4014,16 +4014,16 @@
       <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Employment Services Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Employment Services Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Job Development", "Case Management", "Career Counseling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Job Development"
-- "Case Management"
-- "Career Counseling"
-- "Resume Writing"
-- "Interview Preparation"
-- "Labor Market Analysis"]
-#Hashtags
+Watch as we build a job-winning Employment Services Director from scratch, highlighting key sections and how to effectively showcase your skills in Job Development, Case Management, Career Counseling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Job Development
+- Case Management
+- Career Counseling
+- Resume Writing
+- Interview Preparation
+- Labor Market Analysis
+#resume
 #EmploymentServicesDirectorResume #EmploymentServicesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4074,16 +4074,16 @@
       <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Environmental Analyst? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Environmental Analyst from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Impact Assessment", "Air Quality Monitoring and Modeling", "Water Quality Assessment and Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Impact Assessment"
-- "Air Quality Monitoring and Modeling"
-- "Water Quality Assessment and Management"
-- "Soil and Sediment Sampling and Analysis"
-- "GIS Mapping and Analysis"
-- "Environmental Regulations and Compliance"]
-#Hashtags
+Watch as we build a job-winning Environmental Analyst from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Impact Assessment, Air Quality Monitoring and Modeling, Water Quality Assessment and Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Impact Assessment
+- Air Quality Monitoring and Modeling
+- Water Quality Assessment and Management
+- Soil and Sediment Sampling and Analysis
+- GIS Mapping and Analysis
+- Environmental Regulations and Compliance
+#resume
 #EnvironmentalAnalystResume #EnvironmentalAnalyst #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4134,16 +4134,16 @@
       <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Executive Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Executive Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Administrative Support", "Board and Executive Relations", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Administrative Support"
-- "Board and Executive Relations"
-- "Budget Management"
-- "Calendar Management"
-- "Communication"
-- "Conflict Resolution"]
-#Hashtags
+Watch as we build a job-winning Executive Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Administrative Support, Board and Executive Relations, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Administrative Support
+- Board and Executive Relations
+- Budget Management
+- Calendar Management
+- Communication
+- Conflict Resolution
+#resume
 #ExecutiveAdministratorResume #ExecutiveAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4194,16 +4194,16 @@
       <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Executive Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Executive Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Board and Governance", "Fundraising and Grant Writing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Board and Governance"
-- "Fundraising and Grant Writing"
-- "Team Leadership and Management"
-- "Program Development and Evaluation"
-- "Community Engagement"]
-#Hashtags
+Watch as we build a job-winning Executive Director from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Board and Governance, Fundraising and Grant Writing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Board and Governance
+- Fundraising and Grant Writing
+- Team Leadership and Management
+- Program Development and Evaluation
+- Community Engagement
+#resume
 #ExecutiveDirectorResume #ExecutiveDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4254,16 +4254,16 @@
       <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Executive Vice President (EVP)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Executive Vice President (EVP) from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Management", "Operations Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Management"
-- "Operations Management"
-- "Business Development"
-- "Team Leadership"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Executive Vice President (EVP) from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Management, Operations Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Management
+- Operations Management
+- Business Development
+- Team Leadership
+- Risk Management
+#resume
 #ExecutiveVicePresidentEvpResume #ExecutiveVicePresidentEvp #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4314,18 +4314,18 @@
       <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Federal Aid Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Federal Aid Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Higher Education Act (HEA) and Title IV Regulations", "Federal Student Aid (FSA) Handbook", "Customer Service and Communication Skills", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Higher Education Act (HEA) and Title IV Regulations"
-- "Federal Student Aid (FSA) Handbook"
-- "Customer Service and Communication Skills"
-- "Data Analysis and Reporting"
-- "Problem Solving and Decision Making"
-- "Microsoft Office Suite (Word
+Watch as we build a job-winning Federal Aid Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Higher Education Act (HEA) and Title IV Regulations, Federal Student Aid (FSA) Handbook, Customer Service and Communication Skills, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Higher Education Act (HEA) and Title IV Regulations
+- Federal Student Aid (FSA) Handbook
+- Customer Service and Communication Skills
+- Data Analysis and Reporting
+- Problem Solving and Decision Making
+- Microsoft Office Suite (Word
 - Excel
-- PowerPoint)"]
-#Hashtags
+- PowerPoint)
+#resume
 #FederalAidCoordinatorResume #FederalAidCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4376,16 +4376,16 @@
       <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Field Representatives Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Field Representatives Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Sales Management", "Sales Training", "Performance Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Sales Management"
-- "Sales Training"
-- "Performance Management"
-- "Market Analysis"
-- "Negotiation"
-- "Team Building"]
-#Hashtags
+Watch as we build a job-winning Field Representatives Director from scratch, highlighting key sections and how to effectively showcase your skills in Sales Management, Sales Training, Performance Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Sales Management
+- Sales Training
+- Performance Management
+- Market Analysis
+- Negotiation
+- Team Building
+#resume
 #FieldRepresentativesDirectorResume #FieldRepresentativesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4436,16 +4436,16 @@
       <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Financial Institution President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Financial Institution President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Modeling", "Risk Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Modeling"
-- "Risk Management"
-- "Compliance Management"
-- "Corporate Finance"
-- "Investment Management"]
-#Hashtags
+Watch as we build a job-winning Financial Institution President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Modeling, Risk Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Modeling
+- Risk Management
+- Compliance Management
+- Corporate Finance
+- Investment Management
+#resume
 #FinancialInstitutionPresidentResume #FinancialInstitutionPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4496,16 +4496,16 @@
       <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Financial Responsibility Division Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Financial Responsibility Division Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Responsibility Analysis", "Solvency and Risk Management", "Insurance Regulations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Responsibility Analysis"
-- "Solvency and Risk Management"
-- "Insurance Regulations"
-- "Captive Insurance Management"
-- "Financial Reporting and Disclosure"
-- "Strategic Planning and Forecasting"]
-#Hashtags
+Watch as we build a job-winning Financial Responsibility Division Director from scratch, highlighting key sections and how to effectively showcase your skills in Financial Responsibility Analysis, Solvency and Risk Management, Insurance Regulations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Responsibility Analysis
+- Solvency and Risk Management
+- Insurance Regulations
+- Captive Insurance Management
+- Financial Reporting and Disclosure
+- Strategic Planning and Forecasting
+#resume
 #FinancialResponsibilityDivisionDirectorResume #FinancialResponsibilityDivisionDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4556,16 +4556,16 @@
       <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Financial Secretary? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Financial Secretary from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Accounting", "Operations Management", "Budgeting and Forecasting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Accounting"
-- "Operations Management"
-- "Budgeting and Forecasting"
-- "Financial Reporting and Analysis"
-- "Auditing and Compliance"
-- "Cash Management"]
-#Hashtags
+Watch as we build a job-winning Financial Secretary from scratch, highlighting key sections and how to effectively showcase your skills in Financial Accounting, Operations Management, Budgeting and Forecasting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Accounting
+- Operations Management
+- Budgeting and Forecasting
+- Financial Reporting and Analysis
+- Auditing and Compliance
+- Cash Management
+#resume
 #FinancialSecretaryResume #FinancialSecretary #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4616,16 +4616,16 @@
       <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Fire Chief? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Fire Chief from scratch, highlighting key sections and how to effectively showcase your skills in ["Firefighting Tactics and Strategy", "Emergency Management and Disaster Response", "Personnel Management and Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Firefighting Tactics and Strategy"
-- "Emergency Management and Disaster Response"
-- "Personnel Management and Leadership"
-- "Budget Management and Fiscal Planning"
-- "Public Relations and Community Engagement"
-- "Incident Command and Control"]
-#Hashtags
+Watch as we build a job-winning Fire Chief from scratch, highlighting key sections and how to effectively showcase your skills in Firefighting Tactics and Strategy, Emergency Management and Disaster Response, Personnel Management and Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Firefighting Tactics and Strategy
+- Emergency Management and Disaster Response
+- Personnel Management and Leadership
+- Budget Management and Fiscal Planning
+- Public Relations and Community Engagement
+- Incident Command and Control
+#resume
 #FireChiefResume #FireChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4676,16 +4676,16 @@
       <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Fishery Division Chief? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Fishery Division Chief from scratch, highlighting key sections and how to effectively showcase your skills in ["Fish Population Assessment", "Fishery Management Plan Development", "Fish Habitat Assessment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Fish Population Assessment"
-- "Fishery Management Plan Development"
-- "Fish Habitat Assessment"
-- "Enforcement and Compliance"
-- "Budget Management"
-- "Personnel Management"]
-#Hashtags
+Watch as we build a job-winning Fishery Division Chief from scratch, highlighting key sections and how to effectively showcase your skills in Fish Population Assessment, Fishery Management Plan Development, Fish Habitat Assessment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Fish Population Assessment
+- Fishery Management Plan Development
+- Fish Habitat Assessment
+- Enforcement and Compliance
+- Budget Management
+- Personnel Management
+#resume
 #FisheryDivisionChiefResume #FisheryDivisionChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4736,16 +4736,16 @@
       <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Foreign Diplomat? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Foreign Diplomat from scratch, highlighting key sections and how to effectively showcase your skills in ["Diplomatic Protocol Management", "International Relations Analysis", "Political Negotiations and Dialogue", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Diplomatic Protocol Management"
-- "International Relations Analysis"
-- "Political Negotiations and Dialogue"
-- "Cross-Cultural Communication and Etiquette"
-- "Public Speaking and Presentation Skills"
-- "Conflict Resolution and Mediation"]
-#Hashtags
+Watch as we build a job-winning Foreign Diplomat from scratch, highlighting key sections and how to effectively showcase your skills in Diplomatic Protocol Management, International Relations Analysis, Political Negotiations and Dialogue, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Diplomatic Protocol Management
+- International Relations Analysis
+- Political Negotiations and Dialogue
+- Cross-Cultural Communication and Etiquette
+- Public Speaking and Presentation Skills
+- Conflict Resolution and Mediation
+#resume
 #ForeignDiplomatResume #ForeignDiplomat #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4796,16 +4796,16 @@
       <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Foreign Service Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Foreign Service Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Cross-Cultural Communication", "Negotiation and Conflict Resolution", "Policy Analysis and Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Cross-Cultural Communication"
-- "Negotiation and Conflict Resolution"
-- "Policy Analysis and Development"
-- "Public Diplomacy and Advocacy"
-- "Management and Supervision"
-- "Written and Verbal Communication"]
-#Hashtags
+Watch as we build a job-winning Foreign Service Officer from scratch, highlighting key sections and how to effectively showcase your skills in Cross-Cultural Communication, Negotiation and Conflict Resolution, Policy Analysis and Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Cross-Cultural Communication
+- Negotiation and Conflict Resolution
+- Policy Analysis and Development
+- Public Diplomacy and Advocacy
+- Management and Supervision
+- Written and Verbal Communication
+#resume
 #ForeignServiceOfficerResume #ForeignServiceOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4856,16 +4856,16 @@
       <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Foundation Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Foundation Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Grant Writing", "Donor Cultivation", "Capital Campaign Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Grant Writing"
-- "Donor Cultivation"
-- "Capital Campaign Management"
-- "Nonprofit Management"
-- "Budgeting and Finance"
-- "Board Development"]
-#Hashtags
+Watch as we build a job-winning Foundation Director from scratch, highlighting key sections and how to effectively showcase your skills in Grant Writing, Donor Cultivation, Capital Campaign Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Grant Writing
+- Donor Cultivation
+- Capital Campaign Management
+- Nonprofit Management
+- Budgeting and Finance
+- Board Development
+#resume
 #FoundationDirectorResume #FoundationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4916,16 +4916,16 @@
       <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Government Service Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Government Service Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Public Policy Analysis", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Public Policy Analysis"
-- "Budget Management"
-- "Human Capital Management"
-- "Performance Management"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Government Service Executive from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Public Policy Analysis, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Public Policy Analysis
+- Budget Management
+- Human Capital Management
+- Performance Management
+- Risk Management
+#resume
 #GovernmentServiceExecutiveResume #GovernmentServiceExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4976,16 +4976,16 @@
       <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Governor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Governor from scratch, highlighting key sections and how to effectively showcase your skills in ["Policy Development", "Budget Management", "Public Speaking", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Policy Development"
-- "Budget Management"
-- "Public Speaking"
-- "Constituent Relations"
-- "Stakeholder Management"
-- "Crisis Management"]
-#Hashtags
+Watch as we build a job-winning Governor from scratch, highlighting key sections and how to effectively showcase your skills in Policy Development, Budget Management, Public Speaking, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Policy Development
+- Budget Management
+- Public Speaking
+- Constituent Relations
+- Stakeholder Management
+- Crisis Management
+#resume
 #GovernorResume #Governor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5036,16 +5036,16 @@
       <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Harbor Master? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Harbor Master from scratch, highlighting key sections and how to effectively showcase your skills in ["Vessel Traffic Management", "Marina Management", "Port Operations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Vessel Traffic Management"
-- "Marina Management"
-- "Port Operations"
-- "Navigational Safety"
-- "Emergency Response"
-- "Environmental Compliance"]
-#Hashtags
+Watch as we build a job-winning Harbor Master from scratch, highlighting key sections and how to effectively showcase your skills in Vessel Traffic Management, Marina Management, Port Operations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Vessel Traffic Management
+- Marina Management
+- Port Operations
+- Navigational Safety
+- Emergency Response
+- Environmental Compliance
+#resume
 #HarborMasterResume #HarborMaster #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5096,16 +5096,16 @@
       <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Health Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Health Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Health", "Public Health Administration", "Epidemiology", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Health"
-- "Public Health Administration"
-- "Epidemiology"
-- "Health Policy Analysis"
-- "Community Health Assessment"
-- "Health Communication"]
-#Hashtags
+Watch as we build a job-winning Health Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Health, Public Health Administration, Epidemiology, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Health
+- Public Health Administration
+- Epidemiology
+- Health Policy Analysis
+- Community Health Assessment
+- Health Communication
+#resume
 #HealthCommissionerResume #HealthCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5156,16 +5156,16 @@
       <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Highway Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Highway Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Highway Construction Management", "Roadway Design", "Traffic Engineering", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Highway Construction Management"
-- "Roadway Design"
-- "Traffic Engineering"
-- "Project Management"
-- "Budget Analysis"
-- "Personnel Management"]
-#Hashtags
+Watch as we build a job-winning Highway Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Highway Construction Management, Roadway Design, Traffic Engineering, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Highway Construction Management
+- Roadway Design
+- Traffic Engineering
+- Project Management
+- Budget Analysis
+- Personnel Management
+#resume
 #HighwayCommissionerResume #HighwayCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5216,16 +5216,16 @@
       <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Housing Management Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Housing Management Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Housing Laws", "Rent Collection", "Housing Inspection", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Housing Laws"
-- "Rent Collection"
-- "Housing Inspection"
-- "Property Management"
-- "Resident Screening"
-- "Work Order Management"]
-#Hashtags
+Watch as we build a job-winning Housing Management Officer from scratch, highlighting key sections and how to effectively showcase your skills in Public Housing Laws, Rent Collection, Housing Inspection, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Housing Laws
+- Rent Collection
+- Housing Inspection
+- Property Management
+- Resident Screening
+- Work Order Management
+#resume
 #HousingManagementOfficerResume #HousingManagementOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5276,16 +5276,16 @@
       <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Institution Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Institution Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Grant Writing and Management", "Budget Management and Financial Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Grant Writing and Management"
-- "Budget Management and Financial Planning"
-- "Program Development and Implementation"
-- "Stakeholder Engagement and Relationship Management"
-- "Advocacy and Policy Development"]
-#Hashtags
+Watch as we build a job-winning Institution Director from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Grant Writing and Management, Budget Management and Financial Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Grant Writing and Management
+- Budget Management and Financial Planning
+- Program Development and Implementation
+- Stakeholder Engagement and Relationship Management
+- Advocacy and Policy Development
+#resume
 #InstitutionDirectorResume #InstitutionDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5336,16 +5336,16 @@
       <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Insurance Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Insurance Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Actuarial Analysis", "Financial Modeling", "Insurance Regulatory Knowledge", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Actuarial Analysis"
-- "Financial Modeling"
-- "Insurance Regulatory Knowledge"
-- "Ratemaking Analysis"
-- "Reserve Analysis"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Insurance Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Actuarial Analysis, Financial Modeling, Insurance Regulatory Knowledge, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Actuarial Analysis
+- Financial Modeling
+- Insurance Regulatory Knowledge
+- Ratemaking Analysis
+- Reserve Analysis
+- Risk Management
+#resume
 #InsuranceCommissionerResume #InsuranceCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5396,16 +5396,16 @@
       <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect International Accounting User Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning International Accounting User Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["International Financial Reporting Standards (IFRS)", "Generally Accepted Accounting Principles (GAAP)", "International Accounting Standards (IAS)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["International Financial Reporting Standards (IFRS)"
-- "Generally Accepted Accounting Principles (GAAP)"
-- "International Accounting Standards (IAS)"
-- "Financial Accounting Standards Board (FASB)"
-- "International Accounting Standards Board (IASB)"
-- "Foreign Currency Translation"]
-#Hashtags
+Watch as we build a job-winning International Accounting User Representative from scratch, highlighting key sections and how to effectively showcase your skills in International Financial Reporting Standards (IFRS), Generally Accepted Accounting Principles (GAAP), International Accounting Standards (IAS), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- International Financial Reporting Standards (IFRS)
+- Generally Accepted Accounting Principles (GAAP)
+- International Accounting Standards (IAS)
+- Financial Accounting Standards Board (FASB)
+- International Accounting Standards Board (IASB)
+- Foreign Currency Translation
+#resume
 #InternationalAccountingUserRepresentativeResume #InternationalAccountingUserRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5456,16 +5456,16 @@
       <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Irrigation Tax Assessor-Collector? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Irrigation Tax Assessor-Collector from scratch, highlighting key sections and how to effectively showcase your skills in ["Agricultural Water Management", "Irrigation Tax Assessment and Collection", "Property Valuation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agricultural Water Management"
-- "Irrigation Tax Assessment and Collection"
-- "Property Valuation"
-- "GIS Mapping and Analysis"
-- "Data Analysis and Reporting"
-- "Customer Service and Outreach"]
-#Hashtags
+Watch as we build a job-winning Irrigation Tax Assessor-Collector from scratch, highlighting key sections and how to effectively showcase your skills in Agricultural Water Management, Irrigation Tax Assessment and Collection, Property Valuation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agricultural Water Management
+- Irrigation Tax Assessment and Collection
+- Property Valuation
+- GIS Mapping and Analysis
+- Data Analysis and Reporting
+- Customer Service and Outreach
+#resume
 #IrrigationTaxAssessorCollectorResume #IrrigationTaxAssessorCollector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5516,16 +5516,16 @@
       <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Labor Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Labor Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Federal and State Labor Laws", "Conducting Labor Investigations", "Mediating Labor Disputes", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Federal and State Labor Laws"
-- "Conducting Labor Investigations"
-- "Mediating Labor Disputes"
-- "Drafting and Interpreting Labor Agreements"
-- "Enforcing Labor Standards"
-- "Inspection of Workplaces"]
-#Hashtags
+Watch as we build a job-winning Labor Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Federal and State Labor Laws, Conducting Labor Investigations, Mediating Labor Disputes, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Federal and State Labor Laws
+- Conducting Labor Investigations
+- Mediating Labor Disputes
+- Drafting and Interpreting Labor Agreements
+- Enforcing Labor Standards
+- Inspection of Workplaces
+#resume
 #LaborCommissionerResume #LaborCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5576,16 +5576,16 @@
       <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Labor Standards Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Labor Standards Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Wage and Hour Law Compliance", "Payroll and Benefits Management", "Labor Relations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Wage and Hour Law Compliance"
-- "Payroll and Benefits Management"
-- "Labor Relations"
-- "Human Resources Management"
-- "Employee Management"
-- "Performance Management"]
-#Hashtags
+Watch as we build a job-winning Labor Standards Director from scratch, highlighting key sections and how to effectively showcase your skills in Wage and Hour Law Compliance, Payroll and Benefits Management, Labor Relations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Wage and Hour Law Compliance
+- Payroll and Benefits Management
+- Labor Relations
+- Human Resources Management
+- Employee Management
+- Performance Management
+#resume
 #LaborStandardsDirectorResume #LaborStandardsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5636,16 +5636,16 @@
       <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Law Enforcement Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Law Enforcement Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Community Policing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Community Policing"
-- "Crisis Management"
-- "Criminal Investigation"
-- "Emergency Preparedness"]
-#Hashtags
+Watch as we build a job-winning Law Enforcement Director from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Community Policing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Community Policing
+- Crisis Management
+- Criminal Investigation
+- Emergency Preparedness
+#resume
 #LawEnforcementDirectorResume #LawEnforcementDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5696,16 +5696,16 @@
       <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Licensing and Registration Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Licensing and Registration Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Negotiation", "Policy Analysis", "Regulatory Compliance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Negotiation"
-- "Policy Analysis"
-- "Regulatory Compliance"
-- "License and Permit Management"
-- "Records Management"
-- "Customer Relationship Management"]
-#Hashtags
+Watch as we build a job-winning Licensing and Registration Director from scratch, highlighting key sections and how to effectively showcase your skills in Negotiation, Policy Analysis, Regulatory Compliance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Negotiation
+- Policy Analysis
+- Regulatory Compliance
+- License and Permit Management
+- Records Management
+- Customer Relationship Management
+#resume
 #LicensingAndRegistrationDirectorResume #LicensingAndRegistrationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5756,16 +5756,16 @@
       <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Lieutenant Governor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Lieutenant Governor from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "Constituent Services Management", "Disaster Relief Coordination", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "Constituent Services Management"
-- "Disaster Relief Coordination"
-- "Economic Development Analysis"
-- "Emergency Preparedness Planning"
-- "Government Relations"]
-#Hashtags
+Watch as we build a job-winning Lieutenant Governor from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, Constituent Services Management, Disaster Relief Coordination, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- Constituent Services Management
+- Disaster Relief Coordination
+- Economic Development Analysis
+- Emergency Preparedness Planning
+- Government Relations
+#resume
 #LieutenantGovernorResume #LieutenantGovernor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5816,16 +5816,16 @@
       <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Liquor Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Liquor Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Alcohol Beverage Control", "Regulatory Compliance", "Licensing and Permitting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Alcohol Beverage Control"
-- "Regulatory Compliance"
-- "Licensing and Permitting"
-- "Enforcement and Investigation"
-- "Public Education and Outreach"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Liquor Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Alcohol Beverage Control, Regulatory Compliance, Licensing and Permitting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Alcohol Beverage Control
+- Regulatory Compliance
+- Licensing and Permitting
+- Enforcement and Investigation
+- Public Education and Outreach
+- Budget Management
+#resume
 #LiquorCommissionerResume #LiquorCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5876,16 +5876,16 @@
       <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Liquor Stores and Agencies Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Liquor Stores and Agencies Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Alcohol Management", "Beverage Management", "Budgeting and Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Alcohol Management"
-- "Beverage Management"
-- "Budgeting and Planning"
-- "Customer Relationship Management (CRM)"
-- "Employee Management"
-- "Inventory Management"]
-#Hashtags
+Watch as we build a job-winning Liquor Stores and Agencies Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Alcohol Management, Beverage Management, Budgeting and Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Alcohol Management
+- Beverage Management
+- Budgeting and Planning
+- Customer Relationship Management (CRM)
+- Employee Management
+- Inventory Management
+#resume
 #LiquorStoresAndAgenciesSupervisorResume #LiquorStoresAndAgenciesSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5936,16 +5936,16 @@
       <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Mayor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Mayor from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Policy Analysis", "Budget Management", "Community Engagement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Policy Analysis"
-- "Budget Management"
-- "Community Engagement"
-- "Strategic Planning"
-- "Infrastructure Development"
-- "Land Use Planning"]
-#Hashtags
+Watch as we build a job-winning Mayor from scratch, highlighting key sections and how to effectively showcase your skills in Public Policy Analysis, Budget Management, Community Engagement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Policy Analysis
+- Budget Management
+- Community Engagement
+- Strategic Planning
+- Infrastructure Development
+- Land Use Planning
+#resume
 #MayorResume #Mayor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5996,16 +5996,16 @@
       <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Media Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Media Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Digital Marketing", "Social Media Marketing", "Content Marketing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Digital Marketing"
-- "Social Media Marketing"
-- "Content Marketing"
-- "Media Planning and Buying"
-- "Data Analysis and Reporting"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Media Executive from scratch, highlighting key sections and how to effectively showcase your skills in Digital Marketing, Social Media Marketing, Content Marketing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Digital Marketing
+- Social Media Marketing
+- Content Marketing
+- Media Planning and Buying
+- Data Analysis and Reporting
+- Project Management
+#resume
 #MediaExecutiveResume #MediaExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6056,16 +6056,16 @@
       <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Medical Facilities Section Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Medical Facilities Section Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Operations Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Operations Management"
-- "Risk Management"
-- "Compliance"
-- "Communication"]
-#Hashtags
+Watch as we build a job-winning Medical Facilities Section Director from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Operations Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Operations Management
+- Risk Management
+- Compliance
+- Communication
+#resume
 #MedicalFacilitiesSectionDirectorResume #MedicalFacilitiesSectionDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6116,16 +6116,16 @@
       <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Music Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Music Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Music Licensing and Negotiation", "Artist Development and Management", "Concert and Tour Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Music Licensing and Negotiation"
-- "Artist Development and Management"
-- "Concert and Tour Management"
-- "Music Marketing and Promotion"
-- "Digital Music Distribution"
-- "Music Publishing"]
-#Hashtags
+Watch as we build a job-winning Music Executive from scratch, highlighting key sections and how to effectively showcase your skills in Music Licensing and Negotiation, Artist Development and Management, Concert and Tour Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Music Licensing and Negotiation
+- Artist Development and Management
+- Concert and Tour Management
+- Music Marketing and Promotion
+- Digital Music Distribution
+- Music Publishing
+#resume
 #MusicExecutiveResume #MusicExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6176,16 +6176,16 @@
       <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Music Publisher? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Music Publisher from scratch, highlighting key sections and how to effectively showcase your skills in ["Music Publishing", "Copyright Law", "Contract Negotiation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Music Publishing"
-- "Copyright Law"
-- "Contract Negotiation"
-- "Royalty Audit"
-- "Digital Distribution"
-- "International Music Publishing"]
-#Hashtags
+Watch as we build a job-winning Music Publisher from scratch, highlighting key sections and how to effectively showcase your skills in Music Publishing, Copyright Law, Contract Negotiation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Music Publishing
+- Copyright Law
+- Contract Negotiation
+- Royalty Audit
+- Digital Distribution
+- International Music Publishing
+#resume
 #MusicPublisherResume #MusicPublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6236,16 +6236,16 @@
       <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Newspaper Publisher? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Newspaper Publisher from scratch, highlighting key sections and how to effectively showcase your skills in ["Newspaper Editing", "Page Layout", "Copyediting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Newspaper Editing"
-- "Page Layout"
-- "Copyediting"
-- "News Writing"
-- "Feature Writing"
-- "Reporting"]
-#Hashtags
+Watch as we build a job-winning Newspaper Publisher from scratch, highlighting key sections and how to effectively showcase your skills in Newspaper Editing, Page Layout, Copyediting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Newspaper Editing
+- Page Layout
+- Copyediting
+- News Writing
+- Feature Writing
+- Reporting
+#resume
 #NewspaperPublisherResume #NewspaperPublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6296,16 +6296,16 @@
       <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Nonprofit Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Nonprofit Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Nonprofit Management", "Board Governance", "Fundraising Strategy", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Nonprofit Management"
-- "Board Governance"
-- "Fundraising Strategy"
-- "Program Development"
-- "Stakeholder Engagement"
-- "Policy Analysis"]
-#Hashtags
+Watch as we build a job-winning Nonprofit Director from scratch, highlighting key sections and how to effectively showcase your skills in Nonprofit Management, Board Governance, Fundraising Strategy, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Nonprofit Management
+- Board Governance
+- Fundraising Strategy
+- Program Development
+- Stakeholder Engagement
+- Policy Analysis
+#resume
 #NonprofitDirectorResume #NonprofitDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6356,16 +6356,16 @@
       <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Nonprofit Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Nonprofit Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Fundraising", "Program Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Fundraising"
-- "Program Management"
-- "Donor Relations"
-- "Volunteer Management"
-- "Grant Writing"]
-#Hashtags
+Watch as we build a job-winning Nonprofit Manager from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Fundraising, Program Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Fundraising
+- Program Management
+- Donor Relations
+- Volunteer Management
+- Grant Writing
+#resume
 #NonprofitManagerResume #NonprofitManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6416,16 +6416,16 @@
       <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Operations Vice President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Operations Vice President from scratch, highlighting key sections and how to effectively showcase your skills in ["Process Optimization", "Supply Chain Management", "Inventory Control", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Process Optimization"
-- "Supply Chain Management"
-- "Inventory Control"
-- "Operations Planning"
-- "Quality Management"
-- "Business Strategy"]
-#Hashtags
+Watch as we build a job-winning Operations Vice President from scratch, highlighting key sections and how to effectively showcase your skills in Process Optimization, Supply Chain Management, Inventory Control, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Process Optimization
+- Supply Chain Management
+- Inventory Control
+- Operations Planning
+- Quality Management
+- Business Strategy
+#resume
 #OperationsVicePresidentResume #OperationsVicePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6476,16 +6476,16 @@
       <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Park Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Park Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Planning", "Natural Resource Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Planning"
-- "Natural Resource Management"
-- "Budget Management"
-- "Project Management"
-- "Staff Supervision"
-- "GIS Mapping and Analysis"]
-#Hashtags
+Watch as we build a job-winning Park Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Planning, Natural Resource Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Planning
+- Natural Resource Management
+- Budget Management
+- Project Management
+- Staff Supervision
+- GIS Mapping and Analysis
+#resume
 #ParkSuperintendentResume #ParkSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6536,16 +6536,16 @@
       <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Police Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Police Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Emergency Management", "Public Safety Planning", "Law Enforcement Operations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Emergency Management"
-- "Public Safety Planning"
-- "Law Enforcement Operations"
-- "Budget Management"
-- "Personnel Management"
-- "Community Relations"]
-#Hashtags
+Watch as we build a job-winning Police Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Emergency Management, Public Safety Planning, Law Enforcement Operations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Emergency Management
+- Public Safety Planning
+- Law Enforcement Operations
+- Budget Management
+- Personnel Management
+- Community Relations
+#resume
 #PoliceCommissionerResume #PoliceCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6596,16 +6596,16 @@
       <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Policy Advisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Policy Advisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Policy Analysis and Development", "Legislative Research and Monitoring", "Stakeholder Engagement and Outreach", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Policy Analysis and Development"
-- "Legislative Research and Monitoring"
-- "Stakeholder Engagement and Outreach"
-- "Regulatory Compliance and Interpretation"
-- "Policy Evaluation and Monitoring"
-- "Project Management and Coordination"]
-#Hashtags
+Watch as we build a job-winning Policy Advisor from scratch, highlighting key sections and how to effectively showcase your skills in Policy Analysis and Development, Legislative Research and Monitoring, Stakeholder Engagement and Outreach, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Policy Analysis and Development
+- Legislative Research and Monitoring
+- Stakeholder Engagement and Outreach
+- Regulatory Compliance and Interpretation
+- Policy Evaluation and Monitoring
+- Project Management and Coordination
+#resume
 #PolicyAdvisorResume #PolicyAdvisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6656,16 +6656,16 @@
       <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Policy Officer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Policy Officer from scratch, highlighting key sections and how to effectively showcase your skills in ["Policy Analysis", "Regulatory Research", "Stakeholder Engagement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Policy Analysis"
-- "Regulatory Research"
-- "Stakeholder Engagement"
-- "Policy Advocacy"
-- "Legislative Drafting"
-- "Risk Assessment"]
-#Hashtags
+Watch as we build a job-winning Policy Officer from scratch, highlighting key sections and how to effectively showcase your skills in Policy Analysis, Regulatory Research, Stakeholder Engagement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Policy Analysis
+- Regulatory Research
+- Stakeholder Engagement
+- Policy Advocacy
+- Legislative Drafting
+- Risk Assessment
+#resume
 #PolicyOfficerResume #PolicyOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6716,16 +6716,16 @@
       <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Leadership", "Team Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Leadership"
-- "Team Management"
-- "Business Development"
-- "Financial Management"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Leadership, Team Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Leadership
+- Team Management
+- Business Development
+- Financial Management
+- Risk Management
+#resume
 #PresidentResume #President #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6776,16 +6776,16 @@
       <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Private Sector Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Private Sector Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Business Development", "Financial Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Business Development"
-- "Financial Analysis"
-- "Risk Management"
-- "Project Management"
-- "Team Leadership"]
-#Hashtags
+Watch as we build a job-winning Private Sector Executive from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Business Development, Financial Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Business Development
+- Financial Analysis
+- Risk Management
+- Project Management
+- Team Leadership
+#resume
 #PrivateSectorExecutiveResume #PrivateSectorExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6836,16 +6836,16 @@
       <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Program Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Program Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Project Management", "Budget Management", "Stakeholder Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Project Management"
-- "Budget Management"
-- "Stakeholder Management"
-- "Grant Management"
-- "Data Analysis"
-- "Reporting"]
-#Hashtags
+Watch as we build a job-winning Program Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Project Management, Budget Management, Stakeholder Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Project Management
+- Budget Management
+- Stakeholder Management
+- Grant Management
+- Data Analysis
+- Reporting
+#resume
 #ProgramAdministratorResume #ProgramAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6896,16 +6896,16 @@
       <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Program Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Program Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Agile Development", "Program Planning", "Stakeholder Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agile Development"
-- "Program Planning"
-- "Stakeholder Management"
-- "Risk Management"
-- "Budget Management"
-- "Project Monitoring and Evaluation"]
-#Hashtags
+Watch as we build a job-winning Program Manager from scratch, highlighting key sections and how to effectively showcase your skills in Agile Development, Program Planning, Stakeholder Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agile Development
+- Program Planning
+- Stakeholder Management
+- Risk Management
+- Budget Management
+- Project Monitoring and Evaluation
+#resume
 #ProgramManagerResume #ProgramManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6956,16 +6956,16 @@
       <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Public Health Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Public Health Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Health Program Management", "Epidemic Intelligence", "Health Equity and Social Justice", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Health Program Management"
-- "Epidemic Intelligence"
-- "Health Equity and Social Justice"
-- "Environmental Health"
-- "Disaster Preparedness and Response"
-- "Health Policy Analysis"]
-#Hashtags
+Watch as we build a job-winning Public Health Director from scratch, highlighting key sections and how to effectively showcase your skills in Public Health Program Management, Epidemic Intelligence, Health Equity and Social Justice, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Health Program Management
+- Epidemic Intelligence
+- Health Equity and Social Justice
+- Environmental Health
+- Disaster Preparedness and Response
+- Health Policy Analysis
+#resume
 #PublicHealthDirectorResume #PublicHealthDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7016,16 +7016,16 @@
       <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Public Works Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Public Works Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting", "Capital Project Management", "Construction Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting"
-- "Capital Project Management"
-- "Construction Management"
-- "Contract Administration"
-- "Environmental Compliance"
-- "Facility Maintenance Management"]
-#Hashtags
+Watch as we build a job-winning Public Works Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting, Capital Project Management, Construction Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting
+- Capital Project Management
+- Construction Management
+- Contract Administration
+- Environmental Compliance
+- Facility Maintenance Management
+#resume
 #PublicWorksCommissionerResume #PublicWorksCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7076,16 +7076,16 @@
       <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Public Works Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Public Works Director from scratch, highlighting key sections and how to effectively showcase your skills in ["GIS Mapping and Analysis", "Construction Management", "Project Planning and Execution", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["GIS Mapping and Analysis"
-- "Construction Management"
-- "Project Planning and Execution"
-- "Budget Management"
-- "Capital Improvement Planning"
-- "Stormwater Management"]
-#Hashtags
+Watch as we build a job-winning Public Works Director from scratch, highlighting key sections and how to effectively showcase your skills in GIS Mapping and Analysis, Construction Management, Project Planning and Execution, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- GIS Mapping and Analysis
+- Construction Management
+- Project Planning and Execution
+- Budget Management
+- Capital Improvement Planning
+- Stormwater Management
+#resume
 #PublicWorksDirectorResume #PublicWorksDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7136,16 +7136,16 @@
       <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Railroad Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Railroad Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Railroad Operations", "FRA Regulations", "Railroad Safety", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Railroad Operations"
-- "FRA Regulations"
-- "Railroad Safety"
-- "Regulatory Compliance"
-- "Accident Investigation"
-- "Public Speaking"]
-#Hashtags
+Watch as we build a job-winning Railroad Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Railroad Operations, FRA Regulations, Railroad Safety, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Railroad Operations
+- FRA Regulations
+- Railroad Safety
+- Regulatory Compliance
+- Accident Investigation
+- Public Speaking
+#resume
 #RailroadCommissionerResume #RailroadCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7196,16 +7196,16 @@
       <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Recreation Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Recreation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Park Planning", "Recreation Programming", "Facility Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Park Planning"
-- "Recreation Programming"
-- "Facility Management"
-- "Event Coordination"
-- "Community Outreach"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Recreation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Park Planning, Recreation Programming, Facility Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Park Planning
+- Recreation Programming
+- Facility Management
+- Event Coordination
+- Community Outreach
+- Budget Management
+#resume
 #RecreationSuperintendentResume #RecreationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7256,16 +7256,16 @@
       <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Regional Wildlife Agent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Regional Wildlife Agent from scratch, highlighting key sections and how to effectively showcase your skills in ["Wildlife Management", "Conservation Biology", "Wildlife Law Enforcement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Wildlife Management"
-- "Conservation Biology"
-- "Wildlife Law Enforcement"
-- "Wildlife Monitoring"
-- "Human-Wildlife Conflict Management"
-- "Wildlife Habitat Assessment"]
-#Hashtags
+Watch as we build a job-winning Regional Wildlife Agent from scratch, highlighting key sections and how to effectively showcase your skills in Wildlife Management, Conservation Biology, Wildlife Law Enforcement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Wildlife Management
+- Conservation Biology
+- Wildlife Law Enforcement
+- Wildlife Monitoring
+- Human-Wildlife Conflict Management
+- Wildlife Habitat Assessment
+#resume
 #RegionalWildlifeAgentResume #RegionalWildlifeAgent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7316,16 +7316,16 @@
       <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Regulated Program Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Regulated Program Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Regulatory Compliance Management", "Quality Assurance and Control", "Risk Management and Mitigation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Regulatory Compliance Management"
-- "Quality Assurance and Control"
-- "Risk Management and Mitigation"
-- "Inspection and Enforcement"
-- "Training and Development"
-- "Policy and Procedure Development"]
-#Hashtags
+Watch as we build a job-winning Regulated Program Manager from scratch, highlighting key sections and how to effectively showcase your skills in Regulatory Compliance Management, Quality Assurance and Control, Risk Management and Mitigation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Regulatory Compliance Management
+- Quality Assurance and Control
+- Risk Management and Mitigation
+- Inspection and Enforcement
+- Training and Development
+- Policy and Procedure Development
+#resume
 #RegulatedProgramManagerResume #RegulatedProgramManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7376,16 +7376,16 @@
       <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Regulatory Agency Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Regulatory Agency Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Regulatory Compliance", "Quality Assurance", "Risk Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Regulatory Compliance"
-- "Quality Assurance"
-- "Risk Management"
-- "Audit and Inspection"
-- "Policy Development"
-- "Regulatory Affairs"]
-#Hashtags
+Watch as we build a job-winning Regulatory Agency Director from scratch, highlighting key sections and how to effectively showcase your skills in Regulatory Compliance, Quality Assurance, Risk Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Regulatory Compliance
+- Quality Assurance
+- Risk Management
+- Audit and Inspection
+- Policy Development
+- Regulatory Affairs
+#resume
 #RegulatoryAgencyDirectorResume #RegulatoryAgencyDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7436,16 +7436,16 @@
       <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Regulatory Analyst? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Regulatory Analyst from scratch, highlighting key sections and how to effectively showcase your skills in ["Regulatory Affairs", "FDA Regulations", "ICH Guidelines", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Regulatory Affairs"
-- "FDA Regulations"
-- "ICH Guidelines"
-- "Medical Device Regulations"
-- "Pharmaceutical Regulations"
-- "Clinical Trial Regulations"]
-#Hashtags
+Watch as we build a job-winning Regulatory Analyst from scratch, highlighting key sections and how to effectively showcase your skills in Regulatory Affairs, FDA Regulations, ICH Guidelines, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Regulatory Affairs
+- FDA Regulations
+- ICH Guidelines
+- Medical Device Regulations
+- Pharmaceutical Regulations
+- Clinical Trial Regulations
+#resume
 #RegulatoryAnalystResume #RegulatoryAnalyst #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7496,16 +7496,16 @@
       <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Relocation Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Relocation Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Counseling and Support", "Stress Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Counseling and Support"
-- "Stress Management"
-- "Budget Management"
-- "Conflict Resolution"
-- "Negotiation"
-- "Home Inspection"]
-#Hashtags
+Watch as we build a job-winning Relocation Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Counseling and Support, Stress Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Counseling and Support
+- Stress Management
+- Budget Management
+- Conflict Resolution
+- Negotiation
+- Home Inspection
+#resume
 #RelocationCommissionerResume #RelocationCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7556,16 +7556,16 @@
       <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Revenue Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Revenue Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Revenue Management", "Pricing Strategy", "Market Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Revenue Management"
-- "Pricing Strategy"
-- "Market Analysis"
-- "Customer Relationship Management"
-- "Sales Forecasting"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Revenue Director from scratch, highlighting key sections and how to effectively showcase your skills in Revenue Management, Pricing Strategy, Market Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Revenue Management
+- Pricing Strategy
+- Market Analysis
+- Customer Relationship Management
+- Sales Forecasting
+- Budget Management
+#resume
 #RevenueDirectorResume #RevenueDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7616,16 +7616,16 @@
       <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Road Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Road Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Road Construction and Maintenance", "Budget Management", "Project Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Road Construction and Maintenance"
-- "Budget Management"
-- "Project Management"
-- "Team Leadership"
-- "Communication and Interpersonal Skills"
-- "Knowledge of Roadway Design and Construction Standards"]
-#Hashtags
+Watch as we build a job-winning Road Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Road Construction and Maintenance, Budget Management, Project Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Road Construction and Maintenance
+- Budget Management
+- Project Management
+- Team Leadership
+- Communication and Interpersonal Skills
+- Knowledge of Roadway Design and Construction Standards
+#resume
 #RoadCommissionerResume #RoadCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7676,16 +7676,16 @@
       <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Roads Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Roads Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Road Construction Management", "Pavement Design and Analysis", "Asphalt and Concrete Paving", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Road Construction Management"
-- "Pavement Design and Analysis"
-- "Asphalt and Concrete Paving"
-- "Bridge Inspection and Maintenance"
-- "Traffic Signalization and Control"
-- "Stormwater Management"]
-#Hashtags
+Watch as we build a job-winning Roads Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Road Construction Management, Pavement Design and Analysis, Asphalt and Concrete Paving, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Road Construction Management
+- Pavement Design and Analysis
+- Asphalt and Concrete Paving
+- Bridge Inspection and Maintenance
+- Traffic Signalization and Control
+- Stormwater Management
+#resume
 #RoadsSupervisorResume #RoadsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7736,16 +7736,16 @@
       <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Safety Council Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Safety Council Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Risk Assessment", "Safety Management Systems", "Accident Investigation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Risk Assessment"
-- "Safety Management Systems"
-- "Accident Investigation"
-- "Emergency Preparedness"
-- "Compliance Management"
-- "Employee Training"]
-#Hashtags
+Watch as we build a job-winning Safety Council Director from scratch, highlighting key sections and how to effectively showcase your skills in Risk Assessment, Safety Management Systems, Accident Investigation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Risk Assessment
+- Safety Management Systems
+- Accident Investigation
+- Emergency Preparedness
+- Compliance Management
+- Employee Training
+#resume
 #SafetyCouncilDirectorResume #SafetyCouncilDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7796,16 +7796,16 @@
       <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sanitation Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sanitation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Wastewater Treatment Plant Operations", "Solid Waste Management", "Water Quality Monitoring", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Wastewater Treatment Plant Operations"
-- "Solid Waste Management"
-- "Water Quality Monitoring"
-- "Environmental Compliance"
-- "Budget Management"
-- "Personnel Management"]
-#Hashtags
+Watch as we build a job-winning Sanitation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Wastewater Treatment Plant Operations, Solid Waste Management, Water Quality Monitoring, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Wastewater Treatment Plant Operations
+- Solid Waste Management
+- Water Quality Monitoring
+- Environmental Compliance
+- Budget Management
+- Personnel Management
+#resume
 #SanitationSuperintendentResume #SanitationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7856,16 +7856,16 @@
       <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect School Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning School Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Understanding of School Budgeting and Finance", "Policy Development and Implementation", "Leadership and Vision Setting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Understanding of School Budgeting and Finance"
-- "Policy Development and Implementation"
-- "Leadership and Vision Setting"
-- "Collaboration withStakeholders"
-- "Negotiation and Conflict Resolution"
-- "Problem Solving"]
-#Hashtags
+Watch as we build a job-winning School Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Understanding of School Budgeting and Finance, Policy Development and Implementation, Leadership and Vision Setting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Understanding of School Budgeting and Finance
+- Policy Development and Implementation
+- Leadership and Vision Setting
+- Collaboration withStakeholders
+- Negotiation and Conflict Resolution
+- Problem Solving
+#resume
 #SchoolCommissionerResume #SchoolCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7916,16 +7916,16 @@
       <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Secretary of State? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Secretary of State from scratch, highlighting key sections and how to effectively showcase your skills in ["Election Administration", "Voter Registration", "Campaign Finance Regulation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Election Administration"
-- "Voter Registration"
-- "Campaign Finance Regulation"
-- "Government Ethics Enforcement"
-- "Public Records Management"
-- "Legislative Drafting"]
-#Hashtags
+Watch as we build a job-winning Secretary of State from scratch, highlighting key sections and how to effectively showcase your skills in Election Administration, Voter Registration, Campaign Finance Regulation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Election Administration
+- Voter Registration
+- Campaign Finance Regulation
+- Government Ethics Enforcement
+- Public Records Management
+- Legislative Drafting
+#resume
 #SecretaryOfStateResume #SecretaryOfState #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7976,16 +7976,16 @@
       <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Software Publisher? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Software Publisher from scratch, highlighting key sections and how to effectively showcase your skills in ["Software Development Lifecycle (SDLC)", "Product Knowledge", "Agile Software Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Software Development Lifecycle (SDLC)"
-- "Product Knowledge"
-- "Agile Software Development"
-- "Software Testing"
-- "Microsoft Office Suite"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Software Publisher from scratch, highlighting key sections and how to effectively showcase your skills in Software Development Lifecycle (SDLC), Product Knowledge, Agile Software Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Software Development Lifecycle (SDLC)
+- Product Knowledge
+- Agile Software Development
+- Software Testing
+- Microsoft Office Suite
+- Project Management
+#resume
 #SoftwarePublisherResume #SoftwarePublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8036,16 +8036,16 @@
       <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect State Assessed Properties Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning State Assessed Properties Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Property Appraisal", "Tax Assessment", "Property Tax Administration", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Property Appraisal"
-- "Tax Assessment"
-- "Property Tax Administration"
-- "Mass Appraisal Techniques"
-- "Property Valuation"
-- "Data Analysis"]
-#Hashtags
+Watch as we build a job-winning State Assessed Properties Director from scratch, highlighting key sections and how to effectively showcase your skills in Property Appraisal, Tax Assessment, Property Tax Administration, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Property Appraisal
+- Tax Assessment
+- Property Tax Administration
+- Mass Appraisal Techniques
+- Property Valuation
+- Data Analysis
+#resume
 #StateAssessedPropertiesDirectorResume #StateAssessedPropertiesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8096,16 +8096,16 @@
       <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect State Board of Nursing Executive Secretary? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning State Board of Nursing Executive Secretary from scratch, highlighting key sections and how to effectively showcase your skills in ["Nursing Law and Regulations", "Board Policy Development", "Disciplinary Process Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Nursing Law and Regulations"
-- "Board Policy Development"
-- "Disciplinary Process Management"
-- "Meeting Management"
-- "Records Management"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning State Board of Nursing Executive Secretary from scratch, highlighting key sections and how to effectively showcase your skills in Nursing Law and Regulations, Board Policy Development, Disciplinary Process Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Nursing Law and Regulations
+- Board Policy Development
+- Disciplinary Process Management
+- Meeting Management
+- Records Management
+- Budget Management
+#resume
 #StateBoardOfNursingExecutiveSecretaryResume #StateBoardOfNursingExecutiveSecretary #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8156,18 +8156,18 @@
       <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Sustainability Process Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Sustainability Process Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Greenhouse Gas Emissions Reporting", "Carbon Footprint Analysis", "Sustainability Reporting Frameworks (GRI, and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Greenhouse Gas Emissions Reporting"
-- "Carbon Footprint Analysis"
-- "Sustainability Reporting Frameworks (GRI
+Watch as we build a job-winning Corporate Sustainability Process Manager from scratch, highlighting key sections and how to effectively showcase your skills in Greenhouse Gas Emissions Reporting, Carbon Footprint Analysis, Sustainability Reporting Frameworks (GRI, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Greenhouse Gas Emissions Reporting
+- Carbon Footprint Analysis
+- Sustainability Reporting Frameworks (GRI
 - SASB
-- TCFD)"
-- "Stakeholder Engagement and Communication"
-- "Life Cycle Assessment"
-- "Environmental Policy and Regulation Compliance"]
-#Hashtags
+- TCFD)
+- Stakeholder Engagement and Communication
+- Life Cycle Assessment
+- Environmental Policy and Regulation Compliance
+#resume
 #CorporateSustainabilityProcessManagerResume #CorporateSustainabilityProcessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8218,16 +8218,16 @@
       <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect State Superintendent of Public Instruction? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning State Superintendent of Public Instruction from scratch, highlighting key sections and how to effectively showcase your skills in ["Education Policy Development", "Strategic Planning", "Curriculum Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Education Policy Development"
-- "Strategic Planning"
-- "Curriculum Development"
-- "School Finance"
-- "Student Assessment and Accountability"
-- "Teacher Professional Development"]
-#Hashtags
+Watch as we build a job-winning State Superintendent of Public Instruction from scratch, highlighting key sections and how to effectively showcase your skills in Education Policy Development, Strategic Planning, Curriculum Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Education Policy Development
+- Strategic Planning
+- Curriculum Development
+- School Finance
+- Student Assessment and Accountability
+- Teacher Professional Development
+#resume
 #StateSuperintendentOfPublicInstructionResume #StateSuperintendentOfPublicInstruction #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8278,16 +8278,16 @@
       <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect State Superintendent of Schools? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning State Superintendent of Schools from scratch, highlighting key sections and how to effectively showcase your skills in ["Educational Policy Development", "Curriculum Management", "School Finance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Educational Policy Development"
-- "Curriculum Management"
-- "School Finance"
-- "Educational Leadership"
-- "Teacher Evaluation"
-- "Data Analysis"]
-#Hashtags
+Watch as we build a job-winning State Superintendent of Schools from scratch, highlighting key sections and how to effectively showcase your skills in Educational Policy Development, Curriculum Management, School Finance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Educational Policy Development
+- Curriculum Management
+- School Finance
+- Educational Leadership
+- Teacher Evaluation
+- Data Analysis
+#resume
 #StateSuperintendentOfSchoolsResume #StateSuperintendentOfSchools #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8338,16 +8338,16 @@
       <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Store Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Store Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Inventory Management", "Customer Service", "Sales and Marketing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Inventory Management"
-- "Customer Service"
-- "Sales and Marketing"
-- "Team Leadership"
-- "Problem Solving"
-- "Communication"]
-#Hashtags
+Watch as we build a job-winning Store Manager from scratch, highlighting key sections and how to effectively showcase your skills in Inventory Management, Customer Service, Sales and Marketing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Inventory Management
+- Customer Service
+- Sales and Marketing
+- Team Leadership
+- Problem Solving
+- Communication
+#resume
 #StoreManagerResume #StoreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8398,16 +8398,16 @@
       <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Strategic Planner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Strategic Planner from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Scanning", "Scenario Planning", "SWOT Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Scanning"
-- "Scenario Planning"
-- "SWOT Analysis"
-- "Market Research"
-- "Competitive Analysis"
-- "Forecasting"]
-#Hashtags
+Watch as we build a job-winning Strategic Planner from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Scanning, Scenario Planning, SWOT Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Scanning
+- Scenario Planning
+- SWOT Analysis
+- Market Research
+- Competitive Analysis
+- Forecasting
+#resume
 #StrategicPlannerResume #StrategicPlanner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8458,16 +8458,16 @@
       <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Team Management", "Conflict Resolution", "Performance Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Team Management"
-- "Conflict Resolution"
-- "Performance Management"
-- "Delegation"
-- "Project Management"
-- "Communication"]
-#Hashtags
+Watch as we build a job-winning Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Team Management, Conflict Resolution, Performance Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Team Management
+- Conflict Resolution
+- Performance Management
+- Delegation
+- Project Management
+- Communication
+#resume
 #SupervisorResume #Supervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8518,16 +8518,16 @@
       <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Tax Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Tax Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Tax Law Interpretation", "Tax Audit Techniques", "Tax Policy Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Tax Law Interpretation"
-- "Tax Audit Techniques"
-- "Tax Policy Analysis"
-- "Revenue Forecasting"
-- "Budget Management"
-- "Stakeholder Engagement"]
-#Hashtags
+Watch as we build a job-winning Tax Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Tax Law Interpretation, Tax Audit Techniques, Tax Policy Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Tax Law Interpretation
+- Tax Audit Techniques
+- Tax Policy Analysis
+- Revenue Forecasting
+- Budget Management
+- Stakeholder Engagement
+#resume
 #TaxCommissionerResume #TaxCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8578,16 +8578,16 @@
       <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Top Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Top Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Acumen", "Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Acumen"
-- "Leadership"
-- "Communication"
-- "Negotiation"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Top Executive from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Acumen, Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Acumen
+- Leadership
+- Communication
+- Negotiation
+- Risk Management
+#resume
 #TopExecutiveResume #TopExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8638,16 +8638,16 @@
       <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Township Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Township Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Municipal Finance", "Budget Management", "Contract Administration", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Municipal Finance"
-- "Budget Management"
-- "Contract Administration"
-- "Land Use Planning"
-- "Zoning Enforcement"
-- "Public Works Management"]
-#Hashtags
+Watch as we build a job-winning Township Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Municipal Finance, Budget Management, Contract Administration, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Municipal Finance
+- Budget Management
+- Contract Administration
+- Land Use Planning
+- Zoning Enforcement
+- Public Works Management
+#resume
 #TownshipSupervisorResume #TownshipSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8698,16 +8698,16 @@
       <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Traffic Safety Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Traffic Safety Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Traffic Incident Management", "Roadway Safety Analysis", "Crash Data Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Traffic Incident Management"
-- "Roadway Safety Analysis"
-- "Crash Data Analysis"
-- "Transportation Planning"
-- "Public Education and Outreach"
-- "Grant Management"]
-#Hashtags
+Watch as we build a job-winning Traffic Safety Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Traffic Incident Management, Roadway Safety Analysis, Crash Data Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Traffic Incident Management
+- Roadway Safety Analysis
+- Crash Data Analysis
+- Transportation Planning
+- Public Education and Outreach
+- Grant Management
+#resume
 #TrafficSafetyAdministratorResume #TrafficSafetyAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8758,16 +8758,16 @@
       <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Translation Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Translation Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Translation Management", "Localization", "Project Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Translation Management"
-- "Localization"
-- "Project Management"
-- "Terminology Management"
-- "Machine Translation"
-- "Translation Quality Assessment"]
-#Hashtags
+Watch as we build a job-winning Translation Director from scratch, highlighting key sections and how to effectively showcase your skills in Translation Management, Localization, Project Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Translation Management
+- Localization
+- Project Management
+- Terminology Management
+- Machine Translation
+- Translation Quality Assessment
+#resume
 #TranslationDirectorResume #TranslationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8818,16 +8818,16 @@
       <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Treasurer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Treasurer from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Reporting", "Cash Flow Management", "Budgeting and Forecasting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Reporting"
-- "Cash Flow Management"
-- "Budgeting and Forecasting"
-- "Treasury Operations"
-- "Investment Management"
-- "Risk Management"]
-#Hashtags
+Watch as we build a job-winning Treasurer from scratch, highlighting key sections and how to effectively showcase your skills in Financial Reporting, Cash Flow Management, Budgeting and Forecasting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Reporting
+- Cash Flow Management
+- Budgeting and Forecasting
+- Treasury Operations
+- Investment Management
+- Risk Management
+#resume
 #TreasurerResume #Treasurer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8878,16 +8878,16 @@
       <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect U.S. Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning U.S. Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Policy Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Policy Analysis"
-- "Regulatory Interpretation"
-- "Enforcement Actions"
-- "Interagency Coordination"]
-#Hashtags
+Watch as we build a job-winning U.S. Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Policy Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Policy Analysis
+- Regulatory Interpretation
+- Enforcement Actions
+- Interagency Coordination
+#resume
 #USCommissionerResume #USCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8938,16 +8938,16 @@
       <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Unemployment Insurance Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Unemployment Insurance Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Unemployment Insurance Claim Adjudication", "Unemployment Insurance Benefit Determination", "Unemployment Insurance Fraud Detection", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Unemployment Insurance Claim Adjudication"
-- "Unemployment Insurance Benefit Determination"
-- "Unemployment Insurance Fraud Detection"
-- "Unemployment Insurance Appeals Management"
-- "Unemployment Insurance Compliance Auditing"
-- "Unemployment Insurance Program Administration"]
-#Hashtags
+Watch as we build a job-winning Unemployment Insurance Director from scratch, highlighting key sections and how to effectively showcase your skills in Unemployment Insurance Claim Adjudication, Unemployment Insurance Benefit Determination, Unemployment Insurance Fraud Detection, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Unemployment Insurance Claim Adjudication
+- Unemployment Insurance Benefit Determination
+- Unemployment Insurance Fraud Detection
+- Unemployment Insurance Appeals Management
+- Unemployment Insurance Compliance Auditing
+- Unemployment Insurance Program Administration
+#resume
 #UnemploymentInsuranceDirectorResume #UnemploymentInsuranceDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8998,16 +8998,16 @@
       <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect University President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning University President from scratch, highlighting key sections and how to effectively showcase your skills in ["Institutional Leadership", "Strategic Planning", "Financial Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Institutional Leadership"
-- "Strategic Planning"
-- "Financial Management"
-- "Stakeholder Engagement"
-- "Fundraising and Development"
-- "Academic Affairs Management"]
-#Hashtags
+Watch as we build a job-winning University President from scratch, highlighting key sections and how to effectively showcase your skills in Institutional Leadership, Strategic Planning, Financial Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Institutional Leadership
+- Strategic Planning
+- Financial Management
+- Stakeholder Engagement
+- Fundraising and Development
+- Academic Affairs Management
+#resume
 #UniversityPresidentResume #UniversityPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9058,16 +9058,16 @@
       <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Vice Chancellor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Vice Chancellor from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Organizational Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Organizational Leadership"
-- "Fundraising and Development"
-- "Higher Education Administration"
-- "Policy Development and Implementation"]
-#Hashtags
+Watch as we build a job-winning Vice Chancellor from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Organizational Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Organizational Leadership
+- Fundraising and Development
+- Higher Education Administration
+- Policy Development and Implementation
+#resume
 #ViceChancellorResume #ViceChancellor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9118,16 +9118,16 @@
       <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Vice President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Vice President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Financial Management", "Operations Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Financial Management"
-- "Operations Management"
-- "Risk Management"
-- "Team Leadership"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Vice President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Financial Management, Operations Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Financial Management
+- Operations Management
+- Risk Management
+- Team Leadership
+- Negotiation
+#resume
 #VicePresidentResume #VicePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9178,16 +9178,16 @@
       <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Maintenance", "Wastewater Treatment Plant Operation", "Water Quality Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Maintenance"
-- "Wastewater Treatment Plant Operation"
-- "Water Quality Analysis"
-- "Drinking Water Treatment"
-- "Stormwater Management"
-- "Water Conservation and Efficiency"]
-#Hashtags
+Watch as we build a job-winning Water Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Maintenance, Wastewater Treatment Plant Operation, Water Quality Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Maintenance
+- Wastewater Treatment Plant Operation
+- Water Quality Analysis
+- Drinking Water Treatment
+- Stormwater Management
+- Water Conservation and Efficiency
+#resume
 #WaterCommissionerResume #WaterCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9238,16 +9238,16 @@
       <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Welfare Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Welfare Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Grant Management", "Welfare Program Development", "Policy Analysis and Interpretation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Grant Management"
-- "Welfare Program Development"
-- "Policy Analysis and Interpretation"
-- "Budget Management"
-- "Case Management"
-- "Community Outreach"]
-#Hashtags
+Watch as we build a job-winning Welfare Director from scratch, highlighting key sections and how to effectively showcase your skills in Grant Management, Welfare Program Development, Policy Analysis and Interpretation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Grant Management
+- Welfare Program Development
+- Policy Analysis and Interpretation
+- Budget Management
+- Case Management
+- Community Outreach
+#resume
 #WelfareDirectorResume #WelfareDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9298,16 +9298,16 @@
       <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Environmental Commitment Officer (CECO)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Environmental Commitment Officer (CECO) from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Policy Development", "Environmental Management Systems (EMS)", "Environmental Impact Assessment (EIA)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Policy Development"
-- "Environmental Management Systems (EMS)"
-- "Environmental Impact Assessment (EIA)"
-- "Climate Change Mitigation and Adaptation"
-- "Environmental Auditing and Compliance"
-- "Stakeholder Engagement and Communication"]
-#Hashtags
+Watch as we build a job-winning Chief Environmental Commitment Officer (CECO) from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Policy Development, Environmental Management Systems (EMS), Environmental Impact Assessment (EIA), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Policy Development
+- Environmental Management Systems (EMS)
+- Environmental Impact Assessment (EIA)
+- Climate Change Mitigation and Adaptation
+- Environmental Auditing and Compliance
+- Stakeholder Engagement and Communication
+#resume
 #ChiefEnvironmentalCommitmentOfficerCecoResume #ChiefEnvironmentalCommitmentOfficerCeco #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9358,16 +9358,16 @@
       <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Green Officer (CGO)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Green Officer (CGO) from scratch, highlighting key sections and how to effectively showcase your skills in ["Sustainability Strategy Development", "Carbon Accounting and Reporting", "Renewable Energy Integration", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Sustainability Strategy Development"
-- "Carbon Accounting and Reporting"
-- "Renewable Energy Integration"
-- "Waste Reduction and Management"
-- "Environmental Compliance"
-- "Stakeholder Engagement"]
-#Hashtags
+Watch as we build a job-winning Chief Green Officer (CGO) from scratch, highlighting key sections and how to effectively showcase your skills in Sustainability Strategy Development, Carbon Accounting and Reporting, Renewable Energy Integration, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Sustainability Strategy Development
+- Carbon Accounting and Reporting
+- Renewable Energy Integration
+- Waste Reduction and Management
+- Environmental Compliance
+- Stakeholder Engagement
+#resume
 #ChiefGreenOfficerCgoResume #ChiefGreenOfficerCgo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9418,18 +9418,18 @@
       <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Corporate Sustainability Process Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Corporate Sustainability Process Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Greenhouse Gas Emissions Reporting", "Carbon Footprint Analysis", "Sustainability Reporting Frameworks (GRI, and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Greenhouse Gas Emissions Reporting"
-- "Carbon Footprint Analysis"
-- "Sustainability Reporting Frameworks (GRI
+Watch as we build a job-winning Corporate Sustainability Process Manager from scratch, highlighting key sections and how to effectively showcase your skills in Greenhouse Gas Emissions Reporting, Carbon Footprint Analysis, Sustainability Reporting Frameworks (GRI, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Greenhouse Gas Emissions Reporting
+- Carbon Footprint Analysis
+- Sustainability Reporting Frameworks (GRI
 - SASB
-- TCFD)"
-- "Stakeholder Engagement and Communication"
-- "Life Cycle Assessment"
-- "Environmental Policy and Regulation Compliance"]
-#Hashtags
+- TCFD)
+- Stakeholder Engagement and Communication
+- Life Cycle Assessment
+- Environmental Policy and Regulation Compliance
+#resume
 #CorporateSustainabilityProcessManagerResume #CorporateSustainabilityProcessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9480,16 +9480,16 @@
       <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Director of Sustainability? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Director of Sustainability from scratch, highlighting key sections and how to effectively showcase your skills in ["Greenhouse Gas Accounting", "Carbon Footprint Analysis", "Life Cycle Assessment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Greenhouse Gas Accounting"
-- "Carbon Footprint Analysis"
-- "Life Cycle Assessment"
-- "Sustainable Supply Chain Management"
-- "Environmental Impact Assessment"
-- "Sustainability Reporting"]
-#Hashtags
+Watch as we build a job-winning Director of Sustainability from scratch, highlighting key sections and how to effectively showcase your skills in Greenhouse Gas Accounting, Carbon Footprint Analysis, Life Cycle Assessment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Greenhouse Gas Accounting
+- Carbon Footprint Analysis
+- Life Cycle Assessment
+- Sustainable Supply Chain Management
+- Environmental Impact Assessment
+- Sustainability Reporting
+#resume
 #DirectorOfSustainabilityResume #DirectorOfSustainability #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9540,16 +9540,16 @@
       <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Director of Sustainability Programs? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Director of Sustainability Programs from scratch, highlighting key sections and how to effectively showcase your skills in ["Sustainability Strategy Development", "Environmental Management Systems (ISO 14001)", "Greenhouse Gas Emissions Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Sustainability Strategy Development"
-- "Environmental Management Systems (ISO 14001)"
-- "Greenhouse Gas Emissions Management"
-- "Renewable Energy Integration"
-- "Sustainability Reporting and Disclosure"
-- "Circular Economy Principles"]
-#Hashtags
+Watch as we build a job-winning Director of Sustainability Programs from scratch, highlighting key sections and how to effectively showcase your skills in Sustainability Strategy Development, Environmental Management Systems (ISO 14001), Greenhouse Gas Emissions Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Sustainability Strategy Development
+- Environmental Management Systems (ISO 14001)
+- Greenhouse Gas Emissions Management
+- Renewable Energy Integration
+- Sustainability Reporting and Disclosure
+- Circular Economy Principles
+#resume
 #DirectorOfSustainabilityProgramsResume #DirectorOfSustainabilityPrograms #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9600,16 +9600,16 @@
       <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Director of Sustainable Design? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Director of Sustainable Design from scratch, highlighting key sections and how to effectively showcase your skills in ["LEED Project Management", "Sustainable Site Design", "Green Building Design and Construction", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["LEED Project Management"
-- "Sustainable Site Design"
-- "Green Building Design and Construction"
-- "Energy Modeling and Analysis"
-- "Water Conservation and Management"
-- "Renewable Energy Integration"]
-#Hashtags
+Watch as we build a job-winning Director of Sustainable Design from scratch, highlighting key sections and how to effectively showcase your skills in LEED Project Management, Sustainable Site Design, Green Building Design and Construction, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- LEED Project Management
+- Sustainable Site Design
+- Green Building Design and Construction
+- Energy Modeling and Analysis
+- Water Conservation and Management
+- Renewable Energy Integration
+#resume
 #DirectorOfSustainableDesignResume #DirectorOfSustainableDesign #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9660,16 +9660,16 @@
       <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Energy and Sustainability Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Energy and Sustainability Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Energy Auditing", "Energy Modeling", "Renewable Energy Integration", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Energy Auditing"
-- "Energy Modeling"
-- "Renewable Energy Integration"
-- "Energy Management Systems"
-- "Carbon Accounting and Reporting"
-- "Sustainability Reporting"]
-#Hashtags
+Watch as we build a job-winning Energy and Sustainability Manager from scratch, highlighting key sections and how to effectively showcase your skills in Energy Auditing, Energy Modeling, Renewable Energy Integration, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Energy Auditing
+- Energy Modeling
+- Renewable Energy Integration
+- Energy Management Systems
+- Carbon Accounting and Reporting
+- Sustainability Reporting
+#resume
 #EnergyAndSustainabilityManagerResume #EnergyAndSustainabilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9720,16 +9720,16 @@
       <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Environment Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Environment Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Impact Assessment", "Environmental Management", "Environmental Regulations Compliance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Impact Assessment"
-- "Environmental Management"
-- "Environmental Regulations Compliance"
-- "Sustainability Reporting"
-- "Waste Management"
-- "Water Management"]
-#Hashtags
+Watch as we build a job-winning Environment Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Impact Assessment, Environmental Management, Environmental Regulations Compliance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Impact Assessment
+- Environmental Management
+- Environmental Regulations Compliance
+- Sustainability Reporting
+- Waste Management
+- Water Management
+#resume
 #EnvironmentCoordinatorResume #EnvironmentCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9780,16 +9780,16 @@
       <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Environmental and Sustainability Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Environmental and Sustainability Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Management Systems (EMS)", "Sustainability Reporting", "Environmental Impact Assessment (EIA)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Management Systems (EMS)"
-- "Sustainability Reporting"
-- "Environmental Impact Assessment (EIA)"
-- "Corporate Social Responsibility (CSR)"
-- "Life Cycle Assessment (LCA)"
-- "Environmental Compliance and Regulations"]
-#Hashtags
+Watch as we build a job-winning Environmental and Sustainability Manager from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Management Systems (EMS), Sustainability Reporting, Environmental Impact Assessment (EIA), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Management Systems (EMS)
+- Sustainability Reporting
+- Environmental Impact Assessment (EIA)
+- Corporate Social Responsibility (CSR)
+- Life Cycle Assessment (LCA)
+- Environmental Compliance and Regulations
+#resume
 #EnvironmentalAndSustainabilityManagerResume #EnvironmentalAndSustainabilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9840,16 +9840,16 @@
       <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Safety Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Safety Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Accident Investigation and Analysis", "Compliance Management", "Ergonomics", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Accident Investigation and Analysis"
-- "Compliance Management"
-- "Ergonomics"
-- "Fire Safety Management"
-- "Hazard Recognition and Control"
-- "Incident Reporting and Documentation"]
-#Hashtags
+Watch as we build a job-winning Safety Manager from scratch, highlighting key sections and how to effectively showcase your skills in Accident Investigation and Analysis, Compliance Management, Ergonomics, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Accident Investigation and Analysis
+- Compliance Management
+- Ergonomics
+- Fire Safety Management
+- Hazard Recognition and Control
+- Incident Reporting and Documentation
+#resume
 #SafetyManagerResume #SafetyManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9900,16 +9900,16 @@
       <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Stakeholder Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Stakeholder Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Stakeholder Engagement", "Stakeholder Analysis", "Communication Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Stakeholder Engagement"
-- "Stakeholder Analysis"
-- "Communication Management"
-- "Relationship Management"
-- "Influence Management"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Stakeholder Manager from scratch, highlighting key sections and how to effectively showcase your skills in Stakeholder Engagement, Stakeholder Analysis, Communication Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Stakeholder Engagement
+- Stakeholder Analysis
+- Communication Management
+- Relationship Management
+- Influence Management
+- Project Management
+#resume
 #StakeholderManagerResume #StakeholderManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9960,16 +9960,16 @@
       <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Supply Chain Manager, Sustainability and Energy? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Supply Chain Manager, Sustainability and Energy from scratch, highlighting key sections and how to effectively showcase your skills in ["Biomass Energy Production", "Carbon Accounting and Reporting", "Clean Energy Project Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Biomass Energy Production"
-- "Carbon Accounting and Reporting"
-- "Clean Energy Project Development"
-- "Environmental Impact Assessment"
-- "GHG Emissions Management"
-- "Green Building Design and Construction"]
-#Hashtags
+Watch as we build a job-winning Supply Chain Manager, Sustainability and Energy from scratch, highlighting key sections and how to effectively showcase your skills in Biomass Energy Production, Carbon Accounting and Reporting, Clean Energy Project Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Biomass Energy Production
+- Carbon Accounting and Reporting
+- Clean Energy Project Development
+- Environmental Impact Assessment
+- GHG Emissions Management
+- Green Building Design and Construction
+#resume
 #SupplyChainManagerSustainabilityAndEnergyResume #SupplyChainManagerSustainabilityAndEnergy #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10020,17 +10020,17 @@
       <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sustainability Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sustainability Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Environmental Management Systems (ISO 14001)", "Sustainability Reporting (GRI,  SASB)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Environmental Management Systems (ISO 14001)"
-- "Sustainability Reporting (GRI
-- SASB)"
-- "Carbon Accounting and Management"
-- "Life Cycle Assessment (LCA)"
-- "Renewable Energy and Energy Efficiency"
-- "Waste Management and Circular Economy"]
-#Hashtags
+Watch as we build a job-winning Sustainability Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Environmental Management Systems (ISO 14001), Sustainability Reporting (GRI,  SASB), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Environmental Management Systems (ISO 14001)
+- Sustainability Reporting (GRI
+- SASB)
+- Carbon Accounting and Management
+- Life Cycle Assessment (LCA)
+- Renewable Energy and Energy Efficiency
+- Waste Management and Circular Economy
+#resume
 #SustainabilityCoordinatorResume #SustainabilityCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10081,16 +10081,16 @@
       <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sustainability Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sustainability Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Greenhouse Gas Accounting", "Environmental Impact Assessment", "Sustainability Reporting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Greenhouse Gas Accounting"
-- "Environmental Impact Assessment"
-- "Sustainability Reporting"
-- "Corporate Social Responsibility"
-- "Life Cycle Assessment"
-- "Sustainable Supply Chain Management"]
-#Hashtags
+Watch as we build a job-winning Sustainability Director from scratch, highlighting key sections and how to effectively showcase your skills in Greenhouse Gas Accounting, Environmental Impact Assessment, Sustainability Reporting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Greenhouse Gas Accounting
+- Environmental Impact Assessment
+- Sustainability Reporting
+- Corporate Social Responsibility
+- Life Cycle Assessment
+- Sustainable Supply Chain Management
+#resume
 #SustainabilityDirectorResume #SustainabilityDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10141,16 +10141,16 @@
       <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sustainability Executive Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sustainability Executive Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Sustainability Reporting", "Sustainable Finance", "Environmental Accounting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Sustainability Reporting"
-- "Sustainable Finance"
-- "Environmental Accounting"
-- "Stakeholder Engagement"
-- "Life Cycle Assessment"
-- "Corporate Social Responsibility Management"]
-#Hashtags
+Watch as we build a job-winning Sustainability Executive Director from scratch, highlighting key sections and how to effectively showcase your skills in Sustainability Reporting, Sustainable Finance, Environmental Accounting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Sustainability Reporting
+- Sustainable Finance
+- Environmental Accounting
+- Stakeholder Engagement
+- Life Cycle Assessment
+- Corporate Social Responsibility Management
+#resume
 #SustainabilityExecutiveDirectorResume #SustainabilityExecutiveDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10201,16 +10201,16 @@
       <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sustainability Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sustainability Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Sustainability Reporting", "Environmental Management Systems (EMS)", "Life Cycle Assessment (LCA)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Sustainability Reporting"
-- "Environmental Management Systems (EMS)"
-- "Life Cycle Assessment (LCA)"
-- "Carbon Footprint Analysis"
-- "Environmental Impact Assessment (EIA)"
-- "Sustainability Strategy Development"]
-#Hashtags
+Watch as we build a job-winning Sustainability Manager from scratch, highlighting key sections and how to effectively showcase your skills in Sustainability Reporting, Environmental Management Systems (EMS), Life Cycle Assessment (LCA), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Sustainability Reporting
+- Environmental Management Systems (EMS)
+- Life Cycle Assessment (LCA)
+- Carbon Footprint Analysis
+- Environmental Impact Assessment (EIA)
+- Sustainability Strategy Development
+#resume
 #SustainabilityManagerResume #SustainabilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10261,16 +10261,16 @@
       <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sustainability Research and Advocacy Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sustainability Research and Advocacy Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Sustainability Reporting", "Climate Change Mitigation and Adaptation", "Stakeholder Engagement and Communication", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Sustainability Reporting"
-- "Climate Change Mitigation and Adaptation"
-- "Stakeholder Engagement and Communication"
-- "Environmental Policy Analysis"
-- "Sustainability Risk Management"
-- "Life Cycle Assessment"]
-#Hashtags
+Watch as we build a job-winning Sustainability Research and Advocacy Director from scratch, highlighting key sections and how to effectively showcase your skills in Sustainability Reporting, Climate Change Mitigation and Adaptation, Stakeholder Engagement and Communication, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Sustainability Reporting
+- Climate Change Mitigation and Adaptation
+- Stakeholder Engagement and Communication
+- Environmental Policy Analysis
+- Sustainability Risk Management
+- Life Cycle Assessment
+#resume
 #SustainabilityResearchAndAdvocacyDirectorResume #SustainabilityResearchAndAdvocacyDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10321,16 +10321,16 @@
       <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Vice President, Corporate Social Responsibility and Sustainability (VP CSR and Sustainability)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Vice President, Corporate Social Responsibility and Sustainability (VP CSR and Sustainability) from scratch, highlighting key sections and how to effectively showcase your skills in ["Stakeholder Engagement", "CSR Strategy Development", "ESG Reporting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Stakeholder Engagement"
-- "CSR Strategy Development"
-- "ESG Reporting"
-- "Sustainability Accounting"
-- "Climate Risk Management"
-- "Social Impact Measurement"]
-#Hashtags
+Watch as we build a job-winning Vice President, Corporate Social Responsibility and Sustainability (VP CSR and Sustainability) from scratch, highlighting key sections and how to effectively showcase your skills in Stakeholder Engagement, CSR Strategy Development, ESG Reporting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Stakeholder Engagement
+- CSR Strategy Development
+- ESG Reporting
+- Sustainability Accounting
+- Climate Risk Management
+- Social Impact Measurement
+#resume
 #VicePresidentCorporateSocialResponsibilityAndSustainabilityVpCsrAndSustainabilityResume #VicePresidentCorporateSocialResponsibilityAndSustainabilityVpCsrAndSustainability #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10381,16 +10381,16 @@
       <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Adjutant General? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Adjutant General from scratch, highlighting key sections and how to effectively showcase your skills in ["Military Operations Planning", "Personnel Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Military Operations Planning"
-- "Personnel Management"
-- "Budget Management"
-- "Strategic Planning"
-- "Human Resource Management"
-- "Force Structure Analysis"]
-#Hashtags
+Watch as we build a job-winning Adjutant General from scratch, highlighting key sections and how to effectively showcase your skills in Military Operations Planning, Personnel Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Military Operations Planning
+- Personnel Management
+- Budget Management
+- Strategic Planning
+- Human Resource Management
+- Force Structure Analysis
+#resume
 #AdjutantGeneralResume #AdjutantGeneral #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10441,16 +10441,16 @@
       <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Adult Daycare Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Adult Daycare Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Care Planning", "Medication Management", "Program Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Care Planning"
-- "Medication Management"
-- "Program Development"
-- "Activity Planning"
-- "Client Assessment"
-- "Case Management"]
-#Hashtags
+Watch as we build a job-winning Adult Daycare Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Care Planning, Medication Management, Program Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Care Planning
+- Medication Management
+- Program Development
+- Activity Planning
+- Client Assessment
+- Case Management
+#resume
 #AdultDaycareCoordinatorResume #AdultDaycareCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10501,16 +10501,16 @@
       <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assistant Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assistant Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Reporting", "Budgeting", "Sales Forecasting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Reporting"
-- "Budgeting"
-- "Sales Forecasting"
-- "P&amp;L Management"
-- "Team Leadership"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Assistant Manager from scratch, highlighting key sections and how to effectively showcase your skills in Financial Reporting, Budgeting, Sales Forecasting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Reporting
+- Budgeting
+- Sales Forecasting
+- P&amp;L Management
+- Team Leadership
+- Project Management
+#resume
 #AssistantManagerResume #AssistantManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10561,16 +10561,16 @@
       <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Building Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Building Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Building Maintenance", "Property Management", "HVAC Systems", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Building Maintenance"
-- "Property Management"
-- "HVAC Systems"
-- "Electrical Systems"
-- "Plumbing Systems"
-- "Construction Management"]
-#Hashtags
+Watch as we build a job-winning Building Manager from scratch, highlighting key sections and how to effectively showcase your skills in Building Maintenance, Property Management, HVAC Systems, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Building Maintenance
+- Property Management
+- HVAC Systems
+- Electrical Systems
+- Plumbing Systems
+- Construction Management
+#resume
 #BuildingManagerResume #BuildingManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10621,16 +10621,16 @@
       <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Business &amp; Data Analysis", "Financial Management", "Budgeting and Forecasting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Business &amp; Data Analysis"
-- "Financial Management"
-- "Budgeting and Forecasting"
-- "Operational Planning"
-- "Vendor Management"
-- "Negotiation and Contracts"]
-#Hashtags
+Watch as we build a job-winning Business Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Business &amp; Data Analysis, Financial Management, Budgeting and Forecasting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Business &amp; Data Analysis
+- Financial Management
+- Budgeting and Forecasting
+- Operational Planning
+- Vendor Management
+- Negotiation and Contracts
+#resume
 #BusinessAdministratorResume #BusinessAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10681,16 +10681,16 @@
       <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Project Management", "Process Improvement", "Business Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Project Management"
-- "Process Improvement"
-- "Business Analysis"
-- "Data Entry and Management"
-- "Scheduling and Coordination"
-- "Communication and Interpersonal Skills"]
-#Hashtags
+Watch as we build a job-winning Business Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Project Management, Process Improvement, Business Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Project Management
+- Process Improvement
+- Business Analysis
+- Data Entry and Management
+- Scheduling and Coordination
+- Communication and Interpersonal Skills
+#resume
 #BusinessCoordinatorResume #BusinessCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10741,16 +10741,16 @@
       <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Development Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Development Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Business Development", "Sales Management", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Business Development"
-- "Sales Management"
-- "Strategic Planning"
-- "Relationship Management"
-- "Market Analysis"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Business Development Director from scratch, highlighting key sections and how to effectively showcase your skills in Business Development, Sales Management, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Business Development
+- Sales Management
+- Strategic Planning
+- Relationship Management
+- Market Analysis
+- Negotiation
+#resume
 #BusinessDevelopmentDirectorResume #BusinessDevelopmentDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10801,16 +10801,16 @@
       <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Business Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Business Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Financial Planning and Analysis", "Budget Management", "Forecasting and Modeling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Financial Planning and Analysis"
-- "Budget Management"
-- "Forecasting and Modeling"
-- "Performance Management"
-- "Risk Management"
-- "Investment Analysis"]
-#Hashtags
+Watch as we build a job-winning Business Manager from scratch, highlighting key sections and how to effectively showcase your skills in Financial Planning and Analysis, Budget Management, Forecasting and Modeling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Financial Planning and Analysis
+- Budget Management
+- Forecasting and Modeling
+- Performance Management
+- Risk Management
+- Investment Analysis
+#resume
 #BusinessManagerResume #BusinessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10861,16 +10861,16 @@
       <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Chief Deputy? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Chief Deputy from scratch, highlighting key sections and how to effectively showcase your skills in ["Courtroom Management", "Budget Management", "Case Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Courtroom Management"
-- "Budget Management"
-- "Case Management"
-- "Document Management"
-- "HR Management"
-- "Leadership"]
-#Hashtags
+Watch as we build a job-winning Chief Deputy from scratch, highlighting key sections and how to effectively showcase your skills in Courtroom Management, Budget Management, Case Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Courtroom Management
+- Budget Management
+- Case Management
+- Document Management
+- HR Management
+- Leadership
+#resume
 #ChiefDeputyResume #ChiefDeputy #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10921,16 +10921,16 @@
       <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Department Store General Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Department Store General Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Merchandise Planning", "Inventory Management", "Customer Service Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Merchandise Planning"
-- "Inventory Management"
-- "Customer Service Management"
-- "Budgeting and Financial Management"
-- "Team Leadership and Development"
-- "Sales Analysis and Forecasting"]
-#Hashtags
+Watch as we build a job-winning Department Store General Manager from scratch, highlighting key sections and how to effectively showcase your skills in Merchandise Planning, Inventory Management, Customer Service Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Merchandise Planning
+- Inventory Management
+- Customer Service Management
+- Budgeting and Financial Management
+- Team Leadership and Development
+- Sales Analysis and Forecasting
+#resume
 #DepartmentStoreGeneralManagerResume #DepartmentStoreGeneralManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10981,16 +10981,16 @@
       <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect District Commercial Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning District Commercial Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Construction Management", "Project Management", "Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Construction Management"
-- "Project Management"
-- "Leadership"
-- "Communication"
-- "Negotiation"
-- "Financial Management"]
-#Hashtags
+Watch as we build a job-winning District Commercial Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Construction Management, Project Management, Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Construction Management
+- Project Management
+- Leadership
+- Communication
+- Negotiation
+- Financial Management
+#resume
 #DistrictCommercialSuperintendentResume #DistrictCommercialSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11041,16 +11041,16 @@
       <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect District Plant Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning District Plant Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Power Distribution System Operations", "Electrical Safety Management", "Preventive and Predictive Maintenance Programs", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Power Distribution System Operations"
-- "Electrical Safety Management"
-- "Preventive and Predictive Maintenance Programs"
-- "SCADA and Automation Technologies"
-- "Asset Management and Condition Monitoring"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning District Plant Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Power Distribution System Operations, Electrical Safety Management, Preventive and Predictive Maintenance Programs, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Power Distribution System Operations
+- Electrical Safety Management
+- Preventive and Predictive Maintenance Programs
+- SCADA and Automation Technologies
+- Asset Management and Condition Monitoring
+- Project Management
+#resume
 #DistrictPlantSuperintendentResume #DistrictPlantSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11101,16 +11101,16 @@
       <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect District Traffic Chief? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning District Traffic Chief from scratch, highlighting key sections and how to effectively showcase your skills in ["Traffic Incident Management", "Incident Response Planning and Execution", "Traffic Signal Optimization", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Traffic Incident Management"
-- "Incident Response Planning and Execution"
-- "Traffic Signal Optimization"
-- "Roadway Safety Analysis"
-- "Congestion Management"
-- "Multimodal Transportation Planning"]
-#Hashtags
+Watch as we build a job-winning District Traffic Chief from scratch, highlighting key sections and how to effectively showcase your skills in Traffic Incident Management, Incident Response Planning and Execution, Traffic Signal Optimization, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Traffic Incident Management
+- Incident Response Planning and Execution
+- Traffic Signal Optimization
+- Roadway Safety Analysis
+- Congestion Management
+- Multimodal Transportation Planning
+#resume
 #DistrictTrafficChiefResume #DistrictTrafficChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11161,16 +11161,16 @@
       <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect District Wire Chief? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning District Wire Chief from scratch, highlighting key sections and how to effectively showcase your skills in ["FTTX Planning and Deployment", "Copper and Fiber Splicing", "Outside Plant Engineering", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["FTTX Planning and Deployment"
-- "Copper and Fiber Splicing"
-- "Outside Plant Engineering"
-- "Network Troubleshooting and Repair"
-- "Telecommunications Cabling"
-- "Network Planning and Optimization"]
-#Hashtags
+Watch as we build a job-winning District Wire Chief from scratch, highlighting key sections and how to effectively showcase your skills in FTTX Planning and Deployment, Copper and Fiber Splicing, Outside Plant Engineering, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- FTTX Planning and Deployment
+- Copper and Fiber Splicing
+- Outside Plant Engineering
+- Network Troubleshooting and Repair
+- Telecommunications Cabling
+- Network Planning and Optimization
+#resume
 #DistrictWireChiefResume #DistrictWireChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11221,16 +11221,16 @@
       <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Division Toll Wire Chief? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Division Toll Wire Chief from scratch, highlighting key sections and how to effectively showcase your skills in ["Copper and Fiber Splicing", "Outside Plant Engineering", "Network Troubleshooting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Copper and Fiber Splicing"
-- "Outside Plant Engineering"
-- "Network Troubleshooting"
-- "Telecommunications Maintenance"
-- "Central Office Switch Configuration"
-- "Telecommunications Test Equipment Operation"]
-#Hashtags
+Watch as we build a job-winning Division Toll Wire Chief from scratch, highlighting key sections and how to effectively showcase your skills in Copper and Fiber Splicing, Outside Plant Engineering, Network Troubleshooting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Copper and Fiber Splicing
+- Outside Plant Engineering
+- Network Troubleshooting
+- Telecommunications Maintenance
+- Central Office Switch Configuration
+- Telecommunications Test Equipment Operation
+#resume
 #DivisionTollWireChiefResume #DivisionTollWireChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11281,16 +11281,16 @@
       <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Division Traffic Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Division Traffic Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Incident Management", "Traffic Forecasting and Analysis", "Transportation Planning and Optimization", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Incident Management"
-- "Traffic Forecasting and Analysis"
-- "Transportation Planning and Optimization"
-- "Roadway Capacity Analysis"
-- "Traffic Signal Design and Operation"
-- "ITS (Intelligent Transportation Systems) Implementation"]
-#Hashtags
+Watch as we build a job-winning Division Traffic Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Incident Management, Traffic Forecasting and Analysis, Transportation Planning and Optimization, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Incident Management
+- Traffic Forecasting and Analysis
+- Transportation Planning and Optimization
+- Roadway Capacity Analysis
+- Traffic Signal Design and Operation
+- ITS (Intelligent Transportation Systems) Implementation
+#resume
 #DivisionTrafficSuperintendentResume #DivisionTrafficSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11341,16 +11341,16 @@
       <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Drilling and Production Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Drilling and Production Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Drilling Operations Management", "Production Operations Supervision", "Reservoir Engineering Fundamentals", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Drilling Operations Management"
-- "Production Operations Supervision"
-- "Reservoir Engineering Fundamentals"
-- "Drilling and Completion Cost Control"
-- "HSE Compliance and Risk Management"
-- "Wellbore Integrity Analysis"]
-#Hashtags
+Watch as we build a job-winning Drilling and Production Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Drilling Operations Management, Production Operations Supervision, Reservoir Engineering Fundamentals, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Drilling Operations Management
+- Production Operations Supervision
+- Reservoir Engineering Fundamentals
+- Drilling and Completion Cost Control
+- HSE Compliance and Risk Management
+- Wellbore Integrity Analysis
+#resume
 #DrillingAndProductionSuperintendentResume #DrillingAndProductionSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11401,16 +11401,16 @@
       <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Electrical Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Electrical Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Electrical Distribution System Design", "Electrical Substation Maintenance", "Power System Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Electrical Distribution System Design"
-- "Electrical Substation Maintenance"
-- "Power System Analysis"
-- "Control System Integration"
-- "Arc Flash Hazard Analysis"
-- "NEC and ANSI Code Compliance"]
-#Hashtags
+Watch as we build a job-winning Electrical Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Electrical Distribution System Design, Electrical Substation Maintenance, Power System Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Electrical Distribution System Design
+- Electrical Substation Maintenance
+- Power System Analysis
+- Control System Integration
+- Arc Flash Hazard Analysis
+- NEC and ANSI Code Compliance
+#resume
 #ElectricalSuperintendentResume #ElectricalSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11461,16 +11461,16 @@
       <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Equipment Maintenance Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Equipment Maintenance Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Maintenance and Repair of Industrial Equipment", "Troubleshooting and Diagnostics of Electrical and Mechanical Systems", "Predictive and Preventative Maintenance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Maintenance and Repair of Industrial Equipment"
-- "Troubleshooting and Diagnostics of Electrical and Mechanical Systems"
-- "Predictive and Preventative Maintenance"
-- "Fleet Management and Optimization"
-- "Work Order Management and Scheduling"
-- "Budget Management and Cost Control"]
-#Hashtags
+Watch as we build a job-winning Equipment Maintenance Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Maintenance and Repair of Industrial Equipment, Troubleshooting and Diagnostics of Electrical and Mechanical Systems, Predictive and Preventative Maintenance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Maintenance and Repair of Industrial Equipment
+- Troubleshooting and Diagnostics of Electrical and Mechanical Systems
+- Predictive and Preventative Maintenance
+- Fleet Management and Optimization
+- Work Order Management and Scheduling
+- Budget Management and Cost Control
+#resume
 #EquipmentMaintenanceSuperintendentResume #EquipmentMaintenanceSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11521,16 +11521,16 @@
       <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Facilities Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Facilities Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Asset Management", "Budget Management", "Capital Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Asset Management"
-- "Budget Management"
-- "Capital Planning"
-- "Construction Management"
-- "Contract Management"
-- "Customer Service"]
-#Hashtags
+Watch as we build a job-winning Facilities Manager from scratch, highlighting key sections and how to effectively showcase your skills in Asset Management, Budget Management, Capital Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Asset Management
+- Budget Management
+- Capital Planning
+- Construction Management
+- Contract Management
+- Customer Service
+#resume
 #FacilitiesManagerResume #FacilitiesManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11581,16 +11581,16 @@
       <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Facility Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Facility Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Facility Inspection and Maintenance", "Building Automation Systems (BAS)", "Preventive Maintenance Scheduling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Facility Inspection and Maintenance"
-- "Building Automation Systems (BAS)"
-- "Preventive Maintenance Scheduling"
-- "Energy Management"
-- "Safety and Compliance Audits"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Facility Manager from scratch, highlighting key sections and how to effectively showcase your skills in Facility Inspection and Maintenance, Building Automation Systems (BAS), Preventive Maintenance Scheduling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Facility Inspection and Maintenance
+- Building Automation Systems (BAS)
+- Preventive Maintenance Scheduling
+- Energy Management
+- Safety and Compliance Audits
+- Project Management
+#resume
 #FacilityManagerResume #FacilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11641,16 +11641,16 @@
       <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Field Party Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Field Party Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Field Data Collection", "Project Management", "Team Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Field Data Collection"
-- "Project Management"
-- "Team Leadership"
-- "Data Analysis"
-- "Report Writing"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Field Party Manager from scratch, highlighting key sections and how to effectively showcase your skills in Field Data Collection, Project Management, Team Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Field Data Collection
+- Project Management
+- Team Leadership
+- Data Analysis
+- Report Writing
+- Budget Management
+#resume
 #FieldPartyManagerResume #FieldPartyManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11701,16 +11701,16 @@
       <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Fish and Game Club Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Fish and Game Club Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Wildlife Management", "Fishery Management", "Hunting and Fishing Regulations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Wildlife Management"
-- "Fishery Management"
-- "Hunting and Fishing Regulations"
-- "Outdoor Education"
-- "Fundraising and Grant Writing"
-- "Conservation Biology"]
-#Hashtags
+Watch as we build a job-winning Fish and Game Club Manager from scratch, highlighting key sections and how to effectively showcase your skills in Wildlife Management, Fishery Management, Hunting and Fishing Regulations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Wildlife Management
+- Fishery Management
+- Hunting and Fishing Regulations
+- Outdoor Education
+- Fundraising and Grant Writing
+- Conservation Biology
+#resume
 #FishAndGameClubManagerResume #FishAndGameClubManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11761,16 +11761,16 @@
       <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Fitness Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Fitness Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Personal Training", "Group Fitness Instruction", "Fitness Assessment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Personal Training"
-- "Group Fitness Instruction"
-- "Fitness Assessment"
-- "Program Design"
-- "Nutritional Counseling"
-- "Injury Prevention and Rehabilitation"]
-#Hashtags
+Watch as we build a job-winning Fitness Manager from scratch, highlighting key sections and how to effectively showcase your skills in Personal Training, Group Fitness Instruction, Fitness Assessment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Personal Training
+- Group Fitness Instruction
+- Fitness Assessment
+- Program Design
+- Nutritional Counseling
+- Injury Prevention and Rehabilitation
+#resume
 #FitnessManagerResume #FitnessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11821,16 +11821,16 @@
       <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect General Manager (GM)? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning General Manager (GM) from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Operations Management", "Financial Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Operations Management"
-- "Financial Management"
-- "Team Leadership"
-- "Customer Relationship Management"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning General Manager (GM) from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Operations Management, Financial Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Operations Management
+- Financial Management
+- Team Leadership
+- Customer Relationship Management
+- Project Management
+#resume
 #GeneralManagerGmResume #GeneralManagerGm #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11881,16 +11881,16 @@
       <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect General Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning General Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Construction Management", "Project Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Construction Management"
-- "Project Management"
-- "Budget Management"
-- "Contract Administration"
-- "Leadership"
-- "Team Building"]
-#Hashtags
+Watch as we build a job-winning General Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Construction Management, Project Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Construction Management
+- Project Management
+- Budget Management
+- Contract Administration
+- Leadership
+- Team Building
+#resume
 #GeneralSuperintendentResume #GeneralSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11941,16 +11941,16 @@
       <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Golf Course Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Golf Course Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Golf Course Maintenance and Management", "Turfgrass Management Practices", "Irrigation System Maintenance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Golf Course Maintenance and Management"
-- "Turfgrass Management Practices"
-- "Irrigation System Maintenance"
-- "Budget Planning and Management"
-- "Staff Supervision and Training"
-- "Equipment Operation and Maintenance"]
-#Hashtags
+Watch as we build a job-winning Golf Course Manager from scratch, highlighting key sections and how to effectively showcase your skills in Golf Course Maintenance and Management, Turfgrass Management Practices, Irrigation System Maintenance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Golf Course Maintenance and Management
+- Turfgrass Management Practices
+- Irrigation System Maintenance
+- Budget Planning and Management
+- Staff Supervision and Training
+- Equipment Operation and Maintenance
+#resume
 #GolfCourseManagerResume #GolfCourseManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12001,16 +12001,16 @@
       <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Gym Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Gym Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Fitness Assessment", "Customer Service", "Equipment Maintenance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Fitness Assessment"
-- "Customer Service"
-- "Equipment Maintenance"
-- "Staff Management"
-- "Marketing and Promotions"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Gym Manager from scratch, highlighting key sections and how to effectively showcase your skills in Fitness Assessment, Customer Service, Equipment Maintenance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Fitness Assessment
+- Customer Service
+- Equipment Maintenance
+- Staff Management
+- Marketing and Promotions
+- Budget Management
+#resume
 #GymManagerResume #GymManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12061,16 +12061,16 @@
       <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Head of Store Operations? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Head of Store Operations from scratch, highlighting key sections and how to effectively showcase your skills in ["Customer Service", "Inventory Management", "Staff Supervision", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Customer Service"
-- "Inventory Management"
-- "Staff Supervision"
-- "Profit and Loss (P&amp;L) Management"
-- "Budgeting and Forecasting"
-- "Compliance Management"]
-#Hashtags
+Watch as we build a job-winning Head of Store Operations from scratch, highlighting key sections and how to effectively showcase your skills in Customer Service, Inventory Management, Staff Supervision, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Customer Service
+- Inventory Management
+- Staff Supervision
+- Profit and Loss (P&amp;L) Management
+- Budgeting and Forecasting
+- Compliance Management
+#resume
 #HeadOfStoreOperationsResume #HeadOfStoreOperations #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12121,16 +12121,16 @@
       <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Head of Visual Merchandising? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Head of Visual Merchandising from scratch, highlighting key sections and how to effectively showcase your skills in ["Visual Merchandising Strategy Development", "Trend Forecasting and Analysis", "Space Planning and Layout Optimization", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Visual Merchandising Strategy Development"
-- "Trend Forecasting and Analysis"
-- "Space Planning and Layout Optimization"
-- "Lighting Design and Implementation"
-- "Color Theory and Applications"
-- "Prop Sourcing and Management"]
-#Hashtags
+Watch as we build a job-winning Head of Visual Merchandising from scratch, highlighting key sections and how to effectively showcase your skills in Visual Merchandising Strategy Development, Trend Forecasting and Analysis, Space Planning and Layout Optimization, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Visual Merchandising Strategy Development
+- Trend Forecasting and Analysis
+- Space Planning and Layout Optimization
+- Lighting Design and Implementation
+- Color Theory and Applications
+- Prop Sourcing and Management
+#resume
 #HeadOfVisualMerchandisingResume #HeadOfVisualMerchandising #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12181,16 +12181,16 @@
       <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Industrial Organization Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Industrial Organization Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Operations Management", "Lean Six Sigma", "Industrial Engineering", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Operations Management"
-- "Lean Six Sigma"
-- "Industrial Engineering"
-- "Project Management"
-- "Data Analysis"
-- "Simulation Modeling"]
-#Hashtags
+Watch as we build a job-winning Industrial Organization Manager from scratch, highlighting key sections and how to effectively showcase your skills in Operations Management, Lean Six Sigma, Industrial Engineering, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Operations Management
+- Lean Six Sigma
+- Industrial Engineering
+- Project Management
+- Data Analysis
+- Simulation Modeling
+#resume
 #IndustrialOrganizationManagerResume #IndustrialOrganizationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12241,16 +12241,16 @@
       <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Installation Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Installation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Construction Management", "Project Management", "Team Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Construction Management"
-- "Project Management"
-- "Team Leadership"
-- "Cost Control"
-- "Quality Control"
-- "Electrical Installations"]
-#Hashtags
+Watch as we build a job-winning Installation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Construction Management, Project Management, Team Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Construction Management
+- Project Management
+- Team Leadership
+- Cost Control
+- Quality Control
+- Electrical Installations
+#resume
 #InstallationSuperintendentResume #InstallationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12301,16 +12301,16 @@
       <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Laundry Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Laundry Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Washer and Dryer Operation", "Fabric Care and Handling", "Chemical Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Washer and Dryer Operation"
-- "Fabric Care and Handling"
-- "Chemical Management"
-- "Water Conservation Techniques"
-- "Energy Efficiency Practices"
-- "Quality Control and Inspection"]
-#Hashtags
+Watch as we build a job-winning Laundry Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Washer and Dryer Operation, Fabric Care and Handling, Chemical Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Washer and Dryer Operation
+- Fabric Care and Handling
+- Chemical Management
+- Water Conservation Techniques
+- Energy Efficiency Practices
+- Quality Control and Inspection
+#resume
 #LaundrySuperintendentResume #LaundrySuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12361,16 +12361,16 @@
       <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Lease Operator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Lease Operator from scratch, highlighting key sections and how to effectively showcase your skills in ["Lease Accounting", "Lease Administration", "Capital Lease Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Lease Accounting"
-- "Lease Administration"
-- "Capital Lease Management"
-- "Operating Lease Management"
-- "Contract Review and Analysis"
-- "Lease Negotiation"]
-#Hashtags
+Watch as we build a job-winning Lease Operator from scratch, highlighting key sections and how to effectively showcase your skills in Lease Accounting, Lease Administration, Capital Lease Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Lease Accounting
+- Lease Administration
+- Capital Lease Management
+- Operating Lease Management
+- Contract Review and Analysis
+- Lease Negotiation
+#resume
 #LeaseOperatorResume #LeaseOperator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12421,16 +12421,16 @@
       <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Line Construction Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Line Construction Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Overhead and Underground Line Construction", "Distribution and Transmission Line Construction", "Substation Construction", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Overhead and Underground Line Construction"
-- "Distribution and Transmission Line Construction"
-- "Substation Construction"
-- "Project Management"
-- "Budget Management"
-- "Crew Management"]
-#Hashtags
+Watch as we build a job-winning Line Construction Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Overhead and Underground Line Construction, Distribution and Transmission Line Construction, Substation Construction, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Overhead and Underground Line Construction
+- Distribution and Transmission Line Construction
+- Substation Construction
+- Project Management
+- Budget Management
+- Crew Management
+#resume
 #LineConstructionSuperintendentResume #LineConstructionSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12481,16 +12481,16 @@
       <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Mine Administrator Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Mine Administrator Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Mine Planning", "Mine Ventilation", "Mine Surveying", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Mine Planning"
-- "Mine Ventilation"
-- "Mine Surveying"
-- "Mine Geology"
-- "Mine Safety"
-- "Mine Permitting"]
-#Hashtags
+Watch as we build a job-winning Mine Administrator Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Mine Planning, Mine Ventilation, Mine Surveying, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Mine Planning
+- Mine Ventilation
+- Mine Surveying
+- Mine Geology
+- Mine Safety
+- Mine Permitting
+#resume
 #MineAdministratorSupervisorResume #MineAdministratorSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12541,16 +12541,16 @@
       <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Mine Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Mine Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Mine Production Planning", "Mine Operations Management", "Mine Safety Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Mine Production Planning"
-- "Mine Operations Management"
-- "Mine Safety Management"
-- "Mine Environmental Management"
-- "Mineral Processing"
-- "Explosives Management"]
-#Hashtags
+Watch as we build a job-winning Mine Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Mine Production Planning, Mine Operations Management, Mine Safety Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Mine Production Planning
+- Mine Operations Management
+- Mine Safety Management
+- Mine Environmental Management
+- Mineral Processing
+- Explosives Management
+#resume
 #MineSuperintendentResume #MineSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12601,16 +12601,16 @@
       <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Movie Theater Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Movie Theater Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Cinema Management", "Box Office Operations", "Concession Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Cinema Management"
-- "Box Office Operations"
-- "Concession Management"
-- "Customer Service"
-- "Projection Equipment Operation"
-- "Staff Supervision"]
-#Hashtags
+Watch as we build a job-winning Movie Theater Manager from scratch, highlighting key sections and how to effectively showcase your skills in Cinema Management, Box Office Operations, Concession Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Cinema Management
+- Box Office Operations
+- Concession Management
+- Customer Service
+- Projection Equipment Operation
+- Staff Supervision
+#resume
 #MovieTheaterManagerResume #MovieTheaterManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12661,18 +12661,18 @@
       <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Newspaper Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Newspaper Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["In-depth understanding of newspaper production and distribution", "Expertise in managing editorial and production teams", "Strong knowledge of print and digital publishing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["In-depth understanding of newspaper production and distribution"
-- "Expertise in managing editorial and production teams"
-- "Strong knowledge of print and digital publishing"
-- "Proficient in Adobe Creative Suite and other industry software"
-- "Excellence in budgeting
+Watch as we build a job-winning Newspaper Manager from scratch, highlighting key sections and how to effectively showcase your skills in In-depth understanding of newspaper production and distribution, Expertise in managing editorial and production teams, Strong knowledge of print and digital publishing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- In-depth understanding of newspaper production and distribution
+- Expertise in managing editorial and production teams
+- Strong knowledge of print and digital publishing
+- Proficient in Adobe Creative Suite and other industry software
+- Excellence in budgeting
 - forecasting
-- and financial management"
-- "Exceptional communication and interpersonal skills"]
-#Hashtags
+- and financial management
+- Exceptional communication and interpersonal skills
+#resume
 #NewspaperManagerResume #NewspaperManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12723,16 +12723,16 @@
       <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Office Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Office Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Office Management", "Budget Management", "Human Resources Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Office Management"
-- "Budget Management"
-- "Human Resources Management"
-- "Event Planning"
-- "Customer Service"
-- "Data Entry"]
-#Hashtags
+Watch as we build a job-winning Office Manager from scratch, highlighting key sections and how to effectively showcase your skills in Office Management, Budget Management, Human Resources Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Office Management
+- Budget Management
+- Human Resources Management
+- Event Planning
+- Customer Service
+- Data Entry
+#resume
 #OfficeManagerResume #OfficeManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12783,16 +12783,16 @@
       <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Offshoring Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Offshoring Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Vendor Management", "Cost Optimization", "Global Sourcing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Vendor Management"
-- "Cost Optimization"
-- "Global Sourcing"
-- "Project Management"
-- "Stakeholder Management"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Offshoring Manager from scratch, highlighting key sections and how to effectively showcase your skills in Vendor Management, Cost Optimization, Global Sourcing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Vendor Management
+- Cost Optimization
+- Global Sourcing
+- Project Management
+- Stakeholder Management
+- Negotiation
+#resume
 #OffshoringManagerResume #OffshoringManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12843,16 +12843,16 @@
       <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Oil Lease Operator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Oil Lease Operator from scratch, highlighting key sections and how to effectively showcase your skills in ["Artificial Lift Systems", "Wellhead and Production Equipment Maintenance", "Production Operations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Artificial Lift Systems"
-- "Wellhead and Production Equipment Maintenance"
-- "Production Operations"
-- "Pipeline Maintenance"
-- "Field Safety Procedures"
-- "Oil and Gas Processing"]
-#Hashtags
+Watch as we build a job-winning Oil Lease Operator from scratch, highlighting key sections and how to effectively showcase your skills in Artificial Lift Systems, Wellhead and Production Equipment Maintenance, Production Operations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Artificial Lift Systems
+- Wellhead and Production Equipment Maintenance
+- Production Operations
+- Pipeline Maintenance
+- Field Safety Procedures
+- Oil and Gas Processing
+#resume
 #OilLeaseOperatorResume #OilLeaseOperator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12903,16 +12903,16 @@
       <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Oil Operator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Oil Operator from scratch, highlighting key sections and how to effectively showcase your skills in ["HSE Regulations and Compliance", "Drilling Equipment Maintenance", "Well Monitoring and Control", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["HSE Regulations and Compliance"
-- "Drilling Equipment Maintenance"
-- "Well Monitoring and Control"
-- "Reservoir Pressure Analysis"
-- "Production Optimization"
-- "Pipeline Operations"]
-#Hashtags
+Watch as we build a job-winning Oil Operator from scratch, highlighting key sections and how to effectively showcase your skills in HSE Regulations and Compliance, Drilling Equipment Maintenance, Well Monitoring and Control, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- HSE Regulations and Compliance
+- Drilling Equipment Maintenance
+- Well Monitoring and Control
+- Reservoir Pressure Analysis
+- Production Optimization
+- Pipeline Operations
+#resume
 #OilOperatorResume #OilOperator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12963,16 +12963,16 @@
       <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Oil Producer? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Oil Producer from scratch, highlighting key sections and how to effectively showcase your skills in ["Drilling Operations", "Well Completion", "Reservoir Engineering", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Drilling Operations"
-- "Well Completion"
-- "Reservoir Engineering"
-- "Production Optimization"
-- "Enhanced Oil Recovery"
-- "Artificial Lift Systems"]
-#Hashtags
+Watch as we build a job-winning Oil Producer from scratch, highlighting key sections and how to effectively showcase your skills in Drilling Operations, Well Completion, Reservoir Engineering, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Drilling Operations
+- Well Completion
+- Reservoir Engineering
+- Production Optimization
+- Enhanced Oil Recovery
+- Artificial Lift Systems
+#resume
 #OilProducerResume #OilProducer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13023,16 +13023,16 @@
       <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Operations Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Operations Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Agile Scrum", "Budget Management", "Communication and Presentation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agile Scrum"
-- "Budget Management"
-- "Communication and Presentation"
-- "Customer Relationship Management (CRM)"
-- "Data Analytics and Interpretation"
-- "Enterprise Resource Planning (ERP) Systems"]
-#Hashtags
+Watch as we build a job-winning Operations Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Agile Scrum, Budget Management, Communication and Presentation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agile Scrum
+- Budget Management
+- Communication and Presentation
+- Customer Relationship Management (CRM)
+- Data Analytics and Interpretation
+- Enterprise Resource Planning (ERP) Systems
+#resume
 #OperationsAdministratorResume #OperationsAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13083,16 +13083,16 @@
       <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Operations Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Operations Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Business Process Management", "Operations Planning", "Supply Chain Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Business Process Management"
-- "Operations Planning"
-- "Supply Chain Management"
-- "Project Management"
-- "Quality Control"
-- "Lean Six Sigma"]
-#Hashtags
+Watch as we build a job-winning Operations Director from scratch, highlighting key sections and how to effectively showcase your skills in Business Process Management, Operations Planning, Supply Chain Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Business Process Management
+- Operations Planning
+- Supply Chain Management
+- Project Management
+- Quality Control
+- Lean Six Sigma
+#resume
 #OperationsDirectorResume #OperationsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13143,16 +13143,16 @@
       <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Operations Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Operations Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Operations Management", "Process Improvement", "Lean Six Sigma", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Operations Management"
-- "Process Improvement"
-- "Lean Six Sigma"
-- "Supply Chain Management"
-- "Inventory Management"
-- "Warehouse Management"]
-#Hashtags
+Watch as we build a job-winning Operations Manager from scratch, highlighting key sections and how to effectively showcase your skills in Operations Management, Process Improvement, Lean Six Sigma, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Operations Management
+- Process Improvement
+- Lean Six Sigma
+- Supply Chain Management
+- Inventory Management
+- Warehouse Management
+#resume
 #OperationsManagerResume #OperationsManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13203,16 +13203,16 @@
       <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Operations Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Operations Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Inventory Management", "Logistics and Supply Chain Management", "Quality Control", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Inventory Management"
-- "Logistics and Supply Chain Management"
-- "Quality Control"
-- "Performance Optimization"
-- "Team Management and Leadership"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Operations Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Inventory Management, Logistics and Supply Chain Management, Quality Control, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Inventory Management
+- Logistics and Supply Chain Management
+- Quality Control
+- Performance Optimization
+- Team Management and Leadership
+- Project Management
+#resume
 #OperationsSupervisorResume #OperationsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13263,16 +13263,16 @@
       <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Parks and Recreation Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Parks and Recreation Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Parks and Recreation Management", "Budgeting and Financial Management", "Program Development and Implementation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Parks and Recreation Management"
-- "Budgeting and Financial Management"
-- "Program Development and Implementation"
-- "Community Engagement and Outreach"
-- "Facility Planning and Design"
-- "Risk Management and Emergency Preparedness"]
-#Hashtags
+Watch as we build a job-winning Parks and Recreation Manager from scratch, highlighting key sections and how to effectively showcase your skills in Parks and Recreation Management, Budgeting and Financial Management, Program Development and Implementation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Parks and Recreation Management
+- Budgeting and Financial Management
+- Program Development and Implementation
+- Community Engagement and Outreach
+- Facility Planning and Design
+- Risk Management and Emergency Preparedness
+#resume
 #ParksAndRecreationManagerResume #ParksAndRecreationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13323,16 +13323,16 @@
       <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Plant Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Plant Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Lean Manufacturing", "Six Sigma", "ISO 9001", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Lean Manufacturing"
-- "Six Sigma"
-- "ISO 9001"
-- "OSHA Compliance"
-- "TPM (Total Productive Maintenance)"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Plant Manager from scratch, highlighting key sections and how to effectively showcase your skills in Lean Manufacturing, Six Sigma, ISO 9001, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Lean Manufacturing
+- Six Sigma
+- ISO 9001
+- OSHA Compliance
+- TPM (Total Productive Maintenance)
+- Project Management
+#resume
 #PlantManagerResume #PlantManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13383,16 +13383,16 @@
       <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Plant Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Plant Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Process Safety Management System", "Production Planning and Scheduling", "Continuous Improvement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Process Safety Management System"
-- "Production Planning and Scheduling"
-- "Continuous Improvement"
-- "Cost Reduction"
-- "Inventory Management"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Plant Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Process Safety Management System, Production Planning and Scheduling, Continuous Improvement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Process Safety Management System
+- Production Planning and Scheduling
+- Continuous Improvement
+- Cost Reduction
+- Inventory Management
+- Project Management
+#resume
 #PlantSuperintendentResume #PlantSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13443,16 +13443,16 @@
       <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Plant Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Plant Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Production Planning and Scheduling", "Quality Control and Assurance", "Process Improvement and Optimization", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Production Planning and Scheduling"
-- "Quality Control and Assurance"
-- "Process Improvement and Optimization"
-- "Safety Management and Compliance"
-- "Equipment Maintenance and Repair"
-- "Lean Manufacturing and Six Sigma"]
-#Hashtags
+Watch as we build a job-winning Plant Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Production Planning and Scheduling, Quality Control and Assurance, Process Improvement and Optimization, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Production Planning and Scheduling
+- Quality Control and Assurance
+- Process Improvement and Optimization
+- Safety Management and Compliance
+- Equipment Maintenance and Repair
+- Lean Manufacturing and Six Sigma
+#resume
 #PlantSupervisorResume #PlantSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13503,16 +13503,16 @@
       <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Print Production Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Print Production Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Prepress Production", "Offset Printing", "Digital Printing", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Prepress Production"
-- "Offset Printing"
-- "Digital Printing"
-- "Color Management"
-- "File Preparation"
-- "Proofing"]
-#Hashtags
+Watch as we build a job-winning Print Production Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Prepress Production, Offset Printing, Digital Printing, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Prepress Production
+- Offset Printing
+- Digital Printing
+- Color Management
+- File Preparation
+- Proofing
+#resume
 #PrintProductionCoordinatorResume #PrintProductionCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13563,16 +13563,16 @@
       <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Print Production Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Print Production Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Prepress and Print Production Management", "Digital Printing and Workflow Management", "Color Management and Calibration", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Prepress and Print Production Management"
-- "Digital Printing and Workflow Management"
-- "Color Management and Calibration"
-- "Offset and Digital Press Operation"
-- "Postpress Operations and Finishing Processes"
-- "Bindery and Distribution Management"]
-#Hashtags
+Watch as we build a job-winning Print Production Manager from scratch, highlighting key sections and how to effectively showcase your skills in Prepress and Print Production Management, Digital Printing and Workflow Management, Color Management and Calibration, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Prepress and Print Production Management
+- Digital Printing and Workflow Management
+- Color Management and Calibration
+- Offset and Digital Press Operation
+- Postpress Operations and Finishing Processes
+- Bindery and Distribution Management
+#resume
 #PrintProductionManagerResume #PrintProductionManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13623,16 +13623,16 @@
       <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Printing Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Printing Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Color Management", "Digital Printing", "Estimating and Quoting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Color Management"
-- "Digital Printing"
-- "Estimating and Quoting"
-- "Graphic Design"
-- "Inkjet Printing"
-- "Job Costing"]
-#Hashtags
+Watch as we build a job-winning Printing Manager from scratch, highlighting key sections and how to effectively showcase your skills in Color Management, Digital Printing, Estimating and Quoting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Color Management
+- Digital Printing
+- Estimating and Quoting
+- Graphic Design
+- Inkjet Printing
+- Job Costing
+#resume
 #PrintingManagerResume #PrintingManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13683,16 +13683,16 @@
       <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Prison Warden? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Prison Warden from scratch, highlighting key sections and how to effectively showcase your skills in ["Correctional Facility Management", "Inmate Supervision and Security", "Staff Supervision and Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Correctional Facility Management"
-- "Inmate Supervision and Security"
-- "Staff Supervision and Development"
-- "Budget Planning and Management"
-- "Policy Development and Implementation"
-- "Risk Assessment and Management"]
-#Hashtags
+Watch as we build a job-winning Prison Warden from scratch, highlighting key sections and how to effectively showcase your skills in Correctional Facility Management, Inmate Supervision and Security, Staff Supervision and Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Correctional Facility Management
+- Inmate Supervision and Security
+- Staff Supervision and Development
+- Budget Planning and Management
+- Policy Development and Implementation
+- Risk Assessment and Management
+#resume
 #PrisonWardenResume #PrisonWarden #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13743,16 +13743,16 @@
       <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Production Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Production Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Lean Manufacturing", "ISO 9001:2015 Quality Management", "Six Sigma", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Lean Manufacturing"
-- "ISO 9001:2015 Quality Management"
-- "Six Sigma"
-- "Production Planning and Scheduling"
-- "Inventory Management"
-- "Material Requirements Planning (MRP)"]
-#Hashtags
+Watch as we build a job-winning Production Manager from scratch, highlighting key sections and how to effectively showcase your skills in Lean Manufacturing, ISO 9001:2015 Quality Management, Six Sigma, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Lean Manufacturing
+- ISO 9001:2015 Quality Management
+- Six Sigma
+- Production Planning and Scheduling
+- Inventory Management
+- Material Requirements Planning (MRP)
+#resume
 #ProductionManagerResume #ProductionManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13803,16 +13803,16 @@
       <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Publication Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Publication Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Content Strategy", "Editing and Proofreading", "Layout and Design", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Content Strategy"
-- "Editing and Proofreading"
-- "Layout and Design"
-- "Digital Publishing"
-- "Project Management"
-- "Marketing and Communication"]
-#Hashtags
+Watch as we build a job-winning Publication Director from scratch, highlighting key sections and how to effectively showcase your skills in Content Strategy, Editing and Proofreading, Layout and Design, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Content Strategy
+- Editing and Proofreading
+- Layout and Design
+- Digital Publishing
+- Project Management
+- Marketing and Communication
+#resume
 #PublicationDirectorResume #PublicationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13863,16 +13863,16 @@
       <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Radio Station Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Radio Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Audio Production", "Broadcast Operations", "Content Programming", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Audio Production"
-- "Broadcast Operations"
-- "Content Programming"
-- "FCC Regulations"
-- "Market Analysis"
-- "Budgeting and Finance"]
-#Hashtags
+Watch as we build a job-winning Radio Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in Audio Production, Broadcast Operations, Content Programming, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Audio Production
+- Broadcast Operations
+- Content Programming
+- FCC Regulations
+- Market Analysis
+- Budgeting and Finance
+#resume
 #RadioStationManagerResume #RadioStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13923,16 +13923,16 @@
       <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Refinery Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Refinery Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Hydroprocessing", "Distillation", "Reforming", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Hydroprocessing"
-- "Distillation"
-- "Reforming"
-- "Alkylation"
-- "Polymerization"
-- "Blending"]
-#Hashtags
+Watch as we build a job-winning Refinery Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Hydroprocessing, Distillation, Reforming, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Hydroprocessing
+- Distillation
+- Reforming
+- Alkylation
+- Polymerization
+- Blending
+#resume
 #RefinerySuperintendentResume #RefinerySuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13983,16 +13983,16 @@
       <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Revenue Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Revenue Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Revenue Management", "Pricing Optimization", "Demand Forecasting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Revenue Management"
-- "Pricing Optimization"
-- "Demand Forecasting"
-- "Inventory Management"
-- "Yield Management"
-- "Distribution Management"]
-#Hashtags
+Watch as we build a job-winning Revenue Manager from scratch, highlighting key sections and how to effectively showcase your skills in Revenue Management, Pricing Optimization, Demand Forecasting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Revenue Management
+- Pricing Optimization
+- Demand Forecasting
+- Inventory Management
+- Yield Management
+- Distribution Management
+#resume
 #RevenueManagerResume #RevenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14043,16 +14043,16 @@
       <c r="L227" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Roads Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Roads Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Asphalt Paving", "Bridge Construction", "Concrete Paving", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Asphalt Paving"
-- "Bridge Construction"
-- "Concrete Paving"
-- "Culvert Installation"
-- "Drainage System Design"
-- "Erosion Control"]
-#Hashtags
+Watch as we build a job-winning Roads Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Asphalt Paving, Bridge Construction, Concrete Paving, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Asphalt Paving
+- Bridge Construction
+- Concrete Paving
+- Culvert Installation
+- Drainage System Design
+- Erosion Control
+#resume
 #RoadsSuperintendentResume #RoadsSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14103,16 +14103,16 @@
       <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Salon Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Salon Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Salon Operations Management", "Team Leadership and Development", "Customer Service and Relationship Building", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Salon Operations Management"
-- "Team Leadership and Development"
-- "Customer Service and Relationship Building"
-- "Financial Management and Budgeting"
-- "Inventory and Supply Chain Management"
-- "Product Knowledge and Trend Analysis"]
-#Hashtags
+Watch as we build a job-winning Salon Manager from scratch, highlighting key sections and how to effectively showcase your skills in Salon Operations Management, Team Leadership and Development, Customer Service and Relationship Building, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Salon Operations Management
+- Team Leadership and Development
+- Customer Service and Relationship Building
+- Financial Management and Budgeting
+- Inventory and Supply Chain Management
+- Product Knowledge and Trend Analysis
+#resume
 #SalonManagerResume #SalonManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14163,16 +14163,16 @@
       <c r="L229" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Shelter Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Shelter Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Disaster Management", "Emergency Preparedness Planning", "Animal Welfare Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Disaster Management"
-- "Emergency Preparedness Planning"
-- "Animal Welfare Management"
-- "Community Collaboration"
-- "Budget Management"
-- "Fundraising"]
-#Hashtags
+Watch as we build a job-winning Shelter Director from scratch, highlighting key sections and how to effectively showcase your skills in Disaster Management, Emergency Preparedness Planning, Animal Welfare Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Disaster Management
+- Emergency Preparedness Planning
+- Animal Welfare Management
+- Community Collaboration
+- Budget Management
+- Fundraising
+#resume
 #ShelterDirectorResume #ShelterDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14223,16 +14223,16 @@
       <c r="L230" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Shift Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Shift Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Shift Operations Management", "Incident Command System (ICS)", "OSHA Compliance", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Shift Operations Management"
-- "Incident Command System (ICS)"
-- "OSHA Compliance"
-- "Safety Program Development"
-- "Workforce Management"
-- "Regulatory Compliance"]
-#Hashtags
+Watch as we build a job-winning Shift Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Shift Operations Management, Incident Command System (ICS), OSHA Compliance, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Shift Operations Management
+- Incident Command System (ICS)
+- OSHA Compliance
+- Safety Program Development
+- Workforce Management
+- Regulatory Compliance
+#resume
 #ShiftSuperintendentResume #ShiftSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14283,16 +14283,16 @@
       <c r="L231" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Shop Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Shop Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Lean Manufacturing", "ISO 9001:2015 Quality Management", "Six Sigma", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Lean Manufacturing"
-- "ISO 9001:2015 Quality Management"
-- "Six Sigma"
-- "Project Management"
-- "Team Leadership"
-- "Production Planning and Scheduling"]
-#Hashtags
+Watch as we build a job-winning Shop Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Lean Manufacturing, ISO 9001:2015 Quality Management, Six Sigma, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Lean Manufacturing
+- ISO 9001:2015 Quality Management
+- Six Sigma
+- Project Management
+- Team Leadership
+- Production Planning and Scheduling
+#resume
 #ShopSuperintendentResume #ShopSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14343,16 +14343,16 @@
       <c r="L232" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Social Insurance Administrator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Social Insurance Administrator from scratch, highlighting key sections and how to effectively showcase your skills in ["Social Insurance Program Knowledge", "Claims Processing", "Disability Assessment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Social Insurance Program Knowledge"
-- "Claims Processing"
-- "Disability Assessment"
-- "Benefits Determination"
-- "Case Management"
-- "Policy Interpretation"]
-#Hashtags
+Watch as we build a job-winning Social Insurance Administrator from scratch, highlighting key sections and how to effectively showcase your skills in Social Insurance Program Knowledge, Claims Processing, Disability Assessment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Social Insurance Program Knowledge
+- Claims Processing
+- Disability Assessment
+- Benefits Determination
+- Case Management
+- Policy Interpretation
+#resume
 #SocialInsuranceAdministratorResume #SocialInsuranceAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14403,16 +14403,16 @@
       <c r="L233" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Solid Waste Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Solid Waste Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Wastewater Treatment Plant Operations", "Solid Waste Management Planning", "Landfill Design and Construction", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Wastewater Treatment Plant Operations"
-- "Solid Waste Management Planning"
-- "Landfill Design and Construction"
-- "Waste Reduction and Recycling Programs"
-- "Hazardous Waste Management"
-- "Environmental Regulations Compliance"]
-#Hashtags
+Watch as we build a job-winning Solid Waste Manager from scratch, highlighting key sections and how to effectively showcase your skills in Wastewater Treatment Plant Operations, Solid Waste Management Planning, Landfill Design and Construction, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Wastewater Treatment Plant Operations
+- Solid Waste Management Planning
+- Landfill Design and Construction
+- Waste Reduction and Recycling Programs
+- Hazardous Waste Management
+- Environmental Regulations Compliance
+#resume
 #SolidWasteManagerResume #SolidWasteManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14463,16 +14463,16 @@
       <c r="L234" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sports Team Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sports Team Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Team Management", "Player Development", "Game Strategy", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Team Management"
-- "Player Development"
-- "Game Strategy"
-- "Budget Management"
-- "Event Planning"
-- "Player Evaluation"]
-#Hashtags
+Watch as we build a job-winning Sports Team Manager from scratch, highlighting key sections and how to effectively showcase your skills in Team Management, Player Development, Game Strategy, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Team Management
+- Player Development
+- Game Strategy
+- Budget Management
+- Event Planning
+- Player Evaluation
+#resume
 #SportsTeamManagerResume #SportsTeamManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14523,16 +14523,16 @@
       <c r="L235" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Street Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Street Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Street Maintenance and Repair", "Stormwater Management", "Snow and Ice Removal", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Street Maintenance and Repair"
-- "Stormwater Management"
-- "Snow and Ice Removal"
-- "Traffic Signal Maintenance"
-- "Roadway Design and Engineering"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Street Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Street Maintenance and Repair, Stormwater Management, Snow and Ice Removal, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Street Maintenance and Repair
+- Stormwater Management
+- Snow and Ice Removal
+- Traffic Signal Maintenance
+- Roadway Design and Engineering
+- Project Management
+#resume
 #StreetCommissionerResume #StreetCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14583,16 +14583,16 @@
       <c r="L236" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Street Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Street Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Asphalt Maintenance and Repair", "Concrete Paving and Repair", "Stormwater Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Asphalt Maintenance and Repair"
-- "Concrete Paving and Repair"
-- "Stormwater Management"
-- "Traffic Signal Maintenance"
-- "Street Lighting Maintenance"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Street Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Asphalt Maintenance and Repair, Concrete Paving and Repair, Stormwater Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Asphalt Maintenance and Repair
+- Concrete Paving and Repair
+- Stormwater Management
+- Traffic Signal Maintenance
+- Street Lighting Maintenance
+- Budget Management
+#resume
 #StreetSuperintendentResume #StreetSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14643,16 +14643,16 @@
       <c r="L237" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Substation Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Substation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Overhead and Underground Transmission and Distribution Line Construction", "Substation Design and Engineering", "Protective Relaying and Control Systems", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Overhead and Underground Transmission and Distribution Line Construction"
-- "Substation Design and Engineering"
-- "Protective Relaying and Control Systems"
-- "Transformer Maintenance and Testing"
-- "Circuit Breaker Maintenance and Testing"
-- "Electrical Safety and Compliance"]
-#Hashtags
+Watch as we build a job-winning Substation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Overhead and Underground Transmission and Distribution Line Construction, Substation Design and Engineering, Protective Relaying and Control Systems, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Overhead and Underground Transmission and Distribution Line Construction
+- Substation Design and Engineering
+- Protective Relaying and Control Systems
+- Transformer Maintenance and Testing
+- Circuit Breaker Maintenance and Testing
+- Electrical Safety and Compliance
+#resume
 #SubstationSuperintendentResume #SubstationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14703,16 +14703,16 @@
       <c r="L238" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Television Station Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Television Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Broadcast Production", "Newsroom Management", "Programming Strategy", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Broadcast Production"
-- "Newsroom Management"
-- "Programming Strategy"
-- "Budget Management"
-- "Team Leadership"
-- "Digital Media Management"]
-#Hashtags
+Watch as we build a job-winning Television Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in Broadcast Production, Newsroom Management, Programming Strategy, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Broadcast Production
+- Newsroom Management
+- Programming Strategy
+- Budget Management
+- Team Leadership
+- Digital Media Management
+#resume
 #TelevisionStationManagerResume #TelevisionStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14763,16 +14763,16 @@
       <c r="L239" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Theatre Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Theatre Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Theatre Management", "Box Office Operations", "Event Planning and Coordination", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Theatre Management"
-- "Box Office Operations"
-- "Event Planning and Coordination"
-- "Budgeting and Financial Management"
-- "Staff Management and Leadership"
-- "Marketing and Audience Development"]
-#Hashtags
+Watch as we build a job-winning Theatre Manager from scratch, highlighting key sections and how to effectively showcase your skills in Theatre Management, Box Office Operations, Event Planning and Coordination, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Theatre Management
+- Box Office Operations
+- Event Planning and Coordination
+- Budgeting and Financial Management
+- Staff Management and Leadership
+- Marketing and Audience Development
+#resume
 #TheatreManagerResume #TheatreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14823,16 +14823,16 @@
       <c r="L240" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Venue Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Venue Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Event Coordination", "Venue Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Event Coordination"
-- "Venue Management"
-- "Budget Management"
-- "Vendor Management"
-- "Customer Service"
-- "Team Management"]
-#Hashtags
+Watch as we build a job-winning Venue Manager from scratch, highlighting key sections and how to effectively showcase your skills in Event Coordination, Venue Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Event Coordination
+- Venue Management
+- Budget Management
+- Vendor Management
+- Customer Service
+- Team Management
+#resume
 #VenueManagerResume #VenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14883,16 +14883,16 @@
       <c r="L241" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water and Sewer Systems Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water and Sewer Systems Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["SCADA Control Systems", "GIS Mapping", "Water Treatment Processes", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["SCADA Control Systems"
-- "GIS Mapping"
-- "Water Treatment Processes"
-- "Sewer Collection and Maintenance"
-- "Stormwater Management"
-- "Water Conservation"]
-#Hashtags
+Watch as we build a job-winning Water and Sewer Systems Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in SCADA Control Systems, GIS Mapping, Water Treatment Processes, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- SCADA Control Systems
+- GIS Mapping
+- Water Treatment Processes
+- Sewer Collection and Maintenance
+- Stormwater Management
+- Water Conservation
+#resume
 #WaterAndSewerSystemsSupervisorResume #WaterAndSewerSystemsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14943,16 +14943,16 @@
       <c r="L242" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Control Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Control Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Operations", "Wastewater Collection System Maintenance", "SCADA and PLC Programming", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Operations"
-- "Wastewater Collection System Maintenance"
-- "SCADA and PLC Programming"
-- "GIS Mapping and Analysis"
-- "Hydraulic Modeling"
-- "Water Quality Monitoring and Analysis"]
-#Hashtags
+Watch as we build a job-winning Water Control Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Operations, Wastewater Collection System Maintenance, SCADA and PLC Programming, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Operations
+- Wastewater Collection System Maintenance
+- SCADA and PLC Programming
+- GIS Mapping and Analysis
+- Hydraulic Modeling
+- Water Quality Monitoring and Analysis
+#resume
 #WaterControlSupervisorResume #WaterControlSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15003,16 +15003,16 @@
       <c r="L243" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Treatment Plant Operations", "Distribution System Management", "Water Quality Monitoring and Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Treatment Plant Operations"
-- "Distribution System Management"
-- "Water Quality Monitoring and Analysis"
-- "Wastewater Treatment Processes"
-- "SCADA Systems Operation and Troubleshooting"
-- "Asset Management and Maintenance"]
-#Hashtags
+Watch as we build a job-winning Water Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Water Treatment Plant Operations, Distribution System Management, Water Quality Monitoring and Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Treatment Plant Operations
+- Distribution System Management
+- Water Quality Monitoring and Analysis
+- Wastewater Treatment Processes
+- SCADA Systems Operation and Troubleshooting
+- Asset Management and Maintenance
+#resume
 #WaterSuperintendentResume #WaterSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15063,16 +15063,16 @@
       <c r="L244" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Waterworks Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Waterworks Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Management", "Water Treatment Facility Operations", "Wastewater Collection and Treatment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Management"
-- "Water Treatment Facility Operations"
-- "Wastewater Collection and Treatment"
-- "SCADA Systems"
-- "GIS Mapping and Analysis"
-- "Budgeting and Financial Management"]
-#Hashtags
+Watch as we build a job-winning Waterworks Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Management, Water Treatment Facility Operations, Wastewater Collection and Treatment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Management
+- Water Treatment Facility Operations
+- Wastewater Collection and Treatment
+- SCADA Systems
+- GIS Mapping and Analysis
+- Budgeting and Financial Management
+#resume
 #WaterworksSupervisorResume #WaterworksSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15123,16 +15123,16 @@
       <c r="L245" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Zoo Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Zoo Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Zoological Management", "Animal Welfare and Conservation", "Exhibit Design and Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Zoological Management"
-- "Animal Welfare and Conservation"
-- "Exhibit Design and Development"
-- "Fundraising and Donor Relations"
-- "Public Relations and Outreach"
-- "Financial Management"]
-#Hashtags
+Watch as we build a job-winning Zoo Director from scratch, highlighting key sections and how to effectively showcase your skills in Zoological Management, Animal Welfare and Conservation, Exhibit Design and Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Zoological Management
+- Animal Welfare and Conservation
+- Exhibit Design and Development
+- Fundraising and Donor Relations
+- Public Relations and Outreach
+- Financial Management
+#resume
 #ZooDirectorResume #ZooDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15183,16 +15183,16 @@
       <c r="L246" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Alderman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Alderman from scratch, highlighting key sections and how to effectively showcase your skills in ["Agenda Setting", "Budget Analysis", "Code Enforcement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agenda Setting"
-- "Budget Analysis"
-- "Code Enforcement"
-- "Community Development"
-- "Constituent Relations"
-- "Economic Development"]
-#Hashtags
+Watch as we build a job-winning Alderman from scratch, highlighting key sections and how to effectively showcase your skills in Agenda Setting, Budget Analysis, Code Enforcement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agenda Setting
+- Budget Analysis
+- Code Enforcement
+- Community Development
+- Constituent Relations
+- Economic Development
+#resume
 #AldermanResume #Alderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15243,16 +15243,16 @@
       <c r="L247" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assembly Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assembly Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Assembly Line Optimization", "Lean Manufacturing", "Quality Control", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Assembly Line Optimization"
-- "Lean Manufacturing"
-- "Quality Control"
-- "Inventory Management"
-- "Production Planning"
-- "Time Management"]
-#Hashtags
+Watch as we build a job-winning Assembly Member from scratch, highlighting key sections and how to effectively showcase your skills in Assembly Line Optimization, Lean Manufacturing, Quality Control, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Assembly Line Optimization
+- Lean Manufacturing
+- Quality Control
+- Inventory Management
+- Production Planning
+- Time Management
+#resume
 #AssemblyMemberResume #AssemblyMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15303,16 +15303,16 @@
       <c r="L248" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Street Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Street Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Street Maintenance and Repair", "Stormwater Management", "Snow and Ice Removal", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Street Maintenance and Repair"
-- "Stormwater Management"
-- "Snow and Ice Removal"
-- "Traffic Signal Maintenance"
-- "Roadway Design and Engineering"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Street Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Street Maintenance and Repair, Stormwater Management, Snow and Ice Removal, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Street Maintenance and Repair
+- Stormwater Management
+- Snow and Ice Removal
+- Traffic Signal Maintenance
+- Roadway Design and Engineering
+- Project Management
+#resume
 #StreetCommissionerResume #StreetCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15363,16 +15363,16 @@
       <c r="L249" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Street Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Street Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Asphalt Maintenance and Repair", "Concrete Paving and Repair", "Stormwater Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Asphalt Maintenance and Repair"
-- "Concrete Paving and Repair"
-- "Stormwater Management"
-- "Traffic Signal Maintenance"
-- "Street Lighting Maintenance"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Street Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Asphalt Maintenance and Repair, Concrete Paving and Repair, Stormwater Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Asphalt Maintenance and Repair
+- Concrete Paving and Repair
+- Stormwater Management
+- Traffic Signal Maintenance
+- Street Lighting Maintenance
+- Budget Management
+#resume
 #StreetSuperintendentResume #StreetSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15423,16 +15423,16 @@
       <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Substation Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Substation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Overhead and Underground Transmission and Distribution Line Construction", "Substation Design and Engineering", "Protective Relaying and Control Systems", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Overhead and Underground Transmission and Distribution Line Construction"
-- "Substation Design and Engineering"
-- "Protective Relaying and Control Systems"
-- "Transformer Maintenance and Testing"
-- "Circuit Breaker Maintenance and Testing"
-- "Electrical Safety and Compliance"]
-#Hashtags
+Watch as we build a job-winning Substation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Overhead and Underground Transmission and Distribution Line Construction, Substation Design and Engineering, Protective Relaying and Control Systems, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Overhead and Underground Transmission and Distribution Line Construction
+- Substation Design and Engineering
+- Protective Relaying and Control Systems
+- Transformer Maintenance and Testing
+- Circuit Breaker Maintenance and Testing
+- Electrical Safety and Compliance
+#resume
 #SubstationSuperintendentResume #SubstationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15483,16 +15483,16 @@
       <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Television Station Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Television Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Broadcast Production", "Newsroom Management", "Programming Strategy", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Broadcast Production"
-- "Newsroom Management"
-- "Programming Strategy"
-- "Budget Management"
-- "Team Leadership"
-- "Digital Media Management"]
-#Hashtags
+Watch as we build a job-winning Television Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in Broadcast Production, Newsroom Management, Programming Strategy, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Broadcast Production
+- Newsroom Management
+- Programming Strategy
+- Budget Management
+- Team Leadership
+- Digital Media Management
+#resume
 #TelevisionStationManagerResume #TelevisionStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15543,16 +15543,16 @@
       <c r="L252" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Theatre Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Theatre Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Theatre Management", "Box Office Operations", "Event Planning and Coordination", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Theatre Management"
-- "Box Office Operations"
-- "Event Planning and Coordination"
-- "Budgeting and Financial Management"
-- "Staff Management and Leadership"
-- "Marketing and Audience Development"]
-#Hashtags
+Watch as we build a job-winning Theatre Manager from scratch, highlighting key sections and how to effectively showcase your skills in Theatre Management, Box Office Operations, Event Planning and Coordination, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Theatre Management
+- Box Office Operations
+- Event Planning and Coordination
+- Budgeting and Financial Management
+- Staff Management and Leadership
+- Marketing and Audience Development
+#resume
 #TheatreManagerResume #TheatreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15603,16 +15603,16 @@
       <c r="L253" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Venue Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Venue Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Event Coordination", "Venue Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Event Coordination"
-- "Venue Management"
-- "Budget Management"
-- "Vendor Management"
-- "Customer Service"
-- "Team Management"]
-#Hashtags
+Watch as we build a job-winning Venue Manager from scratch, highlighting key sections and how to effectively showcase your skills in Event Coordination, Venue Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Event Coordination
+- Venue Management
+- Budget Management
+- Vendor Management
+- Customer Service
+- Team Management
+#resume
 #VenueManagerResume #VenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15663,16 +15663,16 @@
       <c r="L254" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water and Sewer Systems Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water and Sewer Systems Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["SCADA Control Systems", "GIS Mapping", "Water Treatment Processes", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["SCADA Control Systems"
-- "GIS Mapping"
-- "Water Treatment Processes"
-- "Sewer Collection and Maintenance"
-- "Stormwater Management"
-- "Water Conservation"]
-#Hashtags
+Watch as we build a job-winning Water and Sewer Systems Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in SCADA Control Systems, GIS Mapping, Water Treatment Processes, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- SCADA Control Systems
+- GIS Mapping
+- Water Treatment Processes
+- Sewer Collection and Maintenance
+- Stormwater Management
+- Water Conservation
+#resume
 #WaterAndSewerSystemsSupervisorResume #WaterAndSewerSystemsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15723,16 +15723,16 @@
       <c r="L255" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Control Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Control Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Operations", "Wastewater Collection System Maintenance", "SCADA and PLC Programming", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Operations"
-- "Wastewater Collection System Maintenance"
-- "SCADA and PLC Programming"
-- "GIS Mapping and Analysis"
-- "Hydraulic Modeling"
-- "Water Quality Monitoring and Analysis"]
-#Hashtags
+Watch as we build a job-winning Water Control Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Operations, Wastewater Collection System Maintenance, SCADA and PLC Programming, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Operations
+- Wastewater Collection System Maintenance
+- SCADA and PLC Programming
+- GIS Mapping and Analysis
+- Hydraulic Modeling
+- Water Quality Monitoring and Analysis
+#resume
 #WaterControlSupervisorResume #WaterControlSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15783,16 +15783,16 @@
       <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Treatment Plant Operations", "Distribution System Management", "Water Quality Monitoring and Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Treatment Plant Operations"
-- "Distribution System Management"
-- "Water Quality Monitoring and Analysis"
-- "Wastewater Treatment Processes"
-- "SCADA Systems Operation and Troubleshooting"
-- "Asset Management and Maintenance"]
-#Hashtags
+Watch as we build a job-winning Water Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Water Treatment Plant Operations, Distribution System Management, Water Quality Monitoring and Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Treatment Plant Operations
+- Distribution System Management
+- Water Quality Monitoring and Analysis
+- Wastewater Treatment Processes
+- SCADA Systems Operation and Troubleshooting
+- Asset Management and Maintenance
+#resume
 #WaterSuperintendentResume #WaterSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15843,16 +15843,16 @@
       <c r="L257" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Waterworks Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Waterworks Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Management", "Water Treatment Facility Operations", "Wastewater Collection and Treatment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Management"
-- "Water Treatment Facility Operations"
-- "Wastewater Collection and Treatment"
-- "SCADA Systems"
-- "GIS Mapping and Analysis"
-- "Budgeting and Financial Management"]
-#Hashtags
+Watch as we build a job-winning Waterworks Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Management, Water Treatment Facility Operations, Wastewater Collection and Treatment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Management
+- Water Treatment Facility Operations
+- Wastewater Collection and Treatment
+- SCADA Systems
+- GIS Mapping and Analysis
+- Budgeting and Financial Management
+#resume
 #WaterworksSupervisorResume #WaterworksSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15903,16 +15903,16 @@
       <c r="L258" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Zoo Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Zoo Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Zoological Management", "Animal Welfare and Conservation", "Exhibit Design and Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Zoological Management"
-- "Animal Welfare and Conservation"
-- "Exhibit Design and Development"
-- "Fundraising and Donor Relations"
-- "Public Relations and Outreach"
-- "Financial Management"]
-#Hashtags
+Watch as we build a job-winning Zoo Director from scratch, highlighting key sections and how to effectively showcase your skills in Zoological Management, Animal Welfare and Conservation, Exhibit Design and Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Zoological Management
+- Animal Welfare and Conservation
+- Exhibit Design and Development
+- Fundraising and Donor Relations
+- Public Relations and Outreach
+- Financial Management
+#resume
 #ZooDirectorResume #ZooDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15963,16 +15963,16 @@
       <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Alderman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Alderman from scratch, highlighting key sections and how to effectively showcase your skills in ["Agenda Setting", "Budget Analysis", "Code Enforcement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agenda Setting"
-- "Budget Analysis"
-- "Code Enforcement"
-- "Community Development"
-- "Constituent Relations"
-- "Economic Development"]
-#Hashtags
+Watch as we build a job-winning Alderman from scratch, highlighting key sections and how to effectively showcase your skills in Agenda Setting, Budget Analysis, Code Enforcement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agenda Setting
+- Budget Analysis
+- Code Enforcement
+- Community Development
+- Constituent Relations
+- Economic Development
+#resume
 #AldermanResume #Alderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16023,16 +16023,16 @@
       <c r="L260" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assembly Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assembly Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Assembly Line Optimization", "Lean Manufacturing", "Quality Control", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Assembly Line Optimization"
-- "Lean Manufacturing"
-- "Quality Control"
-- "Inventory Management"
-- "Production Planning"
-- "Time Management"]
-#Hashtags
+Watch as we build a job-winning Assembly Member from scratch, highlighting key sections and how to effectively showcase your skills in Assembly Line Optimization, Lean Manufacturing, Quality Control, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Assembly Line Optimization
+- Lean Manufacturing
+- Quality Control
+- Inventory Management
+- Production Planning
+- Time Management
+#resume
 #AssemblyMemberResume #AssemblyMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16083,16 +16083,16 @@
       <c r="L261" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assembly Person? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assembly Person from scratch, highlighting key sections and how to effectively showcase your skills in ["Automated Assembly Line", "Bending", "Component Assembly", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Automated Assembly Line"
-- "Bending"
-- "Component Assembly"
-- "Conveyor System Maintenance"
-- "Electrical Wiring"
-- "Fastening"]
-#Hashtags
+Watch as we build a job-winning Assembly Person from scratch, highlighting key sections and how to effectively showcase your skills in Automated Assembly Line, Bending, Component Assembly, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Automated Assembly Line
+- Bending
+- Component Assembly
+- Conveyor System Maintenance
+- Electrical Wiring
+- Fastening
+#resume
 #AssemblyPersonResume #AssemblyPerson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16143,16 +16143,16 @@
       <c r="L262" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assemblyman or Woman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assemblyman or Woman from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Analysis", "Constituent Services", "Constituency Outreach", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Analysis"
-- "Constituent Services"
-- "Constituency Outreach"
-- "Government Relations"
-- "Legislative Bill Analysis"
-- "Legislative Drafting"]
-#Hashtags
+Watch as we build a job-winning Assemblyman or Woman from scratch, highlighting key sections and how to effectively showcase your skills in Budget Analysis, Constituent Services, Constituency Outreach, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Analysis
+- Constituent Services
+- Constituency Outreach
+- Government Relations
+- Legislative Bill Analysis
+- Legislative Drafting
+#resume
 #AssemblymanOrWomanResume #AssemblymanOrWoman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16203,16 +16203,16 @@
       <c r="L263" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Alderman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Alderman from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Policy Analysis", "Budget Management", "Constituency Outreach", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Policy Analysis"
-- "Budget Management"
-- "Constituency Outreach"
-- "Land Use Planning"
-- "Economic Development"
-- "Strategic Planning"]
-#Hashtags
+Watch as we build a job-winning City Alderman from scratch, highlighting key sections and how to effectively showcase your skills in Public Policy Analysis, Budget Management, Constituency Outreach, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Policy Analysis
+- Budget Management
+- Constituency Outreach
+- Land Use Planning
+- Economic Development
+- Strategic Planning
+#resume
 #CityAldermanResume #CityAlderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16263,16 +16263,16 @@
       <c r="L264" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Council Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Council Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Public Speaking", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Public Speaking"
-- "Constituent Relations"
-- "Policy Analysis"
-- "Collaboration"]
-#Hashtags
+Watch as we build a job-winning City Council Member from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Public Speaking, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Public Speaking
+- Constituent Relations
+- Policy Analysis
+- Collaboration
+#resume
 #CityCouncilMemberResume #CityCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16323,16 +16323,16 @@
       <c r="L265" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Councilman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Councilman from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting", "Constituent Services", "Economic Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting"
-- "Constituent Services"
-- "Economic Development"
-- "Environmental Policy"
-- "Ethics and Transparency"
-- "Fiscal Management"]
-#Hashtags
+Watch as we build a job-winning City Councilman from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting, Constituent Services, Economic Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting
+- Constituent Services
+- Economic Development
+- Environmental Policy
+- Ethics and Transparency
+- Fiscal Management
+#resume
 #CityCouncilmanResume #CityCouncilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16383,16 +16383,16 @@
       <c r="L266" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Congressional Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Congressional Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting and Fiscal Analysis", "Constituent Relations Management", "Legislative Drafting and Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting and Fiscal Analysis"
-- "Constituent Relations Management"
-- "Legislative Drafting and Analysis"
-- "Public Policy Formulation"
-- "Strategic Planning and Implementation"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Congressional Representative from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting and Fiscal Analysis, Constituent Relations Management, Legislative Drafting and Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting and Fiscal Analysis
+- Constituent Relations Management
+- Legislative Drafting and Analysis
+- Public Policy Formulation
+- Strategic Planning and Implementation
+- Project Management
+#resume
 #CongressionalRepresentativeResume #CongressionalRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16443,16 +16443,16 @@
       <c r="L267" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Sports Team Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Sports Team Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Team Management", "Player Development", "Game Strategy", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Team Management"
-- "Player Development"
-- "Game Strategy"
-- "Budget Management"
-- "Event Planning"
-- "Player Evaluation"]
-#Hashtags
+Watch as we build a job-winning Sports Team Manager from scratch, highlighting key sections and how to effectively showcase your skills in Team Management, Player Development, Game Strategy, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Team Management
+- Player Development
+- Game Strategy
+- Budget Management
+- Event Planning
+- Player Evaluation
+#resume
 #SportsTeamManagerResume #SportsTeamManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16503,16 +16503,16 @@
       <c r="L268" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Congressman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Congressman from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services", "Policy Development", "Legislating", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services"
-- "Policy Development"
-- "Legislating"
-- "Advocacy"
-- "Public Speaking"
-- "Consensus Building"]
-#Hashtags
+Watch as we build a job-winning Congressman from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services, Policy Development, Legislating, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services
+- Policy Development
+- Legislating
+- Advocacy
+- Public Speaking
+- Consensus Building
+#resume
 #CongressmanResume #Congressman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16563,16 +16563,16 @@
       <c r="L269" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Street Commissioner? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Street Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in ["Street Maintenance and Repair", "Stormwater Management", "Snow and Ice Removal", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Street Maintenance and Repair"
-- "Stormwater Management"
-- "Snow and Ice Removal"
-- "Traffic Signal Maintenance"
-- "Roadway Design and Engineering"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Street Commissioner from scratch, highlighting key sections and how to effectively showcase your skills in Street Maintenance and Repair, Stormwater Management, Snow and Ice Removal, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Street Maintenance and Repair
+- Stormwater Management
+- Snow and Ice Removal
+- Traffic Signal Maintenance
+- Roadway Design and Engineering
+- Project Management
+#resume
 #StreetCommissionerResume #StreetCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16623,16 +16623,16 @@
       <c r="L270" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Council Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Council Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Advising Constituents", "Budget Analysis", "Community Engagement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Advising Constituents"
-- "Budget Analysis"
-- "Community Engagement"
-- "Conflict Resolution"
-- "Constituent Services"
-- "Decision Making"]
-#Hashtags
+Watch as we build a job-winning Council Member from scratch, highlighting key sections and how to effectively showcase your skills in Advising Constituents, Budget Analysis, Community Engagement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Advising Constituents
+- Budget Analysis
+- Community Engagement
+- Conflict Resolution
+- Constituent Services
+- Decision Making
+#resume
 #CouncilMemberResume #CouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16683,16 +16683,16 @@
       <c r="L271" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Street Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Street Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Asphalt Maintenance and Repair", "Concrete Paving and Repair", "Stormwater Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Asphalt Maintenance and Repair"
-- "Concrete Paving and Repair"
-- "Stormwater Management"
-- "Traffic Signal Maintenance"
-- "Street Lighting Maintenance"
-- "Budget Management"]
-#Hashtags
+Watch as we build a job-winning Street Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Asphalt Maintenance and Repair, Concrete Paving and Repair, Stormwater Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Asphalt Maintenance and Repair
+- Concrete Paving and Repair
+- Stormwater Management
+- Traffic Signal Maintenance
+- Street Lighting Maintenance
+- Budget Management
+#resume
 #StreetSuperintendentResume #StreetSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16743,16 +16743,16 @@
       <c r="L272" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Councilman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Councilman from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Policy Analysis", "Community Engagement", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Policy Analysis"
-- "Community Engagement"
-- "Strategic Planning"
-- "Budget Management"
-- "Ordinance Drafting"
-- "Land Use Planning"]
-#Hashtags
+Watch as we build a job-winning Councilman from scratch, highlighting key sections and how to effectively showcase your skills in Public Policy Analysis, Community Engagement, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Policy Analysis
+- Community Engagement
+- Strategic Planning
+- Budget Management
+- Ordinance Drafting
+- Land Use Planning
+#resume
 #CouncilmanResume #Councilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16803,16 +16803,16 @@
       <c r="L273" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Substation Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Substation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Overhead and Underground Transmission and Distribution Line Construction", "Substation Design and Engineering", "Protective Relaying and Control Systems", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Overhead and Underground Transmission and Distribution Line Construction"
-- "Substation Design and Engineering"
-- "Protective Relaying and Control Systems"
-- "Transformer Maintenance and Testing"
-- "Circuit Breaker Maintenance and Testing"
-- "Electrical Safety and Compliance"]
-#Hashtags
+Watch as we build a job-winning Substation Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Overhead and Underground Transmission and Distribution Line Construction, Substation Design and Engineering, Protective Relaying and Control Systems, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Overhead and Underground Transmission and Distribution Line Construction
+- Substation Design and Engineering
+- Protective Relaying and Control Systems
+- Transformer Maintenance and Testing
+- Circuit Breaker Maintenance and Testing
+- Electrical Safety and Compliance
+#resume
 #SubstationSuperintendentResume #SubstationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16863,16 +16863,16 @@
       <c r="L274" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Councilor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Councilor from scratch, highlighting key sections and how to effectively showcase your skills in ["Case Management", "Crisis Intervention", "Counseling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Case Management"
-- "Crisis Intervention"
-- "Counseling"
-- "Advocacy"
-- "Intake Assessment"
-- "Group Facilitation"]
-#Hashtags
+Watch as we build a job-winning Councilor from scratch, highlighting key sections and how to effectively showcase your skills in Case Management, Crisis Intervention, Counseling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Case Management
+- Crisis Intervention
+- Counseling
+- Advocacy
+- Intake Assessment
+- Group Facilitation
+#resume
 #CouncilorResume #Councilor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16923,16 +16923,16 @@
       <c r="L275" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Television Station Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Television Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Broadcast Production", "Newsroom Management", "Programming Strategy", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Broadcast Production"
-- "Newsroom Management"
-- "Programming Strategy"
-- "Budget Management"
-- "Team Leadership"
-- "Digital Media Management"]
-#Hashtags
+Watch as we build a job-winning Television Station Manager from scratch, highlighting key sections and how to effectively showcase your skills in Broadcast Production, Newsroom Management, Programming Strategy, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Broadcast Production
+- Newsroom Management
+- Programming Strategy
+- Budget Management
+- Team Leadership
+- Digital Media Management
+#resume
 #TelevisionStationManagerResume #TelevisionStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16983,16 +16983,16 @@
       <c r="L276" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Councilperson? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Councilperson from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting and Financial Management", "Public Policy Development", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting and Financial Management"
-- "Public Policy Development"
-- "Strategic Planning"
-- "Community Engagement"
-- "Leadership and Governance"
-- "Interpersonal Communication and Negotiation"]
-#Hashtags
+Watch as we build a job-winning Councilperson from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting and Financial Management, Public Policy Development, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting and Financial Management
+- Public Policy Development
+- Strategic Planning
+- Community Engagement
+- Leadership and Governance
+- Interpersonal Communication and Negotiation
+#resume
 #CouncilpersonResume #Councilperson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17043,16 +17043,16 @@
       <c r="L277" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Theatre Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Theatre Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Theatre Management", "Box Office Operations", "Event Planning and Coordination", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Theatre Management"
-- "Box Office Operations"
-- "Event Planning and Coordination"
-- "Budgeting and Financial Management"
-- "Staff Management and Leadership"
-- "Marketing and Audience Development"]
-#Hashtags
+Watch as we build a job-winning Theatre Manager from scratch, highlighting key sections and how to effectively showcase your skills in Theatre Management, Box Office Operations, Event Planning and Coordination, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Theatre Management
+- Box Office Operations
+- Event Planning and Coordination
+- Budgeting and Financial Management
+- Staff Management and Leadership
+- Marketing and Audience Development
+#resume
 #TheatreManagerResume #TheatreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17103,16 +17103,16 @@
       <c r="L278" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Delegate? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Delegate from scratch, highlighting key sections and how to effectively showcase your skills in ["Communication", "Collaboration", "Event Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Communication"
-- "Collaboration"
-- "Event Planning"
-- "Fundraising"
-- "Leadership"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Delegate from scratch, highlighting key sections and how to effectively showcase your skills in Communication, Collaboration, Event Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Communication
+- Collaboration
+- Event Planning
+- Fundraising
+- Leadership
+- Negotiation
+#resume
 #DelegateResume #Delegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17163,16 +17163,16 @@
       <c r="L279" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Venue Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Venue Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Event Coordination", "Venue Management", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Event Coordination"
-- "Venue Management"
-- "Budget Management"
-- "Vendor Management"
-- "Customer Service"
-- "Team Management"]
-#Hashtags
+Watch as we build a job-winning Venue Manager from scratch, highlighting key sections and how to effectively showcase your skills in Event Coordination, Venue Management, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Event Coordination
+- Venue Management
+- Budget Management
+- Vendor Management
+- Customer Service
+- Team Management
+#resume
 #VenueManagerResume #VenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17223,16 +17223,16 @@
       <c r="L280" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Legislator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Legislator from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services", "Community Outreach", "Legislative Research", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services"
-- "Community Outreach"
-- "Legislative Research"
-- "Policy Analysis"
-- "Public Speaking"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Legislator from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services, Community Outreach, Legislative Research, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services
+- Community Outreach
+- Legislative Research
+- Policy Analysis
+- Public Speaking
+- Negotiation
+#resume
 #LegislatorResume #Legislator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17283,16 +17283,16 @@
       <c r="L281" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water and Sewer Systems Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water and Sewer Systems Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["SCADA Control Systems", "GIS Mapping", "Water Treatment Processes", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["SCADA Control Systems"
-- "GIS Mapping"
-- "Water Treatment Processes"
-- "Sewer Collection and Maintenance"
-- "Stormwater Management"
-- "Water Conservation"]
-#Hashtags
+Watch as we build a job-winning Water and Sewer Systems Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in SCADA Control Systems, GIS Mapping, Water Treatment Processes, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- SCADA Control Systems
+- GIS Mapping
+- Water Treatment Processes
+- Sewer Collection and Maintenance
+- Stormwater Management
+- Water Conservation
+#resume
 #WaterAndSewerSystemsSupervisorResume #WaterAndSewerSystemsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17343,16 +17343,16 @@
       <c r="L282" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Member of Congress? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Member of Congress from scratch, highlighting key sections and how to effectively showcase your skills in ["Policy Analysis", "Legislative Drafting", "Constituent Services", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Policy Analysis"
-- "Legislative Drafting"
-- "Constituent Services"
-- "Public Speaking"
-- "Media Relations"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Member of Congress from scratch, highlighting key sections and how to effectively showcase your skills in Policy Analysis, Legislative Drafting, Constituent Services, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Policy Analysis
+- Legislative Drafting
+- Constituent Services
+- Public Speaking
+- Media Relations
+- Negotiation
+#resume
 #MemberOfCongressResume #MemberOfCongress #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17403,16 +17403,16 @@
       <c r="L283" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Control Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Control Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Operations", "Wastewater Collection System Maintenance", "SCADA and PLC Programming", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Operations"
-- "Wastewater Collection System Maintenance"
-- "SCADA and PLC Programming"
-- "GIS Mapping and Analysis"
-- "Hydraulic Modeling"
-- "Water Quality Monitoring and Analysis"]
-#Hashtags
+Watch as we build a job-winning Water Control Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Operations, Wastewater Collection System Maintenance, SCADA and PLC Programming, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Operations
+- Wastewater Collection System Maintenance
+- SCADA and PLC Programming
+- GIS Mapping and Analysis
+- Hydraulic Modeling
+- Water Quality Monitoring and Analysis
+#resume
 #WaterControlSupervisorResume #WaterControlSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17463,16 +17463,16 @@
       <c r="L284" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Customer Relationship Management", "Sales Prospecting", "Negotiation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Customer Relationship Management"
-- "Sales Prospecting"
-- "Negotiation"
-- "Communication"
-- "Interpersonal Skills"
-- "Problem Solving"]
-#Hashtags
+Watch as we build a job-winning Representative from scratch, highlighting key sections and how to effectively showcase your skills in Customer Relationship Management, Sales Prospecting, Negotiation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Customer Relationship Management
+- Sales Prospecting
+- Negotiation
+- Communication
+- Interpersonal Skills
+- Problem Solving
+#resume
 #RepresentativeResume #Representative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17523,16 +17523,16 @@
       <c r="L285" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Water Superintendent? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Water Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Treatment Plant Operations", "Distribution System Management", "Water Quality Monitoring and Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Treatment Plant Operations"
-- "Distribution System Management"
-- "Water Quality Monitoring and Analysis"
-- "Wastewater Treatment Processes"
-- "SCADA Systems Operation and Troubleshooting"
-- "Asset Management and Maintenance"]
-#Hashtags
+Watch as we build a job-winning Water Superintendent from scratch, highlighting key sections and how to effectively showcase your skills in Water Treatment Plant Operations, Distribution System Management, Water Quality Monitoring and Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Treatment Plant Operations
+- Distribution System Management
+- Water Quality Monitoring and Analysis
+- Wastewater Treatment Processes
+- SCADA Systems Operation and Troubleshooting
+- Asset Management and Maintenance
+#resume
 #WaterSuperintendentResume #WaterSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17583,16 +17583,16 @@
       <c r="L286" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Selectman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Selectman from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services", "Budget Management", "Policy Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services"
-- "Budget Management"
-- "Policy Development"
-- "Community Engagement"
-- "Intergovernmental Relations"
-- "Public Speaking"]
-#Hashtags
+Watch as we build a job-winning Selectman from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services, Budget Management, Policy Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services
+- Budget Management
+- Policy Development
+- Community Engagement
+- Intergovernmental Relations
+- Public Speaking
+#resume
 #SelectmanResume #Selectman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17643,16 +17643,16 @@
       <c r="L287" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Waterworks Supervisor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Waterworks Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in ["Water Distribution System Management", "Water Treatment Facility Operations", "Wastewater Collection and Treatment", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Water Distribution System Management"
-- "Water Treatment Facility Operations"
-- "Wastewater Collection and Treatment"
-- "SCADA Systems"
-- "GIS Mapping and Analysis"
-- "Budgeting and Financial Management"]
-#Hashtags
+Watch as we build a job-winning Waterworks Supervisor from scratch, highlighting key sections and how to effectively showcase your skills in Water Distribution System Management, Water Treatment Facility Operations, Wastewater Collection and Treatment, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Water Distribution System Management
+- Water Treatment Facility Operations
+- Wastewater Collection and Treatment
+- SCADA Systems
+- GIS Mapping and Analysis
+- Budgeting and Financial Management
+#resume
 #WaterworksSupervisorResume #WaterworksSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17703,16 +17703,16 @@
       <c r="L288" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Senator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Senator from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services Management", "Legislative Policy Analysis", "Budget and Appropriations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services Management"
-- "Legislative Policy Analysis"
-- "Budget and Appropriations"
-- "Speechwriting and Public Speaking"
-- "Committee Work and Leadership"
-- "Constituent Advocacy"]
-#Hashtags
+Watch as we build a job-winning Senator from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services Management, Legislative Policy Analysis, Budget and Appropriations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services Management
+- Legislative Policy Analysis
+- Budget and Appropriations
+- Speechwriting and Public Speaking
+- Committee Work and Leadership
+- Constituent Advocacy
+#resume
 #SenatorResume #Senator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17763,16 +17763,16 @@
       <c r="L289" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Zoo Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Zoo Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Zoological Management", "Animal Welfare and Conservation", "Exhibit Design and Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Zoological Management"
-- "Animal Welfare and Conservation"
-- "Exhibit Design and Development"
-- "Fundraising and Donor Relations"
-- "Public Relations and Outreach"
-- "Financial Management"]
-#Hashtags
+Watch as we build a job-winning Zoo Director from scratch, highlighting key sections and how to effectively showcase your skills in Zoological Management, Animal Welfare and Conservation, Exhibit Design and Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Zoological Management
+- Animal Welfare and Conservation
+- Exhibit Design and Development
+- Fundraising and Donor Relations
+- Public Relations and Outreach
+- Financial Management
+#resume
 #ZooDirectorResume #ZooDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17823,16 +17823,16 @@
       <c r="L290" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Tribal Council Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Tribal Council Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "Policy Development", "Conflict Resolution", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "Policy Development"
-- "Conflict Resolution"
-- "Stakeholder Engagement"
-- "Community Outreach"
-- "Strategic Planning"]
-#Hashtags
+Watch as we build a job-winning Tribal Council Member from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, Policy Development, Conflict Resolution, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- Policy Development
+- Conflict Resolution
+- Stakeholder Engagement
+- Community Outreach
+- Strategic Planning
+#resume
 #TribalCouncilMemberResume #TribalCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17883,16 +17883,16 @@
       <c r="L291" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Alderman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Alderman from scratch, highlighting key sections and how to effectively showcase your skills in ["Agenda Setting", "Budget Analysis", "Code Enforcement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Agenda Setting"
-- "Budget Analysis"
-- "Code Enforcement"
-- "Community Development"
-- "Constituent Relations"
-- "Economic Development"]
-#Hashtags
+Watch as we build a job-winning Alderman from scratch, highlighting key sections and how to effectively showcase your skills in Agenda Setting, Budget Analysis, Code Enforcement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Agenda Setting
+- Budget Analysis
+- Code Enforcement
+- Community Development
+- Constituent Relations
+- Economic Development
+#resume
 #AldermanResume #Alderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17943,16 +17943,16 @@
       <c r="L292" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Tribal Delegate? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Tribal Delegate from scratch, highlighting key sections and how to effectively showcase your skills in ["Community Building", "Cultural Resource Management", "Economic Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Community Building"
-- "Cultural Resource Management"
-- "Economic Development"
-- "Environmental Protection"
-- "Federal Indian Law"
-- "Government Relations"]
-#Hashtags
+Watch as we build a job-winning Tribal Delegate from scratch, highlighting key sections and how to effectively showcase your skills in Community Building, Cultural Resource Management, Economic Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Community Building
+- Cultural Resource Management
+- Economic Development
+- Environmental Protection
+- Federal Indian Law
+- Government Relations
+#resume
 #TribalDelegateResume #TribalDelegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18003,16 +18003,16 @@
       <c r="L293" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assembly Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assembly Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Assembly Line Optimization", "Lean Manufacturing", "Quality Control", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Assembly Line Optimization"
-- "Lean Manufacturing"
-- "Quality Control"
-- "Inventory Management"
-- "Production Planning"
-- "Time Management"]
-#Hashtags
+Watch as we build a job-winning Assembly Member from scratch, highlighting key sections and how to effectively showcase your skills in Assembly Line Optimization, Lean Manufacturing, Quality Control, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Assembly Line Optimization
+- Lean Manufacturing
+- Quality Control
+- Inventory Management
+- Production Planning
+- Time Management
+#resume
 #AssemblyMemberResume #AssemblyMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18063,16 +18063,16 @@
       <c r="L294" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect U.S. Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning U.S. Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Legislative Expertise", "Constituent Service", "Public speaking", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Legislative Expertise"
-- "Constituent Service"
-- "Public speaking"
-- "Media relations"
-- "Campaign Management"
-- "Policy Analysis"]
-#Hashtags
+Watch as we build a job-winning U.S. Representative from scratch, highlighting key sections and how to effectively showcase your skills in Legislative Expertise, Constituent Service, Public speaking, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Legislative Expertise
+- Constituent Service
+- Public speaking
+- Media relations
+- Campaign Management
+- Policy Analysis
+#resume
 #USRepresentativeResume #USRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18123,16 +18123,16 @@
       <c r="L295" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assembly Person? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assembly Person from scratch, highlighting key sections and how to effectively showcase your skills in ["Automated Assembly Line", "Bending", "Component Assembly", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Automated Assembly Line"
-- "Bending"
-- "Component Assembly"
-- "Conveyor System Maintenance"
-- "Electrical Wiring"
-- "Fastening"]
-#Hashtags
+Watch as we build a job-winning Assembly Person from scratch, highlighting key sections and how to effectively showcase your skills in Automated Assembly Line, Bending, Component Assembly, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Automated Assembly Line
+- Bending
+- Component Assembly
+- Conveyor System Maintenance
+- Electrical Wiring
+- Fastening
+#resume
 #AssemblyPersonResume #AssemblyPerson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18183,16 +18183,16 @@
       <c r="L296" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect U.S. Senator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning U.S. Senator from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services Management", "Legislative Research and Analysis", "Committee Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services Management"
-- "Legislative Research and Analysis"
-- "Committee Leadership"
-- "Policy Development and Implementation"
-- "Budgetary Management"
-- "Media Relations and Communications"]
-#Hashtags
+Watch as we build a job-winning U.S. Senator from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services Management, Legislative Research and Analysis, Committee Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services Management
+- Legislative Research and Analysis
+- Committee Leadership
+- Policy Development and Implementation
+- Budgetary Management
+- Media Relations and Communications
+#resume
 #USSenatorResume #USSenator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18243,16 +18243,16 @@
       <c r="L297" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Assemblyman or Woman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Assemblyman or Woman from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Analysis", "Constituent Services", "Constituency Outreach", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Analysis"
-- "Constituent Services"
-- "Constituency Outreach"
-- "Government Relations"
-- "Legislative Bill Analysis"
-- "Legislative Drafting"]
-#Hashtags
+Watch as we build a job-winning Assemblyman or Woman from scratch, highlighting key sections and how to effectively showcase your skills in Budget Analysis, Constituent Services, Constituency Outreach, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Analysis
+- Constituent Services
+- Constituency Outreach
+- Government Relations
+- Legislative Bill Analysis
+- Legislative Drafting
+#resume
 #AssemblymanOrWomanResume #AssemblymanOrWoman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18303,16 +18303,16 @@
       <c r="L298" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Account Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Account Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Client Relationship Management", "Sales Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Client Relationship Management"
-- "Sales Management"
-- "Budget Management"
-- "Marketing and Advertising"
-- "Team Leadership"]
-#Hashtags
+Watch as we build a job-winning Account Director from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Client Relationship Management, Sales Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Client Relationship Management
+- Sales Management
+- Budget Management
+- Marketing and Advertising
+- Team Leadership
+#resume
 #AccountDirectorResume #AccountDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18363,16 +18363,16 @@
       <c r="L299" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Alderman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Alderman from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Policy Analysis", "Budget Management", "Constituency Outreach", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Policy Analysis"
-- "Budget Management"
-- "Constituency Outreach"
-- "Land Use Planning"
-- "Economic Development"
-- "Strategic Planning"]
-#Hashtags
+Watch as we build a job-winning City Alderman from scratch, highlighting key sections and how to effectively showcase your skills in Public Policy Analysis, Budget Management, Constituency Outreach, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Policy Analysis
+- Budget Management
+- Constituency Outreach
+- Land Use Planning
+- Economic Development
+- Strategic Planning
+#resume
 #CityAldermanResume #CityAlderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18423,16 +18423,16 @@
       <c r="L300" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Account Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Account Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Salesforce", "Microsoft Dynamics 365 CRM", "HubSpot", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Salesforce"
-- "Microsoft Dynamics 365 CRM"
-- "HubSpot"
-- "Zoho CRM"
-- "SAP Hybris"
-- "Oracle Siebel CRM"]
-#Hashtags
+Watch as we build a job-winning Account Executive from scratch, highlighting key sections and how to effectively showcase your skills in Salesforce, Microsoft Dynamics 365 CRM, HubSpot, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Salesforce
+- Microsoft Dynamics 365 CRM
+- HubSpot
+- Zoho CRM
+- SAP Hybris
+- Oracle Siebel CRM
+#resume
 #AccountExecutiveResume #AccountExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18483,16 +18483,16 @@
       <c r="L301" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Council Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Council Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Budget Management", "Public Speaking", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Budget Management"
-- "Public Speaking"
-- "Constituent Relations"
-- "Policy Analysis"
-- "Collaboration"]
-#Hashtags
+Watch as we build a job-winning City Council Member from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Budget Management, Public Speaking, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Budget Management
+- Public Speaking
+- Constituent Relations
+- Policy Analysis
+- Collaboration
+#resume
 #CityCouncilMemberResume #CityCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18543,16 +18543,16 @@
       <c r="L302" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Account Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Account Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Salesforce", "Microsoft Office Suite", "Client Relationship Management (CRM)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Salesforce"
-- "Microsoft Office Suite"
-- "Client Relationship Management (CRM)"
-- "Business Development"
-- "Account Planning"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Account Manager from scratch, highlighting key sections and how to effectively showcase your skills in Salesforce, Microsoft Office Suite, Client Relationship Management (CRM), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Salesforce
+- Microsoft Office Suite
+- Client Relationship Management (CRM)
+- Business Development
+- Account Planning
+- Negotiation
+#resume
 #AccountManagerResume #AccountManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18603,16 +18603,16 @@
       <c r="L303" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect City Councilman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning City Councilman from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting", "Constituent Services", "Economic Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting"
-- "Constituent Services"
-- "Economic Development"
-- "Environmental Policy"
-- "Ethics and Transparency"
-- "Fiscal Management"]
-#Hashtags
+Watch as we build a job-winning City Councilman from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting, Constituent Services, Economic Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting
+- Constituent Services
+- Economic Development
+- Environmental Policy
+- Ethics and Transparency
+- Fiscal Management
+#resume
 #CityCouncilmanResume #CityCouncilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18663,16 +18663,16 @@
       <c r="L304" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Account Specialist? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Account Specialist from scratch, highlighting key sections and how to effectively showcase your skills in ["Accounts Payable", "Accounts Receivable", "Bank Reconciliation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Accounts Payable"
-- "Accounts Receivable"
-- "Bank Reconciliation"
-- "Bookkeeping"
-- "Cash Flow Analysis"
-- "Customer Relationship Management (CRM)"]
-#Hashtags
+Watch as we build a job-winning Account Specialist from scratch, highlighting key sections and how to effectively showcase your skills in Accounts Payable, Accounts Receivable, Bank Reconciliation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Accounts Payable
+- Accounts Receivable
+- Bank Reconciliation
+- Bookkeeping
+- Cash Flow Analysis
+- Customer Relationship Management (CRM)
+#resume
 #AccountSpecialistResume #AccountSpecialist #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18723,16 +18723,16 @@
       <c r="L305" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Congressional Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Congressional Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting and Fiscal Analysis", "Constituent Relations Management", "Legislative Drafting and Analysis", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting and Fiscal Analysis"
-- "Constituent Relations Management"
-- "Legislative Drafting and Analysis"
-- "Public Policy Formulation"
-- "Strategic Planning and Implementation"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Congressional Representative from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting and Fiscal Analysis, Constituent Relations Management, Legislative Drafting and Analysis, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting and Fiscal Analysis
+- Constituent Relations Management
+- Legislative Drafting and Analysis
+- Public Policy Formulation
+- Strategic Planning and Implementation
+- Project Management
+#resume
 #CongressionalRepresentativeResume #CongressionalRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18783,16 +18783,16 @@
       <c r="L306" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Account Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Account Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Google AdWords", "Google Analytics", "Facebook Ads", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Google AdWords"
-- "Google Analytics"
-- "Facebook Ads"
-- "Instagram Ads"
-- "Twitter Ads"
-- "LinkedIn Ads"]
-#Hashtags
+Watch as we build a job-winning Advertising Account Executive from scratch, highlighting key sections and how to effectively showcase your skills in Google AdWords, Google Analytics, Facebook Ads, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Google AdWords
+- Google Analytics
+- Facebook Ads
+- Instagram Ads
+- Twitter Ads
+- LinkedIn Ads
+#resume
 #AdvertisingAccountExecutiveResume #AdvertisingAccountExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18843,16 +18843,16 @@
       <c r="L307" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Congressman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Congressman from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services", "Policy Development", "Legislating", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services"
-- "Policy Development"
-- "Legislating"
-- "Advocacy"
-- "Public Speaking"
-- "Consensus Building"]
-#Hashtags
+Watch as we build a job-winning Congressman from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services, Policy Development, Legislating, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services
+- Policy Development
+- Legislating
+- Advocacy
+- Public Speaking
+- Consensus Building
+#resume
 #CongressmanResume #Congressman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18903,16 +18903,16 @@
       <c r="L308" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Account Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Account Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Campaign Planning", "Budget Management", "Media Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Campaign Planning"
-- "Budget Management"
-- "Media Planning"
-- "Analytics Analysis"
-- "Client Relationship Management"
-- "Creative Development"]
-#Hashtags
+Watch as we build a job-winning Advertising Account Manager from scratch, highlighting key sections and how to effectively showcase your skills in Campaign Planning, Budget Management, Media Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Campaign Planning
+- Budget Management
+- Media Planning
+- Analytics Analysis
+- Client Relationship Management
+- Creative Development
+#resume
 #AdvertisingAccountManagerResume #AdvertisingAccountManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18963,16 +18963,16 @@
       <c r="L309" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Council Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Council Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Advising Constituents", "Budget Analysis", "Community Engagement", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Advising Constituents"
-- "Budget Analysis"
-- "Community Engagement"
-- "Conflict Resolution"
-- "Constituent Services"
-- "Decision Making"]
-#Hashtags
+Watch as we build a job-winning Council Member from scratch, highlighting key sections and how to effectively showcase your skills in Advising Constituents, Budget Analysis, Community Engagement, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Advising Constituents
+- Budget Analysis
+- Community Engagement
+- Conflict Resolution
+- Constituent Services
+- Decision Making
+#resume
 #CouncilMemberResume #CouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19023,16 +19023,16 @@
       <c r="L310" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Agency Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Agency Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Programmatic Advertising", "Native Advertising", "Search Advertising", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Programmatic Advertising"
-- "Native Advertising"
-- "Search Advertising"
-- "Content Marketing"
-- "Social Media Advertising"
-- "Omnichannel Advertising"]
-#Hashtags
+Watch as we build a job-winning Advertising Agency Manager from scratch, highlighting key sections and how to effectively showcase your skills in Programmatic Advertising, Native Advertising, Search Advertising, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Programmatic Advertising
+- Native Advertising
+- Search Advertising
+- Content Marketing
+- Social Media Advertising
+- Omnichannel Advertising
+#resume
 #AdvertisingAgencyManagerResume #AdvertisingAgencyManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19083,16 +19083,16 @@
       <c r="L311" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Councilman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Councilman from scratch, highlighting key sections and how to effectively showcase your skills in ["Public Policy Analysis", "Community Engagement", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Public Policy Analysis"
-- "Community Engagement"
-- "Strategic Planning"
-- "Budget Management"
-- "Ordinance Drafting"
-- "Land Use Planning"]
-#Hashtags
+Watch as we build a job-winning Councilman from scratch, highlighting key sections and how to effectively showcase your skills in Public Policy Analysis, Community Engagement, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Public Policy Analysis
+- Community Engagement
+- Strategic Planning
+- Budget Management
+- Ordinance Drafting
+- Land Use Planning
+#resume
 #CouncilmanResume #Councilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19143,16 +19143,16 @@
       <c r="L312" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Campaign Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Campaign Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Ad Campaign Planning", "Budget Management", "Campaign Analysis and Reporting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Ad Campaign Planning"
-- "Budget Management"
-- "Campaign Analysis and Reporting"
-- "Client Relationship Management"
-- "Creative Concept Development"
-- "Data Analytics and Interpretation"]
-#Hashtags
+Watch as we build a job-winning Advertising Campaign Manager from scratch, highlighting key sections and how to effectively showcase your skills in Ad Campaign Planning, Budget Management, Campaign Analysis and Reporting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Ad Campaign Planning
+- Budget Management
+- Campaign Analysis and Reporting
+- Client Relationship Management
+- Creative Concept Development
+- Data Analytics and Interpretation
+#resume
 #AdvertisingCampaignManagerResume #AdvertisingCampaignManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19203,16 +19203,16 @@
       <c r="L313" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Councilor? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Councilor from scratch, highlighting key sections and how to effectively showcase your skills in ["Case Management", "Crisis Intervention", "Counseling", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Case Management"
-- "Crisis Intervention"
-- "Counseling"
-- "Advocacy"
-- "Intake Assessment"
-- "Group Facilitation"]
-#Hashtags
+Watch as we build a job-winning Councilor from scratch, highlighting key sections and how to effectively showcase your skills in Case Management, Crisis Intervention, Counseling, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Case Management
+- Crisis Intervention
+- Counseling
+- Advocacy
+- Intake Assessment
+- Group Facilitation
+#resume
 #CouncilorResume #Councilor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19263,17 +19263,17 @@
       <c r="L314" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Coordinator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in ["Paid Advertising (Google AdWords,  Facebook Ads)", "Search Engine Marketing (SEM)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Paid Advertising (Google AdWords
-- Facebook Ads)"
-- "Search Engine Marketing (SEM)"
-- "Display Advertising"
-- "Affiliate Marketing"
-- "Email Marketing"
-- "Social Media Marketing"]
-#Hashtags
+Watch as we build a job-winning Advertising Coordinator from scratch, highlighting key sections and how to effectively showcase your skills in Paid Advertising (Google AdWords,  Facebook Ads), Search Engine Marketing (SEM), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Paid Advertising (Google AdWords
+- Facebook Ads)
+- Search Engine Marketing (SEM)
+- Display Advertising
+- Affiliate Marketing
+- Email Marketing
+- Social Media Marketing
+#resume
 #AdvertisingCoordinatorResume #AdvertisingCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19324,16 +19324,16 @@
       <c r="L315" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Councilperson? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Councilperson from scratch, highlighting key sections and how to effectively showcase your skills in ["Budgeting and Financial Management", "Public Policy Development", "Strategic Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budgeting and Financial Management"
-- "Public Policy Development"
-- "Strategic Planning"
-- "Community Engagement"
-- "Leadership and Governance"
-- "Interpersonal Communication and Negotiation"]
-#Hashtags
+Watch as we build a job-winning Councilperson from scratch, highlighting key sections and how to effectively showcase your skills in Budgeting and Financial Management, Public Policy Development, Strategic Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budgeting and Financial Management
+- Public Policy Development
+- Strategic Planning
+- Community Engagement
+- Leadership and Governance
+- Interpersonal Communication and Negotiation
+#resume
 #CouncilpersonResume #Councilperson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19384,16 +19384,16 @@
       <c r="L316" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Programmatic Advertising", "Digital Marketing Strategy", "Paid Social Media Advertising", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Programmatic Advertising"
-- "Digital Marketing Strategy"
-- "Paid Social Media Advertising"
-- "Paid Search Advertising"
-- "Display Advertising"
-- "Affiliate Marketing"]
-#Hashtags
+Watch as we build a job-winning Advertising Director from scratch, highlighting key sections and how to effectively showcase your skills in Programmatic Advertising, Digital Marketing Strategy, Paid Social Media Advertising, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Programmatic Advertising
+- Digital Marketing Strategy
+- Paid Social Media Advertising
+- Paid Search Advertising
+- Display Advertising
+- Affiliate Marketing
+#resume
 #AdvertisingDirectorResume #AdvertisingDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19444,16 +19444,16 @@
       <c r="L317" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Delegate? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Delegate from scratch, highlighting key sections and how to effectively showcase your skills in ["Communication", "Collaboration", "Event Planning", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Communication"
-- "Collaboration"
-- "Event Planning"
-- "Fundraising"
-- "Leadership"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Delegate from scratch, highlighting key sections and how to effectively showcase your skills in Communication, Collaboration, Event Planning, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Communication
+- Collaboration
+- Event Planning
+- Fundraising
+- Leadership
+- Negotiation
+#resume
 #DelegateResume #Delegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19504,16 +19504,16 @@
       <c r="L318" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Executive? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Executive from scratch, highlighting key sections and how to effectively showcase your skills in ["Digital Advertising", "Social Media Marketing", "Search Engine Optimization (SEO)", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Digital Advertising"
-- "Social Media Marketing"
-- "Search Engine Optimization (SEO)"
-- "Google Ads Management"
-- "Content Marketing"
-- "Email Marketing"]
-#Hashtags
+Watch as we build a job-winning Advertising Executive from scratch, highlighting key sections and how to effectively showcase your skills in Digital Advertising, Social Media Marketing, Search Engine Optimization (SEO), and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Digital Advertising
+- Social Media Marketing
+- Search Engine Optimization (SEO)
+- Google Ads Management
+- Content Marketing
+- Email Marketing
+#resume
 #AdvertisingExecutiveResume #AdvertisingExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19564,16 +19564,16 @@
       <c r="L319" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Legislator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Legislator from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services", "Community Outreach", "Legislative Research", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services"
-- "Community Outreach"
-- "Legislative Research"
-- "Policy Analysis"
-- "Public Speaking"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Legislator from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services, Community Outreach, Legislative Research, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services
+- Community Outreach
+- Legislative Research
+- Policy Analysis
+- Public Speaking
+- Negotiation
+#resume
 #LegislatorResume #Legislator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19624,16 +19624,16 @@
       <c r="L320" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Campaign Planning", "Media Buying", "Budget Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Campaign Planning"
-- "Media Buying"
-- "Budget Management"
-- "Team Leadership"
-- "Data Analysis"
-- "Creative Development"]
-#Hashtags
+Watch as we build a job-winning Advertising Manager from scratch, highlighting key sections and how to effectively showcase your skills in Campaign Planning, Media Buying, Budget Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Campaign Planning
+- Media Buying
+- Budget Management
+- Team Leadership
+- Data Analysis
+- Creative Development
+#resume
 #AdvertisingManagerResume #AdvertisingManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19684,16 +19684,16 @@
       <c r="L321" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Member of Congress? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Member of Congress from scratch, highlighting key sections and how to effectively showcase your skills in ["Policy Analysis", "Legislative Drafting", "Constituent Services", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Policy Analysis"
-- "Legislative Drafting"
-- "Constituent Services"
-- "Public Speaking"
-- "Media Relations"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Member of Congress from scratch, highlighting key sections and how to effectively showcase your skills in Policy Analysis, Legislative Drafting, Constituent Services, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Policy Analysis
+- Legislative Drafting
+- Constituent Services
+- Public Speaking
+- Media Relations
+- Negotiation
+#resume
 #MemberOfCongressResume #MemberOfCongress #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19744,16 +19744,16 @@
       <c r="L322" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Operations Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Operations Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Ad Exchange Platforms", "Data Analytics and Reporting", "Campaign Optimization", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Ad Exchange Platforms"
-- "Data Analytics and Reporting"
-- "Campaign Optimization"
-- "Supply Side Platforms (SSPs)"
-- "Demand Side Platforms (DSPs)"
-- "Yield Management"]
-#Hashtags
+Watch as we build a job-winning Advertising Operations Manager from scratch, highlighting key sections and how to effectively showcase your skills in Ad Exchange Platforms, Data Analytics and Reporting, Campaign Optimization, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Ad Exchange Platforms
+- Data Analytics and Reporting
+- Campaign Optimization
+- Supply Side Platforms (SSPs)
+- Demand Side Platforms (DSPs)
+- Yield Management
+#resume
 #AdvertisingOperationsManagerResume #AdvertisingOperationsManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19804,16 +19804,16 @@
       <c r="L323" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Customer Relationship Management", "Sales Prospecting", "Negotiation", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Customer Relationship Management"
-- "Sales Prospecting"
-- "Negotiation"
-- "Communication"
-- "Interpersonal Skills"
-- "Problem Solving"]
-#Hashtags
+Watch as we build a job-winning Representative from scratch, highlighting key sections and how to effectively showcase your skills in Customer Relationship Management, Sales Prospecting, Negotiation, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Customer Relationship Management
+- Sales Prospecting
+- Negotiation
+- Communication
+- Interpersonal Skills
+- Problem Solving
+#resume
 #RepresentativeResume #Representative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19864,16 +19864,16 @@
       <c r="L324" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Sales Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Sales Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Salesforce", "Microsoft Excel", "Google Analytics", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Salesforce"
-- "Microsoft Excel"
-- "Google Analytics"
-- "Digital Advertising"
-- "Media Planning"
-- "Negotiation"]
-#Hashtags
+Watch as we build a job-winning Advertising Sales Manager from scratch, highlighting key sections and how to effectively showcase your skills in Salesforce, Microsoft Excel, Google Analytics, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Salesforce
+- Microsoft Excel
+- Google Analytics
+- Digital Advertising
+- Media Planning
+- Negotiation
+#resume
 #AdvertisingSalesManagerResume #AdvertisingSalesManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19924,16 +19924,16 @@
       <c r="L325" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Selectman? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Selectman from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services", "Budget Management", "Policy Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services"
-- "Budget Management"
-- "Policy Development"
-- "Community Engagement"
-- "Intergovernmental Relations"
-- "Public Speaking"]
-#Hashtags
+Watch as we build a job-winning Selectman from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services, Budget Management, Policy Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services
+- Budget Management
+- Policy Development
+- Community Engagement
+- Intergovernmental Relations
+- Public Speaking
+#resume
 #SelectmanResume #Selectman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19984,16 +19984,16 @@
       <c r="L326" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Sales Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Sales Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Cold Calling", "Negotiation", "Sales Prospecting", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Cold Calling"
-- "Negotiation"
-- "Sales Prospecting"
-- "Advertising Analytics"
-- "Digital Marketing"
-- "Market Research"]
-#Hashtags
+Watch as we build a job-winning Advertising Sales Representative from scratch, highlighting key sections and how to effectively showcase your skills in Cold Calling, Negotiation, Sales Prospecting, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Cold Calling
+- Negotiation
+- Sales Prospecting
+- Advertising Analytics
+- Digital Marketing
+- Market Research
+#resume
 #AdvertisingSalesRepresentativeResume #AdvertisingSalesRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20044,16 +20044,16 @@
       <c r="L327" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Senator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Senator from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services Management", "Legislative Policy Analysis", "Budget and Appropriations", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services Management"
-- "Legislative Policy Analysis"
-- "Budget and Appropriations"
-- "Speechwriting and Public Speaking"
-- "Committee Work and Leadership"
-- "Constituent Advocacy"]
-#Hashtags
+Watch as we build a job-winning Senator from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services Management, Legislative Policy Analysis, Budget and Appropriations, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services Management
+- Legislative Policy Analysis
+- Budget and Appropriations
+- Speechwriting and Public Speaking
+- Committee Work and Leadership
+- Constituent Advocacy
+#resume
 #SenatorResume #Senator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20104,16 +20104,16 @@
       <c r="L328" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Advertising Vice President? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Advertising Vice President from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Creative Direction", "Brand Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Creative Direction"
-- "Brand Management"
-- "Media Planning"
-- "Audience Analysis"
-- "Digital Advertising"]
-#Hashtags
+Watch as we build a job-winning Advertising Vice President from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Creative Direction, Brand Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Creative Direction
+- Brand Management
+- Media Planning
+- Audience Analysis
+- Digital Advertising
+#resume
 #AdvertisingVicePresidentResume #AdvertisingVicePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20164,16 +20164,16 @@
       <c r="L329" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Tribal Council Member? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Tribal Council Member from scratch, highlighting key sections and how to effectively showcase your skills in ["Budget Management", "Policy Development", "Conflict Resolution", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Budget Management"
-- "Policy Development"
-- "Conflict Resolution"
-- "Stakeholder Engagement"
-- "Community Outreach"
-- "Strategic Planning"]
-#Hashtags
+Watch as we build a job-winning Tribal Council Member from scratch, highlighting key sections and how to effectively showcase your skills in Budget Management, Policy Development, Conflict Resolution, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Budget Management
+- Policy Development
+- Conflict Resolution
+- Stakeholder Engagement
+- Community Outreach
+- Strategic Planning
+#resume
 #TribalCouncilMemberResume #TribalCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20224,16 +20224,16 @@
       <c r="L330" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Art Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Art Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Art Direction", "UX Design", "Visual Design", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Art Direction"
-- "UX Design"
-- "Visual Design"
-- "Typography"
-- "Composition"
-- "Color Theory"]
-#Hashtags
+Watch as we build a job-winning Art Director from scratch, highlighting key sections and how to effectively showcase your skills in Art Direction, UX Design, Visual Design, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Art Direction
+- UX Design
+- Visual Design
+- Typography
+- Composition
+- Color Theory
+#resume
 #ArtDirectorResume #ArtDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20284,16 +20284,16 @@
       <c r="L331" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Tribal Delegate? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Tribal Delegate from scratch, highlighting key sections and how to effectively showcase your skills in ["Community Building", "Cultural Resource Management", "Economic Development", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Community Building"
-- "Cultural Resource Management"
-- "Economic Development"
-- "Environmental Protection"
-- "Federal Indian Law"
-- "Government Relations"]
-#Hashtags
+Watch as we build a job-winning Tribal Delegate from scratch, highlighting key sections and how to effectively showcase your skills in Community Building, Cultural Resource Management, Economic Development, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Community Building
+- Cultural Resource Management
+- Economic Development
+- Environmental Protection
+- Federal Indian Law
+- Government Relations
+#resume
 #TribalDelegateResume #TribalDelegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20344,16 +20344,16 @@
       <c r="L332" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Brand Manager? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Brand Manager from scratch, highlighting key sections and how to effectively showcase your skills in ["Brand Strategy Development", "Marketing Communications", "Brand Identity Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Brand Strategy Development"
-- "Marketing Communications"
-- "Brand Identity Management"
-- "Target Audience Analysis"
-- "Product Development"
-- "Brand Positioning"]
-#Hashtags
+Watch as we build a job-winning Brand Manager from scratch, highlighting key sections and how to effectively showcase your skills in Brand Strategy Development, Marketing Communications, Brand Identity Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Brand Strategy Development
+- Marketing Communications
+- Brand Identity Management
+- Target Audience Analysis
+- Product Development
+- Brand Positioning
+#resume
 #BrandManagerResume #BrandManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20404,16 +20404,16 @@
       <c r="L333" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect U.S. Representative? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning U.S. Representative from scratch, highlighting key sections and how to effectively showcase your skills in ["Legislative Expertise", "Constituent Service", "Public speaking", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Legislative Expertise"
-- "Constituent Service"
-- "Public speaking"
-- "Media relations"
-- "Campaign Management"
-- "Policy Analysis"]
-#Hashtags
+Watch as we build a job-winning U.S. Representative from scratch, highlighting key sections and how to effectively showcase your skills in Legislative Expertise, Constituent Service, Public speaking, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Legislative Expertise
+- Constituent Service
+- Public speaking
+- Media relations
+- Campaign Management
+- Policy Analysis
+#resume
 #USRepresentativeResume #USRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20464,16 +20464,16 @@
       <c r="L334" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Campaign Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Campaign Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Email Marketing", "Social Media Marketing", "Campaign Planning and Execution", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Email Marketing"
-- "Social Media Marketing"
-- "Campaign Planning and Execution"
-- "Data Analysis and Reporting"
-- "Budget Management"
-- "Project Management"]
-#Hashtags
+Watch as we build a job-winning Campaign Director from scratch, highlighting key sections and how to effectively showcase your skills in Email Marketing, Social Media Marketing, Campaign Planning and Execution, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Email Marketing
+- Social Media Marketing
+- Campaign Planning and Execution
+- Data Analysis and Reporting
+- Budget Management
+- Project Management
+#resume
 #CampaignDirectorResume #CampaignDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20524,16 +20524,16 @@
       <c r="L335" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect U.S. Senator? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning U.S. Senator from scratch, highlighting key sections and how to effectively showcase your skills in ["Constituent Services Management", "Legislative Research and Analysis", "Committee Leadership", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Constituent Services Management"
-- "Legislative Research and Analysis"
-- "Committee Leadership"
-- "Policy Development and Implementation"
-- "Budgetary Management"
-- "Media Relations and Communications"]
-#Hashtags
+Watch as we build a job-winning U.S. Senator from scratch, highlighting key sections and how to effectively showcase your skills in Constituent Services Management, Legislative Research and Analysis, Committee Leadership, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Constituent Services Management
+- Legislative Research and Analysis
+- Committee Leadership
+- Policy Development and Implementation
+- Budgetary Management
+- Media Relations and Communications
+#resume
 #USSenatorResume #USSenator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20584,16 +20584,16 @@
       <c r="L336" t="inlineStr">
         <is>
           <t xml:space="preserve">Struggling to write the perfect Account Director? This quick video shows you how to create a professional resume in minutes using ResumeGemini!
-Watch as we build a job-winning Account Director from scratch, highlighting key sections and how to effectively showcase your skills in ["Strategic Planning", "Client Relationship Management", "Sales Management", and more.
-✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
-Key skills covered in this resume:
-- ["Strategic Planning"
-- "Client Relationship Management"
-- "Sales Management"
-- "Budget Management"
-- "Marketing and Advertising"
-- "Team Leadership"]
-#Hashtags
+Watch as we build a job-winning Account Director from scratch, highlighting key sections and how to effectively showcase your skills in Strategic Planning, Client Relationship Management, Sales Management, and more.
+✨ Ready to build your own? Visit ResumeGemini now and create your perfect resume for FREE: https://www.resumegemini.com
+Key skills covered in this resume:
+- Strategic Planning
+- Client Relationship Management
+- Sales Management
+- Budget Management
+- Marketing and Advertising
+- Team Leadership
+#resume
 #AccountDirectorResume #AccountDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:

--- a/assets/SEOVideos.xlsx
+++ b/assets/SEOVideos.xlsx
@@ -541,7 +541,7 @@
 - Pest and Disease Control
 - Soil and Water Management
 - Farm Management
-#resume
+#Resume
 #AgriculturalServicesDirectorResume #AgriculturalServicesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -551,7 +551,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>agricultural services director resume,how to make a agricultural services director resume,director level resume,["Agronomy","Crop Production","Livestock Management","Pest and Disease Control","Soil and Water Management","Farm Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>agricultural services director resume,how to make a agricultural services director resume,director level resume,Agronomy,Crop Production,Livestock Management,Pest and Disease Control,Soil and Water Management,Farm Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
 - Pest and Disease Control
 - Soil and Water Management
 - Farm Management
-#resume
+#Resume
 #AgriculturalServicesDirectorResume #AgriculturalServicesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>agricultural services director resume,how to make a agricultural services director resume,director level resume,["Agronomy","Crop Production","Livestock Management","Pest and Disease Control","Soil and Water Management","Farm Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>agricultural services director resume,how to make a agricultural services director resume,director level resume,Agronomy,Crop Production,Livestock Management,Pest and Disease Control,Soil and Water Management,Farm Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
 - Client Advocacy
 - Crisis Intervention
 - Group Therapy Facilitation
-#resume
+#Resume
 #AlcoholAndDrugAbuseAssistanceProgramAdministratorResume #AlcoholAndDrugAbuseAssistanceProgramAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -671,7 +671,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>alcohol and drug abuse assistance program administrator resume,how to make a alcohol and drug abuse assistance program administrator resume,["Substance Use Disorder Assessment","Treatment Planning","Case Management","Client Advocacy","Crisis Intervention","Group Therapy Facilitation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>alcohol and drug abuse assistance program administrator resume,how to make a alcohol and drug abuse assistance program administrator resume,Substance Use Disorder Assessment,Treatment Planning,Case Management,Client Advocacy,Crisis Intervention,Group Therapy Facilitation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
 - Grant Writing and Administration
 - Strategic Planning for Arts Organizations
 - Arts Advocacy and Policy Development
-#resume
+#Resume
 #ArtsAndHumanitiesCouncilDirectorResume #ArtsAndHumanitiesCouncilDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -731,7 +731,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>arts and humanities council director resume,how to make a arts and humanities council director resume,director level resume,["Arts Program Management","Cultural Event Coordination","Arts Education Development","Grant Writing and Administration","Strategic Planning for Arts Organizations","Arts Advocacy and Policy Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>arts and humanities council director resume,how to make a arts and humanities council director resume,director level resume,Arts Program Management,Cultural Event Coordination,Arts Education Development,Grant Writing and Administration,Strategic Planning for Arts Organizations,Arts Advocacy and Policy Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
 - Bread Scoring
 - Sourdough Culture Management
 - Food Safety and Sanitation
-#resume
+#Resume
 #BakeryManagerResume #BakeryManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -791,7 +791,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bakery manager resume,how to make a bakery manager resume,management resume,["Baking Techniques","Yeast Handling","Dough Preparation","Bread Scoring","Sourdough Culture Management","Food Safety and Sanitation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>bakery manager resume,how to make a bakery manager resume,management resume,Baking Techniques,Yeast Handling,Dough Preparation,Bread Scoring,Sourdough Culture Management,Food Safety and Sanitation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
 - Business Development
 - Customer Relationship Management
 - Leadership and Motivation
-#resume
+#Resume
 #BankPresidentResume #BankPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -851,7 +851,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bank president resume,how to make a bank president resume,["Strategic Planning","Financial Management","Risk Management","Business Development","Customer Relationship Management","Leadership and Motivation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>bank president resume,how to make a bank president resume,Strategic Planning,Financial Management,Risk Management,Business Development,Customer Relationship Management,Leadership and Motivation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
 - Manuscript Evaluation
 - Book Development
 - Project Management
-#resume
+#Resume
 #BookPublisherResume #BookPublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -911,7 +911,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>book publisher resume,how to make a book publisher resume,["Proofreading","Copyediting","Acquisition","Manuscript Evaluation","Book Development","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>book publisher resume,how to make a book publisher resume,Proofreading,Copyediting,Acquisition,Manuscript Evaluation,Book Development,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
 - Investment Strategies
 - Regulatory Compliance
 - Client Relationship Management
-#resume
+#Resume
 #BrokerageOfficeManagerResume #BrokerageOfficeManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -971,7 +971,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>brokerage office manager resume,how to make a brokerage office manager resume,management resume,["Brokerage Operations","Financial Analysis","Risk Management","Investment Strategies","Regulatory Compliance","Client Relationship Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>brokerage office manager resume,how to make a brokerage office manager resume,management resume,Brokerage Operations,Financial Analysis,Risk Management,Investment Strategies,Regulatory Compliance,Client Relationship Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
 - Department Supervision
 - Employee Discipline and Performance Management
 - Financial Planning and Forecasting
-#resume
+#Resume
 #BureauChiefResume #BureauChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1031,7 +1031,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bureau chief resume,how to make a bureau chief resume,["Budget Management","Contract Creation and Negotiation","Data Analysis and Interpretation","Department Supervision","Employee Discipline and Performance Management","Financial Planning and Forecasting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>bureau chief resume,how to make a bureau chief resume,Budget Management,Contract Creation and Negotiation,Data Analysis and Interpretation,Department Supervision,Employee Discipline and Performance Management,Financial Planning and Forecasting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
 - Client Relationship Management
 - Sales Forecasting
 - Business Development
-#resume
+#Resume
 #BusinessDevelopmentOfficerResume #BusinessDevelopmentOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1091,7 +1091,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>business development officer resume,how to make a business development officer resume,["Market Analysis","Competitive Intelligence","Strategic Planning","Client Relationship Management","Sales Forecasting","Business Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business development officer resume,how to make a business development officer resume,Market Analysis,Competitive Intelligence,Strategic Planning,Client Relationship Management,Sales Forecasting,Business Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
 - Business Analysis
 - Project Management
 - Risk Management
-#resume
+#Resume
 #BusinessEnterpriseOfficerResume #BusinessEnterpriseOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1151,7 +1151,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>business enterprise officer resume,how to make a business enterprise officer resume,["Financial Acumen","Business Process Improvement","Strategic Planning","Business Analysis","Project Management","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business enterprise officer resume,how to make a business enterprise officer resume,Financial Acumen,Business Process Improvement,Strategic Planning,Business Analysis,Project Management,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
 - Marketing and Sales
 - Business Development
 - Team Leadership
-#resume
+#Resume
 #BusinessExecutiveResume #BusinessExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>business executive resume,how to make a business executive resume,["Strategic Planning","Financial Analysis","Operations Management","Marketing and Sales","Business Development","Team Leadership"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business executive resume,how to make a business executive resume,Strategic Planning,Financial Analysis,Operations Management,Marketing and Sales,Business Development,Team Leadership,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
 - Grief Counseling
 - Human Remains Disposal
 - Monument Installation
-#resume
+#Resume
 #CemeteryManagerResume #CemeteryManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1271,7 +1271,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>cemetery manager resume,how to make a cemetery manager resume,management resume,["Burial Site Planning","Funeral Planning","Grave Maintenance","Grief Counseling","Human Remains Disposal","Monument Installation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>cemetery manager resume,how to make a cemetery manager resume,management resume,Burial Site Planning,Funeral Planning,Grave Maintenance,Grief Counseling,Human Remains Disposal,Monument Installation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
 - Risk Management
 - Leadership
 - Communication
-#resume
+#Resume
 #ChairmanResume #Chairman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1331,7 +1331,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>chairman resume,how to make a chairman resume,["Strategic Planning","Board Management","Corporate Governance","Risk Management","Leadership","Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chairman resume,how to make a chairman resume,Strategic Planning,Board Management,Corporate Governance,Risk Management,Leadership,Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
 - Faculty Development
 - Student Success
 - Alumni Relations
-#resume
+#Resume
 #ChancellorResume #Chancellor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>chancellor resume,how to make a chancellor resume,["Academic Leadership","Strategic Planning","Budget Management","Faculty Development","Student Success","Alumni Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chancellor resume,how to make a chancellor resume,Academic Leadership,Strategic Planning,Budget Management,Faculty Development,Student Success,Alumni Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
 - Human Resources Management
 - Compliance Management
 - Risk Management
-#resume
+#Resume
 #ChiefAdministrativeOfficerResume #ChiefAdministrativeOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>chief administrative officer resume,how to make a chief administrative officer resume,["Strategic Planning","Budget Management","Operations Management","Human Resources Management","Compliance Management","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief administrative officer resume,how to make a chief administrative officer resume,Strategic Planning,Budget Management,Operations Management,Human Resources Management,Compliance Management,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
 - Supplier Diversity Program Implementation
 - Cross-Cultural Communication and Sensitivity
 - Organizational Culture Transformation
-#resume
+#Resume
 #ChiefDiversityOfficerCdoResume #ChiefDiversityOfficerCdo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1513,7 +1513,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>chief diversity officer (cdo) resume,how to make a chief diversity officer (cdo) resume,["Diversity,Equity,and Inclusion (DEI) Strategy Development","Unconscious Bias Training and Education","Employee Resource Group (ERG) Management","Supplier Diversity Program Implementation","Cross-Cultural Communication and Sensitivity","Organizational Culture Transformation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
+          <t>chief diversity officer (cdo) resume,how to make a chief diversity officer (cdo) resume,Diversity,Equity,and Inclusion (DEI) Strategy Development,Unconscious Bias Training and Education,Employee Resource Group (ERG) Management,Supplier Diversity Program Implementation,Cross-Cultural Communication and Sensitivity,Organizational Culture Transformation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
 - Stakeholder Management
 - Risk Management
 - Business Development
-#resume
+#Resume
 #ChiefExecutiveOfficerCeoResume #ChiefExecutiveOfficerCeo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1573,7 +1573,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>chief executive officer (ceo) resume,how to make a chief executive officer (ceo) resume,["Strategic Planning","Financial Management","Team Leadership","Stakeholder Management","Risk Management","Business Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief executive officer (ceo) resume,how to make a chief executive officer (ceo) resume,Strategic Planning,Financial Management,Team Leadership,Stakeholder Management,Risk Management,Business Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
 - Risk Management
 - Strategic Planning
 - Treasury Management
-#resume
+#Resume
 #ChiefFinancialOfficerCfoResume #ChiefFinancialOfficerCfo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>chief financial officer (cfo) resume,how to make a chief financial officer (cfo) resume,["Financial Planning and Analysis","Budgeting and Forecasting","Financial Reporting and Compliance","Risk Management","Strategic Planning","Treasury Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief financial officer (cfo) resume,how to make a chief financial officer (cfo) resume,Financial Planning and Analysis,Budgeting and Forecasting,Financial Reporting and Compliance,Risk Management,Strategic Planning,Treasury Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
 - Business Model Innovation
 - Product Development
 - Intellectual Property Management
-#resume
+#Resume
 #ChiefInnovationOfficerResume #ChiefInnovationOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1693,7 +1693,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>chief innovation officer resume,how to make a chief innovation officer resume,["Innovation Management","Disruptive Technology Analysis","Trend Forecasting","Business Model Innovation","Product Development","Intellectual Property Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief innovation officer resume,how to make a chief innovation officer resume,Innovation Management,Disruptive Technology Analysis,Trend Forecasting,Business Model Innovation,Product Development,Intellectual Property Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
 - Patient Care Delivery
 - Quality Improvement
 - Budget Management
-#resume
+#Resume
 #ChiefNursingOfficerResume #ChiefNursingOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>chief nursing officer resume,how to make a chief nursing officer resume,["Leadership and Management","Strategic Planning and Execution","Operational Management","Patient Care Delivery","Quality Improvement","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief nursing officer resume,how to make a chief nursing officer resume,Leadership and Management,Strategic Planning and Execution,Operational Management,Patient Care Delivery,Quality Improvement,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
 - Team Leadership
 - Process Improvement
 - Risk Management
-#resume
+#Resume
 #ChiefOperatingOfficerCooResume #ChiefOperatingOfficerCoo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>chief operating officer (coo) resume,how to make a chief operating officer (coo) resume,["Strategic Planning","Operational Management","Financial Management","Team Leadership","Process Improvement","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief operating officer (coo) resume,how to make a chief operating officer (coo) resume,Strategic Planning,Operational Management,Financial Management,Team Leadership,Process Improvement,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
 - Fire Prevention
 - Building Evacuation Procedures
 - CPR and First Aid
-#resume
+#Resume
 #ChiefWardenResume #ChiefWarden #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>chief warden resume,how to make a chief warden resume,["Fire Safety Management","Emergency Response Planning","Incident Command Systems (ICS)","Fire Prevention","Building Evacuation Procedures","CPR and First Aid"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief warden resume,how to make a chief warden resume,Fire Safety Management,Emergency Response Planning,Incident Command Systems (ICS),Fire Prevention,Building Evacuation Procedures,CPR and First Aid,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
 - Grant Writing
 - Economic Development
 - Government Relations
-#resume
+#Resume
 #CityAdministratorResume #CityAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1933,7 +1933,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>city administrator resume,how to make a city administrator resume,["Budget Management","Financial Planning","Strategic Planning","Grant Writing","Economic Development","Government Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city administrator resume,how to make a city administrator resume,Budget Management,Financial Planning,Strategic Planning,Grant Writing,Economic Development,Government Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
 - Public Policy Analysis
 - Stakeholder Engagement
 - Human Resource Management
-#resume
+#Resume
 #CityManagerResume #CityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -1993,7 +1993,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>city manager resume,how to make a city manager resume,management resume,["Strategic Planning","Budget Management","Infrastructure Planning and Development","Public Policy Analysis","Stakeholder Engagement","Human Resource Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city manager resume,how to make a city manager resume,management resume,Strategic Planning,Budget Management,Infrastructure Planning and Development,Public Policy Analysis,Stakeholder Engagement,Human Resource Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
 - Budgeting and Cost Control
 - Scheduling and Planning
 - Safety Management
-#resume
+#Resume
 #CitySuperintendentResume #CitySuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2053,7 +2053,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>city superintendent resume,how to make a city superintendent resume,["Project Management","Construction Management","Contract Management","Budgeting and Cost Control","Scheduling and Planning","Safety Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city superintendent resume,how to make a city superintendent resume,Project Management,Construction Management,Contract Management,Budgeting and Cost Control,Scheduling and Planning,Safety Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
 - School Finance
 - Data Analysis
 - Stakeholder Relations
-#resume
+#Resume
 #CitySuperintendentOfSchoolsResume #CitySuperintendentOfSchools #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2113,7 +2113,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>city superintendent of schools resume,how to make a city superintendent of schools resume,["Strategic Planning","Curriculum Development","Instructional Leadership","School Finance","Data Analysis","Stakeholder Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city superintendent of schools resume,how to make a city superintendent of schools resume,Strategic Planning,Curriculum Development,Instructional Leadership,School Finance,Data Analysis,Stakeholder Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
 - Policy Analysis
 - Performance Management
 - Community Engagement
-#resume
+#Resume
 #CitySupervisorResume #CitySupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2173,7 +2173,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>city supervisor resume,how to make a city supervisor resume,["Budget Management","Strategic Planning","Public Administration","Policy Analysis","Performance Management","Community Engagement"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city supervisor resume,how to make a city supervisor resume,Budget Management,Strategic Planning,Public Administration,Policy Analysis,Performance Management,Community Engagement,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
 - Program Development and Implementation
 - Trauma-Informed Care
 - Supervision and Leadership
-#resume
+#Resume
 #ClassificationAndTreatmentDirectorResume #ClassificationAndTreatmentDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2233,7 +2233,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>classification and treatment director resume,how to make a classification and treatment director resume,director level resume,["Statistical Analysis","Risk Assessment and Management","Case Management","Program Development and Implementation","Trauma-Informed Care","Supervision and Leadership"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>classification and treatment director resume,how to make a classification and treatment director resume,director level resume,Statistical Analysis,Risk Assessment and Management,Case Management,Program Development and Implementation,Trauma-Informed Care,Supervision and Leadership,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
 - Fundraising
 - Alumni Relations
 - Crisis Management
-#resume
+#Resume
 #CollegePresidentResume #CollegePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2293,7 +2293,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>college president resume,how to make a college president resume,["Strategic Planning","Budget Management","Board Governance","Fundraising","Alumni Relations","Crisis Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>college president resume,how to make a college president resume,Strategic Planning,Budget Management,Board Governance,Fundraising,Alumni Relations,Crisis Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
 - Budget and Financial Planning
 - Strategic Planning and Leadership
 - Public Policy Analysis and Advocacy
-#resume
+#Resume
 #CommissionerOfInternalRevenueResume #CommissionerOfInternalRevenue #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2353,7 +2353,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>commissioner of internal revenue resume,how to make a commissioner of internal revenue resume,["Tax Policy Development and Implementation","Tax Law Interpretation and Enforcement","Tax Administration and Management","Budget and Financial Planning","Strategic Planning and Leadership","Public Policy Analysis and Advocacy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>commissioner of internal revenue resume,how to make a commissioner of internal revenue resume,Tax Policy Development and Implementation,Tax Law Interpretation and Enforcement,Tax Administration and Management,Budget and Financial Planning,Strategic Planning and Leadership,Public Policy Analysis and Advocacy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
 - Grant Writing
 - Needs Assessment
 - Public Speaking
-#resume
+#Resume
 #CommunityServicesAndHealthEducationOfficerResume #CommunityServicesAndHealthEducationOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>community services and health education officer resume,how to make a community services and health education officer resume,["Program Planning","Community Assessment","Health Education","Grant Writing","Needs Assessment","Public Speaking"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>community services and health education officer resume,how to make a community services and health education officer resume,Program Planning,Community Assessment,Health Education,Grant Writing,Needs Assessment,Public Speaking,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
 - Internal Controls
 - Ethics and Compliance
 - Data Privacy
-#resume
+#Resume
 #ComplianceDirectorResume #ComplianceDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>compliance director resume,how to make a compliance director resume,director level resume,["Risk Management","Compliance Auditing","Regulatory Compliance","Internal Controls","Ethics and Compliance","Data Privacy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>compliance director resume,how to make a compliance director resume,director level resume,Risk Management,Compliance Auditing,Regulatory Compliance,Internal Controls,Ethics and Compliance,Data Privacy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
 - Land Use Planning
 - Water Resource Management
 - Forestry
-#resume
+#Resume
 #ConservationOfResourcesCommissionerResume #ConservationOfResourcesCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2533,7 +2533,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>conservation of resources commissioner resume,how to make a conservation of resources commissioner resume,["Environmental Resource Management","Natural Resource Conservation","Ecosystem Management","Land Use Planning","Water Resource Management","Forestry"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>conservation of resources commissioner resume,how to make a conservation of resources commissioner resume,Environmental Resource Management,Natural Resource Conservation,Ecosystem Management,Land Use Planning,Water Resource Management,Forestry,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
 - Regulatory Compliance
 - Product Development
 - Customer Experience Management
-#resume
+#Resume
 #ConsumerAffairsDirectorResume #ConsumerAffairsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>consumer affairs director resume,how to make a consumer affairs director resume,director level resume,["Consumer Advocacy","Dispute Resolution","Complaint Handling","Regulatory Compliance","Product Development","Customer Experience Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>consumer affairs director resume,how to make a consumer affairs director resume,director level resume,Consumer Advocacy,Dispute Resolution,Complaint Handling,Regulatory Compliance,Product Development,Customer Experience Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
 - Regulatory Compliance
 - Product Development
 - Customer Experience Management
-#resume
+#Resume
 #ConsumerAffairsDirectorResume #ConsumerAffairsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>consumer affairs director resume,how to make a consumer affairs director resume,director level resume,["Consumer Advocacy","Dispute Resolution","Complaint Handling","Regulatory Compliance","Product Development","Customer Experience Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>consumer affairs director resume,how to make a consumer affairs director resume,director level resume,Consumer Advocacy,Dispute Resolution,Complaint Handling,Regulatory Compliance,Product Development,Customer Experience Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
 - Event Planning
 - Office Management
 - Vendor Management
-#resume
+#Resume
 #CorporateAdministratorResume #CorporateAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2713,7 +2713,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>corporate administrator resume,how to make a corporate administrator resume,["Administrative Support","Meeting Management","Travel Coordination","Event Planning","Office Management","Vendor Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>corporate administrator resume,how to make a corporate administrator resume,Administrative Support,Meeting Management,Travel Coordination,Event Planning,Office Management,Vendor Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
 - Corporate Governance
 - Risk Management
 - Business Development
-#resume
+#Resume
 #CorporateExecutiveResume #CorporateExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2773,7 +2773,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>corporate executive resume,how to make a corporate executive resume,["Strategic Planning","Financial Analysis","Leadership and Management","Corporate Governance","Risk Management","Business Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>corporate executive resume,how to make a corporate executive resume,Strategic Planning,Financial Analysis,Leadership and Management,Corporate Governance,Risk Management,Business Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
 - Business Analysis
 - Corporate Governance
 - Risk Management
-#resume
+#Resume
 #CorporateManagerResume #CorporateManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2833,7 +2833,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>corporate manager resume,how to make a corporate manager resume,management resume,["Financial Modeling","Project Management","Strategic Planning","Business Analysis","Corporate Governance","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>corporate manager resume,how to make a corporate manager resume,management resume,Financial Modeling,Project Management,Strategic Planning,Business Analysis,Corporate Governance,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
 - Board Relations
 - Corporate Finance
 - Regulatory Compliance
-#resume
+#Resume
 #CorporateOfficerResume #CorporateOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2893,7 +2893,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>corporate officer resume,how to make a corporate officer resume,["Corporate Governance","Legal Compliance","Strategic Planning","Board Relations","Corporate Finance","Regulatory Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>corporate officer resume,how to make a corporate officer resume,Corporate Governance,Legal Compliance,Strategic Planning,Board Relations,Corporate Finance,Regulatory Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
 - Market Research
 - Risk Management
 - Scenario Planning
-#resume
+#Resume
 #CorporatePlannerResume #CorporatePlanner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -2953,7 +2953,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>corporate planner resume,how to make a corporate planner resume,["Strategic Planning","Business Analysis","Financial Modeling","Market Research","Risk Management","Scenario Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>corporate planner resume,how to make a corporate planner resume,Strategic Planning,Business Analysis,Financial Modeling,Market Research,Risk Management,Scenario Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
 - Fiduciary Duties
 - Corporate Law
 - Business Ethics
-#resume
+#Resume
 #CorporationOfficerResume #CorporationOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3013,7 +3013,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>corporation officer resume,how to make a corporation officer resume,["Corporate Governance","Compliance Management","Risk Management","Fiduciary Duties","Corporate Law","Business Ethics"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>corporation officer resume,how to make a corporation officer resume,Corporate Governance,Compliance Management,Risk Management,Fiduciary Duties,Corporate Law,Business Ethics,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
 - Program Evaluation
 - Budget Management
 - Staff Development
-#resume
+#Resume
 #CorrectionalAgencyDirectorResume #CorrectionalAgencyDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3073,7 +3073,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>correctional agency director resume,how to make a correctional agency director resume,director level resume,["Correctional Management","Offender Rehabilitation","Policy Development","Program Evaluation","Budget Management","Staff Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>correctional agency director resume,how to make a correctional agency director resume,director level resume,Correctional Management,Offender Rehabilitation,Policy Development,Program Evaluation,Budget Management,Staff Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
 - Aging Services Policy
 - Community Collaboration
 - Budgeting and Financial Management
-#resume
+#Resume
 #CouncilOnAgingDirectorResume #CouncilOnAgingDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3133,7 +3133,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>council on aging director resume,how to make a council on aging director resume,director level resume,["Program Management","Advocacy and Outreach","Geriatric Care Management","Aging Services Policy","Community Collaboration","Budgeting and Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>council on aging director resume,how to make a council on aging director resume,director level resume,Program Management,Advocacy and Outreach,Geriatric Care Management,Aging Services Policy,Community Collaboration,Budgeting and Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
 - Leadership
 - Negotiation
 - Public Policy
-#resume
+#Resume
 #CountyAdministratorResume #CountyAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3193,7 +3193,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>county administrator resume,how to make a county administrator resume,["Budget Analysis","Human Resources Management","Project Management","Leadership","Negotiation","Public Policy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>county administrator resume,how to make a county administrator resume,Budget Analysis,Human Resources Management,Project Management,Leadership,Negotiation,Public Policy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
 - Economic Development
 - Community Engagement and Outreach
 - Negotiation and Conflict Resolution
-#resume
+#Resume
 #CountyCommissionerResume #CountyCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3253,7 +3253,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>county commissioner resume,how to make a county commissioner resume,["Public Policy Analysis","Budgeting and Financial Management","Land Use Planning and Zoning","Economic Development","Community Engagement and Outreach","Negotiation and Conflict Resolution"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>county commissioner resume,how to make a county commissioner resume,Public Policy Analysis,Budgeting and Financial Management,Land Use Planning and Zoning,Economic Development,Community Engagement and Outreach,Negotiation and Conflict Resolution,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
 - Budget Management
 - School Law
 - Community Relations
-#resume
+#Resume
 #CountySuperintendentOfSchoolsResume #CountySuperintendentOfSchools #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3313,7 +3313,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>county superintendent of schools resume,how to make a county superintendent of schools resume,["Educational Leadership","Curriculum Development","Student Assessment","Budget Management","School Law","Community Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>county superintendent of schools resume,how to make a county superintendent of schools resume,Educational Leadership,Curriculum Development,Student Assessment,Budget Management,School Law,Community Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
 - Environmental Management
 - Financial Management
 - Government Relations
-#resume
+#Resume
 #CountySupervisorResume #CountySupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3373,7 +3373,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>county supervisor resume,how to make a county supervisor resume,["Budget Management","County Planning and Development","Economic Development","Environmental Management","Financial Management","Government Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>county supervisor resume,how to make a county supervisor resume,Budget Management,County Planning and Development,Economic Development,Environmental Management,Financial Management,Government Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
 - Customer Relationship Management
 - Problem Solving
 - Communication Skills
-#resume
+#Resume
 #DepartmentManagerResume #DepartmentManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3433,7 +3433,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>department manager resume,how to make a department manager resume,management resume,["Inventory Management","Budgeting and Forecasting","Team Management","Customer Relationship Management","Problem Solving","Communication Skills"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>department manager resume,how to make a department manager resume,management resume,Inventory Management,Budgeting and Forecasting,Team Management,Customer Relationship Management,Problem Solving,Communication Skills,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
 - Budgeting
 - Staff Management
 - Sales Management
-#resume
+#Resume
 #DepartmentStoreManagerResume #DepartmentStoreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3493,7 +3493,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>department store manager resume,how to make a department store manager resume,management resume,["Inventory Management","Sales Forecasting","Customer Relationship Management (CRM)","Budgeting","Staff Management","Sales Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>department store manager resume,how to make a department store manager resume,management resume,Inventory Management,Sales Forecasting,Customer Relationship Management (CRM),Budgeting,Staff Management,Sales Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
 - Enforcement and Investigations
 - Leadership and Management
 - Strategic Planning
-#resume
+#Resume
 #DeputyDistrictCustomsDirectorResume #DeputyDistrictCustomsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3553,7 +3553,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>deputy district customs director resume,how to make a deputy district customs director resume,director level resume,["Customs Regulations and Procedures","International Trade Law","Risk Assessment and Mitigation","Enforcement and Investigations","Leadership and Management","Strategic Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>deputy district customs director resume,how to make a deputy district customs director resume,director level resume,Customs Regulations and Procedures,International Trade Law,Risk Assessment and Mitigation,Enforcement and Investigations,Leadership and Management,Strategic Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
 - Risk Management
 - Insurance Policy Development
 - Insurance Market Analysis
-#resume
+#Resume
 #DeputyInsuranceCommissionerResume #DeputyInsuranceCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>deputy insurance commissioner resume,how to make a deputy insurance commissioner resume,["Insurance Law","Regulatory Compliance","Financial Analysis","Risk Management","Insurance Policy Development","Insurance Market Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>deputy insurance commissioner resume,how to make a deputy insurance commissioner resume,Insurance Law,Regulatory Compliance,Financial Analysis,Risk Management,Insurance Policy Development,Insurance Market Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
 - Project Management
 - Budget Management
 - Legal and Ethical Considerations
-#resume
+#Resume
 #DirectorOfVitalStatisticsResume #DirectorOfVitalStatistics #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3673,7 +3673,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>director of vital statistics resume,how to make a director of vital statistics resume,director level resume,["Data Management","Vital Records Administration","Statistical Analysis","Project Management","Budget Management","Legal and Ethical Considerations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>director of vital statistics resume,how to make a director of vital statistics resume,director level resume,Data Management,Vital Records Administration,Statistical Analysis,Project Management,Budget Management,Legal and Ethical Considerations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
 - Duty Collection and Accounting
 - Customs Enforcement and Investigations
 - Import/Export Compliance
-#resume
+#Resume
 #DistrictCustomsDirectorResume #DistrictCustomsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3733,7 +3733,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>district customs director resume,how to make a district customs director resume,director level resume,["Customs Regulations and Procedures","Tariff Classification","Valuation of Merchandise","Duty Collection and Accounting","Customs Enforcement and Investigations","Import/Export Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>district customs director resume,how to make a district customs director resume,director level resume,Customs Regulations and Procedures,Tariff Classification,Valuation of Merchandise,Duty Collection and Accounting,Customs Enforcement and Investigations,Import/Export Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
 - Grant Writing and Management
 - Data Analysis and Reporting
 - Project Management
-#resume
+#Resume
 #EconomicDevelopmentCoordinatorResume #EconomicDevelopmentCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3793,7 +3793,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>economic development coordinator resume,how to make a economic development coordinator resume,["Economic Development Strategy Development","Business Attraction and Retention","Community Outreach and Engagement","Grant Writing and Management","Data Analysis and Reporting","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>economic development coordinator resume,how to make a economic development coordinator resume,Economic Development Strategy Development,Business Attraction and Retention,Community Outreach and Engagement,Grant Writing and Management,Data Analysis and Reporting,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
 - Budget Management
 - Stakeholder Relations
 - Curriculum Development
-#resume
+#Resume
 #EducationalInstitutionPresidentResume #EducationalInstitutionPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>educational institution president resume,how to make a educational institution president resume,["Strategic Planning","Institutional Management","Academic Leadership","Budget Management","Stakeholder Relations","Curriculum Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>educational institution president resume,how to make a educational institution president resume,Strategic Planning,Institutional Management,Academic Leadership,Budget Management,Stakeholder Relations,Curriculum Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
 - Poll Worker Training
 - Absentee Voting Management
 - Early Voting Procedures
-#resume
+#Resume
 #ElectionAssistantResume #ElectionAssistant #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3913,7 +3913,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>election assistant resume,how to make a election assistant resume,["Ballot Processing","Voter Registration","Election Canvassing","Poll Worker Training","Absentee Voting Management","Early Voting Procedures"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>election assistant resume,how to make a election assistant resume,Ballot Processing,Voter Registration,Election Canvassing,Poll Worker Training,Absentee Voting Management,Early Voting Procedures,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
 - Data Analysis
 - Forecasting
 - Project Management
-#resume
+#Resume
 #EmploymentResearchAndPlanningDirectorResume #EmploymentResearchAndPlanningDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -3973,7 +3973,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>employment research and planning director resume,how to make a employment research and planning director resume,director level resume,["Labor Market Analysis","Workforce Planning","Strategic Planning","Data Analysis","Forecasting","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>employment research and planning director resume,how to make a employment research and planning director resume,director level resume,Labor Market Analysis,Workforce Planning,Strategic Planning,Data Analysis,Forecasting,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
 - Resume Writing
 - Interview Preparation
 - Labor Market Analysis
-#resume
+#Resume
 #EmploymentServicesDirectorResume #EmploymentServicesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4033,7 +4033,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>employment services director resume,how to make a employment services director resume,director level resume,["Job Development","Case Management","Career Counseling","Resume Writing","Interview Preparation","Labor Market Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>employment services director resume,how to make a employment services director resume,director level resume,Job Development,Case Management,Career Counseling,Resume Writing,Interview Preparation,Labor Market Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
 - Soil and Sediment Sampling and Analysis
 - GIS Mapping and Analysis
 - Environmental Regulations and Compliance
-#resume
+#Resume
 #EnvironmentalAnalystResume #EnvironmentalAnalyst #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>environmental analyst resume,how to make a environmental analyst resume,data science resume,business analyst resume,["Environmental Impact Assessment","Air Quality Monitoring and Modeling","Water Quality Assessment and Management","Soil and Sediment Sampling and Analysis","GIS Mapping and Analysis","Environmental Regulations and Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>environmental analyst resume,how to make a environmental analyst resume,data science resume,business analyst resume,Environmental Impact Assessment,Air Quality Monitoring and Modeling,Water Quality Assessment and Management,Soil and Sediment Sampling and Analysis,GIS Mapping and Analysis,Environmental Regulations and Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
 - Calendar Management
 - Communication
 - Conflict Resolution
-#resume
+#Resume
 #ExecutiveAdministratorResume #ExecutiveAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4153,7 +4153,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>executive administrator resume,how to make a executive administrator resume,["Administrative Support","Board and Executive Relations","Budget Management","Calendar Management","Communication","Conflict Resolution"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>executive administrator resume,how to make a executive administrator resume,Administrative Support,Board and Executive Relations,Budget Management,Calendar Management,Communication,Conflict Resolution,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
 - Team Leadership and Management
 - Program Development and Evaluation
 - Community Engagement
-#resume
+#Resume
 #ExecutiveDirectorResume #ExecutiveDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4213,7 +4213,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>executive director resume,how to make a executive director resume,director level resume,["Strategic Planning","Board and Governance","Fundraising and Grant Writing","Team Leadership and Management","Program Development and Evaluation","Community Engagement"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>executive director resume,how to make a executive director resume,director level resume,Strategic Planning,Board and Governance,Fundraising and Grant Writing,Team Leadership and Management,Program Development and Evaluation,Community Engagement,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
 - Business Development
 - Team Leadership
 - Risk Management
-#resume
+#Resume
 #ExecutiveVicePresidentEvpResume #ExecutiveVicePresidentEvp #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4273,7 +4273,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>executive vice president (evp) resume,how to make a executive vice president (evp) resume,["Strategic Planning","Financial Management","Operations Management","Business Development","Team Leadership","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>executive vice president (evp) resume,how to make a executive vice president (evp) resume,Strategic Planning,Financial Management,Operations Management,Business Development,Team Leadership,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
 - Microsoft Office Suite (Word
 - Excel
 - PowerPoint)
-#resume
+#Resume
 #FederalAidCoordinatorResume #FederalAidCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4335,7 +4335,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>federal aid coordinator resume,how to make a federal aid coordinator resume,["Higher Education Act (HEA) and Title IV Regulations","Federal Student Aid (FSA) Handbook","Customer Service and Communication Skills","Data Analysis and Reporting","Problem Solving and Decision Making","Microsoft Office Suite (Word,Excel,PowerPoint)"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>federal aid coordinator resume,how to make a federal aid coordinator resume,Higher Education Act (HEA) and Title IV Regulations,Federal Student Aid (FSA) Handbook,Customer Service and Communication Skills,Data Analysis and Reporting,Problem Solving and Decision Making,Microsoft Office Suite (Word,Excel,PowerPoint),how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
 - Market Analysis
 - Negotiation
 - Team Building
-#resume
+#Resume
 #FieldRepresentativesDirectorResume #FieldRepresentativesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4395,7 +4395,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>field representatives director resume,how to make a field representatives director resume,director level resume,["Sales Management","Sales Training","Performance Management","Market Analysis","Negotiation","Team Building"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>field representatives director resume,how to make a field representatives director resume,director level resume,Sales Management,Sales Training,Performance Management,Market Analysis,Negotiation,Team Building,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
 - Compliance Management
 - Corporate Finance
 - Investment Management
-#resume
+#Resume
 #FinancialInstitutionPresidentResume #FinancialInstitutionPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4455,7 +4455,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>financial institution president resume,how to make a financial institution president resume,["Strategic Planning","Financial Modeling","Risk Management","Compliance Management","Corporate Finance","Investment Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>financial institution president resume,how to make a financial institution president resume,Strategic Planning,Financial Modeling,Risk Management,Compliance Management,Corporate Finance,Investment Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
 - Captive Insurance Management
 - Financial Reporting and Disclosure
 - Strategic Planning and Forecasting
-#resume
+#Resume
 #FinancialResponsibilityDivisionDirectorResume #FinancialResponsibilityDivisionDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4515,7 +4515,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>financial responsibility division director resume,how to make a financial responsibility division director resume,director level resume,["Financial Responsibility Analysis","Solvency and Risk Management","Insurance Regulations","Captive Insurance Management","Financial Reporting and Disclosure","Strategic Planning and Forecasting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>financial responsibility division director resume,how to make a financial responsibility division director resume,director level resume,Financial Responsibility Analysis,Solvency and Risk Management,Insurance Regulations,Captive Insurance Management,Financial Reporting and Disclosure,Strategic Planning and Forecasting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
 - Financial Reporting and Analysis
 - Auditing and Compliance
 - Cash Management
-#resume
+#Resume
 #FinancialSecretaryResume #FinancialSecretary #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4575,7 +4575,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>financial secretary resume,how to make a financial secretary resume,["Financial Accounting","Operations Management","Budgeting and Forecasting","Financial Reporting and Analysis","Auditing and Compliance","Cash Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>financial secretary resume,how to make a financial secretary resume,Financial Accounting,Operations Management,Budgeting and Forecasting,Financial Reporting and Analysis,Auditing and Compliance,Cash Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
 - Budget Management and Fiscal Planning
 - Public Relations and Community Engagement
 - Incident Command and Control
-#resume
+#Resume
 #FireChiefResume #FireChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4635,7 +4635,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>fire chief resume,how to make a fire chief resume,["Firefighting Tactics and Strategy","Emergency Management and Disaster Response","Personnel Management and Leadership","Budget Management and Fiscal Planning","Public Relations and Community Engagement","Incident Command and Control"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>fire chief resume,how to make a fire chief resume,Firefighting Tactics and Strategy,Emergency Management and Disaster Response,Personnel Management and Leadership,Budget Management and Fiscal Planning,Public Relations and Community Engagement,Incident Command and Control,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
 - Enforcement and Compliance
 - Budget Management
 - Personnel Management
-#resume
+#Resume
 #FisheryDivisionChiefResume #FisheryDivisionChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4695,7 +4695,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>fishery division chief resume,how to make a fishery division chief resume,["Fish Population Assessment","Fishery Management Plan Development","Fish Habitat Assessment","Enforcement and Compliance","Budget Management","Personnel Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>fishery division chief resume,how to make a fishery division chief resume,Fish Population Assessment,Fishery Management Plan Development,Fish Habitat Assessment,Enforcement and Compliance,Budget Management,Personnel Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
 - Cross-Cultural Communication and Etiquette
 - Public Speaking and Presentation Skills
 - Conflict Resolution and Mediation
-#resume
+#Resume
 #ForeignDiplomatResume #ForeignDiplomat #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4755,7 +4755,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>foreign diplomat resume,how to make a foreign diplomat resume,["Diplomatic Protocol Management","International Relations Analysis","Political Negotiations and Dialogue","Cross-Cultural Communication and Etiquette","Public Speaking and Presentation Skills","Conflict Resolution and Mediation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>foreign diplomat resume,how to make a foreign diplomat resume,Diplomatic Protocol Management,International Relations Analysis,Political Negotiations and Dialogue,Cross-Cultural Communication and Etiquette,Public Speaking and Presentation Skills,Conflict Resolution and Mediation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
 - Public Diplomacy and Advocacy
 - Management and Supervision
 - Written and Verbal Communication
-#resume
+#Resume
 #ForeignServiceOfficerResume #ForeignServiceOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4815,7 +4815,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>foreign service officer resume,how to make a foreign service officer resume,["Cross-Cultural Communication","Negotiation and Conflict Resolution","Policy Analysis and Development","Public Diplomacy and Advocacy","Management and Supervision","Written and Verbal Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>foreign service officer resume,how to make a foreign service officer resume,Cross-Cultural Communication,Negotiation and Conflict Resolution,Policy Analysis and Development,Public Diplomacy and Advocacy,Management and Supervision,Written and Verbal Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
 - Nonprofit Management
 - Budgeting and Finance
 - Board Development
-#resume
+#Resume
 #FoundationDirectorResume #FoundationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4875,7 +4875,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>foundation director resume,how to make a foundation director resume,director level resume,["Grant Writing","Donor Cultivation","Capital Campaign Management","Nonprofit Management","Budgeting and Finance","Board Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>foundation director resume,how to make a foundation director resume,director level resume,Grant Writing,Donor Cultivation,Capital Campaign Management,Nonprofit Management,Budgeting and Finance,Board Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
 - Human Capital Management
 - Performance Management
 - Risk Management
-#resume
+#Resume
 #GovernmentServiceExecutiveResume #GovernmentServiceExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4935,7 +4935,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>government service executive resume,how to make a government service executive resume,["Strategic Planning","Public Policy Analysis","Budget Management","Human Capital Management","Performance Management","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>government service executive resume,how to make a government service executive resume,Strategic Planning,Public Policy Analysis,Budget Management,Human Capital Management,Performance Management,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
 - Constituent Relations
 - Stakeholder Management
 - Crisis Management
-#resume
+#Resume
 #GovernorResume #Governor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -4995,7 +4995,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>governor resume,how to make a governor resume,["Policy Development","Budget Management","Public Speaking","Constituent Relations","Stakeholder Management","Crisis Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>governor resume,how to make a governor resume,Policy Development,Budget Management,Public Speaking,Constituent Relations,Stakeholder Management,Crisis Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
 - Navigational Safety
 - Emergency Response
 - Environmental Compliance
-#resume
+#Resume
 #HarborMasterResume #HarborMaster #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5055,7 +5055,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>harbor master resume,how to make a harbor master resume,["Vessel Traffic Management","Marina Management","Port Operations","Navigational Safety","Emergency Response","Environmental Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>harbor master resume,how to make a harbor master resume,Vessel Traffic Management,Marina Management,Port Operations,Navigational Safety,Emergency Response,Environmental Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
 - Health Policy Analysis
 - Community Health Assessment
 - Health Communication
-#resume
+#Resume
 #HealthCommissionerResume #HealthCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5115,7 +5115,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>health commissioner resume,how to make a health commissioner resume,["Environmental Health","Public Health Administration","Epidemiology","Health Policy Analysis","Community Health Assessment","Health Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>health commissioner resume,how to make a health commissioner resume,Environmental Health,Public Health Administration,Epidemiology,Health Policy Analysis,Community Health Assessment,Health Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5165,7 @@
 - Project Management
 - Budget Analysis
 - Personnel Management
-#resume
+#Resume
 #HighwayCommissionerResume #HighwayCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5175,7 +5175,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>highway commissioner resume,how to make a highway commissioner resume,["Highway Construction Management","Roadway Design","Traffic Engineering","Project Management","Budget Analysis","Personnel Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>highway commissioner resume,how to make a highway commissioner resume,Highway Construction Management,Roadway Design,Traffic Engineering,Project Management,Budget Analysis,Personnel Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
 - Property Management
 - Resident Screening
 - Work Order Management
-#resume
+#Resume
 #HousingManagementOfficerResume #HousingManagementOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5235,7 +5235,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>housing management officer resume,how to make a housing management officer resume,["Public Housing Laws","Rent Collection","Housing Inspection","Property Management","Resident Screening","Work Order Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>housing management officer resume,how to make a housing management officer resume,Public Housing Laws,Rent Collection,Housing Inspection,Property Management,Resident Screening,Work Order Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
 - Program Development and Implementation
 - Stakeholder Engagement and Relationship Management
 - Advocacy and Policy Development
-#resume
+#Resume
 #InstitutionDirectorResume #InstitutionDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5295,7 +5295,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>institution director resume,how to make a institution director resume,director level resume,["Strategic Planning","Grant Writing and Management","Budget Management and Financial Planning","Program Development and Implementation","Stakeholder Engagement and Relationship Management","Advocacy and Policy Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>institution director resume,how to make a institution director resume,director level resume,Strategic Planning,Grant Writing and Management,Budget Management and Financial Planning,Program Development and Implementation,Stakeholder Engagement and Relationship Management,Advocacy and Policy Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
 - Ratemaking Analysis
 - Reserve Analysis
 - Risk Management
-#resume
+#Resume
 #InsuranceCommissionerResume #InsuranceCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5355,7 +5355,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>insurance commissioner resume,how to make a insurance commissioner resume,["Actuarial Analysis","Financial Modeling","Insurance Regulatory Knowledge","Ratemaking Analysis","Reserve Analysis","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>insurance commissioner resume,how to make a insurance commissioner resume,Actuarial Analysis,Financial Modeling,Insurance Regulatory Knowledge,Ratemaking Analysis,Reserve Analysis,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
 - Financial Accounting Standards Board (FASB)
 - International Accounting Standards Board (IASB)
 - Foreign Currency Translation
-#resume
+#Resume
 #InternationalAccountingUserRepresentativeResume #InternationalAccountingUserRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>international accounting user representative resume,how to make a international accounting user representative resume,["International Financial Reporting Standards (IFRS)","Generally Accepted Accounting Principles (GAAP)","International Accounting Standards (IAS)","Financial Accounting Standards Board (FASB)","International Accounting Standards Board (IASB)","Foreign Currency Translation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder</t>
+          <t>international accounting user representative resume,how to make a international accounting user representative resume,International Financial Reporting Standards (IFRS),Generally Accepted Accounting Principles (GAAP),International Accounting Standards (IAS),Financial Accounting Standards Board (FASB),International Accounting Standards Board (IASB),Foreign Currency Translation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
 - GIS Mapping and Analysis
 - Data Analysis and Reporting
 - Customer Service and Outreach
-#resume
+#Resume
 #IrrigationTaxAssessorCollectorResume #IrrigationTaxAssessorCollector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5475,7 +5475,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>irrigation tax assessor-collector resume,how to make a irrigation tax assessor-collector resume,["Agricultural Water Management","Irrigation Tax Assessment and Collection","Property Valuation","GIS Mapping and Analysis","Data Analysis and Reporting","Customer Service and Outreach"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>irrigation tax assessor-collector resume,how to make a irrigation tax assessor-collector resume,Agricultural Water Management,Irrigation Tax Assessment and Collection,Property Valuation,GIS Mapping and Analysis,Data Analysis and Reporting,Customer Service and Outreach,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
 - Drafting and Interpreting Labor Agreements
 - Enforcing Labor Standards
 - Inspection of Workplaces
-#resume
+#Resume
 #LaborCommissionerResume #LaborCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5535,7 +5535,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>labor commissioner resume,how to make a labor commissioner resume,["Federal and State Labor Laws","Conducting Labor Investigations","Mediating Labor Disputes","Drafting and Interpreting Labor Agreements","Enforcing Labor Standards","Inspection of Workplaces"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>labor commissioner resume,how to make a labor commissioner resume,Federal and State Labor Laws,Conducting Labor Investigations,Mediating Labor Disputes,Drafting and Interpreting Labor Agreements,Enforcing Labor Standards,Inspection of Workplaces,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
 - Human Resources Management
 - Employee Management
 - Performance Management
-#resume
+#Resume
 #LaborStandardsDirectorResume #LaborStandardsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5595,7 +5595,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>labor standards director resume,how to make a labor standards director resume,director level resume,["Wage and Hour Law Compliance","Payroll and Benefits Management","Labor Relations","Human Resources Management","Employee Management","Performance Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>labor standards director resume,how to make a labor standards director resume,director level resume,Wage and Hour Law Compliance,Payroll and Benefits Management,Labor Relations,Human Resources Management,Employee Management,Performance Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
 - Crisis Management
 - Criminal Investigation
 - Emergency Preparedness
-#resume
+#Resume
 #LawEnforcementDirectorResume #LawEnforcementDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5655,7 +5655,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>law enforcement director resume,how to make a law enforcement director resume,director level resume,["Strategic Planning","Budget Management","Community Policing","Crisis Management","Criminal Investigation","Emergency Preparedness"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>law enforcement director resume,how to make a law enforcement director resume,director level resume,Strategic Planning,Budget Management,Community Policing,Crisis Management,Criminal Investigation,Emergency Preparedness,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
 - License and Permit Management
 - Records Management
 - Customer Relationship Management
-#resume
+#Resume
 #LicensingAndRegistrationDirectorResume #LicensingAndRegistrationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5715,7 +5715,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>licensing and registration director resume,how to make a licensing and registration director resume,director level resume,["Negotiation","Policy Analysis","Regulatory Compliance","License and Permit Management","Records Management","Customer Relationship Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>licensing and registration director resume,how to make a licensing and registration director resume,director level resume,Negotiation,Policy Analysis,Regulatory Compliance,License and Permit Management,Records Management,Customer Relationship Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
 - Economic Development Analysis
 - Emergency Preparedness Planning
 - Government Relations
-#resume
+#Resume
 #LieutenantGovernorResume #LieutenantGovernor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5775,7 +5775,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>lieutenant governor resume,how to make a lieutenant governor resume,["Budget Management","Constituent Services Management","Disaster Relief Coordination","Economic Development Analysis","Emergency Preparedness Planning","Government Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>lieutenant governor resume,how to make a lieutenant governor resume,Budget Management,Constituent Services Management,Disaster Relief Coordination,Economic Development Analysis,Emergency Preparedness Planning,Government Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
 - Enforcement and Investigation
 - Public Education and Outreach
 - Budget Management
-#resume
+#Resume
 #LiquorCommissionerResume #LiquorCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5835,7 +5835,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>liquor commissioner resume,how to make a liquor commissioner resume,["Alcohol Beverage Control","Regulatory Compliance","Licensing and Permitting","Enforcement and Investigation","Public Education and Outreach","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>liquor commissioner resume,how to make a liquor commissioner resume,Alcohol Beverage Control,Regulatory Compliance,Licensing and Permitting,Enforcement and Investigation,Public Education and Outreach,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
 - Customer Relationship Management (CRM)
 - Employee Management
 - Inventory Management
-#resume
+#Resume
 #LiquorStoresAndAgenciesSupervisorResume #LiquorStoresAndAgenciesSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5895,7 +5895,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>liquor stores and agencies supervisor resume,how to make a liquor stores and agencies supervisor resume,["Alcohol Management","Beverage Management","Budgeting and Planning","Customer Relationship Management (CRM)","Employee Management","Inventory Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>liquor stores and agencies supervisor resume,how to make a liquor stores and agencies supervisor resume,Alcohol Management,Beverage Management,Budgeting and Planning,Customer Relationship Management (CRM),Employee Management,Inventory Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
 - Strategic Planning
 - Infrastructure Development
 - Land Use Planning
-#resume
+#Resume
 #MayorResume #Mayor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -5955,7 +5955,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>mayor resume,how to make a mayor resume,["Public Policy Analysis","Budget Management","Community Engagement","Strategic Planning","Infrastructure Development","Land Use Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>mayor resume,how to make a mayor resume,Public Policy Analysis,Budget Management,Community Engagement,Strategic Planning,Infrastructure Development,Land Use Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
 - Media Planning and Buying
 - Data Analysis and Reporting
 - Project Management
-#resume
+#Resume
 #MediaExecutiveResume #MediaExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6015,7 +6015,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>media executive resume,how to make a media executive resume,["Digital Marketing","Social Media Marketing","Content Marketing","Media Planning and Buying","Data Analysis and Reporting","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>media executive resume,how to make a media executive resume,Digital Marketing,Social Media Marketing,Content Marketing,Media Planning and Buying,Data Analysis and Reporting,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
 - Risk Management
 - Compliance
 - Communication
-#resume
+#Resume
 #MedicalFacilitiesSectionDirectorResume #MedicalFacilitiesSectionDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6075,7 +6075,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>medical facilities section director resume,how to make a medical facilities section director resume,director level resume,["Strategic Planning","Budget Management","Operations Management","Risk Management","Compliance","Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>medical facilities section director resume,how to make a medical facilities section director resume,director level resume,Strategic Planning,Budget Management,Operations Management,Risk Management,Compliance,Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
 - Music Marketing and Promotion
 - Digital Music Distribution
 - Music Publishing
-#resume
+#Resume
 #MusicExecutiveResume #MusicExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6135,7 +6135,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>music executive resume,how to make a music executive resume,["Music Licensing and Negotiation","Artist Development and Management","Concert and Tour Management","Music Marketing and Promotion","Digital Music Distribution","Music Publishing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>music executive resume,how to make a music executive resume,Music Licensing and Negotiation,Artist Development and Management,Concert and Tour Management,Music Marketing and Promotion,Digital Music Distribution,Music Publishing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
 - Royalty Audit
 - Digital Distribution
 - International Music Publishing
-#resume
+#Resume
 #MusicPublisherResume #MusicPublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6195,7 +6195,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>music publisher resume,how to make a music publisher resume,["Music Publishing","Copyright Law","Contract Negotiation","Royalty Audit","Digital Distribution","International Music Publishing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>music publisher resume,how to make a music publisher resume,Music Publishing,Copyright Law,Contract Negotiation,Royalty Audit,Digital Distribution,International Music Publishing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
 - News Writing
 - Feature Writing
 - Reporting
-#resume
+#Resume
 #NewspaperPublisherResume #NewspaperPublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6255,7 +6255,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>newspaper publisher resume,how to make a newspaper publisher resume,["Newspaper Editing","Page Layout","Copyediting","News Writing","Feature Writing","Reporting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>newspaper publisher resume,how to make a newspaper publisher resume,Newspaper Editing,Page Layout,Copyediting,News Writing,Feature Writing,Reporting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
 - Program Development
 - Stakeholder Engagement
 - Policy Analysis
-#resume
+#Resume
 #NonprofitDirectorResume #NonprofitDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6315,7 +6315,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>nonprofit director resume,how to make a nonprofit director resume,director level resume,["Nonprofit Management","Board Governance","Fundraising Strategy","Program Development","Stakeholder Engagement","Policy Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>nonprofit director resume,how to make a nonprofit director resume,director level resume,Nonprofit Management,Board Governance,Fundraising Strategy,Program Development,Stakeholder Engagement,Policy Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
 - Donor Relations
 - Volunteer Management
 - Grant Writing
-#resume
+#Resume
 #NonprofitManagerResume #NonprofitManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6375,7 +6375,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>nonprofit manager resume,how to make a nonprofit manager resume,management resume,["Strategic Planning","Fundraising","Program Management","Donor Relations","Volunteer Management","Grant Writing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>nonprofit manager resume,how to make a nonprofit manager resume,management resume,Strategic Planning,Fundraising,Program Management,Donor Relations,Volunteer Management,Grant Writing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
 - Operations Planning
 - Quality Management
 - Business Strategy
-#resume
+#Resume
 #OperationsVicePresidentResume #OperationsVicePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6435,7 +6435,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>operations vice president resume,how to make a operations vice president resume,["Process Optimization","Supply Chain Management","Inventory Control","Operations Planning","Quality Management","Business Strategy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>operations vice president resume,how to make a operations vice president resume,Process Optimization,Supply Chain Management,Inventory Control,Operations Planning,Quality Management,Business Strategy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
 - Project Management
 - Staff Supervision
 - GIS Mapping and Analysis
-#resume
+#Resume
 #ParkSuperintendentResume #ParkSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6495,7 +6495,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>park superintendent resume,how to make a park superintendent resume,["Environmental Planning","Natural Resource Management","Budget Management","Project Management","Staff Supervision","GIS Mapping and Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>park superintendent resume,how to make a park superintendent resume,Environmental Planning,Natural Resource Management,Budget Management,Project Management,Staff Supervision,GIS Mapping and Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
 - Budget Management
 - Personnel Management
 - Community Relations
-#resume
+#Resume
 #PoliceCommissionerResume #PoliceCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6555,7 +6555,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>police commissioner resume,how to make a police commissioner resume,["Emergency Management","Public Safety Planning","Law Enforcement Operations","Budget Management","Personnel Management","Community Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>police commissioner resume,how to make a police commissioner resume,Emergency Management,Public Safety Planning,Law Enforcement Operations,Budget Management,Personnel Management,Community Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
 - Regulatory Compliance and Interpretation
 - Policy Evaluation and Monitoring
 - Project Management and Coordination
-#resume
+#Resume
 #PolicyAdvisorResume #PolicyAdvisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6615,7 +6615,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>policy advisor resume,how to make a policy advisor resume,["Policy Analysis and Development","Legislative Research and Monitoring","Stakeholder Engagement and Outreach","Regulatory Compliance and Interpretation","Policy Evaluation and Monitoring","Project Management and Coordination"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>policy advisor resume,how to make a policy advisor resume,Policy Analysis and Development,Legislative Research and Monitoring,Stakeholder Engagement and Outreach,Regulatory Compliance and Interpretation,Policy Evaluation and Monitoring,Project Management and Coordination,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
 - Policy Advocacy
 - Legislative Drafting
 - Risk Assessment
-#resume
+#Resume
 #PolicyOfficerResume #PolicyOfficer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6675,7 +6675,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>policy officer resume,how to make a policy officer resume,["Policy Analysis","Regulatory Research","Stakeholder Engagement","Policy Advocacy","Legislative Drafting","Risk Assessment"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>policy officer resume,how to make a policy officer resume,Policy Analysis,Regulatory Research,Stakeholder Engagement,Policy Advocacy,Legislative Drafting,Risk Assessment,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
 - Business Development
 - Financial Management
 - Risk Management
-#resume
+#Resume
 #PresidentResume #President #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6735,7 +6735,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>president resume,how to make a president resume,["Strategic Planning","Leadership","Team Management","Business Development","Financial Management","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>president resume,how to make a president resume,Strategic Planning,Leadership,Team Management,Business Development,Financial Management,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
 - Risk Management
 - Project Management
 - Team Leadership
-#resume
+#Resume
 #PrivateSectorExecutiveResume #PrivateSectorExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6795,7 +6795,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>private sector executive resume,how to make a private sector executive resume,["Strategic Planning","Business Development","Financial Analysis","Risk Management","Project Management","Team Leadership"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>private sector executive resume,how to make a private sector executive resume,Strategic Planning,Business Development,Financial Analysis,Risk Management,Project Management,Team Leadership,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
 - Grant Management
 - Data Analysis
 - Reporting
-#resume
+#Resume
 #ProgramAdministratorResume #ProgramAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6855,7 +6855,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>program administrator resume,how to make a program administrator resume,["Project Management","Budget Management","Stakeholder Management","Grant Management","Data Analysis","Reporting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>program administrator resume,how to make a program administrator resume,Project Management,Budget Management,Stakeholder Management,Grant Management,Data Analysis,Reporting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
 - Risk Management
 - Budget Management
 - Project Monitoring and Evaluation
-#resume
+#Resume
 #ProgramManagerResume #ProgramManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6915,7 +6915,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>program manager resume,how to make a program manager resume,management resume,["Agile Development","Program Planning","Stakeholder Management","Risk Management","Budget Management","Project Monitoring and Evaluation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>program manager resume,how to make a program manager resume,management resume,Agile Development,Program Planning,Stakeholder Management,Risk Management,Budget Management,Project Monitoring and Evaluation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
 - Environmental Health
 - Disaster Preparedness and Response
 - Health Policy Analysis
-#resume
+#Resume
 #PublicHealthDirectorResume #PublicHealthDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -6975,7 +6975,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>public health director resume,how to make a public health director resume,director level resume,["Public Health Program Management","Epidemic Intelligence","Health Equity and Social Justice","Environmental Health","Disaster Preparedness and Response","Health Policy Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>public health director resume,how to make a public health director resume,director level resume,Public Health Program Management,Epidemic Intelligence,Health Equity and Social Justice,Environmental Health,Disaster Preparedness and Response,Health Policy Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
 - Contract Administration
 - Environmental Compliance
 - Facility Maintenance Management
-#resume
+#Resume
 #PublicWorksCommissionerResume #PublicWorksCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7035,7 +7035,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>public works commissioner resume,how to make a public works commissioner resume,["Budgeting","Capital Project Management","Construction Management","Contract Administration","Environmental Compliance","Facility Maintenance Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>public works commissioner resume,how to make a public works commissioner resume,Budgeting,Capital Project Management,Construction Management,Contract Administration,Environmental Compliance,Facility Maintenance Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
 - Budget Management
 - Capital Improvement Planning
 - Stormwater Management
-#resume
+#Resume
 #PublicWorksDirectorResume #PublicWorksDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7095,7 +7095,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>public works director resume,how to make a public works director resume,director level resume,["GIS Mapping and Analysis","Construction Management","Project Planning and Execution","Budget Management","Capital Improvement Planning","Stormwater Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>public works director resume,how to make a public works director resume,director level resume,GIS Mapping and Analysis,Construction Management,Project Planning and Execution,Budget Management,Capital Improvement Planning,Stormwater Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
 - Regulatory Compliance
 - Accident Investigation
 - Public Speaking
-#resume
+#Resume
 #RailroadCommissionerResume #RailroadCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7155,7 +7155,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>railroad commissioner resume,how to make a railroad commissioner resume,["Railroad Operations","FRA Regulations","Railroad Safety","Regulatory Compliance","Accident Investigation","Public Speaking"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>railroad commissioner resume,how to make a railroad commissioner resume,Railroad Operations,FRA Regulations,Railroad Safety,Regulatory Compliance,Accident Investigation,Public Speaking,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
 - Event Coordination
 - Community Outreach
 - Budget Management
-#resume
+#Resume
 #RecreationSuperintendentResume #RecreationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7215,7 +7215,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>recreation superintendent resume,how to make a recreation superintendent resume,["Park Planning","Recreation Programming","Facility Management","Event Coordination","Community Outreach","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>recreation superintendent resume,how to make a recreation superintendent resume,Park Planning,Recreation Programming,Facility Management,Event Coordination,Community Outreach,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
 - Wildlife Monitoring
 - Human-Wildlife Conflict Management
 - Wildlife Habitat Assessment
-#resume
+#Resume
 #RegionalWildlifeAgentResume #RegionalWildlifeAgent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7275,7 +7275,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>regional wildlife agent resume,how to make a regional wildlife agent resume,["Wildlife Management","Conservation Biology","Wildlife Law Enforcement","Wildlife Monitoring","Human-Wildlife Conflict Management","Wildlife Habitat Assessment"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>regional wildlife agent resume,how to make a regional wildlife agent resume,Wildlife Management,Conservation Biology,Wildlife Law Enforcement,Wildlife Monitoring,Human-Wildlife Conflict Management,Wildlife Habitat Assessment,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
 - Inspection and Enforcement
 - Training and Development
 - Policy and Procedure Development
-#resume
+#Resume
 #RegulatedProgramManagerResume #RegulatedProgramManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7335,7 +7335,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>regulated program manager resume,how to make a regulated program manager resume,management resume,["Regulatory Compliance Management","Quality Assurance and Control","Risk Management and Mitigation","Inspection and Enforcement","Training and Development","Policy and Procedure Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>regulated program manager resume,how to make a regulated program manager resume,management resume,Regulatory Compliance Management,Quality Assurance and Control,Risk Management and Mitigation,Inspection and Enforcement,Training and Development,Policy and Procedure Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
 - Audit and Inspection
 - Policy Development
 - Regulatory Affairs
-#resume
+#Resume
 #RegulatoryAgencyDirectorResume #RegulatoryAgencyDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7395,7 +7395,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>regulatory agency director resume,how to make a regulatory agency director resume,director level resume,["Regulatory Compliance","Quality Assurance","Risk Management","Audit and Inspection","Policy Development","Regulatory Affairs"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>regulatory agency director resume,how to make a regulatory agency director resume,director level resume,Regulatory Compliance,Quality Assurance,Risk Management,Audit and Inspection,Policy Development,Regulatory Affairs,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
 - Medical Device Regulations
 - Pharmaceutical Regulations
 - Clinical Trial Regulations
-#resume
+#Resume
 #RegulatoryAnalystResume #RegulatoryAnalyst #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7455,7 +7455,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>regulatory analyst resume,how to make a regulatory analyst resume,data science resume,business analyst resume,["Regulatory Affairs","FDA Regulations","ICH Guidelines","Medical Device Regulations","Pharmaceutical Regulations","Clinical Trial Regulations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>regulatory analyst resume,how to make a regulatory analyst resume,data science resume,business analyst resume,Regulatory Affairs,FDA Regulations,ICH Guidelines,Medical Device Regulations,Pharmaceutical Regulations,Clinical Trial Regulations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
 - Conflict Resolution
 - Negotiation
 - Home Inspection
-#resume
+#Resume
 #RelocationCommissionerResume #RelocationCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7515,7 +7515,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>relocation commissioner resume,how to make a relocation commissioner resume,["Counseling and Support","Stress Management","Budget Management","Conflict Resolution","Negotiation","Home Inspection"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>relocation commissioner resume,how to make a relocation commissioner resume,Counseling and Support,Stress Management,Budget Management,Conflict Resolution,Negotiation,Home Inspection,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
 - Customer Relationship Management
 - Sales Forecasting
 - Budget Management
-#resume
+#Resume
 #RevenueDirectorResume #RevenueDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7575,7 +7575,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>revenue director resume,how to make a revenue director resume,director level resume,["Revenue Management","Pricing Strategy","Market Analysis","Customer Relationship Management","Sales Forecasting","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>revenue director resume,how to make a revenue director resume,director level resume,Revenue Management,Pricing Strategy,Market Analysis,Customer Relationship Management,Sales Forecasting,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
 - Team Leadership
 - Communication and Interpersonal Skills
 - Knowledge of Roadway Design and Construction Standards
-#resume
+#Resume
 #RoadCommissionerResume #RoadCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7635,7 +7635,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>road commissioner resume,how to make a road commissioner resume,["Road Construction and Maintenance","Budget Management","Project Management","Team Leadership","Communication and Interpersonal Skills","Knowledge of Roadway Design and Construction Standards"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>road commissioner resume,how to make a road commissioner resume,Road Construction and Maintenance,Budget Management,Project Management,Team Leadership,Communication and Interpersonal Skills,Knowledge of Roadway Design and Construction Standards,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
 - Bridge Inspection and Maintenance
 - Traffic Signalization and Control
 - Stormwater Management
-#resume
+#Resume
 #RoadsSupervisorResume #RoadsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7695,7 +7695,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>roads supervisor resume,how to make a roads supervisor resume,["Road Construction Management","Pavement Design and Analysis","Asphalt and Concrete Paving","Bridge Inspection and Maintenance","Traffic Signalization and Control","Stormwater Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>roads supervisor resume,how to make a roads supervisor resume,Road Construction Management,Pavement Design and Analysis,Asphalt and Concrete Paving,Bridge Inspection and Maintenance,Traffic Signalization and Control,Stormwater Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
 - Emergency Preparedness
 - Compliance Management
 - Employee Training
-#resume
+#Resume
 #SafetyCouncilDirectorResume #SafetyCouncilDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7755,7 +7755,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>safety council director resume,how to make a safety council director resume,director level resume,["Risk Assessment","Safety Management Systems","Accident Investigation","Emergency Preparedness","Compliance Management","Employee Training"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>safety council director resume,how to make a safety council director resume,director level resume,Risk Assessment,Safety Management Systems,Accident Investigation,Emergency Preparedness,Compliance Management,Employee Training,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
 - Environmental Compliance
 - Budget Management
 - Personnel Management
-#resume
+#Resume
 #SanitationSuperintendentResume #SanitationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7815,7 +7815,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>sanitation superintendent resume,how to make a sanitation superintendent resume,["Wastewater Treatment Plant Operations","Solid Waste Management","Water Quality Monitoring","Environmental Compliance","Budget Management","Personnel Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sanitation superintendent resume,how to make a sanitation superintendent resume,Wastewater Treatment Plant Operations,Solid Waste Management,Water Quality Monitoring,Environmental Compliance,Budget Management,Personnel Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
 - Collaboration withStakeholders
 - Negotiation and Conflict Resolution
 - Problem Solving
-#resume
+#Resume
 #SchoolCommissionerResume #SchoolCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7875,7 +7875,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>school commissioner resume,how to make a school commissioner resume,["Understanding of School Budgeting and Finance","Policy Development and Implementation","Leadership and Vision Setting","Collaboration withStakeholders","Negotiation and Conflict Resolution","Problem Solving"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>school commissioner resume,how to make a school commissioner resume,Understanding of School Budgeting and Finance,Policy Development and Implementation,Leadership and Vision Setting,Collaboration withStakeholders,Negotiation and Conflict Resolution,Problem Solving,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
 - Government Ethics Enforcement
 - Public Records Management
 - Legislative Drafting
-#resume
+#Resume
 #SecretaryOfStateResume #SecretaryOfState #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7935,7 +7935,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>secretary of state resume,how to make a secretary of state resume,["Election Administration","Voter Registration","Campaign Finance Regulation","Government Ethics Enforcement","Public Records Management","Legislative Drafting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>secretary of state resume,how to make a secretary of state resume,Election Administration,Voter Registration,Campaign Finance Regulation,Government Ethics Enforcement,Public Records Management,Legislative Drafting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
 - Software Testing
 - Microsoft Office Suite
 - Project Management
-#resume
+#Resume
 #SoftwarePublisherResume #SoftwarePublisher #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -7995,7 +7995,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>software publisher resume,how to make a software publisher resume,software engineer resume,IT resume,tech resume,["Software Development Lifecycle (SDLC)","Product Knowledge","Agile Software Development","Software Testing","Microsoft Office Suite","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>software publisher resume,how to make a software publisher resume,software engineer resume,IT resume,tech resume,Software Development Lifecycle (SDLC),Product Knowledge,Agile Software Development,Software Testing,Microsoft Office Suite,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
 - Mass Appraisal Techniques
 - Property Valuation
 - Data Analysis
-#resume
+#Resume
 #StateAssessedPropertiesDirectorResume #StateAssessedPropertiesDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>state assessed properties director resume,how to make a state assessed properties director resume,director level resume,["Property Appraisal","Tax Assessment","Property Tax Administration","Mass Appraisal Techniques","Property Valuation","Data Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>state assessed properties director resume,how to make a state assessed properties director resume,director level resume,Property Appraisal,Tax Assessment,Property Tax Administration,Mass Appraisal Techniques,Property Valuation,Data Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
 - Meeting Management
 - Records Management
 - Budget Management
-#resume
+#Resume
 #StateBoardOfNursingExecutiveSecretaryResume #StateBoardOfNursingExecutiveSecretary #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8115,7 +8115,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>state board of nursing executive secretary resume,how to make a state board of nursing executive secretary resume,["Nursing Law and Regulations","Board Policy Development","Disciplinary Process Management","Meeting Management","Records Management","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>state board of nursing executive secretary resume,how to make a state board of nursing executive secretary resume,Nursing Law and Regulations,Board Policy Development,Disciplinary Process Management,Meeting Management,Records Management,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
 - Stakeholder Engagement and Communication
 - Life Cycle Assessment
 - Environmental Policy and Regulation Compliance
-#resume
+#Resume
 #CorporateSustainabilityProcessManagerResume #CorporateSustainabilityProcessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8177,7 +8177,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>corporate sustainability process manager resume,how to make a corporate sustainability process manager resume,management resume,["Greenhouse Gas Emissions Reporting","Carbon Footprint Analysis","Sustainability Reporting Frameworks (GRI,SASB,TCFD)","Stakeholder Engagement and Communication","Life Cycle Assessment","Environmental Policy and Regulation Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
+          <t>corporate sustainability process manager resume,how to make a corporate sustainability process manager resume,management resume,Greenhouse Gas Emissions Reporting,Carbon Footprint Analysis,Sustainability Reporting Frameworks (GRI,SASB,TCFD),Stakeholder Engagement and Communication,Life Cycle Assessment,Environmental Policy and Regulation Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
 - School Finance
 - Student Assessment and Accountability
 - Teacher Professional Development
-#resume
+#Resume
 #StateSuperintendentOfPublicInstructionResume #StateSuperintendentOfPublicInstruction #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8237,7 +8237,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>state superintendent of public instruction resume,how to make a state superintendent of public instruction resume,["Education Policy Development","Strategic Planning","Curriculum Development","School Finance","Student Assessment and Accountability","Teacher Professional Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>state superintendent of public instruction resume,how to make a state superintendent of public instruction resume,Education Policy Development,Strategic Planning,Curriculum Development,School Finance,Student Assessment and Accountability,Teacher Professional Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
 - Educational Leadership
 - Teacher Evaluation
 - Data Analysis
-#resume
+#Resume
 #StateSuperintendentOfSchoolsResume #StateSuperintendentOfSchools #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8297,7 +8297,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>state superintendent of schools resume,how to make a state superintendent of schools resume,["Educational Policy Development","Curriculum Management","School Finance","Educational Leadership","Teacher Evaluation","Data Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>state superintendent of schools resume,how to make a state superintendent of schools resume,Educational Policy Development,Curriculum Management,School Finance,Educational Leadership,Teacher Evaluation,Data Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
 - Team Leadership
 - Problem Solving
 - Communication
-#resume
+#Resume
 #StoreManagerResume #StoreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8357,7 +8357,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>store manager resume,how to make a store manager resume,management resume,["Inventory Management","Customer Service","Sales and Marketing","Team Leadership","Problem Solving","Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>store manager resume,how to make a store manager resume,management resume,Inventory Management,Customer Service,Sales and Marketing,Team Leadership,Problem Solving,Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
 - Market Research
 - Competitive Analysis
 - Forecasting
-#resume
+#Resume
 #StrategicPlannerResume #StrategicPlanner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8417,7 +8417,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>strategic planner resume,how to make a strategic planner resume,["Environmental Scanning","Scenario Planning","SWOT Analysis","Market Research","Competitive Analysis","Forecasting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>strategic planner resume,how to make a strategic planner resume,Environmental Scanning,Scenario Planning,SWOT Analysis,Market Research,Competitive Analysis,Forecasting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
 - Delegation
 - Project Management
 - Communication
-#resume
+#Resume
 #SupervisorResume #Supervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8477,7 +8477,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>supervisor resume,how to make a supervisor resume,["Team Management","Conflict Resolution","Performance Management","Delegation","Project Management","Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>supervisor resume,how to make a supervisor resume,Team Management,Conflict Resolution,Performance Management,Delegation,Project Management,Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
 - Revenue Forecasting
 - Budget Management
 - Stakeholder Engagement
-#resume
+#Resume
 #TaxCommissionerResume #TaxCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>tax commissioner resume,how to make a tax commissioner resume,["Tax Law Interpretation","Tax Audit Techniques","Tax Policy Analysis","Revenue Forecasting","Budget Management","Stakeholder Engagement"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>tax commissioner resume,how to make a tax commissioner resume,Tax Law Interpretation,Tax Audit Techniques,Tax Policy Analysis,Revenue Forecasting,Budget Management,Stakeholder Engagement,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
 - Communication
 - Negotiation
 - Risk Management
-#resume
+#Resume
 #TopExecutiveResume #TopExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8597,7 +8597,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>top executive resume,how to make a top executive resume,["Strategic Planning","Financial Acumen","Leadership","Communication","Negotiation","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>top executive resume,how to make a top executive resume,Strategic Planning,Financial Acumen,Leadership,Communication,Negotiation,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
 - Land Use Planning
 - Zoning Enforcement
 - Public Works Management
-#resume
+#Resume
 #TownshipSupervisorResume #TownshipSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8657,7 +8657,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>township supervisor resume,how to make a township supervisor resume,["Municipal Finance","Budget Management","Contract Administration","Land Use Planning","Zoning Enforcement","Public Works Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>township supervisor resume,how to make a township supervisor resume,Municipal Finance,Budget Management,Contract Administration,Land Use Planning,Zoning Enforcement,Public Works Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
 - Transportation Planning
 - Public Education and Outreach
 - Grant Management
-#resume
+#Resume
 #TrafficSafetyAdministratorResume #TrafficSafetyAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8717,7 +8717,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>traffic safety administrator resume,how to make a traffic safety administrator resume,["Traffic Incident Management","Roadway Safety Analysis","Crash Data Analysis","Transportation Planning","Public Education and Outreach","Grant Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>traffic safety administrator resume,how to make a traffic safety administrator resume,Traffic Incident Management,Roadway Safety Analysis,Crash Data Analysis,Transportation Planning,Public Education and Outreach,Grant Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
 - Terminology Management
 - Machine Translation
 - Translation Quality Assessment
-#resume
+#Resume
 #TranslationDirectorResume #TranslationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8777,7 +8777,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>translation director resume,how to make a translation director resume,director level resume,["Translation Management","Localization","Project Management","Terminology Management","Machine Translation","Translation Quality Assessment"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>translation director resume,how to make a translation director resume,director level resume,Translation Management,Localization,Project Management,Terminology Management,Machine Translation,Translation Quality Assessment,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
 - Treasury Operations
 - Investment Management
 - Risk Management
-#resume
+#Resume
 #TreasurerResume #Treasurer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8837,7 +8837,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>treasurer resume,how to make a treasurer resume,["Financial Reporting","Cash Flow Management","Budgeting and Forecasting","Treasury Operations","Investment Management","Risk Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>treasurer resume,how to make a treasurer resume,Financial Reporting,Cash Flow Management,Budgeting and Forecasting,Treasury Operations,Investment Management,Risk Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
 - Regulatory Interpretation
 - Enforcement Actions
 - Interagency Coordination
-#resume
+#Resume
 #USCommissionerResume #USCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8897,7 +8897,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>u.s. commissioner resume,how to make a u.s. commissioner resume,["Strategic Planning","Budget Management","Policy Analysis","Regulatory Interpretation","Enforcement Actions","Interagency Coordination"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>u.s. commissioner resume,how to make a u.s. commissioner resume,Strategic Planning,Budget Management,Policy Analysis,Regulatory Interpretation,Enforcement Actions,Interagency Coordination,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
 - Unemployment Insurance Appeals Management
 - Unemployment Insurance Compliance Auditing
 - Unemployment Insurance Program Administration
-#resume
+#Resume
 #UnemploymentInsuranceDirectorResume #UnemploymentInsuranceDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -8957,7 +8957,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>unemployment insurance director resume,how to make a unemployment insurance director resume,director level resume,["Unemployment Insurance Claim Adjudication","Unemployment Insurance Benefit Determination","Unemployment Insurance Fraud Detection","Unemployment Insurance Appeals Management","Unemployment Insurance Compliance Auditing","Unemployment Insurance Program Administration"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder</t>
+          <t>unemployment insurance director resume,how to make a unemployment insurance director resume,director level resume,Unemployment Insurance Claim Adjudication,Unemployment Insurance Benefit Determination,Unemployment Insurance Fraud Detection,Unemployment Insurance Appeals Management,Unemployment Insurance Compliance Auditing,Unemployment Insurance Program Administration,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
 - Stakeholder Engagement
 - Fundraising and Development
 - Academic Affairs Management
-#resume
+#Resume
 #UniversityPresidentResume #UniversityPresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9017,7 +9017,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>university president resume,how to make a university president resume,["Institutional Leadership","Strategic Planning","Financial Management","Stakeholder Engagement","Fundraising and Development","Academic Affairs Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>university president resume,how to make a university president resume,Institutional Leadership,Strategic Planning,Financial Management,Stakeholder Engagement,Fundraising and Development,Academic Affairs Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
 - Fundraising and Development
 - Higher Education Administration
 - Policy Development and Implementation
-#resume
+#Resume
 #ViceChancellorResume #ViceChancellor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>vice chancellor resume,how to make a vice chancellor resume,["Strategic Planning","Budget Management","Organizational Leadership","Fundraising and Development","Higher Education Administration","Policy Development and Implementation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>vice chancellor resume,how to make a vice chancellor resume,Strategic Planning,Budget Management,Organizational Leadership,Fundraising and Development,Higher Education Administration,Policy Development and Implementation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
 - Risk Management
 - Team Leadership
 - Negotiation
-#resume
+#Resume
 #VicePresidentResume #VicePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9137,7 +9137,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>vice president resume,how to make a vice president resume,["Strategic Planning","Financial Management","Operations Management","Risk Management","Team Leadership","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>vice president resume,how to make a vice president resume,Strategic Planning,Financial Management,Operations Management,Risk Management,Team Leadership,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
 - Drinking Water Treatment
 - Stormwater Management
 - Water Conservation and Efficiency
-#resume
+#Resume
 #WaterCommissionerResume #WaterCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9197,7 +9197,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>water commissioner resume,how to make a water commissioner resume,["Water Distribution System Maintenance","Wastewater Treatment Plant Operation","Water Quality Analysis","Drinking Water Treatment","Stormwater Management","Water Conservation and Efficiency"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water commissioner resume,how to make a water commissioner resume,Water Distribution System Maintenance,Wastewater Treatment Plant Operation,Water Quality Analysis,Drinking Water Treatment,Stormwater Management,Water Conservation and Efficiency,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
 - Budget Management
 - Case Management
 - Community Outreach
-#resume
+#Resume
 #WelfareDirectorResume #WelfareDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9257,7 +9257,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>welfare director resume,how to make a welfare director resume,director level resume,["Grant Management","Welfare Program Development","Policy Analysis and Interpretation","Budget Management","Case Management","Community Outreach"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>welfare director resume,how to make a welfare director resume,director level resume,Grant Management,Welfare Program Development,Policy Analysis and Interpretation,Budget Management,Case Management,Community Outreach,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9307,7 @@
 - Climate Change Mitigation and Adaptation
 - Environmental Auditing and Compliance
 - Stakeholder Engagement and Communication
-#resume
+#Resume
 #ChiefEnvironmentalCommitmentOfficerCecoResume #ChiefEnvironmentalCommitmentOfficerCeco #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9317,7 +9317,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>chief environmental commitment officer (ceco) resume,how to make a chief environmental commitment officer (ceco) resume,["Environmental Policy Development","Environmental Management Systems (EMS)","Environmental Impact Assessment (EIA)","Climate Change Mitigation and Adaptation","Environmental Auditing and Compliance","Stakeholder Engagement and Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
+          <t>chief environmental commitment officer (ceco) resume,how to make a chief environmental commitment officer (ceco) resume,Environmental Policy Development,Environmental Management Systems (EMS),Environmental Impact Assessment (EIA),Climate Change Mitigation and Adaptation,Environmental Auditing and Compliance,Stakeholder Engagement and Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
 - Waste Reduction and Management
 - Environmental Compliance
 - Stakeholder Engagement
-#resume
+#Resume
 #ChiefGreenOfficerCgoResume #ChiefGreenOfficerCgo #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9377,7 +9377,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>chief green officer (cgo) resume,how to make a chief green officer (cgo) resume,["Sustainability Strategy Development","Carbon Accounting and Reporting","Renewable Energy Integration","Waste Reduction and Management","Environmental Compliance","Stakeholder Engagement"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief green officer (cgo) resume,how to make a chief green officer (cgo) resume,Sustainability Strategy Development,Carbon Accounting and Reporting,Renewable Energy Integration,Waste Reduction and Management,Environmental Compliance,Stakeholder Engagement,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
 - Stakeholder Engagement and Communication
 - Life Cycle Assessment
 - Environmental Policy and Regulation Compliance
-#resume
+#Resume
 #CorporateSustainabilityProcessManagerResume #CorporateSustainabilityProcessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9439,7 +9439,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>corporate sustainability process manager resume,how to make a corporate sustainability process manager resume,management resume,["Greenhouse Gas Emissions Reporting","Carbon Footprint Analysis","Sustainability Reporting Frameworks (GRI,SASB,TCFD)","Stakeholder Engagement and Communication","Life Cycle Assessment","Environmental Policy and Regulation Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
+          <t>corporate sustainability process manager resume,how to make a corporate sustainability process manager resume,management resume,Greenhouse Gas Emissions Reporting,Carbon Footprint Analysis,Sustainability Reporting Frameworks (GRI,SASB,TCFD),Stakeholder Engagement and Communication,Life Cycle Assessment,Environmental Policy and Regulation Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
 - Sustainable Supply Chain Management
 - Environmental Impact Assessment
 - Sustainability Reporting
-#resume
+#Resume
 #DirectorOfSustainabilityResume #DirectorOfSustainability #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9499,7 +9499,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>director of sustainability resume,how to make a director of sustainability resume,director level resume,["Greenhouse Gas Accounting","Carbon Footprint Analysis","Life Cycle Assessment","Sustainable Supply Chain Management","Environmental Impact Assessment","Sustainability Reporting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>director of sustainability resume,how to make a director of sustainability resume,director level resume,Greenhouse Gas Accounting,Carbon Footprint Analysis,Life Cycle Assessment,Sustainable Supply Chain Management,Environmental Impact Assessment,Sustainability Reporting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
 - Renewable Energy Integration
 - Sustainability Reporting and Disclosure
 - Circular Economy Principles
-#resume
+#Resume
 #DirectorOfSustainabilityProgramsResume #DirectorOfSustainabilityPrograms #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9559,7 +9559,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>director of sustainability programs resume,how to make a director of sustainability programs resume,director level resume,["Sustainability Strategy Development","Environmental Management Systems (ISO 14001)","Greenhouse Gas Emissions Management","Renewable Energy Integration","Sustainability Reporting and Disclosure","Circular Economy Principles"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>director of sustainability programs resume,how to make a director of sustainability programs resume,director level resume,Sustainability Strategy Development,Environmental Management Systems (ISO 14001),Greenhouse Gas Emissions Management,Renewable Energy Integration,Sustainability Reporting and Disclosure,Circular Economy Principles,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
 - Energy Modeling and Analysis
 - Water Conservation and Management
 - Renewable Energy Integration
-#resume
+#Resume
 #DirectorOfSustainableDesignResume #DirectorOfSustainableDesign #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9619,7 +9619,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>director of sustainable design resume,how to make a director of sustainable design resume,director level resume,["LEED Project Management","Sustainable Site Design","Green Building Design and Construction","Energy Modeling and Analysis","Water Conservation and Management","Renewable Energy Integration"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>director of sustainable design resume,how to make a director of sustainable design resume,director level resume,LEED Project Management,Sustainable Site Design,Green Building Design and Construction,Energy Modeling and Analysis,Water Conservation and Management,Renewable Energy Integration,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
 - Energy Management Systems
 - Carbon Accounting and Reporting
 - Sustainability Reporting
-#resume
+#Resume
 #EnergyAndSustainabilityManagerResume #EnergyAndSustainabilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9679,7 +9679,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>energy and sustainability manager resume,how to make a energy and sustainability manager resume,management resume,["Energy Auditing","Energy Modeling","Renewable Energy Integration","Energy Management Systems","Carbon Accounting and Reporting","Sustainability Reporting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>energy and sustainability manager resume,how to make a energy and sustainability manager resume,management resume,Energy Auditing,Energy Modeling,Renewable Energy Integration,Energy Management Systems,Carbon Accounting and Reporting,Sustainability Reporting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
 - Sustainability Reporting
 - Waste Management
 - Water Management
-#resume
+#Resume
 #EnvironmentCoordinatorResume #EnvironmentCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>environment coordinator resume,how to make a environment coordinator resume,["Environmental Impact Assessment","Environmental Management","Environmental Regulations Compliance","Sustainability Reporting","Waste Management","Water Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>environment coordinator resume,how to make a environment coordinator resume,Environmental Impact Assessment,Environmental Management,Environmental Regulations Compliance,Sustainability Reporting,Waste Management,Water Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
 - Corporate Social Responsibility (CSR)
 - Life Cycle Assessment (LCA)
 - Environmental Compliance and Regulations
-#resume
+#Resume
 #EnvironmentalAndSustainabilityManagerResume #EnvironmentalAndSustainabilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9799,7 +9799,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>environmental and sustainability manager resume,how to make a environmental and sustainability manager resume,management resume,["Environmental Management Systems (EMS)","Sustainability Reporting","Environmental Impact Assessment (EIA)","Corporate Social Responsibility (CSR)","Life Cycle Assessment (LCA)","Environmental Compliance and Regulations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>environmental and sustainability manager resume,how to make a environmental and sustainability manager resume,management resume,Environmental Management Systems (EMS),Sustainability Reporting,Environmental Impact Assessment (EIA),Corporate Social Responsibility (CSR),Life Cycle Assessment (LCA),Environmental Compliance and Regulations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
 - Fire Safety Management
 - Hazard Recognition and Control
 - Incident Reporting and Documentation
-#resume
+#Resume
 #SafetyManagerResume #SafetyManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9859,7 +9859,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>safety manager resume,how to make a safety manager resume,management resume,["Accident Investigation and Analysis","Compliance Management","Ergonomics","Fire Safety Management","Hazard Recognition and Control","Incident Reporting and Documentation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>safety manager resume,how to make a safety manager resume,management resume,Accident Investigation and Analysis,Compliance Management,Ergonomics,Fire Safety Management,Hazard Recognition and Control,Incident Reporting and Documentation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
 - Relationship Management
 - Influence Management
 - Project Management
-#resume
+#Resume
 #StakeholderManagerResume #StakeholderManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9919,7 +9919,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>stakeholder manager resume,how to make a stakeholder manager resume,management resume,["Stakeholder Engagement","Stakeholder Analysis","Communication Management","Relationship Management","Influence Management","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>stakeholder manager resume,how to make a stakeholder manager resume,management resume,Stakeholder Engagement,Stakeholder Analysis,Communication Management,Relationship Management,Influence Management,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
 - Environmental Impact Assessment
 - GHG Emissions Management
 - Green Building Design and Construction
-#resume
+#Resume
 #SupplyChainManagerSustainabilityAndEnergyResume #SupplyChainManagerSustainabilityAndEnergy #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -9979,7 +9979,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>supply chain manager, sustainability and energy resume,how to make a supply chain manager, sustainability and energy resume,management resume,["Biomass Energy Production","Carbon Accounting and Reporting","Clean Energy Project Development","Environmental Impact Assessment","GHG Emissions Management","Green Building Design and Construction"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>supply chain manager, sustainability and energy resume,how to make a supply chain manager, sustainability and energy resume,management resume,Biomass Energy Production,Carbon Accounting and Reporting,Clean Energy Project Development,Environmental Impact Assessment,GHG Emissions Management,Green Building Design and Construction,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
 - Life Cycle Assessment (LCA)
 - Renewable Energy and Energy Efficiency
 - Waste Management and Circular Economy
-#resume
+#Resume
 #SustainabilityCoordinatorResume #SustainabilityCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10040,7 +10040,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>sustainability coordinator resume,how to make a sustainability coordinator resume,["Environmental Management Systems (ISO 14001)","Sustainability Reporting (GRI,SASB)","Carbon Accounting and Management","Life Cycle Assessment (LCA)","Renewable Energy and Energy Efficiency","Waste Management and Circular Economy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sustainability coordinator resume,how to make a sustainability coordinator resume,Environmental Management Systems (ISO 14001),Sustainability Reporting (GRI,SASB),Carbon Accounting and Management,Life Cycle Assessment (LCA),Renewable Energy and Energy Efficiency,Waste Management and Circular Economy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
 - Corporate Social Responsibility
 - Life Cycle Assessment
 - Sustainable Supply Chain Management
-#resume
+#Resume
 #SustainabilityDirectorResume #SustainabilityDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>sustainability director resume,how to make a sustainability director resume,director level resume,["Greenhouse Gas Accounting","Environmental Impact Assessment","Sustainability Reporting","Corporate Social Responsibility","Life Cycle Assessment","Sustainable Supply Chain Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sustainability director resume,how to make a sustainability director resume,director level resume,Greenhouse Gas Accounting,Environmental Impact Assessment,Sustainability Reporting,Corporate Social Responsibility,Life Cycle Assessment,Sustainable Supply Chain Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
 - Stakeholder Engagement
 - Life Cycle Assessment
 - Corporate Social Responsibility Management
-#resume
+#Resume
 #SustainabilityExecutiveDirectorResume #SustainabilityExecutiveDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10160,7 +10160,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>sustainability executive director resume,how to make a sustainability executive director resume,director level resume,["Sustainability Reporting","Sustainable Finance","Environmental Accounting","Stakeholder Engagement","Life Cycle Assessment","Corporate Social Responsibility Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sustainability executive director resume,how to make a sustainability executive director resume,director level resume,Sustainability Reporting,Sustainable Finance,Environmental Accounting,Stakeholder Engagement,Life Cycle Assessment,Corporate Social Responsibility Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
 - Carbon Footprint Analysis
 - Environmental Impact Assessment (EIA)
 - Sustainability Strategy Development
-#resume
+#Resume
 #SustainabilityManagerResume #SustainabilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10220,7 +10220,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>sustainability manager resume,how to make a sustainability manager resume,management resume,["Sustainability Reporting","Environmental Management Systems (EMS)","Life Cycle Assessment (LCA)","Carbon Footprint Analysis","Environmental Impact Assessment (EIA)","Sustainability Strategy Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sustainability manager resume,how to make a sustainability manager resume,management resume,Sustainability Reporting,Environmental Management Systems (EMS),Life Cycle Assessment (LCA),Carbon Footprint Analysis,Environmental Impact Assessment (EIA),Sustainability Strategy Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
 - Environmental Policy Analysis
 - Sustainability Risk Management
 - Life Cycle Assessment
-#resume
+#Resume
 #SustainabilityResearchAndAdvocacyDirectorResume #SustainabilityResearchAndAdvocacyDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10280,7 +10280,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>sustainability research and advocacy director resume,how to make a sustainability research and advocacy director resume,director level resume,["Sustainability Reporting","Climate Change Mitigation and Adaptation","Stakeholder Engagement and Communication","Environmental Policy Analysis","Sustainability Risk Management","Life Cycle Assessment"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sustainability research and advocacy director resume,how to make a sustainability research and advocacy director resume,director level resume,Sustainability Reporting,Climate Change Mitigation and Adaptation,Stakeholder Engagement and Communication,Environmental Policy Analysis,Sustainability Risk Management,Life Cycle Assessment,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
 - Sustainability Accounting
 - Climate Risk Management
 - Social Impact Measurement
-#resume
+#Resume
 #VicePresidentCorporateSocialResponsibilityAndSustainabilityVpCsrAndSustainabilityResume #VicePresidentCorporateSocialResponsibilityAndSustainabilityVpCsrAndSustainability #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10340,7 +10340,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>vice president, corporate social responsibility and sustainability (vp csr and sustainability) resume,how to make a vice president, corporate social responsibility and sustainability (vp csr and sustainability) resume,["Stakeholder Engagement","CSR Strategy Development","ESG Reporting","Sustainability Accounting","Climate Risk Management","Social Impact Measurement"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
+          <t>vice president, corporate social responsibility and sustainability (vp csr and sustainability) resume,how to make a vice president, corporate social responsibility and sustainability (vp csr and sustainability) resume,Stakeholder Engagement,CSR Strategy Development,ESG Reporting,Sustainability Accounting,Climate Risk Management,Social Impact Measurement,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
 - Strategic Planning
 - Human Resource Management
 - Force Structure Analysis
-#resume
+#Resume
 #AdjutantGeneralResume #AdjutantGeneral #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10400,7 +10400,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>adjutant general resume,how to make a adjutant general resume,["Military Operations Planning","Personnel Management","Budget Management","Strategic Planning","Human Resource Management","Force Structure Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>adjutant general resume,how to make a adjutant general resume,Military Operations Planning,Personnel Management,Budget Management,Strategic Planning,Human Resource Management,Force Structure Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
 - Activity Planning
 - Client Assessment
 - Case Management
-#resume
+#Resume
 #AdultDaycareCoordinatorResume #AdultDaycareCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10460,7 +10460,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>adult daycare coordinator resume,how to make a adult daycare coordinator resume,["Care Planning","Medication Management","Program Development","Activity Planning","Client Assessment","Case Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>adult daycare coordinator resume,how to make a adult daycare coordinator resume,Care Planning,Medication Management,Program Development,Activity Planning,Client Assessment,Case Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
 - P&amp;L Management
 - Team Leadership
 - Project Management
-#resume
+#Resume
 #AssistantManagerResume #AssistantManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>assistant manager resume,how to make a assistant manager resume,management resume,["Financial Reporting","Budgeting","Sales Forecasting","P&amp;L Management","Team Leadership","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assistant manager resume,how to make a assistant manager resume,management resume,Financial Reporting,Budgeting,Sales Forecasting,P&amp;L Management,Team Leadership,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
 - Electrical Systems
 - Plumbing Systems
 - Construction Management
-#resume
+#Resume
 #BuildingManagerResume #BuildingManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10580,7 +10580,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>building manager resume,how to make a building manager resume,management resume,["Building Maintenance","Property Management","HVAC Systems","Electrical Systems","Plumbing Systems","Construction Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>building manager resume,how to make a building manager resume,management resume,Building Maintenance,Property Management,HVAC Systems,Electrical Systems,Plumbing Systems,Construction Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
 - Operational Planning
 - Vendor Management
 - Negotiation and Contracts
-#resume
+#Resume
 #BusinessAdministratorResume #BusinessAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10640,7 +10640,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>business administrator resume,how to make a business administrator resume,["Business &amp; Data Analysis","Financial Management","Budgeting and Forecasting","Operational Planning","Vendor Management","Negotiation and Contracts"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business administrator resume,how to make a business administrator resume,Business &amp; Data Analysis,Financial Management,Budgeting and Forecasting,Operational Planning,Vendor Management,Negotiation and Contracts,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
 - Data Entry and Management
 - Scheduling and Coordination
 - Communication and Interpersonal Skills
-#resume
+#Resume
 #BusinessCoordinatorResume #BusinessCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10700,7 +10700,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>business coordinator resume,how to make a business coordinator resume,["Project Management","Process Improvement","Business Analysis","Data Entry and Management","Scheduling and Coordination","Communication and Interpersonal Skills"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business coordinator resume,how to make a business coordinator resume,Project Management,Process Improvement,Business Analysis,Data Entry and Management,Scheduling and Coordination,Communication and Interpersonal Skills,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
 - Relationship Management
 - Market Analysis
 - Negotiation
-#resume
+#Resume
 #BusinessDevelopmentDirectorResume #BusinessDevelopmentDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10760,7 +10760,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>business development director resume,how to make a business development director resume,director level resume,["Business Development","Sales Management","Strategic Planning","Relationship Management","Market Analysis","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business development director resume,how to make a business development director resume,director level resume,Business Development,Sales Management,Strategic Planning,Relationship Management,Market Analysis,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
 - Performance Management
 - Risk Management
 - Investment Analysis
-#resume
+#Resume
 #BusinessManagerResume #BusinessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10820,7 +10820,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>business manager resume,how to make a business manager resume,management resume,["Financial Planning and Analysis","Budget Management","Forecasting and Modeling","Performance Management","Risk Management","Investment Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>business manager resume,how to make a business manager resume,management resume,Financial Planning and Analysis,Budget Management,Forecasting and Modeling,Performance Management,Risk Management,Investment Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
 - Document Management
 - HR Management
 - Leadership
-#resume
+#Resume
 #ChiefDeputyResume #ChiefDeputy #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10880,7 +10880,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>chief deputy resume,how to make a chief deputy resume,["Courtroom Management","Budget Management","Case Management","Document Management","HR Management","Leadership"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>chief deputy resume,how to make a chief deputy resume,Courtroom Management,Budget Management,Case Management,Document Management,HR Management,Leadership,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
 - Budgeting and Financial Management
 - Team Leadership and Development
 - Sales Analysis and Forecasting
-#resume
+#Resume
 #DepartmentStoreGeneralManagerResume #DepartmentStoreGeneralManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -10940,7 +10940,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>department store general manager resume,how to make a department store general manager resume,management resume,["Merchandise Planning","Inventory Management","Customer Service Management","Budgeting and Financial Management","Team Leadership and Development","Sales Analysis and Forecasting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>department store general manager resume,how to make a department store general manager resume,management resume,Merchandise Planning,Inventory Management,Customer Service Management,Budgeting and Financial Management,Team Leadership and Development,Sales Analysis and Forecasting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
 - Communication
 - Negotiation
 - Financial Management
-#resume
+#Resume
 #DistrictCommercialSuperintendentResume #DistrictCommercialSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11000,7 +11000,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>district commercial superintendent resume,how to make a district commercial superintendent resume,["Construction Management","Project Management","Leadership","Communication","Negotiation","Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>district commercial superintendent resume,how to make a district commercial superintendent resume,Construction Management,Project Management,Leadership,Communication,Negotiation,Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
 - SCADA and Automation Technologies
 - Asset Management and Condition Monitoring
 - Project Management
-#resume
+#Resume
 #DistrictPlantSuperintendentResume #DistrictPlantSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11060,7 +11060,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>district plant superintendent resume,how to make a district plant superintendent resume,["Power Distribution System Operations","Electrical Safety Management","Preventive and Predictive Maintenance Programs","SCADA and Automation Technologies","Asset Management and Condition Monitoring","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>district plant superintendent resume,how to make a district plant superintendent resume,Power Distribution System Operations,Electrical Safety Management,Preventive and Predictive Maintenance Programs,SCADA and Automation Technologies,Asset Management and Condition Monitoring,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
 - Roadway Safety Analysis
 - Congestion Management
 - Multimodal Transportation Planning
-#resume
+#Resume
 #DistrictTrafficChiefResume #DistrictTrafficChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11120,7 +11120,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>district traffic chief resume,how to make a district traffic chief resume,["Traffic Incident Management","Incident Response Planning and Execution","Traffic Signal Optimization","Roadway Safety Analysis","Congestion Management","Multimodal Transportation Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>district traffic chief resume,how to make a district traffic chief resume,Traffic Incident Management,Incident Response Planning and Execution,Traffic Signal Optimization,Roadway Safety Analysis,Congestion Management,Multimodal Transportation Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11170,7 @@
 - Network Troubleshooting and Repair
 - Telecommunications Cabling
 - Network Planning and Optimization
-#resume
+#Resume
 #DistrictWireChiefResume #DistrictWireChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11180,7 +11180,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>district wire chief resume,how to make a district wire chief resume,["FTTX Planning and Deployment","Copper and Fiber Splicing","Outside Plant Engineering","Network Troubleshooting and Repair","Telecommunications Cabling","Network Planning and Optimization"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>district wire chief resume,how to make a district wire chief resume,FTTX Planning and Deployment,Copper and Fiber Splicing,Outside Plant Engineering,Network Troubleshooting and Repair,Telecommunications Cabling,Network Planning and Optimization,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11230,7 @@
 - Telecommunications Maintenance
 - Central Office Switch Configuration
 - Telecommunications Test Equipment Operation
-#resume
+#Resume
 #DivisionTollWireChiefResume #DivisionTollWireChief #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>division toll wire chief resume,how to make a division toll wire chief resume,["Copper and Fiber Splicing","Outside Plant Engineering","Network Troubleshooting","Telecommunications Maintenance","Central Office Switch Configuration","Telecommunications Test Equipment Operation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>division toll wire chief resume,how to make a division toll wire chief resume,Copper and Fiber Splicing,Outside Plant Engineering,Network Troubleshooting,Telecommunications Maintenance,Central Office Switch Configuration,Telecommunications Test Equipment Operation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
 - Roadway Capacity Analysis
 - Traffic Signal Design and Operation
 - ITS (Intelligent Transportation Systems) Implementation
-#resume
+#Resume
 #DivisionTrafficSuperintendentResume #DivisionTrafficSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11300,7 +11300,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>division traffic superintendent resume,how to make a division traffic superintendent resume,["Incident Management","Traffic Forecasting and Analysis","Transportation Planning and Optimization","Roadway Capacity Analysis","Traffic Signal Design and Operation","ITS (Intelligent Transportation Systems) Implementation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>division traffic superintendent resume,how to make a division traffic superintendent resume,Incident Management,Traffic Forecasting and Analysis,Transportation Planning and Optimization,Roadway Capacity Analysis,Traffic Signal Design and Operation,ITS (Intelligent Transportation Systems) Implementation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
 - Drilling and Completion Cost Control
 - HSE Compliance and Risk Management
 - Wellbore Integrity Analysis
-#resume
+#Resume
 #DrillingAndProductionSuperintendentResume #DrillingAndProductionSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11360,7 +11360,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>drilling and production superintendent resume,how to make a drilling and production superintendent resume,["Drilling Operations Management","Production Operations Supervision","Reservoir Engineering Fundamentals","Drilling and Completion Cost Control","HSE Compliance and Risk Management","Wellbore Integrity Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>drilling and production superintendent resume,how to make a drilling and production superintendent resume,Drilling Operations Management,Production Operations Supervision,Reservoir Engineering Fundamentals,Drilling and Completion Cost Control,HSE Compliance and Risk Management,Wellbore Integrity Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
 - Control System Integration
 - Arc Flash Hazard Analysis
 - NEC and ANSI Code Compliance
-#resume
+#Resume
 #ElectricalSuperintendentResume #ElectricalSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11420,7 +11420,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>electrical superintendent resume,how to make a electrical superintendent resume,["Electrical Distribution System Design","Electrical Substation Maintenance","Power System Analysis","Control System Integration","Arc Flash Hazard Analysis","NEC and ANSI Code Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>electrical superintendent resume,how to make a electrical superintendent resume,Electrical Distribution System Design,Electrical Substation Maintenance,Power System Analysis,Control System Integration,Arc Flash Hazard Analysis,NEC and ANSI Code Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
 - Fleet Management and Optimization
 - Work Order Management and Scheduling
 - Budget Management and Cost Control
-#resume
+#Resume
 #EquipmentMaintenanceSuperintendentResume #EquipmentMaintenanceSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11480,7 +11480,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>equipment maintenance superintendent resume,how to make a equipment maintenance superintendent resume,["Maintenance and Repair of Industrial Equipment","Troubleshooting and Diagnostics of Electrical and Mechanical Systems","Predictive and Preventative Maintenance","Fleet Management and Optimization","Work Order Management and Scheduling","Budget Management and Cost Control"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume</t>
+          <t>equipment maintenance superintendent resume,how to make a equipment maintenance superintendent resume,Maintenance and Repair of Industrial Equipment,Troubleshooting and Diagnostics of Electrical and Mechanical Systems,Predictive and Preventative Maintenance,Fleet Management and Optimization,Work Order Management and Scheduling,Budget Management and Cost Control,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
 - Construction Management
 - Contract Management
 - Customer Service
-#resume
+#Resume
 #FacilitiesManagerResume #FacilitiesManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11540,7 +11540,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>facilities manager resume,how to make a facilities manager resume,management resume,["Asset Management","Budget Management","Capital Planning","Construction Management","Contract Management","Customer Service"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>facilities manager resume,how to make a facilities manager resume,management resume,Asset Management,Budget Management,Capital Planning,Construction Management,Contract Management,Customer Service,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
 - Energy Management
 - Safety and Compliance Audits
 - Project Management
-#resume
+#Resume
 #FacilityManagerResume #FacilityManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11600,7 +11600,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>facility manager resume,how to make a facility manager resume,management resume,["Facility Inspection and Maintenance","Building Automation Systems (BAS)","Preventive Maintenance Scheduling","Energy Management","Safety and Compliance Audits","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>facility manager resume,how to make a facility manager resume,management resume,Facility Inspection and Maintenance,Building Automation Systems (BAS),Preventive Maintenance Scheduling,Energy Management,Safety and Compliance Audits,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
 - Data Analysis
 - Report Writing
 - Budget Management
-#resume
+#Resume
 #FieldPartyManagerResume #FieldPartyManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11660,7 +11660,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>field party manager resume,how to make a field party manager resume,management resume,["Field Data Collection","Project Management","Team Leadership","Data Analysis","Report Writing","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>field party manager resume,how to make a field party manager resume,management resume,Field Data Collection,Project Management,Team Leadership,Data Analysis,Report Writing,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
 - Outdoor Education
 - Fundraising and Grant Writing
 - Conservation Biology
-#resume
+#Resume
 #FishAndGameClubManagerResume #FishAndGameClubManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11720,7 +11720,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>fish and game club manager resume,how to make a fish and game club manager resume,management resume,["Wildlife Management","Fishery Management","Hunting and Fishing Regulations","Outdoor Education","Fundraising and Grant Writing","Conservation Biology"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>fish and game club manager resume,how to make a fish and game club manager resume,management resume,Wildlife Management,Fishery Management,Hunting and Fishing Regulations,Outdoor Education,Fundraising and Grant Writing,Conservation Biology,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
 - Program Design
 - Nutritional Counseling
 - Injury Prevention and Rehabilitation
-#resume
+#Resume
 #FitnessManagerResume #FitnessManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11780,7 +11780,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>fitness manager resume,how to make a fitness manager resume,management resume,["Personal Training","Group Fitness Instruction","Fitness Assessment","Program Design","Nutritional Counseling","Injury Prevention and Rehabilitation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>fitness manager resume,how to make a fitness manager resume,management resume,Personal Training,Group Fitness Instruction,Fitness Assessment,Program Design,Nutritional Counseling,Injury Prevention and Rehabilitation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
 - Team Leadership
 - Customer Relationship Management
 - Project Management
-#resume
+#Resume
 #GeneralManagerGmResume #GeneralManagerGm #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11840,7 +11840,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>general manager (gm) resume,how to make a general manager (gm) resume,management resume,["Strategic Planning","Operations Management","Financial Management","Team Leadership","Customer Relationship Management","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>general manager (gm) resume,how to make a general manager (gm) resume,management resume,Strategic Planning,Operations Management,Financial Management,Team Leadership,Customer Relationship Management,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
 - Contract Administration
 - Leadership
 - Team Building
-#resume
+#Resume
 #GeneralSuperintendentResume #GeneralSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11900,7 +11900,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>general superintendent resume,how to make a general superintendent resume,["Construction Management","Project Management","Budget Management","Contract Administration","Leadership","Team Building"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>general superintendent resume,how to make a general superintendent resume,Construction Management,Project Management,Budget Management,Contract Administration,Leadership,Team Building,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
 - Budget Planning and Management
 - Staff Supervision and Training
 - Equipment Operation and Maintenance
-#resume
+#Resume
 #GolfCourseManagerResume #GolfCourseManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -11960,7 +11960,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>golf course manager resume,how to make a golf course manager resume,management resume,["Golf Course Maintenance and Management","Turfgrass Management Practices","Irrigation System Maintenance","Budget Planning and Management","Staff Supervision and Training","Equipment Operation and Maintenance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>golf course manager resume,how to make a golf course manager resume,management resume,Golf Course Maintenance and Management,Turfgrass Management Practices,Irrigation System Maintenance,Budget Planning and Management,Staff Supervision and Training,Equipment Operation and Maintenance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
 - Staff Management
 - Marketing and Promotions
 - Budget Management
-#resume
+#Resume
 #GymManagerResume #GymManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12020,7 +12020,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>gym manager resume,how to make a gym manager resume,management resume,["Fitness Assessment","Customer Service","Equipment Maintenance","Staff Management","Marketing and Promotions","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>gym manager resume,how to make a gym manager resume,management resume,Fitness Assessment,Customer Service,Equipment Maintenance,Staff Management,Marketing and Promotions,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
 - Profit and Loss (P&amp;L) Management
 - Budgeting and Forecasting
 - Compliance Management
-#resume
+#Resume
 #HeadOfStoreOperationsResume #HeadOfStoreOperations #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12080,7 +12080,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>head of store operations resume,how to make a head of store operations resume,["Customer Service","Inventory Management","Staff Supervision","Profit and Loss (P&amp;L) Management","Budgeting and Forecasting","Compliance Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>head of store operations resume,how to make a head of store operations resume,Customer Service,Inventory Management,Staff Supervision,Profit and Loss (P&amp;L) Management,Budgeting and Forecasting,Compliance Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
 - Lighting Design and Implementation
 - Color Theory and Applications
 - Prop Sourcing and Management
-#resume
+#Resume
 #HeadOfVisualMerchandisingResume #HeadOfVisualMerchandising #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12140,7 +12140,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>head of visual merchandising resume,how to make a head of visual merchandising resume,["Visual Merchandising Strategy Development","Trend Forecasting and Analysis","Space Planning and Layout Optimization","Lighting Design and Implementation","Color Theory and Applications","Prop Sourcing and Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>head of visual merchandising resume,how to make a head of visual merchandising resume,Visual Merchandising Strategy Development,Trend Forecasting and Analysis,Space Planning and Layout Optimization,Lighting Design and Implementation,Color Theory and Applications,Prop Sourcing and Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
 - Project Management
 - Data Analysis
 - Simulation Modeling
-#resume
+#Resume
 #IndustrialOrganizationManagerResume #IndustrialOrganizationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12200,7 +12200,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>industrial organization manager resume,how to make a industrial organization manager resume,management resume,["Operations Management","Lean Six Sigma","Industrial Engineering","Project Management","Data Analysis","Simulation Modeling"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>industrial organization manager resume,how to make a industrial organization manager resume,management resume,Operations Management,Lean Six Sigma,Industrial Engineering,Project Management,Data Analysis,Simulation Modeling,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
 - Cost Control
 - Quality Control
 - Electrical Installations
-#resume
+#Resume
 #InstallationSuperintendentResume #InstallationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12260,7 +12260,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>installation superintendent resume,how to make a installation superintendent resume,["Construction Management","Project Management","Team Leadership","Cost Control","Quality Control","Electrical Installations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>installation superintendent resume,how to make a installation superintendent resume,Construction Management,Project Management,Team Leadership,Cost Control,Quality Control,Electrical Installations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
 - Water Conservation Techniques
 - Energy Efficiency Practices
 - Quality Control and Inspection
-#resume
+#Resume
 #LaundrySuperintendentResume #LaundrySuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12320,7 +12320,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>laundry superintendent resume,how to make a laundry superintendent resume,["Washer and Dryer Operation","Fabric Care and Handling","Chemical Management","Water Conservation Techniques","Energy Efficiency Practices","Quality Control and Inspection"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>laundry superintendent resume,how to make a laundry superintendent resume,Washer and Dryer Operation,Fabric Care and Handling,Chemical Management,Water Conservation Techniques,Energy Efficiency Practices,Quality Control and Inspection,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
 - Operating Lease Management
 - Contract Review and Analysis
 - Lease Negotiation
-#resume
+#Resume
 #LeaseOperatorResume #LeaseOperator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12380,7 +12380,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>lease operator resume,how to make a lease operator resume,["Lease Accounting","Lease Administration","Capital Lease Management","Operating Lease Management","Contract Review and Analysis","Lease Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>lease operator resume,how to make a lease operator resume,Lease Accounting,Lease Administration,Capital Lease Management,Operating Lease Management,Contract Review and Analysis,Lease Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
 - Project Management
 - Budget Management
 - Crew Management
-#resume
+#Resume
 #LineConstructionSuperintendentResume #LineConstructionSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12440,7 +12440,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>line construction superintendent resume,how to make a line construction superintendent resume,["Overhead and Underground Line Construction","Distribution and Transmission Line Construction","Substation Construction","Project Management","Budget Management","Crew Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>line construction superintendent resume,how to make a line construction superintendent resume,Overhead and Underground Line Construction,Distribution and Transmission Line Construction,Substation Construction,Project Management,Budget Management,Crew Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12490,7 @@
 - Mine Geology
 - Mine Safety
 - Mine Permitting
-#resume
+#Resume
 #MineAdministratorSupervisorResume #MineAdministratorSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12500,7 +12500,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>mine administrator supervisor resume,how to make a mine administrator supervisor resume,["Mine Planning","Mine Ventilation","Mine Surveying","Mine Geology","Mine Safety","Mine Permitting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>mine administrator supervisor resume,how to make a mine administrator supervisor resume,Mine Planning,Mine Ventilation,Mine Surveying,Mine Geology,Mine Safety,Mine Permitting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
 - Mine Environmental Management
 - Mineral Processing
 - Explosives Management
-#resume
+#Resume
 #MineSuperintendentResume #MineSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12560,7 +12560,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>mine superintendent resume,how to make a mine superintendent resume,["Mine Production Planning","Mine Operations Management","Mine Safety Management","Mine Environmental Management","Mineral Processing","Explosives Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>mine superintendent resume,how to make a mine superintendent resume,Mine Production Planning,Mine Operations Management,Mine Safety Management,Mine Environmental Management,Mineral Processing,Explosives Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
 - Customer Service
 - Projection Equipment Operation
 - Staff Supervision
-#resume
+#Resume
 #MovieTheaterManagerResume #MovieTheaterManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12620,7 +12620,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>movie theater manager resume,how to make a movie theater manager resume,management resume,["Cinema Management","Box Office Operations","Concession Management","Customer Service","Projection Equipment Operation","Staff Supervision"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>movie theater manager resume,how to make a movie theater manager resume,management resume,Cinema Management,Box Office Operations,Concession Management,Customer Service,Projection Equipment Operation,Staff Supervision,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
 - forecasting
 - and financial management
 - Exceptional communication and interpersonal skills
-#resume
+#Resume
 #NewspaperManagerResume #NewspaperManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12682,7 +12682,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>newspaper manager resume,how to make a newspaper manager resume,management resume,["In-depth understanding of newspaper production and distribution","Expertise in managing editorial and production teams","Strong knowledge of print and digital publishing","Proficient in Adobe Creative Suite and other industry software","Excellence in budgeting,forecasting,and financial management","Exceptional communication and interpersonal skills"],how to write a resume,resume writing,resume builder,cv format</t>
+          <t>newspaper manager resume,how to make a newspaper manager resume,management resume,In-depth understanding of newspaper production and distribution,Expertise in managing editorial and production teams,Strong knowledge of print and digital publishing,Proficient in Adobe Creative Suite and other industry software,Excellence in budgeting,forecasting,and financial management,Exceptional communication and interpersonal skills,how to write a resume,resume writing,resume builder,cv format</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
 - Event Planning
 - Customer Service
 - Data Entry
-#resume
+#Resume
 #OfficeManagerResume #OfficeManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12742,7 +12742,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>office manager resume,how to make a office manager resume,management resume,["Office Management","Budget Management","Human Resources Management","Event Planning","Customer Service","Data Entry"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>office manager resume,how to make a office manager resume,management resume,Office Management,Budget Management,Human Resources Management,Event Planning,Customer Service,Data Entry,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12792,7 @@
 - Project Management
 - Stakeholder Management
 - Negotiation
-#resume
+#Resume
 #OffshoringManagerResume #OffshoringManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12802,7 +12802,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>offshoring manager resume,how to make a offshoring manager resume,management resume,["Vendor Management","Cost Optimization","Global Sourcing","Project Management","Stakeholder Management","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>offshoring manager resume,how to make a offshoring manager resume,management resume,Vendor Management,Cost Optimization,Global Sourcing,Project Management,Stakeholder Management,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
 - Pipeline Maintenance
 - Field Safety Procedures
 - Oil and Gas Processing
-#resume
+#Resume
 #OilLeaseOperatorResume #OilLeaseOperator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12862,7 +12862,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>oil lease operator resume,how to make a oil lease operator resume,["Artificial Lift Systems","Wellhead and Production Equipment Maintenance","Production Operations","Pipeline Maintenance","Field Safety Procedures","Oil and Gas Processing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>oil lease operator resume,how to make a oil lease operator resume,Artificial Lift Systems,Wellhead and Production Equipment Maintenance,Production Operations,Pipeline Maintenance,Field Safety Procedures,Oil and Gas Processing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
 - Reservoir Pressure Analysis
 - Production Optimization
 - Pipeline Operations
-#resume
+#Resume
 #OilOperatorResume #OilOperator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12922,7 +12922,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>oil operator resume,how to make a oil operator resume,["HSE Regulations and Compliance","Drilling Equipment Maintenance","Well Monitoring and Control","Reservoir Pressure Analysis","Production Optimization","Pipeline Operations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>oil operator resume,how to make a oil operator resume,HSE Regulations and Compliance,Drilling Equipment Maintenance,Well Monitoring and Control,Reservoir Pressure Analysis,Production Optimization,Pipeline Operations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
 - Production Optimization
 - Enhanced Oil Recovery
 - Artificial Lift Systems
-#resume
+#Resume
 #OilProducerResume #OilProducer #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -12982,7 +12982,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>oil producer resume,how to make a oil producer resume,["Drilling Operations","Well Completion","Reservoir Engineering","Production Optimization","Enhanced Oil Recovery","Artificial Lift Systems"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>oil producer resume,how to make a oil producer resume,Drilling Operations,Well Completion,Reservoir Engineering,Production Optimization,Enhanced Oil Recovery,Artificial Lift Systems,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
 - Customer Relationship Management (CRM)
 - Data Analytics and Interpretation
 - Enterprise Resource Planning (ERP) Systems
-#resume
+#Resume
 #OperationsAdministratorResume #OperationsAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13042,7 +13042,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>operations administrator resume,how to make a operations administrator resume,["Agile Scrum","Budget Management","Communication and Presentation","Customer Relationship Management (CRM)","Data Analytics and Interpretation","Enterprise Resource Planning (ERP) Systems"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>operations administrator resume,how to make a operations administrator resume,Agile Scrum,Budget Management,Communication and Presentation,Customer Relationship Management (CRM),Data Analytics and Interpretation,Enterprise Resource Planning (ERP) Systems,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
 - Project Management
 - Quality Control
 - Lean Six Sigma
-#resume
+#Resume
 #OperationsDirectorResume #OperationsDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13102,7 +13102,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>operations director resume,how to make a operations director resume,director level resume,["Business Process Management","Operations Planning","Supply Chain Management","Project Management","Quality Control","Lean Six Sigma"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>operations director resume,how to make a operations director resume,director level resume,Business Process Management,Operations Planning,Supply Chain Management,Project Management,Quality Control,Lean Six Sigma,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
 - Supply Chain Management
 - Inventory Management
 - Warehouse Management
-#resume
+#Resume
 #OperationsManagerResume #OperationsManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13162,7 +13162,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>operations manager resume,how to make a operations manager resume,management resume,["Operations Management","Process Improvement","Lean Six Sigma","Supply Chain Management","Inventory Management","Warehouse Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>operations manager resume,how to make a operations manager resume,management resume,Operations Management,Process Improvement,Lean Six Sigma,Supply Chain Management,Inventory Management,Warehouse Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
 - Performance Optimization
 - Team Management and Leadership
 - Project Management
-#resume
+#Resume
 #OperationsSupervisorResume #OperationsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13222,7 +13222,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>operations supervisor resume,how to make a operations supervisor resume,["Inventory Management","Logistics and Supply Chain Management","Quality Control","Performance Optimization","Team Management and Leadership","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>operations supervisor resume,how to make a operations supervisor resume,Inventory Management,Logistics and Supply Chain Management,Quality Control,Performance Optimization,Team Management and Leadership,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
 - Community Engagement and Outreach
 - Facility Planning and Design
 - Risk Management and Emergency Preparedness
-#resume
+#Resume
 #ParksAndRecreationManagerResume #ParksAndRecreationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13282,7 +13282,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>parks and recreation manager resume,how to make a parks and recreation manager resume,management resume,["Parks and Recreation Management","Budgeting and Financial Management","Program Development and Implementation","Community Engagement and Outreach","Facility Planning and Design","Risk Management and Emergency Preparedness"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>parks and recreation manager resume,how to make a parks and recreation manager resume,management resume,Parks and Recreation Management,Budgeting and Financial Management,Program Development and Implementation,Community Engagement and Outreach,Facility Planning and Design,Risk Management and Emergency Preparedness,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
 - OSHA Compliance
 - TPM (Total Productive Maintenance)
 - Project Management
-#resume
+#Resume
 #PlantManagerResume #PlantManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13342,7 +13342,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>plant manager resume,how to make a plant manager resume,management resume,["Lean Manufacturing","Six Sigma","ISO 9001","OSHA Compliance","TPM (Total Productive Maintenance)","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>plant manager resume,how to make a plant manager resume,management resume,Lean Manufacturing,Six Sigma,ISO 9001,OSHA Compliance,TPM (Total Productive Maintenance),Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13392,7 @@
 - Cost Reduction
 - Inventory Management
 - Project Management
-#resume
+#Resume
 #PlantSuperintendentResume #PlantSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>plant superintendent resume,how to make a plant superintendent resume,["Process Safety Management System","Production Planning and Scheduling","Continuous Improvement","Cost Reduction","Inventory Management","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>plant superintendent resume,how to make a plant superintendent resume,Process Safety Management System,Production Planning and Scheduling,Continuous Improvement,Cost Reduction,Inventory Management,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
 - Safety Management and Compliance
 - Equipment Maintenance and Repair
 - Lean Manufacturing and Six Sigma
-#resume
+#Resume
 #PlantSupervisorResume #PlantSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13462,7 +13462,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>plant supervisor resume,how to make a plant supervisor resume,["Production Planning and Scheduling","Quality Control and Assurance","Process Improvement and Optimization","Safety Management and Compliance","Equipment Maintenance and Repair","Lean Manufacturing and Six Sigma"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>plant supervisor resume,how to make a plant supervisor resume,Production Planning and Scheduling,Quality Control and Assurance,Process Improvement and Optimization,Safety Management and Compliance,Equipment Maintenance and Repair,Lean Manufacturing and Six Sigma,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
 - Color Management
 - File Preparation
 - Proofing
-#resume
+#Resume
 #PrintProductionCoordinatorResume #PrintProductionCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13522,7 +13522,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>print production coordinator resume,how to make a print production coordinator resume,["Prepress Production","Offset Printing","Digital Printing","Color Management","File Preparation","Proofing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>print production coordinator resume,how to make a print production coordinator resume,Prepress Production,Offset Printing,Digital Printing,Color Management,File Preparation,Proofing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
 - Offset and Digital Press Operation
 - Postpress Operations and Finishing Processes
 - Bindery and Distribution Management
-#resume
+#Resume
 #PrintProductionManagerResume #PrintProductionManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13582,7 +13582,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>print production manager resume,how to make a print production manager resume,management resume,["Prepress and Print Production Management","Digital Printing and Workflow Management","Color Management and Calibration","Offset and Digital Press Operation","Postpress Operations and Finishing Processes","Bindery and Distribution Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>print production manager resume,how to make a print production manager resume,management resume,Prepress and Print Production Management,Digital Printing and Workflow Management,Color Management and Calibration,Offset and Digital Press Operation,Postpress Operations and Finishing Processes,Bindery and Distribution Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
 - Graphic Design
 - Inkjet Printing
 - Job Costing
-#resume
+#Resume
 #PrintingManagerResume #PrintingManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13642,7 +13642,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>printing manager resume,how to make a printing manager resume,management resume,["Color Management","Digital Printing","Estimating and Quoting","Graphic Design","Inkjet Printing","Job Costing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>printing manager resume,how to make a printing manager resume,management resume,Color Management,Digital Printing,Estimating and Quoting,Graphic Design,Inkjet Printing,Job Costing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
 - Budget Planning and Management
 - Policy Development and Implementation
 - Risk Assessment and Management
-#resume
+#Resume
 #PrisonWardenResume #PrisonWarden #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13702,7 +13702,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>prison warden resume,how to make a prison warden resume,["Correctional Facility Management","Inmate Supervision and Security","Staff Supervision and Development","Budget Planning and Management","Policy Development and Implementation","Risk Assessment and Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>prison warden resume,how to make a prison warden resume,Correctional Facility Management,Inmate Supervision and Security,Staff Supervision and Development,Budget Planning and Management,Policy Development and Implementation,Risk Assessment and Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
 - Production Planning and Scheduling
 - Inventory Management
 - Material Requirements Planning (MRP)
-#resume
+#Resume
 #ProductionManagerResume #ProductionManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13762,7 +13762,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>production manager resume,how to make a production manager resume,management resume,["Lean Manufacturing","ISO 9001:2015 Quality Management","Six Sigma","Production Planning and Scheduling","Inventory Management","Material Requirements Planning (MRP)"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>production manager resume,how to make a production manager resume,management resume,Lean Manufacturing,ISO 9001:2015 Quality Management,Six Sigma,Production Planning and Scheduling,Inventory Management,Material Requirements Planning (MRP),how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
 - Digital Publishing
 - Project Management
 - Marketing and Communication
-#resume
+#Resume
 #PublicationDirectorResume #PublicationDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13822,7 +13822,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>publication director resume,how to make a publication director resume,director level resume,["Content Strategy","Editing and Proofreading","Layout and Design","Digital Publishing","Project Management","Marketing and Communication"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>publication director resume,how to make a publication director resume,director level resume,Content Strategy,Editing and Proofreading,Layout and Design,Digital Publishing,Project Management,Marketing and Communication,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13872,7 @@
 - FCC Regulations
 - Market Analysis
 - Budgeting and Finance
-#resume
+#Resume
 #RadioStationManagerResume #RadioStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13882,7 +13882,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>radio station manager resume,how to make a radio station manager resume,management resume,["Audio Production","Broadcast Operations","Content Programming","FCC Regulations","Market Analysis","Budgeting and Finance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>radio station manager resume,how to make a radio station manager resume,management resume,Audio Production,Broadcast Operations,Content Programming,FCC Regulations,Market Analysis,Budgeting and Finance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
 - Alkylation
 - Polymerization
 - Blending
-#resume
+#Resume
 #RefinerySuperintendentResume #RefinerySuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -13942,7 +13942,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>refinery superintendent resume,how to make a refinery superintendent resume,["Hydroprocessing","Distillation","Reforming","Alkylation","Polymerization","Blending"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>refinery superintendent resume,how to make a refinery superintendent resume,Hydroprocessing,Distillation,Reforming,Alkylation,Polymerization,Blending,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -13992,7 +13992,7 @@
 - Inventory Management
 - Yield Management
 - Distribution Management
-#resume
+#Resume
 #RevenueManagerResume #RevenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14002,7 +14002,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>revenue manager resume,how to make a revenue manager resume,management resume,["Revenue Management","Pricing Optimization","Demand Forecasting","Inventory Management","Yield Management","Distribution Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>revenue manager resume,how to make a revenue manager resume,management resume,Revenue Management,Pricing Optimization,Demand Forecasting,Inventory Management,Yield Management,Distribution Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
 - Culvert Installation
 - Drainage System Design
 - Erosion Control
-#resume
+#Resume
 #RoadsSuperintendentResume #RoadsSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14062,7 +14062,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>roads superintendent resume,how to make a roads superintendent resume,["Asphalt Paving","Bridge Construction","Concrete Paving","Culvert Installation","Drainage System Design","Erosion Control"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>roads superintendent resume,how to make a roads superintendent resume,Asphalt Paving,Bridge Construction,Concrete Paving,Culvert Installation,Drainage System Design,Erosion Control,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
 - Financial Management and Budgeting
 - Inventory and Supply Chain Management
 - Product Knowledge and Trend Analysis
-#resume
+#Resume
 #SalonManagerResume #SalonManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14122,7 +14122,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>salon manager resume,how to make a salon manager resume,management resume,["Salon Operations Management","Team Leadership and Development","Customer Service and Relationship Building","Financial Management and Budgeting","Inventory and Supply Chain Management","Product Knowledge and Trend Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>salon manager resume,how to make a salon manager resume,management resume,Salon Operations Management,Team Leadership and Development,Customer Service and Relationship Building,Financial Management and Budgeting,Inventory and Supply Chain Management,Product Knowledge and Trend Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
 - Community Collaboration
 - Budget Management
 - Fundraising
-#resume
+#Resume
 #ShelterDirectorResume #ShelterDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14182,7 +14182,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>shelter director resume,how to make a shelter director resume,director level resume,["Disaster Management","Emergency Preparedness Planning","Animal Welfare Management","Community Collaboration","Budget Management","Fundraising"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>shelter director resume,how to make a shelter director resume,director level resume,Disaster Management,Emergency Preparedness Planning,Animal Welfare Management,Community Collaboration,Budget Management,Fundraising,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
 - Safety Program Development
 - Workforce Management
 - Regulatory Compliance
-#resume
+#Resume
 #ShiftSuperintendentResume #ShiftSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14242,7 +14242,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>shift superintendent resume,how to make a shift superintendent resume,["Shift Operations Management","Incident Command System (ICS)","OSHA Compliance","Safety Program Development","Workforce Management","Regulatory Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>shift superintendent resume,how to make a shift superintendent resume,Shift Operations Management,Incident Command System (ICS),OSHA Compliance,Safety Program Development,Workforce Management,Regulatory Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
 - Project Management
 - Team Leadership
 - Production Planning and Scheduling
-#resume
+#Resume
 #ShopSuperintendentResume #ShopSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14302,7 +14302,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>shop superintendent resume,how to make a shop superintendent resume,["Lean Manufacturing","ISO 9001:2015 Quality Management","Six Sigma","Project Management","Team Leadership","Production Planning and Scheduling"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>shop superintendent resume,how to make a shop superintendent resume,Lean Manufacturing,ISO 9001:2015 Quality Management,Six Sigma,Project Management,Team Leadership,Production Planning and Scheduling,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
 - Benefits Determination
 - Case Management
 - Policy Interpretation
-#resume
+#Resume
 #SocialInsuranceAdministratorResume #SocialInsuranceAdministrator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14362,7 +14362,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>social insurance administrator resume,how to make a social insurance administrator resume,["Social Insurance Program Knowledge","Claims Processing","Disability Assessment","Benefits Determination","Case Management","Policy Interpretation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>social insurance administrator resume,how to make a social insurance administrator resume,Social Insurance Program Knowledge,Claims Processing,Disability Assessment,Benefits Determination,Case Management,Policy Interpretation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14412,7 @@
 - Waste Reduction and Recycling Programs
 - Hazardous Waste Management
 - Environmental Regulations Compliance
-#resume
+#Resume
 #SolidWasteManagerResume #SolidWasteManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14422,7 +14422,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>solid waste manager resume,how to make a solid waste manager resume,management resume,["Wastewater Treatment Plant Operations","Solid Waste Management Planning","Landfill Design and Construction","Waste Reduction and Recycling Programs","Hazardous Waste Management","Environmental Regulations Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>solid waste manager resume,how to make a solid waste manager resume,management resume,Wastewater Treatment Plant Operations,Solid Waste Management Planning,Landfill Design and Construction,Waste Reduction and Recycling Programs,Hazardous Waste Management,Environmental Regulations Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
 - Budget Management
 - Event Planning
 - Player Evaluation
-#resume
+#Resume
 #SportsTeamManagerResume #SportsTeamManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14482,7 +14482,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>sports team manager resume,how to make a sports team manager resume,management resume,["Team Management","Player Development","Game Strategy","Budget Management","Event Planning","Player Evaluation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sports team manager resume,how to make a sports team manager resume,management resume,Team Management,Player Development,Game Strategy,Budget Management,Event Planning,Player Evaluation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14532,7 @@
 - Traffic Signal Maintenance
 - Roadway Design and Engineering
 - Project Management
-#resume
+#Resume
 #StreetCommissionerResume #StreetCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14542,7 +14542,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>street commissioner resume,how to make a street commissioner resume,["Street Maintenance and Repair","Stormwater Management","Snow and Ice Removal","Traffic Signal Maintenance","Roadway Design and Engineering","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>street commissioner resume,how to make a street commissioner resume,Street Maintenance and Repair,Stormwater Management,Snow and Ice Removal,Traffic Signal Maintenance,Roadway Design and Engineering,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
 - Traffic Signal Maintenance
 - Street Lighting Maintenance
 - Budget Management
-#resume
+#Resume
 #StreetSuperintendentResume #StreetSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14602,7 +14602,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>street superintendent resume,how to make a street superintendent resume,["Asphalt Maintenance and Repair","Concrete Paving and Repair","Stormwater Management","Traffic Signal Maintenance","Street Lighting Maintenance","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>street superintendent resume,how to make a street superintendent resume,Asphalt Maintenance and Repair,Concrete Paving and Repair,Stormwater Management,Traffic Signal Maintenance,Street Lighting Maintenance,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
 - Transformer Maintenance and Testing
 - Circuit Breaker Maintenance and Testing
 - Electrical Safety and Compliance
-#resume
+#Resume
 #SubstationSuperintendentResume #SubstationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14662,7 +14662,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>substation superintendent resume,how to make a substation superintendent resume,["Overhead and Underground Transmission and Distribution Line Construction","Substation Design and Engineering","Protective Relaying and Control Systems","Transformer Maintenance and Testing","Circuit Breaker Maintenance and Testing","Electrical Safety and Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>substation superintendent resume,how to make a substation superintendent resume,Overhead and Underground Transmission and Distribution Line Construction,Substation Design and Engineering,Protective Relaying and Control Systems,Transformer Maintenance and Testing,Circuit Breaker Maintenance and Testing,Electrical Safety and Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
 - Budget Management
 - Team Leadership
 - Digital Media Management
-#resume
+#Resume
 #TelevisionStationManagerResume #TelevisionStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14722,7 +14722,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>television station manager resume,how to make a television station manager resume,management resume,["Broadcast Production","Newsroom Management","Programming Strategy","Budget Management","Team Leadership","Digital Media Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>television station manager resume,how to make a television station manager resume,management resume,Broadcast Production,Newsroom Management,Programming Strategy,Budget Management,Team Leadership,Digital Media Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
 - Budgeting and Financial Management
 - Staff Management and Leadership
 - Marketing and Audience Development
-#resume
+#Resume
 #TheatreManagerResume #TheatreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14782,7 +14782,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>theatre manager resume,how to make a theatre manager resume,management resume,["Theatre Management","Box Office Operations","Event Planning and Coordination","Budgeting and Financial Management","Staff Management and Leadership","Marketing and Audience Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>theatre manager resume,how to make a theatre manager resume,management resume,Theatre Management,Box Office Operations,Event Planning and Coordination,Budgeting and Financial Management,Staff Management and Leadership,Marketing and Audience Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
 - Vendor Management
 - Customer Service
 - Team Management
-#resume
+#Resume
 #VenueManagerResume #VenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14842,7 +14842,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>venue manager resume,how to make a venue manager resume,management resume,["Event Coordination","Venue Management","Budget Management","Vendor Management","Customer Service","Team Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>venue manager resume,how to make a venue manager resume,management resume,Event Coordination,Venue Management,Budget Management,Vendor Management,Customer Service,Team Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
 - Sewer Collection and Maintenance
 - Stormwater Management
 - Water Conservation
-#resume
+#Resume
 #WaterAndSewerSystemsSupervisorResume #WaterAndSewerSystemsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14902,7 +14902,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>water and sewer systems supervisor resume,how to make a water and sewer systems supervisor resume,["SCADA Control Systems","GIS Mapping","Water Treatment Processes","Sewer Collection and Maintenance","Stormwater Management","Water Conservation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water and sewer systems supervisor resume,how to make a water and sewer systems supervisor resume,SCADA Control Systems,GIS Mapping,Water Treatment Processes,Sewer Collection and Maintenance,Stormwater Management,Water Conservation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
 - GIS Mapping and Analysis
 - Hydraulic Modeling
 - Water Quality Monitoring and Analysis
-#resume
+#Resume
 #WaterControlSupervisorResume #WaterControlSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -14962,7 +14962,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>water control supervisor resume,how to make a water control supervisor resume,["Water Distribution System Operations","Wastewater Collection System Maintenance","SCADA and PLC Programming","GIS Mapping and Analysis","Hydraulic Modeling","Water Quality Monitoring and Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water control supervisor resume,how to make a water control supervisor resume,Water Distribution System Operations,Wastewater Collection System Maintenance,SCADA and PLC Programming,GIS Mapping and Analysis,Hydraulic Modeling,Water Quality Monitoring and Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
 - Wastewater Treatment Processes
 - SCADA Systems Operation and Troubleshooting
 - Asset Management and Maintenance
-#resume
+#Resume
 #WaterSuperintendentResume #WaterSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15022,7 +15022,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>water superintendent resume,how to make a water superintendent resume,["Water Treatment Plant Operations","Distribution System Management","Water Quality Monitoring and Analysis","Wastewater Treatment Processes","SCADA Systems Operation and Troubleshooting","Asset Management and Maintenance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water superintendent resume,how to make a water superintendent resume,Water Treatment Plant Operations,Distribution System Management,Water Quality Monitoring and Analysis,Wastewater Treatment Processes,SCADA Systems Operation and Troubleshooting,Asset Management and Maintenance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
 - SCADA Systems
 - GIS Mapping and Analysis
 - Budgeting and Financial Management
-#resume
+#Resume
 #WaterworksSupervisorResume #WaterworksSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15082,7 +15082,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>waterworks supervisor resume,how to make a waterworks supervisor resume,["Water Distribution System Management","Water Treatment Facility Operations","Wastewater Collection and Treatment","SCADA Systems","GIS Mapping and Analysis","Budgeting and Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>waterworks supervisor resume,how to make a waterworks supervisor resume,Water Distribution System Management,Water Treatment Facility Operations,Wastewater Collection and Treatment,SCADA Systems,GIS Mapping and Analysis,Budgeting and Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
 - Fundraising and Donor Relations
 - Public Relations and Outreach
 - Financial Management
-#resume
+#Resume
 #ZooDirectorResume #ZooDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15142,7 +15142,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>zoo director resume,how to make a zoo director resume,director level resume,["Zoological Management","Animal Welfare and Conservation","Exhibit Design and Development","Fundraising and Donor Relations","Public Relations and Outreach","Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>zoo director resume,how to make a zoo director resume,director level resume,Zoological Management,Animal Welfare and Conservation,Exhibit Design and Development,Fundraising and Donor Relations,Public Relations and Outreach,Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15192,7 +15192,7 @@
 - Community Development
 - Constituent Relations
 - Economic Development
-#resume
+#Resume
 #AldermanResume #Alderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15202,7 +15202,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>alderman resume,how to make a alderman resume,["Agenda Setting","Budget Analysis","Code Enforcement","Community Development","Constituent Relations","Economic Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>alderman resume,how to make a alderman resume,Agenda Setting,Budget Analysis,Code Enforcement,Community Development,Constituent Relations,Economic Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
 - Inventory Management
 - Production Planning
 - Time Management
-#resume
+#Resume
 #AssemblyMemberResume #AssemblyMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15262,7 +15262,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>assembly member resume,how to make a assembly member resume,["Assembly Line Optimization","Lean Manufacturing","Quality Control","Inventory Management","Production Planning","Time Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assembly member resume,how to make a assembly member resume,Assembly Line Optimization,Lean Manufacturing,Quality Control,Inventory Management,Production Planning,Time Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15312,7 +15312,7 @@
 - Traffic Signal Maintenance
 - Roadway Design and Engineering
 - Project Management
-#resume
+#Resume
 #StreetCommissionerResume #StreetCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15322,7 +15322,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>street commissioner resume,how to make a street commissioner resume,["Street Maintenance and Repair","Stormwater Management","Snow and Ice Removal","Traffic Signal Maintenance","Roadway Design and Engineering","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>street commissioner resume,how to make a street commissioner resume,Street Maintenance and Repair,Stormwater Management,Snow and Ice Removal,Traffic Signal Maintenance,Roadway Design and Engineering,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
 - Traffic Signal Maintenance
 - Street Lighting Maintenance
 - Budget Management
-#resume
+#Resume
 #StreetSuperintendentResume #StreetSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15382,7 +15382,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>street superintendent resume,how to make a street superintendent resume,["Asphalt Maintenance and Repair","Concrete Paving and Repair","Stormwater Management","Traffic Signal Maintenance","Street Lighting Maintenance","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>street superintendent resume,how to make a street superintendent resume,Asphalt Maintenance and Repair,Concrete Paving and Repair,Stormwater Management,Traffic Signal Maintenance,Street Lighting Maintenance,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
 - Transformer Maintenance and Testing
 - Circuit Breaker Maintenance and Testing
 - Electrical Safety and Compliance
-#resume
+#Resume
 #SubstationSuperintendentResume #SubstationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15442,7 +15442,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>substation superintendent resume,how to make a substation superintendent resume,["Overhead and Underground Transmission and Distribution Line Construction","Substation Design and Engineering","Protective Relaying and Control Systems","Transformer Maintenance and Testing","Circuit Breaker Maintenance and Testing","Electrical Safety and Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>substation superintendent resume,how to make a substation superintendent resume,Overhead and Underground Transmission and Distribution Line Construction,Substation Design and Engineering,Protective Relaying and Control Systems,Transformer Maintenance and Testing,Circuit Breaker Maintenance and Testing,Electrical Safety and Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
 - Budget Management
 - Team Leadership
 - Digital Media Management
-#resume
+#Resume
 #TelevisionStationManagerResume #TelevisionStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15502,7 +15502,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>television station manager resume,how to make a television station manager resume,management resume,["Broadcast Production","Newsroom Management","Programming Strategy","Budget Management","Team Leadership","Digital Media Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>television station manager resume,how to make a television station manager resume,management resume,Broadcast Production,Newsroom Management,Programming Strategy,Budget Management,Team Leadership,Digital Media Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
 - Budgeting and Financial Management
 - Staff Management and Leadership
 - Marketing and Audience Development
-#resume
+#Resume
 #TheatreManagerResume #TheatreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15562,7 +15562,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>theatre manager resume,how to make a theatre manager resume,management resume,["Theatre Management","Box Office Operations","Event Planning and Coordination","Budgeting and Financial Management","Staff Management and Leadership","Marketing and Audience Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>theatre manager resume,how to make a theatre manager resume,management resume,Theatre Management,Box Office Operations,Event Planning and Coordination,Budgeting and Financial Management,Staff Management and Leadership,Marketing and Audience Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
 - Vendor Management
 - Customer Service
 - Team Management
-#resume
+#Resume
 #VenueManagerResume #VenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15622,7 +15622,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>venue manager resume,how to make a venue manager resume,management resume,["Event Coordination","Venue Management","Budget Management","Vendor Management","Customer Service","Team Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>venue manager resume,how to make a venue manager resume,management resume,Event Coordination,Venue Management,Budget Management,Vendor Management,Customer Service,Team Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15672,7 @@
 - Sewer Collection and Maintenance
 - Stormwater Management
 - Water Conservation
-#resume
+#Resume
 #WaterAndSewerSystemsSupervisorResume #WaterAndSewerSystemsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15682,7 +15682,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>water and sewer systems supervisor resume,how to make a water and sewer systems supervisor resume,["SCADA Control Systems","GIS Mapping","Water Treatment Processes","Sewer Collection and Maintenance","Stormwater Management","Water Conservation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water and sewer systems supervisor resume,how to make a water and sewer systems supervisor resume,SCADA Control Systems,GIS Mapping,Water Treatment Processes,Sewer Collection and Maintenance,Stormwater Management,Water Conservation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
 - GIS Mapping and Analysis
 - Hydraulic Modeling
 - Water Quality Monitoring and Analysis
-#resume
+#Resume
 #WaterControlSupervisorResume #WaterControlSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15742,7 +15742,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>water control supervisor resume,how to make a water control supervisor resume,["Water Distribution System Operations","Wastewater Collection System Maintenance","SCADA and PLC Programming","GIS Mapping and Analysis","Hydraulic Modeling","Water Quality Monitoring and Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water control supervisor resume,how to make a water control supervisor resume,Water Distribution System Operations,Wastewater Collection System Maintenance,SCADA and PLC Programming,GIS Mapping and Analysis,Hydraulic Modeling,Water Quality Monitoring and Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15792,7 @@
 - Wastewater Treatment Processes
 - SCADA Systems Operation and Troubleshooting
 - Asset Management and Maintenance
-#resume
+#Resume
 #WaterSuperintendentResume #WaterSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15802,7 +15802,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>water superintendent resume,how to make a water superintendent resume,["Water Treatment Plant Operations","Distribution System Management","Water Quality Monitoring and Analysis","Wastewater Treatment Processes","SCADA Systems Operation and Troubleshooting","Asset Management and Maintenance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water superintendent resume,how to make a water superintendent resume,Water Treatment Plant Operations,Distribution System Management,Water Quality Monitoring and Analysis,Wastewater Treatment Processes,SCADA Systems Operation and Troubleshooting,Asset Management and Maintenance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
 - SCADA Systems
 - GIS Mapping and Analysis
 - Budgeting and Financial Management
-#resume
+#Resume
 #WaterworksSupervisorResume #WaterworksSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15862,7 +15862,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>waterworks supervisor resume,how to make a waterworks supervisor resume,["Water Distribution System Management","Water Treatment Facility Operations","Wastewater Collection and Treatment","SCADA Systems","GIS Mapping and Analysis","Budgeting and Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>waterworks supervisor resume,how to make a waterworks supervisor resume,Water Distribution System Management,Water Treatment Facility Operations,Wastewater Collection and Treatment,SCADA Systems,GIS Mapping and Analysis,Budgeting and Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15912,7 @@
 - Fundraising and Donor Relations
 - Public Relations and Outreach
 - Financial Management
-#resume
+#Resume
 #ZooDirectorResume #ZooDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15922,7 +15922,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>zoo director resume,how to make a zoo director resume,director level resume,["Zoological Management","Animal Welfare and Conservation","Exhibit Design and Development","Fundraising and Donor Relations","Public Relations and Outreach","Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>zoo director resume,how to make a zoo director resume,director level resume,Zoological Management,Animal Welfare and Conservation,Exhibit Design and Development,Fundraising and Donor Relations,Public Relations and Outreach,Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
 - Community Development
 - Constituent Relations
 - Economic Development
-#resume
+#Resume
 #AldermanResume #Alderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -15982,7 +15982,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>alderman resume,how to make a alderman resume,["Agenda Setting","Budget Analysis","Code Enforcement","Community Development","Constituent Relations","Economic Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>alderman resume,how to make a alderman resume,Agenda Setting,Budget Analysis,Code Enforcement,Community Development,Constituent Relations,Economic Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
 - Inventory Management
 - Production Planning
 - Time Management
-#resume
+#Resume
 #AssemblyMemberResume #AssemblyMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16042,7 +16042,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>assembly member resume,how to make a assembly member resume,["Assembly Line Optimization","Lean Manufacturing","Quality Control","Inventory Management","Production Planning","Time Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assembly member resume,how to make a assembly member resume,Assembly Line Optimization,Lean Manufacturing,Quality Control,Inventory Management,Production Planning,Time Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
 - Conveyor System Maintenance
 - Electrical Wiring
 - Fastening
-#resume
+#Resume
 #AssemblyPersonResume #AssemblyPerson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16102,7 +16102,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>assembly person resume,how to make a assembly person resume,["Automated Assembly Line","Bending","Component Assembly","Conveyor System Maintenance","Electrical Wiring","Fastening"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assembly person resume,how to make a assembly person resume,Automated Assembly Line,Bending,Component Assembly,Conveyor System Maintenance,Electrical Wiring,Fastening,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
 - Government Relations
 - Legislative Bill Analysis
 - Legislative Drafting
-#resume
+#Resume
 #AssemblymanOrWomanResume #AssemblymanOrWoman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16162,7 +16162,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>assemblyman or woman resume,how to make a assemblyman or woman resume,["Budget Analysis","Constituent Services","Constituency Outreach","Government Relations","Legislative Bill Analysis","Legislative Drafting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assemblyman or woman resume,how to make a assemblyman or woman resume,Budget Analysis,Constituent Services,Constituency Outreach,Government Relations,Legislative Bill Analysis,Legislative Drafting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
 - Land Use Planning
 - Economic Development
 - Strategic Planning
-#resume
+#Resume
 #CityAldermanResume #CityAlderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16222,7 +16222,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>city alderman resume,how to make a city alderman resume,["Public Policy Analysis","Budget Management","Constituency Outreach","Land Use Planning","Economic Development","Strategic Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city alderman resume,how to make a city alderman resume,Public Policy Analysis,Budget Management,Constituency Outreach,Land Use Planning,Economic Development,Strategic Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
 - Constituent Relations
 - Policy Analysis
 - Collaboration
-#resume
+#Resume
 #CityCouncilMemberResume #CityCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16282,7 +16282,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>city council member resume,how to make a city council member resume,["Strategic Planning","Budget Management","Public Speaking","Constituent Relations","Policy Analysis","Collaboration"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city council member resume,how to make a city council member resume,Strategic Planning,Budget Management,Public Speaking,Constituent Relations,Policy Analysis,Collaboration,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
 - Environmental Policy
 - Ethics and Transparency
 - Fiscal Management
-#resume
+#Resume
 #CityCouncilmanResume #CityCouncilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16342,7 +16342,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>city councilman resume,how to make a city councilman resume,["Budgeting","Constituent Services","Economic Development","Environmental Policy","Ethics and Transparency","Fiscal Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city councilman resume,how to make a city councilman resume,Budgeting,Constituent Services,Economic Development,Environmental Policy,Ethics and Transparency,Fiscal Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
 - Public Policy Formulation
 - Strategic Planning and Implementation
 - Project Management
-#resume
+#Resume
 #CongressionalRepresentativeResume #CongressionalRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16402,7 +16402,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>congressional representative resume,how to make a congressional representative resume,["Budgeting and Fiscal Analysis","Constituent Relations Management","Legislative Drafting and Analysis","Public Policy Formulation","Strategic Planning and Implementation","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>congressional representative resume,how to make a congressional representative resume,Budgeting and Fiscal Analysis,Constituent Relations Management,Legislative Drafting and Analysis,Public Policy Formulation,Strategic Planning and Implementation,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16452,7 @@
 - Budget Management
 - Event Planning
 - Player Evaluation
-#resume
+#Resume
 #SportsTeamManagerResume #SportsTeamManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16462,7 +16462,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>sports team manager resume,how to make a sports team manager resume,management resume,["Team Management","Player Development","Game Strategy","Budget Management","Event Planning","Player Evaluation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>sports team manager resume,how to make a sports team manager resume,management resume,Team Management,Player Development,Game Strategy,Budget Management,Event Planning,Player Evaluation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16512,7 +16512,7 @@
 - Advocacy
 - Public Speaking
 - Consensus Building
-#resume
+#Resume
 #CongressmanResume #Congressman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16522,7 +16522,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>congressman resume,how to make a congressman resume,["Constituent Services","Policy Development","Legislating","Advocacy","Public Speaking","Consensus Building"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>congressman resume,how to make a congressman resume,Constituent Services,Policy Development,Legislating,Advocacy,Public Speaking,Consensus Building,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16572,7 +16572,7 @@
 - Traffic Signal Maintenance
 - Roadway Design and Engineering
 - Project Management
-#resume
+#Resume
 #StreetCommissionerResume #StreetCommissioner #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16582,7 +16582,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>street commissioner resume,how to make a street commissioner resume,["Street Maintenance and Repair","Stormwater Management","Snow and Ice Removal","Traffic Signal Maintenance","Roadway Design and Engineering","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>street commissioner resume,how to make a street commissioner resume,Street Maintenance and Repair,Stormwater Management,Snow and Ice Removal,Traffic Signal Maintenance,Roadway Design and Engineering,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16632,7 +16632,7 @@
 - Conflict Resolution
 - Constituent Services
 - Decision Making
-#resume
+#Resume
 #CouncilMemberResume #CouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16642,7 +16642,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>council member resume,how to make a council member resume,["Advising Constituents","Budget Analysis","Community Engagement","Conflict Resolution","Constituent Services","Decision Making"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>council member resume,how to make a council member resume,Advising Constituents,Budget Analysis,Community Engagement,Conflict Resolution,Constituent Services,Decision Making,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
 - Traffic Signal Maintenance
 - Street Lighting Maintenance
 - Budget Management
-#resume
+#Resume
 #StreetSuperintendentResume #StreetSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16702,7 +16702,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>street superintendent resume,how to make a street superintendent resume,["Asphalt Maintenance and Repair","Concrete Paving and Repair","Stormwater Management","Traffic Signal Maintenance","Street Lighting Maintenance","Budget Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>street superintendent resume,how to make a street superintendent resume,Asphalt Maintenance and Repair,Concrete Paving and Repair,Stormwater Management,Traffic Signal Maintenance,Street Lighting Maintenance,Budget Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
 - Budget Management
 - Ordinance Drafting
 - Land Use Planning
-#resume
+#Resume
 #CouncilmanResume #Councilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16762,7 +16762,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>councilman resume,how to make a councilman resume,["Public Policy Analysis","Community Engagement","Strategic Planning","Budget Management","Ordinance Drafting","Land Use Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>councilman resume,how to make a councilman resume,Public Policy Analysis,Community Engagement,Strategic Planning,Budget Management,Ordinance Drafting,Land Use Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
 - Transformer Maintenance and Testing
 - Circuit Breaker Maintenance and Testing
 - Electrical Safety and Compliance
-#resume
+#Resume
 #SubstationSuperintendentResume #SubstationSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16822,7 +16822,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>substation superintendent resume,how to make a substation superintendent resume,["Overhead and Underground Transmission and Distribution Line Construction","Substation Design and Engineering","Protective Relaying and Control Systems","Transformer Maintenance and Testing","Circuit Breaker Maintenance and Testing","Electrical Safety and Compliance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>substation superintendent resume,how to make a substation superintendent resume,Overhead and Underground Transmission and Distribution Line Construction,Substation Design and Engineering,Protective Relaying and Control Systems,Transformer Maintenance and Testing,Circuit Breaker Maintenance and Testing,Electrical Safety and Compliance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
 - Advocacy
 - Intake Assessment
 - Group Facilitation
-#resume
+#Resume
 #CouncilorResume #Councilor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16882,7 +16882,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>councilor resume,how to make a councilor resume,["Case Management","Crisis Intervention","Counseling","Advocacy","Intake Assessment","Group Facilitation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>councilor resume,how to make a councilor resume,Case Management,Crisis Intervention,Counseling,Advocacy,Intake Assessment,Group Facilitation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16932,7 @@
 - Budget Management
 - Team Leadership
 - Digital Media Management
-#resume
+#Resume
 #TelevisionStationManagerResume #TelevisionStationManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -16942,7 +16942,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>television station manager resume,how to make a television station manager resume,management resume,["Broadcast Production","Newsroom Management","Programming Strategy","Budget Management","Team Leadership","Digital Media Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>television station manager resume,how to make a television station manager resume,management resume,Broadcast Production,Newsroom Management,Programming Strategy,Budget Management,Team Leadership,Digital Media Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
 - Community Engagement
 - Leadership and Governance
 - Interpersonal Communication and Negotiation
-#resume
+#Resume
 #CouncilpersonResume #Councilperson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17002,7 +17002,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>councilperson resume,how to make a councilperson resume,["Budgeting and Financial Management","Public Policy Development","Strategic Planning","Community Engagement","Leadership and Governance","Interpersonal Communication and Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>councilperson resume,how to make a councilperson resume,Budgeting and Financial Management,Public Policy Development,Strategic Planning,Community Engagement,Leadership and Governance,Interpersonal Communication and Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
 - Budgeting and Financial Management
 - Staff Management and Leadership
 - Marketing and Audience Development
-#resume
+#Resume
 #TheatreManagerResume #TheatreManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17062,7 +17062,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>theatre manager resume,how to make a theatre manager resume,management resume,["Theatre Management","Box Office Operations","Event Planning and Coordination","Budgeting and Financial Management","Staff Management and Leadership","Marketing and Audience Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>theatre manager resume,how to make a theatre manager resume,management resume,Theatre Management,Box Office Operations,Event Planning and Coordination,Budgeting and Financial Management,Staff Management and Leadership,Marketing and Audience Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17112,7 @@
 - Fundraising
 - Leadership
 - Negotiation
-#resume
+#Resume
 #DelegateResume #Delegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17122,7 +17122,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>delegate resume,how to make a delegate resume,["Communication","Collaboration","Event Planning","Fundraising","Leadership","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>delegate resume,how to make a delegate resume,Communication,Collaboration,Event Planning,Fundraising,Leadership,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
 - Vendor Management
 - Customer Service
 - Team Management
-#resume
+#Resume
 #VenueManagerResume #VenueManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17182,7 +17182,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>venue manager resume,how to make a venue manager resume,management resume,["Event Coordination","Venue Management","Budget Management","Vendor Management","Customer Service","Team Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>venue manager resume,how to make a venue manager resume,management resume,Event Coordination,Venue Management,Budget Management,Vendor Management,Customer Service,Team Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,7 @@
 - Policy Analysis
 - Public Speaking
 - Negotiation
-#resume
+#Resume
 #LegislatorResume #Legislator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17242,7 +17242,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>legislator resume,how to make a legislator resume,["Constituent Services","Community Outreach","Legislative Research","Policy Analysis","Public Speaking","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>legislator resume,how to make a legislator resume,Constituent Services,Community Outreach,Legislative Research,Policy Analysis,Public Speaking,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
 - Sewer Collection and Maintenance
 - Stormwater Management
 - Water Conservation
-#resume
+#Resume
 #WaterAndSewerSystemsSupervisorResume #WaterAndSewerSystemsSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17302,7 +17302,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>water and sewer systems supervisor resume,how to make a water and sewer systems supervisor resume,["SCADA Control Systems","GIS Mapping","Water Treatment Processes","Sewer Collection and Maintenance","Stormwater Management","Water Conservation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water and sewer systems supervisor resume,how to make a water and sewer systems supervisor resume,SCADA Control Systems,GIS Mapping,Water Treatment Processes,Sewer Collection and Maintenance,Stormwater Management,Water Conservation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17352,7 @@
 - Public Speaking
 - Media Relations
 - Negotiation
-#resume
+#Resume
 #MemberOfCongressResume #MemberOfCongress #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17362,7 +17362,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>member of congress resume,how to make a member of congress resume,["Policy Analysis","Legislative Drafting","Constituent Services","Public Speaking","Media Relations","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>member of congress resume,how to make a member of congress resume,Policy Analysis,Legislative Drafting,Constituent Services,Public Speaking,Media Relations,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17412,7 +17412,7 @@
 - GIS Mapping and Analysis
 - Hydraulic Modeling
 - Water Quality Monitoring and Analysis
-#resume
+#Resume
 #WaterControlSupervisorResume #WaterControlSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17422,7 +17422,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>water control supervisor resume,how to make a water control supervisor resume,["Water Distribution System Operations","Wastewater Collection System Maintenance","SCADA and PLC Programming","GIS Mapping and Analysis","Hydraulic Modeling","Water Quality Monitoring and Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water control supervisor resume,how to make a water control supervisor resume,Water Distribution System Operations,Wastewater Collection System Maintenance,SCADA and PLC Programming,GIS Mapping and Analysis,Hydraulic Modeling,Water Quality Monitoring and Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17472,7 +17472,7 @@
 - Communication
 - Interpersonal Skills
 - Problem Solving
-#resume
+#Resume
 #RepresentativeResume #Representative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17482,7 +17482,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>representative resume,how to make a representative resume,["Customer Relationship Management","Sales Prospecting","Negotiation","Communication","Interpersonal Skills","Problem Solving"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>representative resume,how to make a representative resume,Customer Relationship Management,Sales Prospecting,Negotiation,Communication,Interpersonal Skills,Problem Solving,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
 - Wastewater Treatment Processes
 - SCADA Systems Operation and Troubleshooting
 - Asset Management and Maintenance
-#resume
+#Resume
 #WaterSuperintendentResume #WaterSuperintendent #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17542,7 +17542,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>water superintendent resume,how to make a water superintendent resume,["Water Treatment Plant Operations","Distribution System Management","Water Quality Monitoring and Analysis","Wastewater Treatment Processes","SCADA Systems Operation and Troubleshooting","Asset Management and Maintenance"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>water superintendent resume,how to make a water superintendent resume,Water Treatment Plant Operations,Distribution System Management,Water Quality Monitoring and Analysis,Wastewater Treatment Processes,SCADA Systems Operation and Troubleshooting,Asset Management and Maintenance,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17592,7 +17592,7 @@
 - Community Engagement
 - Intergovernmental Relations
 - Public Speaking
-#resume
+#Resume
 #SelectmanResume #Selectman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17602,7 +17602,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>selectman resume,how to make a selectman resume,["Constituent Services","Budget Management","Policy Development","Community Engagement","Intergovernmental Relations","Public Speaking"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>selectman resume,how to make a selectman resume,Constituent Services,Budget Management,Policy Development,Community Engagement,Intergovernmental Relations,Public Speaking,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
 - SCADA Systems
 - GIS Mapping and Analysis
 - Budgeting and Financial Management
-#resume
+#Resume
 #WaterworksSupervisorResume #WaterworksSupervisor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17662,7 +17662,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>waterworks supervisor resume,how to make a waterworks supervisor resume,["Water Distribution System Management","Water Treatment Facility Operations","Wastewater Collection and Treatment","SCADA Systems","GIS Mapping and Analysis","Budgeting and Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>waterworks supervisor resume,how to make a waterworks supervisor resume,Water Distribution System Management,Water Treatment Facility Operations,Wastewater Collection and Treatment,SCADA Systems,GIS Mapping and Analysis,Budgeting and Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17712,7 +17712,7 @@
 - Speechwriting and Public Speaking
 - Committee Work and Leadership
 - Constituent Advocacy
-#resume
+#Resume
 #SenatorResume #Senator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17722,7 +17722,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>senator resume,how to make a senator resume,["Constituent Services Management","Legislative Policy Analysis","Budget and Appropriations","Speechwriting and Public Speaking","Committee Work and Leadership","Constituent Advocacy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>senator resume,how to make a senator resume,Constituent Services Management,Legislative Policy Analysis,Budget and Appropriations,Speechwriting and Public Speaking,Committee Work and Leadership,Constituent Advocacy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
 - Fundraising and Donor Relations
 - Public Relations and Outreach
 - Financial Management
-#resume
+#Resume
 #ZooDirectorResume #ZooDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17782,7 +17782,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>zoo director resume,how to make a zoo director resume,director level resume,["Zoological Management","Animal Welfare and Conservation","Exhibit Design and Development","Fundraising and Donor Relations","Public Relations and Outreach","Financial Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>zoo director resume,how to make a zoo director resume,director level resume,Zoological Management,Animal Welfare and Conservation,Exhibit Design and Development,Fundraising and Donor Relations,Public Relations and Outreach,Financial Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
 - Stakeholder Engagement
 - Community Outreach
 - Strategic Planning
-#resume
+#Resume
 #TribalCouncilMemberResume #TribalCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17842,7 +17842,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>tribal council member resume,how to make a tribal council member resume,["Budget Management","Policy Development","Conflict Resolution","Stakeholder Engagement","Community Outreach","Strategic Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>tribal council member resume,how to make a tribal council member resume,Budget Management,Policy Development,Conflict Resolution,Stakeholder Engagement,Community Outreach,Strategic Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
 - Community Development
 - Constituent Relations
 - Economic Development
-#resume
+#Resume
 #AldermanResume #Alderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17902,7 +17902,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>alderman resume,how to make a alderman resume,["Agenda Setting","Budget Analysis","Code Enforcement","Community Development","Constituent Relations","Economic Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>alderman resume,how to make a alderman resume,Agenda Setting,Budget Analysis,Code Enforcement,Community Development,Constituent Relations,Economic Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -17952,7 +17952,7 @@
 - Environmental Protection
 - Federal Indian Law
 - Government Relations
-#resume
+#Resume
 #TribalDelegateResume #TribalDelegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -17962,7 +17962,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>tribal delegate resume,how to make a tribal delegate resume,["Community Building","Cultural Resource Management","Economic Development","Environmental Protection","Federal Indian Law","Government Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>tribal delegate resume,how to make a tribal delegate resume,Community Building,Cultural Resource Management,Economic Development,Environmental Protection,Federal Indian Law,Government Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
 - Inventory Management
 - Production Planning
 - Time Management
-#resume
+#Resume
 #AssemblyMemberResume #AssemblyMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18022,7 +18022,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>assembly member resume,how to make a assembly member resume,["Assembly Line Optimization","Lean Manufacturing","Quality Control","Inventory Management","Production Planning","Time Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assembly member resume,how to make a assembly member resume,Assembly Line Optimization,Lean Manufacturing,Quality Control,Inventory Management,Production Planning,Time Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18072,7 @@
 - Media relations
 - Campaign Management
 - Policy Analysis
-#resume
+#Resume
 #USRepresentativeResume #USRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18082,7 +18082,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>u.s. representative resume,how to make a u.s. representative resume,["Legislative Expertise","Constituent Service","Public speaking","Media relations","Campaign Management","Policy Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>u.s. representative resume,how to make a u.s. representative resume,Legislative Expertise,Constituent Service,Public speaking,Media relations,Campaign Management,Policy Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18132,7 +18132,7 @@
 - Conveyor System Maintenance
 - Electrical Wiring
 - Fastening
-#resume
+#Resume
 #AssemblyPersonResume #AssemblyPerson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18142,7 +18142,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>assembly person resume,how to make a assembly person resume,["Automated Assembly Line","Bending","Component Assembly","Conveyor System Maintenance","Electrical Wiring","Fastening"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assembly person resume,how to make a assembly person resume,Automated Assembly Line,Bending,Component Assembly,Conveyor System Maintenance,Electrical Wiring,Fastening,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
 - Policy Development and Implementation
 - Budgetary Management
 - Media Relations and Communications
-#resume
+#Resume
 #USSenatorResume #USSenator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18202,7 +18202,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>u.s. senator resume,how to make a u.s. senator resume,["Constituent Services Management","Legislative Research and Analysis","Committee Leadership","Policy Development and Implementation","Budgetary Management","Media Relations and Communications"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>u.s. senator resume,how to make a u.s. senator resume,Constituent Services Management,Legislative Research and Analysis,Committee Leadership,Policy Development and Implementation,Budgetary Management,Media Relations and Communications,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18252,7 @@
 - Government Relations
 - Legislative Bill Analysis
 - Legislative Drafting
-#resume
+#Resume
 #AssemblymanOrWomanResume #AssemblymanOrWoman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18262,7 +18262,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>assemblyman or woman resume,how to make a assemblyman or woman resume,["Budget Analysis","Constituent Services","Constituency Outreach","Government Relations","Legislative Bill Analysis","Legislative Drafting"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>assemblyman or woman resume,how to make a assemblyman or woman resume,Budget Analysis,Constituent Services,Constituency Outreach,Government Relations,Legislative Bill Analysis,Legislative Drafting,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18312,7 +18312,7 @@
 - Budget Management
 - Marketing and Advertising
 - Team Leadership
-#resume
+#Resume
 #AccountDirectorResume #AccountDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18322,7 +18322,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>account director resume,how to make a account director resume,director level resume,["Strategic Planning","Client Relationship Management","Sales Management","Budget Management","Marketing and Advertising","Team Leadership"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>account director resume,how to make a account director resume,director level resume,Strategic Planning,Client Relationship Management,Sales Management,Budget Management,Marketing and Advertising,Team Leadership,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
 - Land Use Planning
 - Economic Development
 - Strategic Planning
-#resume
+#Resume
 #CityAldermanResume #CityAlderman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18382,7 +18382,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>city alderman resume,how to make a city alderman resume,["Public Policy Analysis","Budget Management","Constituency Outreach","Land Use Planning","Economic Development","Strategic Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city alderman resume,how to make a city alderman resume,Public Policy Analysis,Budget Management,Constituency Outreach,Land Use Planning,Economic Development,Strategic Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18432,7 @@
 - Zoho CRM
 - SAP Hybris
 - Oracle Siebel CRM
-#resume
+#Resume
 #AccountExecutiveResume #AccountExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18442,7 +18442,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>account executive resume,how to make a account executive resume,["Salesforce","Microsoft Dynamics 365 CRM","HubSpot","Zoho CRM","SAP Hybris","Oracle Siebel CRM"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>account executive resume,how to make a account executive resume,Salesforce,Microsoft Dynamics 365 CRM,HubSpot,Zoho CRM,SAP Hybris,Oracle Siebel CRM,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18492,7 +18492,7 @@
 - Constituent Relations
 - Policy Analysis
 - Collaboration
-#resume
+#Resume
 #CityCouncilMemberResume #CityCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18502,7 +18502,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>city council member resume,how to make a city council member resume,["Strategic Planning","Budget Management","Public Speaking","Constituent Relations","Policy Analysis","Collaboration"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city council member resume,how to make a city council member resume,Strategic Planning,Budget Management,Public Speaking,Constituent Relations,Policy Analysis,Collaboration,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
 - Business Development
 - Account Planning
 - Negotiation
-#resume
+#Resume
 #AccountManagerResume #AccountManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18562,7 +18562,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>account manager resume,how to make a account manager resume,management resume,["Salesforce","Microsoft Office Suite","Client Relationship Management (CRM)","Business Development","Account Planning","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>account manager resume,how to make a account manager resume,management resume,Salesforce,Microsoft Office Suite,Client Relationship Management (CRM),Business Development,Account Planning,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18612,7 +18612,7 @@
 - Environmental Policy
 - Ethics and Transparency
 - Fiscal Management
-#resume
+#Resume
 #CityCouncilmanResume #CityCouncilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18622,7 +18622,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>city councilman resume,how to make a city councilman resume,["Budgeting","Constituent Services","Economic Development","Environmental Policy","Ethics and Transparency","Fiscal Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>city councilman resume,how to make a city councilman resume,Budgeting,Constituent Services,Economic Development,Environmental Policy,Ethics and Transparency,Fiscal Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18672,7 +18672,7 @@
 - Bookkeeping
 - Cash Flow Analysis
 - Customer Relationship Management (CRM)
-#resume
+#Resume
 #AccountSpecialistResume #AccountSpecialist #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18682,7 +18682,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>account specialist resume,how to make a account specialist resume,["Accounts Payable","Accounts Receivable","Bank Reconciliation","Bookkeeping","Cash Flow Analysis","Customer Relationship Management (CRM)"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>account specialist resume,how to make a account specialist resume,Accounts Payable,Accounts Receivable,Bank Reconciliation,Bookkeeping,Cash Flow Analysis,Customer Relationship Management (CRM),how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
 - Public Policy Formulation
 - Strategic Planning and Implementation
 - Project Management
-#resume
+#Resume
 #CongressionalRepresentativeResume #CongressionalRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18742,7 +18742,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>congressional representative resume,how to make a congressional representative resume,["Budgeting and Fiscal Analysis","Constituent Relations Management","Legislative Drafting and Analysis","Public Policy Formulation","Strategic Planning and Implementation","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>congressional representative resume,how to make a congressional representative resume,Budgeting and Fiscal Analysis,Constituent Relations Management,Legislative Drafting and Analysis,Public Policy Formulation,Strategic Planning and Implementation,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18792,7 @@
 - Instagram Ads
 - Twitter Ads
 - LinkedIn Ads
-#resume
+#Resume
 #AdvertisingAccountExecutiveResume #AdvertisingAccountExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18802,7 +18802,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>advertising account executive resume,how to make a advertising account executive resume,["Google AdWords","Google Analytics","Facebook Ads","Instagram Ads","Twitter Ads","LinkedIn Ads"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising account executive resume,how to make a advertising account executive resume,Google AdWords,Google Analytics,Facebook Ads,Instagram Ads,Twitter Ads,LinkedIn Ads,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
 - Advocacy
 - Public Speaking
 - Consensus Building
-#resume
+#Resume
 #CongressmanResume #Congressman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18862,7 +18862,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>congressman resume,how to make a congressman resume,["Constituent Services","Policy Development","Legislating","Advocacy","Public Speaking","Consensus Building"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>congressman resume,how to make a congressman resume,Constituent Services,Policy Development,Legislating,Advocacy,Public Speaking,Consensus Building,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
 - Analytics Analysis
 - Client Relationship Management
 - Creative Development
-#resume
+#Resume
 #AdvertisingAccountManagerResume #AdvertisingAccountManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18922,7 +18922,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>advertising account manager resume,how to make a advertising account manager resume,management resume,["Campaign Planning","Budget Management","Media Planning","Analytics Analysis","Client Relationship Management","Creative Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising account manager resume,how to make a advertising account manager resume,management resume,Campaign Planning,Budget Management,Media Planning,Analytics Analysis,Client Relationship Management,Creative Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -18972,7 +18972,7 @@
 - Conflict Resolution
 - Constituent Services
 - Decision Making
-#resume
+#Resume
 #CouncilMemberResume #CouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -18982,7 +18982,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>council member resume,how to make a council member resume,["Advising Constituents","Budget Analysis","Community Engagement","Conflict Resolution","Constituent Services","Decision Making"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>council member resume,how to make a council member resume,Advising Constituents,Budget Analysis,Community Engagement,Conflict Resolution,Constituent Services,Decision Making,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
 - Content Marketing
 - Social Media Advertising
 - Omnichannel Advertising
-#resume
+#Resume
 #AdvertisingAgencyManagerResume #AdvertisingAgencyManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19042,7 +19042,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>advertising agency manager resume,how to make a advertising agency manager resume,management resume,["Programmatic Advertising","Native Advertising","Search Advertising","Content Marketing","Social Media Advertising","Omnichannel Advertising"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising agency manager resume,how to make a advertising agency manager resume,management resume,Programmatic Advertising,Native Advertising,Search Advertising,Content Marketing,Social Media Advertising,Omnichannel Advertising,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19092,7 +19092,7 @@
 - Budget Management
 - Ordinance Drafting
 - Land Use Planning
-#resume
+#Resume
 #CouncilmanResume #Councilman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19102,7 +19102,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>councilman resume,how to make a councilman resume,["Public Policy Analysis","Community Engagement","Strategic Planning","Budget Management","Ordinance Drafting","Land Use Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>councilman resume,how to make a councilman resume,Public Policy Analysis,Community Engagement,Strategic Planning,Budget Management,Ordinance Drafting,Land Use Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
 - Client Relationship Management
 - Creative Concept Development
 - Data Analytics and Interpretation
-#resume
+#Resume
 #AdvertisingCampaignManagerResume #AdvertisingCampaignManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19162,7 +19162,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>advertising campaign manager resume,how to make a advertising campaign manager resume,management resume,["Ad Campaign Planning","Budget Management","Campaign Analysis and Reporting","Client Relationship Management","Creative Concept Development","Data Analytics and Interpretation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising campaign manager resume,how to make a advertising campaign manager resume,management resume,Ad Campaign Planning,Budget Management,Campaign Analysis and Reporting,Client Relationship Management,Creative Concept Development,Data Analytics and Interpretation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19212,7 +19212,7 @@
 - Advocacy
 - Intake Assessment
 - Group Facilitation
-#resume
+#Resume
 #CouncilorResume #Councilor #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19222,7 +19222,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>councilor resume,how to make a councilor resume,["Case Management","Crisis Intervention","Counseling","Advocacy","Intake Assessment","Group Facilitation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>councilor resume,how to make a councilor resume,Case Management,Crisis Intervention,Counseling,Advocacy,Intake Assessment,Group Facilitation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19273,7 +19273,7 @@
 - Affiliate Marketing
 - Email Marketing
 - Social Media Marketing
-#resume
+#Resume
 #AdvertisingCoordinatorResume #AdvertisingCoordinator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19283,7 +19283,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>advertising coordinator resume,how to make a advertising coordinator resume,["Paid Advertising (Google AdWords,Facebook Ads)","Search Engine Marketing (SEM)","Display Advertising","Affiliate Marketing","Email Marketing","Social Media Marketing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising coordinator resume,how to make a advertising coordinator resume,Paid Advertising (Google AdWords,Facebook Ads),Search Engine Marketing (SEM),Display Advertising,Affiliate Marketing,Email Marketing,Social Media Marketing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19333,7 +19333,7 @@
 - Community Engagement
 - Leadership and Governance
 - Interpersonal Communication and Negotiation
-#resume
+#Resume
 #CouncilpersonResume #Councilperson #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19343,7 +19343,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>councilperson resume,how to make a councilperson resume,["Budgeting and Financial Management","Public Policy Development","Strategic Planning","Community Engagement","Leadership and Governance","Interpersonal Communication and Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>councilperson resume,how to make a councilperson resume,Budgeting and Financial Management,Public Policy Development,Strategic Planning,Community Engagement,Leadership and Governance,Interpersonal Communication and Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
 - Paid Search Advertising
 - Display Advertising
 - Affiliate Marketing
-#resume
+#Resume
 #AdvertisingDirectorResume #AdvertisingDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19403,7 +19403,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>advertising director resume,how to make a advertising director resume,director level resume,["Programmatic Advertising","Digital Marketing Strategy","Paid Social Media Advertising","Paid Search Advertising","Display Advertising","Affiliate Marketing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising director resume,how to make a advertising director resume,director level resume,Programmatic Advertising,Digital Marketing Strategy,Paid Social Media Advertising,Paid Search Advertising,Display Advertising,Affiliate Marketing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19453,7 +19453,7 @@
 - Fundraising
 - Leadership
 - Negotiation
-#resume
+#Resume
 #DelegateResume #Delegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19463,7 +19463,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>delegate resume,how to make a delegate resume,["Communication","Collaboration","Event Planning","Fundraising","Leadership","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>delegate resume,how to make a delegate resume,Communication,Collaboration,Event Planning,Fundraising,Leadership,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19513,7 @@
 - Google Ads Management
 - Content Marketing
 - Email Marketing
-#resume
+#Resume
 #AdvertisingExecutiveResume #AdvertisingExecutive #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19523,7 +19523,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>advertising executive resume,how to make a advertising executive resume,["Digital Advertising","Social Media Marketing","Search Engine Optimization (SEO)","Google Ads Management","Content Marketing","Email Marketing"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising executive resume,how to make a advertising executive resume,Digital Advertising,Social Media Marketing,Search Engine Optimization (SEO),Google Ads Management,Content Marketing,Email Marketing,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19573,7 +19573,7 @@
 - Policy Analysis
 - Public Speaking
 - Negotiation
-#resume
+#Resume
 #LegislatorResume #Legislator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19583,7 +19583,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>legislator resume,how to make a legislator resume,["Constituent Services","Community Outreach","Legislative Research","Policy Analysis","Public Speaking","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>legislator resume,how to make a legislator resume,Constituent Services,Community Outreach,Legislative Research,Policy Analysis,Public Speaking,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
 - Team Leadership
 - Data Analysis
 - Creative Development
-#resume
+#Resume
 #AdvertisingManagerResume #AdvertisingManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19643,7 +19643,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>advertising manager resume,how to make a advertising manager resume,management resume,["Campaign Planning","Media Buying","Budget Management","Team Leadership","Data Analysis","Creative Development"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising manager resume,how to make a advertising manager resume,management resume,Campaign Planning,Media Buying,Budget Management,Team Leadership,Data Analysis,Creative Development,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
 - Public Speaking
 - Media Relations
 - Negotiation
-#resume
+#Resume
 #MemberOfCongressResume #MemberOfCongress #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19703,7 +19703,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>member of congress resume,how to make a member of congress resume,["Policy Analysis","Legislative Drafting","Constituent Services","Public Speaking","Media Relations","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>member of congress resume,how to make a member of congress resume,Policy Analysis,Legislative Drafting,Constituent Services,Public Speaking,Media Relations,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
 - Supply Side Platforms (SSPs)
 - Demand Side Platforms (DSPs)
 - Yield Management
-#resume
+#Resume
 #AdvertisingOperationsManagerResume #AdvertisingOperationsManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19763,7 +19763,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>advertising operations manager resume,how to make a advertising operations manager resume,management resume,["Ad Exchange Platforms","Data Analytics and Reporting","Campaign Optimization","Supply Side Platforms (SSPs)","Demand Side Platforms (DSPs)","Yield Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising operations manager resume,how to make a advertising operations manager resume,management resume,Ad Exchange Platforms,Data Analytics and Reporting,Campaign Optimization,Supply Side Platforms (SSPs),Demand Side Platforms (DSPs),Yield Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19813,7 +19813,7 @@
 - Communication
 - Interpersonal Skills
 - Problem Solving
-#resume
+#Resume
 #RepresentativeResume #Representative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19823,7 +19823,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>representative resume,how to make a representative resume,["Customer Relationship Management","Sales Prospecting","Negotiation","Communication","Interpersonal Skills","Problem Solving"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>representative resume,how to make a representative resume,Customer Relationship Management,Sales Prospecting,Negotiation,Communication,Interpersonal Skills,Problem Solving,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
 - Digital Advertising
 - Media Planning
 - Negotiation
-#resume
+#Resume
 #AdvertisingSalesManagerResume #AdvertisingSalesManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19883,7 +19883,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>advertising sales manager resume,how to make a advertising sales manager resume,management resume,sales resume,["Salesforce","Microsoft Excel","Google Analytics","Digital Advertising","Media Planning","Negotiation"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising sales manager resume,how to make a advertising sales manager resume,management resume,sales resume,Salesforce,Microsoft Excel,Google Analytics,Digital Advertising,Media Planning,Negotiation,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
 - Community Engagement
 - Intergovernmental Relations
 - Public Speaking
-#resume
+#Resume
 #SelectmanResume #Selectman #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -19943,7 +19943,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>selectman resume,how to make a selectman resume,["Constituent Services","Budget Management","Policy Development","Community Engagement","Intergovernmental Relations","Public Speaking"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>selectman resume,how to make a selectman resume,Constituent Services,Budget Management,Policy Development,Community Engagement,Intergovernmental Relations,Public Speaking,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -19993,7 +19993,7 @@
 - Advertising Analytics
 - Digital Marketing
 - Market Research
-#resume
+#Resume
 #AdvertisingSalesRepresentativeResume #AdvertisingSalesRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20003,7 +20003,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>advertising sales representative resume,how to make a advertising sales representative resume,sales resume,["Cold Calling","Negotiation","Sales Prospecting","Advertising Analytics","Digital Marketing","Market Research"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising sales representative resume,how to make a advertising sales representative resume,sales resume,Cold Calling,Negotiation,Sales Prospecting,Advertising Analytics,Digital Marketing,Market Research,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20053,7 +20053,7 @@
 - Speechwriting and Public Speaking
 - Committee Work and Leadership
 - Constituent Advocacy
-#resume
+#Resume
 #SenatorResume #Senator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20063,7 +20063,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>senator resume,how to make a senator resume,["Constituent Services Management","Legislative Policy Analysis","Budget and Appropriations","Speechwriting and Public Speaking","Committee Work and Leadership","Constituent Advocacy"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>senator resume,how to make a senator resume,Constituent Services Management,Legislative Policy Analysis,Budget and Appropriations,Speechwriting and Public Speaking,Committee Work and Leadership,Constituent Advocacy,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20113,7 +20113,7 @@
 - Media Planning
 - Audience Analysis
 - Digital Advertising
-#resume
+#Resume
 #AdvertisingVicePresidentResume #AdvertisingVicePresident #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20123,7 +20123,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>advertising vice president resume,how to make a advertising vice president resume,["Strategic Planning","Creative Direction","Brand Management","Media Planning","Audience Analysis","Digital Advertising"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>advertising vice president resume,how to make a advertising vice president resume,Strategic Planning,Creative Direction,Brand Management,Media Planning,Audience Analysis,Digital Advertising,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20173,7 +20173,7 @@
 - Stakeholder Engagement
 - Community Outreach
 - Strategic Planning
-#resume
+#Resume
 #TribalCouncilMemberResume #TribalCouncilMember #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20183,7 +20183,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>tribal council member resume,how to make a tribal council member resume,["Budget Management","Policy Development","Conflict Resolution","Stakeholder Engagement","Community Outreach","Strategic Planning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>tribal council member resume,how to make a tribal council member resume,Budget Management,Policy Development,Conflict Resolution,Stakeholder Engagement,Community Outreach,Strategic Planning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20233,7 +20233,7 @@
 - Typography
 - Composition
 - Color Theory
-#resume
+#Resume
 #ArtDirectorResume #ArtDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20243,7 +20243,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>art director resume,how to make a art director resume,director level resume,["Art Direction","UX Design","Visual Design","Typography","Composition","Color Theory"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>art director resume,how to make a art director resume,director level resume,Art Direction,UX Design,Visual Design,Typography,Composition,Color Theory,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
 - Environmental Protection
 - Federal Indian Law
 - Government Relations
-#resume
+#Resume
 #TribalDelegateResume #TribalDelegate #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20303,7 +20303,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>tribal delegate resume,how to make a tribal delegate resume,["Community Building","Cultural Resource Management","Economic Development","Environmental Protection","Federal Indian Law","Government Relations"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>tribal delegate resume,how to make a tribal delegate resume,Community Building,Cultural Resource Management,Economic Development,Environmental Protection,Federal Indian Law,Government Relations,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20353,7 +20353,7 @@
 - Target Audience Analysis
 - Product Development
 - Brand Positioning
-#resume
+#Resume
 #BrandManagerResume #BrandManager #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20363,7 +20363,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>brand manager resume,how to make a brand manager resume,management resume,["Brand Strategy Development","Marketing Communications","Brand Identity Management","Target Audience Analysis","Product Development","Brand Positioning"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>brand manager resume,how to make a brand manager resume,management resume,Brand Strategy Development,Marketing Communications,Brand Identity Management,Target Audience Analysis,Product Development,Brand Positioning,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20413,7 +20413,7 @@
 - Media relations
 - Campaign Management
 - Policy Analysis
-#resume
+#Resume
 #USRepresentativeResume #USRepresentative #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20423,7 +20423,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>u.s. representative resume,how to make a u.s. representative resume,["Legislative Expertise","Constituent Service","Public speaking","Media relations","Campaign Management","Policy Analysis"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>u.s. representative resume,how to make a u.s. representative resume,Legislative Expertise,Constituent Service,Public speaking,Media relations,Campaign Management,Policy Analysis,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20473,7 +20473,7 @@
 - Data Analysis and Reporting
 - Budget Management
 - Project Management
-#resume
+#Resume
 #CampaignDirectorResume #CampaignDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20483,7 +20483,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>campaign director resume,how to make a campaign director resume,director level resume,["Email Marketing","Social Media Marketing","Campaign Planning and Execution","Data Analysis and Reporting","Budget Management","Project Management"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>campaign director resume,how to make a campaign director resume,director level resume,Email Marketing,Social Media Marketing,Campaign Planning and Execution,Data Analysis and Reporting,Budget Management,Project Management,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
 - Policy Development and Implementation
 - Budgetary Management
 - Media Relations and Communications
-#resume
+#Resume
 #USSenatorResume #USSenator #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20543,7 +20543,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>u.s. senator resume,how to make a u.s. senator resume,["Constituent Services Management","Legislative Research and Analysis","Committee Leadership","Policy Development and Implementation","Budgetary Management","Media Relations and Communications"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>u.s. senator resume,how to make a u.s. senator resume,Constituent Services Management,Legislative Research and Analysis,Committee Leadership,Policy Development and Implementation,Budgetary Management,Media Relations and Communications,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
@@ -20593,7 +20593,7 @@
 - Budget Management
 - Marketing and Advertising
 - Team Leadership
-#resume
+#Resume
 #AccountDirectorResume #AccountDirector #ResumeTips #ResumeBuilder #ResumeGemini
 ---
 About ResumeGemini:
@@ -20603,7 +20603,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>account director resume,how to make a account director resume,director level resume,["Strategic Planning","Client Relationship Management","Sales Management","Budget Management","Marketing and Advertising","Team Leadership"],how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
+          <t>account director resume,how to make a account director resume,director level resume,Strategic Planning,Client Relationship Management,Sales Management,Budget Management,Marketing and Advertising,Team Leadership,how to write a resume,resume writing,resume builder,cv format,resume template,free resume builder,professional resume,ResumeGemini,ResumeGemini.com</t>
         </is>
       </c>
     </row>
